--- a/nmds_results.xlsx
+++ b/nmds_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drake\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75673BB4-A9E7-4FD2-81CE-705BE4378C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324F88AC-7FC8-469E-9897-77643F41413E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1170" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site_Scores" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6263" uniqueCount="2601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6263" uniqueCount="2600">
   <si>
     <t>Name</t>
   </si>
@@ -6564,16 +6564,6 @@
     <t>NicolaTassotti</t>
   </si>
   <si>
-    <t>17Ã‚Â° Mhysteria Modern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Marco Caputo</t>
-  </si>
-  <si>
-    <t>19Ã‚Âº Mhysteria Modern</t>
-  </si>
-  <si>
     <t>Manuel FernÃ¡ndez</t>
   </si>
   <si>
@@ -6592,33 +6582,21 @@
     <t>Anna BoÅ‚ka</t>
   </si>
   <si>
-    <t>MOLE 5Ã‚Â°</t>
-  </si>
-  <si>
     <t>Piotr GÅ‚ogowski</t>
   </si>
   <si>
     <t>ThÃ©ophile Granger</t>
   </si>
   <si>
-    <t>Torneo Medio Ã¢Â€Â“ WPNQ</t>
-  </si>
-  <si>
     <t>JosÃ© Moniz</t>
   </si>
   <si>
-    <t>DalamÃƒÂ¤sterskapet 2023 6k</t>
-  </si>
-  <si>
     <t>DonegÃ  Francesco</t>
   </si>
   <si>
     <t>Francesco DonegÃ </t>
   </si>
   <si>
-    <t>Final da 9Ã‚Âª Liga</t>
-  </si>
-  <si>
     <t>Eduardo PatrÃ­cio Ventura</t>
   </si>
   <si>
@@ -6634,9 +6612,6 @@
     <t>Mateus TÃ³foli</t>
   </si>
   <si>
-    <t>Campeonato de EspaÃƒÂ±a de Modern 2023</t>
-  </si>
-  <si>
     <t>Alejandro Olea GarcÃ­a</t>
   </si>
   <si>
@@ -6652,9 +6627,6 @@
     <t>MatyÃ¡Å¡ KaluÅ¾nÃ½</t>
   </si>
   <si>
-    <t>FinaÃ…Â‚ Paprykarz Series 23/24</t>
-  </si>
-  <si>
     <t>Caleb BjÃ¶rnler</t>
   </si>
   <si>
@@ -6670,54 +6642,27 @@
     <t>GaÃ«tan Bossy</t>
   </si>
   <si>
-    <t>Campeonato de EspaÃƒÂ±a 2024</t>
-  </si>
-  <si>
     <t>AdriÃ  Mourad Martinez</t>
   </si>
   <si>
     <t>Joel AvilÃ©s</t>
   </si>
   <si>
-    <t>Destination Qualifier IV - Campeonato de EspaÃƒÂ±a</t>
-  </si>
-  <si>
-    <t>MTGO AspiringSpikeÃƒÂ¢Ã¢Â‚Â¬Ã¢Â„Â¢s Madness</t>
-  </si>
-  <si>
     <t>Philipp MÃ¼ller</t>
   </si>
   <si>
     <t>AdriÃ¡n Quevedo</t>
   </si>
   <si>
-    <t>BreCH Cup Qualifier by BreezÃƒÂ© BreezÃƒÂ©</t>
-  </si>
-  <si>
     <t>Fynn JÃ¤nich</t>
   </si>
   <si>
-    <t>3Ã‚Âº Mulligan Invitational</t>
-  </si>
-  <si>
     <t>RamÃ³n Nogueira</t>
   </si>
   <si>
-    <t>CarnicerÃƒÂƒÃ‚ÂƒÃƒÂ‚a Campeonato EspaÃƒÂƒÃ‚ÂƒÃƒÂ‚Ã‚Â±a 2025</t>
-  </si>
-  <si>
     <t>AdriÃ¡n IÃ±igo Tastet</t>
   </si>
   <si>
-    <t>MetrÃƒÂ³polis Series - Unity League Grand Prix</t>
-  </si>
-  <si>
-    <t>MetrÃƒÂ³polis Series</t>
-  </si>
-  <si>
-    <t>MetrÃƒÂ³polis Series - EMEA Destination Qualifier - Amberes</t>
-  </si>
-  <si>
     <t>Konstantin HÃ¼bner</t>
   </si>
   <si>
@@ -6736,9 +6681,6 @@
     <t>ÃÃ±igo Sanz Torres</t>
   </si>
   <si>
-    <t>Campeonato de EspaÃƒÂ±a de Modern 2025</t>
-  </si>
-  <si>
     <t>PrzemysÅ‚aw Olszewski</t>
   </si>
   <si>
@@ -7826,6 +7768,60 @@
   </si>
   <si>
     <t>Card</t>
+  </si>
+  <si>
+    <t>17Â° Mhysteria Modern</t>
+  </si>
+  <si>
+    <t>19Âº Mhysteria Modern</t>
+  </si>
+  <si>
+    <t>MOLE 5Â°</t>
+  </si>
+  <si>
+    <t>Torneo Medio â€“ WPNQ</t>
+  </si>
+  <si>
+    <t>DalamÃ¤sterskapet 2023 6k</t>
+  </si>
+  <si>
+    <t>Final da 9Âª Liga</t>
+  </si>
+  <si>
+    <t>Campeonato de EspaÃ±a de Modern 2023</t>
+  </si>
+  <si>
+    <t>FinaÅ‚ Paprykarz Series 23/24</t>
+  </si>
+  <si>
+    <t>Campeonato de EspaÃ±a 2024</t>
+  </si>
+  <si>
+    <t>Destination Qualifier IV - Campeonato de EspaÃ±a</t>
+  </si>
+  <si>
+    <t>MTGO AspiringSpike's Madness</t>
+  </si>
+  <si>
+    <t>BreCH Cup Qualifier by BreezÃ© BreezÃ©</t>
+  </si>
+  <si>
+    <t>3Âº Mulligan Invitational</t>
+  </si>
+  <si>
+    <t>CarnicerÃ­a Campeonato EspaÃ±a 2025</t>
+  </si>
+  <si>
+    <t>MetrÃ³polis Series - Unity League Grand Prix</t>
+  </si>
+  <si>
+    <t>MetrÃ³polis Series</t>
+  </si>
+  <si>
+    <t>MetrÃ³polis Series - EMEA Destination Qualifier - Amberes</t>
+  </si>
+  <si>
+    <t>Campeonato de EspaÃ±a de Modern 2025</t>
   </si>
 </sst>
 </file>
@@ -7881,15 +7877,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -10311,7 +10304,7 @@
         <v>194</v>
       </c>
       <c r="B125" t="s">
-        <v>2180</v>
+        <v>2582</v>
       </c>
       <c r="C125" s="2">
         <v>43477</v>
@@ -10748,9 +10741,9 @@
         <v>-0.50234953406370497</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
-        <v>2181</v>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>784</v>
       </c>
       <c r="B151" t="s">
         <v>231</v>
@@ -10787,7 +10780,7 @@
         <v>194</v>
       </c>
       <c r="B153" t="s">
-        <v>2182</v>
+        <v>2583</v>
       </c>
       <c r="C153" s="2">
         <v>43561</v>
@@ -11328,7 +11321,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="B185" t="s">
         <v>265</v>
@@ -12977,7 +12970,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="B282" t="s">
         <v>353</v>
@@ -14388,7 +14381,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="B365" t="s">
         <v>425</v>
@@ -14575,7 +14568,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="B376" t="s">
         <v>429</v>
@@ -16445,7 +16438,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B486" t="s">
         <v>1</v>
@@ -16819,7 +16812,7 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="B508" t="s">
         <v>1</v>
@@ -17686,7 +17679,7 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B559" t="s">
         <v>581</v>
@@ -17859,7 +17852,7 @@
         <v>590</v>
       </c>
       <c r="B569" t="s">
-        <v>2189</v>
+        <v>2584</v>
       </c>
       <c r="C569" s="2">
         <v>44640</v>
@@ -17893,7 +17886,7 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>2189</v>
+        <v>2584</v>
       </c>
       <c r="C571" s="2">
         <v>44640</v>
@@ -18638,7 +18631,7 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B615" t="s">
         <v>629</v>
@@ -18910,7 +18903,7 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="B631" t="s">
         <v>640</v>
@@ -20678,7 +20671,7 @@
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>2191</v>
+        <v>2187</v>
       </c>
       <c r="B735" t="s">
         <v>740</v>
@@ -21256,7 +21249,7 @@
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>2191</v>
+        <v>2187</v>
       </c>
       <c r="B769" t="s">
         <v>768</v>
@@ -21273,7 +21266,7 @@
     </row>
     <row r="770" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>2191</v>
+        <v>2187</v>
       </c>
       <c r="B770" t="s">
         <v>768</v>
@@ -21460,7 +21453,7 @@
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B781" t="s">
         <v>782</v>
@@ -21888,7 +21881,7 @@
         <v>784</v>
       </c>
       <c r="B806" t="s">
-        <v>2192</v>
+        <v>2585</v>
       </c>
       <c r="C806" s="2">
         <v>44934</v>
@@ -23840,7 +23833,7 @@
     </row>
     <row r="921" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
       <c r="B921" t="s">
         <v>894</v>
@@ -24693,7 +24686,7 @@
         <v>937</v>
       </c>
       <c r="B971" t="s">
-        <v>2194</v>
+        <v>2586</v>
       </c>
       <c r="C971" s="2">
         <v>45157</v>
@@ -24761,7 +24754,7 @@
         <v>941</v>
       </c>
       <c r="B975" t="s">
-        <v>2194</v>
+        <v>2586</v>
       </c>
       <c r="C975" s="2">
         <v>45157</v>
@@ -25506,7 +25499,7 @@
     </row>
     <row r="1019" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
-        <v>2195</v>
+        <v>2189</v>
       </c>
       <c r="B1019" t="s">
         <v>351</v>
@@ -25829,7 +25822,7 @@
     </row>
     <row r="1038" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
-        <v>2196</v>
+        <v>2190</v>
       </c>
       <c r="B1038" t="s">
         <v>986</v>
@@ -26342,7 +26335,7 @@
         <v>1006</v>
       </c>
       <c r="B1068" t="s">
-        <v>2197</v>
+        <v>2587</v>
       </c>
       <c r="C1068" s="2">
         <v>45215</v>
@@ -26883,7 +26876,7 @@
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1100" t="s">
-        <v>2198</v>
+        <v>2191</v>
       </c>
       <c r="B1100" t="s">
         <v>671</v>
@@ -26900,7 +26893,7 @@
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1101" t="s">
-        <v>2199</v>
+        <v>2192</v>
       </c>
       <c r="B1101" t="s">
         <v>1032</v>
@@ -27087,7 +27080,7 @@
     </row>
     <row r="1112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1112" t="s">
-        <v>2200</v>
+        <v>2193</v>
       </c>
       <c r="B1112" t="s">
         <v>1038</v>
@@ -27104,7 +27097,7 @@
     </row>
     <row r="1113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1113" t="s">
-        <v>2200</v>
+        <v>2193</v>
       </c>
       <c r="B1113" t="s">
         <v>1038</v>
@@ -27767,7 +27760,7 @@
     </row>
     <row r="1152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1152" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B1152" t="s">
         <v>1063</v>
@@ -27852,7 +27845,7 @@
     </row>
     <row r="1157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1157" t="s">
-        <v>2201</v>
+        <v>2194</v>
       </c>
       <c r="B1157" t="s">
         <v>671</v>
@@ -27886,7 +27879,7 @@
     </row>
     <row r="1159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1159" t="s">
-        <v>2202</v>
+        <v>2195</v>
       </c>
       <c r="B1159" t="s">
         <v>671</v>
@@ -28144,7 +28137,7 @@
         <v>1075</v>
       </c>
       <c r="B1174" t="s">
-        <v>2203</v>
+        <v>2588</v>
       </c>
       <c r="C1174" s="2">
         <v>45268</v>
@@ -28161,7 +28154,7 @@
         <v>1076</v>
       </c>
       <c r="B1175" t="s">
-        <v>2203</v>
+        <v>2588</v>
       </c>
       <c r="C1175" s="2">
         <v>45268</v>
@@ -28178,7 +28171,7 @@
         <v>1077</v>
       </c>
       <c r="B1176" t="s">
-        <v>2203</v>
+        <v>2588</v>
       </c>
       <c r="C1176" s="2">
         <v>45268</v>
@@ -28192,10 +28185,10 @@
     </row>
     <row r="1177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1177" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B1177" t="s">
-        <v>2203</v>
+        <v>2588</v>
       </c>
       <c r="C1177" s="2">
         <v>45268</v>
@@ -28209,10 +28202,10 @@
     </row>
     <row r="1178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1178" t="s">
-        <v>2204</v>
+        <v>2196</v>
       </c>
       <c r="B1178" t="s">
-        <v>2203</v>
+        <v>2588</v>
       </c>
       <c r="C1178" s="2">
         <v>45268</v>
@@ -28277,7 +28270,7 @@
     </row>
     <row r="1182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1182" t="s">
-        <v>2205</v>
+        <v>2197</v>
       </c>
       <c r="B1182" t="s">
         <v>1081</v>
@@ -28328,7 +28321,7 @@
     </row>
     <row r="1185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1185" t="s">
-        <v>2206</v>
+        <v>2198</v>
       </c>
       <c r="B1185" t="s">
         <v>1081</v>
@@ -28345,7 +28338,7 @@
     </row>
     <row r="1186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1186" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
       <c r="B1186" t="s">
         <v>1081</v>
@@ -29875,7 +29868,7 @@
     </row>
     <row r="1276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1276" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
       <c r="B1276" t="s">
         <v>1138</v>
@@ -29926,7 +29919,7 @@
     </row>
     <row r="1279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1279" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
       <c r="B1279" t="s">
         <v>1138</v>
@@ -29960,7 +29953,7 @@
     </row>
     <row r="1281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1281" t="s">
-        <v>2208</v>
+        <v>2200</v>
       </c>
       <c r="B1281" t="s">
         <v>1138</v>
@@ -29977,7 +29970,7 @@
     </row>
     <row r="1282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1282" t="s">
-        <v>2208</v>
+        <v>2200</v>
       </c>
       <c r="B1282" t="s">
         <v>1138</v>
@@ -30728,7 +30721,7 @@
         <v>1184</v>
       </c>
       <c r="B1326" t="s">
-        <v>2209</v>
+        <v>2589</v>
       </c>
       <c r="C1326" s="2">
         <v>45333</v>
@@ -30759,7 +30752,7 @@
     </row>
     <row r="1328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1328" t="s">
-        <v>2210</v>
+        <v>2201</v>
       </c>
       <c r="B1328" t="s">
         <v>1186</v>
@@ -31099,7 +31092,7 @@
     </row>
     <row r="1348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1348" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="B1348" t="s">
         <v>1199</v>
@@ -32153,7 +32146,7 @@
     </row>
     <row r="1410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1410" t="s">
-        <v>2208</v>
+        <v>2200</v>
       </c>
       <c r="B1410" t="s">
         <v>1247</v>
@@ -33309,7 +33302,7 @@
     </row>
     <row r="1478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1478" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="B1478" t="s">
         <v>1278</v>
@@ -34057,7 +34050,7 @@
     </row>
     <row r="1522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1522" t="s">
-        <v>2212</v>
+        <v>2203</v>
       </c>
       <c r="B1522" t="s">
         <v>1300</v>
@@ -36097,7 +36090,7 @@
     </row>
     <row r="1642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1642" t="s">
-        <v>2212</v>
+        <v>2203</v>
       </c>
       <c r="B1642" t="s">
         <v>1345</v>
@@ -36488,7 +36481,7 @@
     </row>
     <row r="1665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1665" t="s">
-        <v>2200</v>
+        <v>2193</v>
       </c>
       <c r="B1665" t="s">
         <v>671</v>
@@ -36862,7 +36855,7 @@
     </row>
     <row r="1687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1687" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="B1687" t="s">
         <v>671</v>
@@ -36964,7 +36957,7 @@
     </row>
     <row r="1693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1693" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="B1693" t="s">
         <v>1369</v>
@@ -37627,7 +37620,7 @@
     </row>
     <row r="1732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1732" t="s">
-        <v>2214</v>
+        <v>2205</v>
       </c>
       <c r="B1732" t="s">
         <v>1388</v>
@@ -38293,7 +38286,7 @@
         <v>1360</v>
       </c>
       <c r="B1771" t="s">
-        <v>2215</v>
+        <v>2590</v>
       </c>
       <c r="C1771" s="2">
         <v>45626</v>
@@ -38307,10 +38300,10 @@
     </row>
     <row r="1772" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1772" t="s">
-        <v>2216</v>
+        <v>2206</v>
       </c>
       <c r="B1772" t="s">
-        <v>2215</v>
+        <v>2590</v>
       </c>
       <c r="C1772" s="2">
         <v>45626</v>
@@ -38358,10 +38351,10 @@
     </row>
     <row r="1775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1775" t="s">
-        <v>2217</v>
+        <v>2207</v>
       </c>
       <c r="B1775" t="s">
-        <v>2218</v>
+        <v>2591</v>
       </c>
       <c r="C1775" s="2">
         <v>45627</v>
@@ -38378,7 +38371,7 @@
         <v>1408</v>
       </c>
       <c r="B1776" t="s">
-        <v>2219</v>
+        <v>2592</v>
       </c>
       <c r="C1776" s="2">
         <v>45627</v>
@@ -38494,7 +38487,7 @@
     </row>
     <row r="1783" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1783" t="s">
-        <v>2220</v>
+        <v>2208</v>
       </c>
       <c r="B1783" t="s">
         <v>1411</v>
@@ -39208,7 +39201,7 @@
     </row>
     <row r="1825" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1825" t="s">
-        <v>2221</v>
+        <v>2209</v>
       </c>
       <c r="B1825" t="s">
         <v>1429</v>
@@ -39449,7 +39442,7 @@
         <v>1435</v>
       </c>
       <c r="B1839" t="s">
-        <v>2222</v>
+        <v>2593</v>
       </c>
       <c r="C1839" s="2">
         <v>45675</v>
@@ -39837,7 +39830,7 @@
     </row>
     <row r="1862" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1862" t="s">
-        <v>2223</v>
+        <v>2210</v>
       </c>
       <c r="B1862" t="s">
         <v>1448</v>
@@ -40639,7 +40632,7 @@
         <v>1308</v>
       </c>
       <c r="B1909" t="s">
-        <v>2224</v>
+        <v>2594</v>
       </c>
       <c r="C1909" s="2">
         <v>45711</v>
@@ -40755,7 +40748,7 @@
     </row>
     <row r="1916" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1916" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="B1916" t="s">
         <v>1477</v>
@@ -40857,7 +40850,7 @@
     </row>
     <row r="1922" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1922" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="B1922" t="s">
         <v>1483</v>
@@ -40908,7 +40901,7 @@
     </row>
     <row r="1925" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1925" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="B1925" t="s">
         <v>1479</v>
@@ -41758,7 +41751,7 @@
     </row>
     <row r="1975" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1975" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="B1975" t="s">
         <v>1516</v>
@@ -42030,7 +42023,7 @@
     </row>
     <row r="1991" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1991" t="s">
-        <v>2216</v>
+        <v>2206</v>
       </c>
       <c r="B1991" t="s">
         <v>1530</v>
@@ -42064,7 +42057,7 @@
     </row>
     <row r="1993" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1993" t="s">
-        <v>2216</v>
+        <v>2206</v>
       </c>
       <c r="B1993" t="s">
         <v>1530</v>
@@ -42710,7 +42703,7 @@
     </row>
     <row r="2031" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2031" t="s">
-        <v>2225</v>
+        <v>2211</v>
       </c>
       <c r="B2031" t="s">
         <v>919</v>
@@ -42764,7 +42757,7 @@
         <v>1542</v>
       </c>
       <c r="B2034" t="s">
-        <v>2226</v>
+        <v>2595</v>
       </c>
       <c r="C2034" s="2">
         <v>45759</v>
@@ -42812,10 +42805,10 @@
     </row>
     <row r="2037" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2037" t="s">
-        <v>2227</v>
+        <v>2212</v>
       </c>
       <c r="B2037" t="s">
-        <v>2228</v>
+        <v>2596</v>
       </c>
       <c r="C2037" s="2">
         <v>45759</v>
@@ -42832,7 +42825,7 @@
         <v>764</v>
       </c>
       <c r="B2038" t="s">
-        <v>2229</v>
+        <v>2597</v>
       </c>
       <c r="C2038" s="2">
         <v>45759</v>
@@ -42866,7 +42859,7 @@
         <v>1357</v>
       </c>
       <c r="B2040" t="s">
-        <v>2229</v>
+        <v>2597</v>
       </c>
       <c r="C2040" s="2">
         <v>45759</v>
@@ -42880,10 +42873,10 @@
     </row>
     <row r="2041" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2041" t="s">
-        <v>2227</v>
+        <v>2212</v>
       </c>
       <c r="B2041" t="s">
-        <v>2229</v>
+        <v>2597</v>
       </c>
       <c r="C2041" s="2">
         <v>45759</v>
@@ -42900,7 +42893,7 @@
         <v>426</v>
       </c>
       <c r="B2042" t="s">
-        <v>2229</v>
+        <v>2597</v>
       </c>
       <c r="C2042" s="2">
         <v>45759</v>
@@ -42968,7 +42961,7 @@
         <v>1547</v>
       </c>
       <c r="B2046" t="s">
-        <v>2230</v>
+        <v>2598</v>
       </c>
       <c r="C2046" s="2">
         <v>45760</v>
@@ -43509,7 +43502,7 @@
     </row>
     <row r="2078" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2078" t="s">
-        <v>2231</v>
+        <v>2213</v>
       </c>
       <c r="B2078" t="s">
         <v>671</v>
@@ -44682,7 +44675,7 @@
     </row>
     <row r="2147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2147" t="s">
-        <v>2225</v>
+        <v>2211</v>
       </c>
       <c r="B2147" t="s">
         <v>1604</v>
@@ -45090,7 +45083,7 @@
     </row>
     <row r="2171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2171" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="B2171" t="s">
         <v>671</v>
@@ -45107,7 +45100,7 @@
     </row>
     <row r="2172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2172" t="s">
-        <v>2232</v>
+        <v>2214</v>
       </c>
       <c r="B2172" t="s">
         <v>671</v>
@@ -49850,7 +49843,7 @@
     </row>
     <row r="2451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2451" t="s">
-        <v>2233</v>
+        <v>2215</v>
       </c>
       <c r="B2451" t="s">
         <v>1734</v>
@@ -49969,7 +49962,7 @@
     </row>
     <row r="2458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2458" t="s">
-        <v>2233</v>
+        <v>2215</v>
       </c>
       <c r="B2458" t="s">
         <v>1734</v>
@@ -50802,7 +50795,7 @@
     </row>
     <row r="2507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2507" t="s">
-        <v>2234</v>
+        <v>2216</v>
       </c>
       <c r="B2507" t="s">
         <v>1773</v>
@@ -51805,7 +51798,7 @@
     </row>
     <row r="2566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2566" t="s">
-        <v>2235</v>
+        <v>2217</v>
       </c>
       <c r="B2566" t="s">
         <v>1801</v>
@@ -51822,7 +51815,7 @@
     </row>
     <row r="2567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2567" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="B2567" t="s">
         <v>1801</v>
@@ -52179,7 +52172,7 @@
     </row>
     <row r="2588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2588" t="s">
-        <v>2205</v>
+        <v>2197</v>
       </c>
       <c r="B2588" t="s">
         <v>1442</v>
@@ -52434,10 +52427,10 @@
     </row>
     <row r="2603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2603" t="s">
-        <v>2236</v>
+        <v>2218</v>
       </c>
       <c r="B2603" t="s">
-        <v>2237</v>
+        <v>2599</v>
       </c>
       <c r="C2603" s="2">
         <v>45997</v>
@@ -52536,7 +52529,7 @@
     </row>
     <row r="2609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2609" t="s">
-        <v>2238</v>
+        <v>2219</v>
       </c>
       <c r="B2609" t="s">
         <v>1833</v>
@@ -55307,7 +55300,7 @@
     </row>
     <row r="2772" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2772" t="s">
-        <v>2239</v>
+        <v>2220</v>
       </c>
       <c r="B2772" t="s">
         <v>1883</v>
@@ -55895,7 +55888,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2600</v>
+        <v>2581</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -55917,7 +55910,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2240</v>
+        <v>2221</v>
       </c>
       <c r="B3">
         <v>-1.1975365577836601</v>
@@ -55928,7 +55921,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2241</v>
+        <v>2222</v>
       </c>
       <c r="B4">
         <v>-0.104866834750914</v>
@@ -55950,7 +55943,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2242</v>
+        <v>2223</v>
       </c>
       <c r="B6">
         <v>-1.14467583239654</v>
@@ -55972,7 +55965,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2243</v>
+        <v>2224</v>
       </c>
       <c r="B8">
         <v>-0.31600794816400601</v>
@@ -55988,7 +55981,7 @@
       <c r="B9">
         <v>-4.32072588180323E-4</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>8.6717634203475303E-5</v>
       </c>
     </row>
@@ -56005,7 +55998,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2244</v>
+        <v>2225</v>
       </c>
       <c r="B11">
         <v>-1.12940367668362</v>
@@ -56027,7 +56020,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2245</v>
+        <v>2226</v>
       </c>
       <c r="B13">
         <v>-0.41644449536737299</v>
@@ -56060,7 +56053,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2246</v>
+        <v>2227</v>
       </c>
       <c r="B16">
         <v>-1.2982381012994</v>
@@ -56071,7 +56064,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2247</v>
+        <v>2228</v>
       </c>
       <c r="B17">
         <v>-0.99067077060282205</v>
@@ -56093,7 +56086,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2248</v>
+        <v>2229</v>
       </c>
       <c r="B19">
         <v>0.71028964092128399</v>
@@ -56104,7 +56097,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2249</v>
+        <v>2230</v>
       </c>
       <c r="B20">
         <v>-1.5242742955158399</v>
@@ -56115,7 +56108,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2250</v>
+        <v>2231</v>
       </c>
       <c r="B21">
         <v>0.90162600039333696</v>
@@ -56137,7 +56130,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2251</v>
+        <v>2232</v>
       </c>
       <c r="B23">
         <v>-5.0250876203260901E-2</v>
@@ -56170,7 +56163,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2252</v>
+        <v>2233</v>
       </c>
       <c r="B26">
         <v>-7.2007577001160006E-2</v>
@@ -56203,7 +56196,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2253</v>
+        <v>2234</v>
       </c>
       <c r="B29">
         <v>0.78852250879226005</v>
@@ -56214,7 +56207,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2254</v>
+        <v>2235</v>
       </c>
       <c r="B30">
         <v>0.434220423094625</v>
@@ -56225,7 +56218,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2255</v>
+        <v>2236</v>
       </c>
       <c r="B31">
         <v>0.54171144198635002</v>
@@ -56236,7 +56229,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2256</v>
+        <v>2237</v>
       </c>
       <c r="B32">
         <v>0.27241982605702803</v>
@@ -56247,7 +56240,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>2257</v>
+        <v>2238</v>
       </c>
       <c r="B33">
         <v>-0.36954427034950899</v>
@@ -56258,7 +56251,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>2258</v>
+        <v>2239</v>
       </c>
       <c r="B34">
         <v>-0.47775085271819601</v>
@@ -56291,7 +56284,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>2259</v>
+        <v>2240</v>
       </c>
       <c r="B37">
         <v>0.66730794977226104</v>
@@ -56324,7 +56317,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>2260</v>
+        <v>2241</v>
       </c>
       <c r="B40">
         <v>0.852941419485022</v>
@@ -56346,7 +56339,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>2261</v>
+        <v>2242</v>
       </c>
       <c r="B42">
         <v>-1.0891667616296901</v>
@@ -56390,7 +56383,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>2262</v>
+        <v>2243</v>
       </c>
       <c r="B46">
         <v>-1.73774248874966</v>
@@ -56401,7 +56394,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>2263</v>
+        <v>2244</v>
       </c>
       <c r="B47">
         <v>-1.3165484415167701</v>
@@ -56412,7 +56405,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>2264</v>
+        <v>2245</v>
       </c>
       <c r="B48">
         <v>2.0946534021116198E-2</v>
@@ -56434,7 +56427,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>2265</v>
+        <v>2246</v>
       </c>
       <c r="B50">
         <v>-1.18529369194404</v>
@@ -56445,7 +56438,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>2266</v>
+        <v>2247</v>
       </c>
       <c r="B51">
         <v>-1.2171214653353899</v>
@@ -56456,7 +56449,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>2267</v>
+        <v>2248</v>
       </c>
       <c r="B52">
         <v>-0.41644449536737299</v>
@@ -56467,7 +56460,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>2268</v>
+        <v>2249</v>
       </c>
       <c r="B53">
         <v>-0.356684677316564</v>
@@ -56522,7 +56515,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>2269</v>
+        <v>2250</v>
       </c>
       <c r="B58">
         <v>-0.92854028368723596</v>
@@ -56555,7 +56548,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>2270</v>
+        <v>2251</v>
       </c>
       <c r="B61">
         <v>-0.42225372048816101</v>
@@ -56599,7 +56592,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>2271</v>
+        <v>2252</v>
       </c>
       <c r="B65">
         <v>-0.98847640153211502</v>
@@ -56632,7 +56625,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>2272</v>
+        <v>2253</v>
       </c>
       <c r="B68">
         <v>0.58728248441467801</v>
@@ -56643,7 +56636,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>2273</v>
+        <v>2254</v>
       </c>
       <c r="B69">
         <v>0.49446698012826201</v>
@@ -56665,7 +56658,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>2274</v>
+        <v>2255</v>
       </c>
       <c r="B71">
         <v>-1.3642206244305599</v>
@@ -56687,7 +56680,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>2275</v>
+        <v>2256</v>
       </c>
       <c r="B73">
         <v>-0.916100136107736</v>
@@ -56709,7 +56702,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>2276</v>
+        <v>2257</v>
       </c>
       <c r="B75">
         <v>-1.4573888203726599</v>
@@ -56720,7 +56713,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>2277</v>
+        <v>2258</v>
       </c>
       <c r="B76">
         <v>-1.17706472237271</v>
@@ -56731,7 +56724,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>2278</v>
+        <v>2259</v>
       </c>
       <c r="B77">
         <v>0.82672795958165801</v>
@@ -56742,7 +56735,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>2279</v>
+        <v>2260</v>
       </c>
       <c r="B78">
         <v>-0.25966193064721599</v>
@@ -56775,7 +56768,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>2280</v>
+        <v>2261</v>
       </c>
       <c r="B81">
         <v>0.78068573968465305</v>
@@ -56786,7 +56779,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>2281</v>
+        <v>2262</v>
       </c>
       <c r="B82">
         <v>-1.15095029713565</v>
@@ -56819,7 +56812,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>2282</v>
+        <v>2263</v>
       </c>
       <c r="B85">
         <v>-0.233103217991042</v>
@@ -56841,7 +56834,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>2283</v>
+        <v>2264</v>
       </c>
       <c r="B87">
         <v>0.72417775037173404</v>
@@ -56852,7 +56845,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>2284</v>
+        <v>2265</v>
       </c>
       <c r="B88">
         <v>-1.10511852293532</v>
@@ -56885,7 +56878,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>2285</v>
+        <v>2266</v>
       </c>
       <c r="B91">
         <v>-1.4231293230174999</v>
@@ -56951,7 +56944,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>2286</v>
+        <v>2267</v>
       </c>
       <c r="B97">
         <v>-0.60404219419342298</v>
@@ -56973,7 +56966,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>2287</v>
+        <v>2268</v>
       </c>
       <c r="B99">
         <v>-0.17546276778980699</v>
@@ -56984,7 +56977,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>2288</v>
+        <v>2269</v>
       </c>
       <c r="B100">
         <v>-0.28566224468917301</v>
@@ -57017,7 +57010,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>2289</v>
+        <v>2270</v>
       </c>
       <c r="B103">
         <v>-1.4955977689103499</v>
@@ -57061,7 +57054,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>2290</v>
+        <v>2271</v>
       </c>
       <c r="B107">
         <v>-1.10704113231942</v>
@@ -57072,7 +57065,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>2291</v>
+        <v>2272</v>
       </c>
       <c r="B108">
         <v>0.77815860292300698</v>
@@ -57083,7 +57076,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>2292</v>
+        <v>2273</v>
       </c>
       <c r="B109">
         <v>-0.22799471115727299</v>
@@ -57105,7 +57098,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>2293</v>
+        <v>2274</v>
       </c>
       <c r="B111">
         <v>-1.15838318195871</v>
@@ -57116,7 +57109,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>2294</v>
+        <v>2275</v>
       </c>
       <c r="B112">
         <v>-0.127483412736246</v>
@@ -57127,7 +57120,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>2295</v>
+        <v>2276</v>
       </c>
       <c r="B113">
         <v>-0.30042982120391198</v>
@@ -57193,7 +57186,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>2296</v>
+        <v>2277</v>
       </c>
       <c r="B119">
         <v>-1.17305403375191</v>
@@ -57204,7 +57197,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>2297</v>
+        <v>2278</v>
       </c>
       <c r="B120">
         <v>-0.22799471115727299</v>
@@ -57248,7 +57241,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>2298</v>
+        <v>2279</v>
       </c>
       <c r="B124">
         <v>-1.1859859902827701</v>
@@ -57281,7 +57274,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>2299</v>
+        <v>2280</v>
       </c>
       <c r="B127">
         <v>0.69433470082420301</v>
@@ -57325,7 +57318,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>2300</v>
+        <v>2281</v>
       </c>
       <c r="B131">
         <v>-1.3535877032549199</v>
@@ -57336,7 +57329,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>2301</v>
+        <v>2282</v>
       </c>
       <c r="B132">
         <v>-1.11932552616956</v>
@@ -57347,7 +57340,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>2302</v>
+        <v>2283</v>
       </c>
       <c r="B133">
         <v>-0.17523526007596699</v>
@@ -57380,7 +57373,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>2303</v>
+        <v>2284</v>
       </c>
       <c r="B136">
         <v>-0.51054769080846596</v>
@@ -57391,7 +57384,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>2304</v>
+        <v>2285</v>
       </c>
       <c r="B137">
         <v>0.39412754200509797</v>
@@ -57402,7 +57395,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>2305</v>
+        <v>2286</v>
       </c>
       <c r="B138">
         <v>-0.34587592758995001</v>
@@ -57413,7 +57406,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>2306</v>
+        <v>2287</v>
       </c>
       <c r="B139">
         <v>0.81015205276378099</v>
@@ -57424,7 +57417,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>2307</v>
+        <v>2288</v>
       </c>
       <c r="B140">
         <v>-1.4114428168308299</v>
@@ -57435,7 +57428,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>2308</v>
+        <v>2289</v>
       </c>
       <c r="B141">
         <v>-1.2946656863066901</v>
@@ -57479,7 +57472,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>2309</v>
+        <v>2290</v>
       </c>
       <c r="B145">
         <v>-0.792059514783513</v>
@@ -57512,7 +57505,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>2310</v>
+        <v>2291</v>
       </c>
       <c r="B148">
         <v>-1.35082479487429</v>
@@ -57534,7 +57527,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>2311</v>
+        <v>2292</v>
       </c>
       <c r="B150">
         <v>-1.4937937537691199</v>
@@ -57545,7 +57538,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>2312</v>
+        <v>2293</v>
       </c>
       <c r="B151">
         <v>0.26126620839220799</v>
@@ -57578,7 +57571,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>2313</v>
+        <v>2294</v>
       </c>
       <c r="B154">
         <v>-0.39481370670344701</v>
@@ -57589,7 +57582,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>2314</v>
+        <v>2295</v>
       </c>
       <c r="B155">
         <v>-0.449953783041598</v>
@@ -57600,7 +57593,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>2315</v>
+        <v>2296</v>
       </c>
       <c r="B156">
         <v>0.805814660560635</v>
@@ -57644,7 +57637,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>2316</v>
+        <v>2297</v>
       </c>
       <c r="B160">
         <v>-0.58672143702467106</v>
@@ -57655,7 +57648,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>2317</v>
+        <v>2298</v>
       </c>
       <c r="B161">
         <v>-0.21607086790621599</v>
@@ -57666,7 +57659,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>2318</v>
+        <v>2299</v>
       </c>
       <c r="B162">
         <v>-1.1020080789064699</v>
@@ -57688,7 +57681,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>2319</v>
+        <v>2300</v>
       </c>
       <c r="B164">
         <v>-1.5178085086170201</v>
@@ -57699,7 +57692,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>2320</v>
+        <v>2301</v>
       </c>
       <c r="B165">
         <v>0.79678778208371204</v>
@@ -57710,7 +57703,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>2321</v>
+        <v>2302</v>
       </c>
       <c r="B166">
         <v>-1.18789950936753</v>
@@ -57732,7 +57725,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>2322</v>
+        <v>2303</v>
       </c>
       <c r="B168">
         <v>-1.11284095458607</v>
@@ -57754,7 +57747,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>2323</v>
+        <v>2304</v>
       </c>
       <c r="B170">
         <v>-0.19463674831244601</v>
@@ -57765,7 +57758,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>2324</v>
+        <v>2305</v>
       </c>
       <c r="B171">
         <v>0.175798551531134</v>
@@ -57776,7 +57769,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>2325</v>
+        <v>2306</v>
       </c>
       <c r="B172">
         <v>-1.1978047728177501</v>
@@ -57820,7 +57813,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>2326</v>
+        <v>2307</v>
       </c>
       <c r="B176">
         <v>-1.1002188913401101</v>
@@ -57831,7 +57824,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>2327</v>
+        <v>2308</v>
       </c>
       <c r="B177">
         <v>-0.74907633318580202</v>
@@ -57842,7 +57835,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>2328</v>
+        <v>2309</v>
       </c>
       <c r="B178">
         <v>-1.0908951899750701</v>
@@ -57853,7 +57846,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>2329</v>
+        <v>2310</v>
       </c>
       <c r="B179">
         <v>0.69016333577071998</v>
@@ -57886,7 +57879,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>2330</v>
+        <v>2311</v>
       </c>
       <c r="B182">
         <v>-1.1062084943653601</v>
@@ -57908,7 +57901,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>2331</v>
+        <v>2312</v>
       </c>
       <c r="B184">
         <v>-0.17090463465556299</v>
@@ -57930,7 +57923,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>2332</v>
+        <v>2313</v>
       </c>
       <c r="B186">
         <v>-1.0763359124613201</v>
@@ -57941,7 +57934,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>2333</v>
+        <v>2314</v>
       </c>
       <c r="B187">
         <v>-1.21155511484486</v>
@@ -57952,7 +57945,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>2334</v>
+        <v>2315</v>
       </c>
       <c r="B188">
         <v>-0.69076417024465497</v>
@@ -57963,7 +57956,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>2335</v>
+        <v>2316</v>
       </c>
       <c r="B189">
         <v>-0.77967242858585095</v>
@@ -57985,7 +57978,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>2336</v>
+        <v>2317</v>
       </c>
       <c r="B191">
         <v>-0.345302675847239</v>
@@ -57996,7 +57989,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>2337</v>
+        <v>2318</v>
       </c>
       <c r="B192">
         <v>-1.3703626996490601</v>
@@ -58007,7 +58000,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>2338</v>
+        <v>2319</v>
       </c>
       <c r="B193">
         <v>0.54116671832074403</v>
@@ -58018,7 +58011,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>2339</v>
+        <v>2320</v>
       </c>
       <c r="B194">
         <v>-0.26937430286921898</v>
@@ -58029,7 +58022,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>2340</v>
+        <v>2321</v>
       </c>
       <c r="B195">
         <v>-1.1191562260355301</v>
@@ -58040,7 +58033,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>2341</v>
+        <v>2322</v>
       </c>
       <c r="B196">
         <v>-0.32451487466852202</v>
@@ -58051,7 +58044,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>2342</v>
+        <v>2323</v>
       </c>
       <c r="B197">
         <v>0.238047994416867</v>
@@ -58062,7 +58055,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>2343</v>
+        <v>2324</v>
       </c>
       <c r="B198">
         <v>0.613384496010275</v>
@@ -58073,7 +58066,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>2344</v>
+        <v>2325</v>
       </c>
       <c r="B199">
         <v>-0.256619407260674</v>
@@ -58084,7 +58077,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>2345</v>
+        <v>2326</v>
       </c>
       <c r="B200">
         <v>-0.95291643152001704</v>
@@ -58095,7 +58088,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>2346</v>
+        <v>2327</v>
       </c>
       <c r="B201">
         <v>-1.1946078615896401</v>
@@ -58106,7 +58099,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>2347</v>
+        <v>2328</v>
       </c>
       <c r="B202">
         <v>0.79995832372196696</v>
@@ -58128,7 +58121,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>2348</v>
+        <v>2329</v>
       </c>
       <c r="B204">
         <v>0.33965124287224302</v>
@@ -58139,7 +58132,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>2349</v>
+        <v>2330</v>
       </c>
       <c r="B205">
         <v>-0.70895312744180705</v>
@@ -58150,7 +58143,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>2350</v>
+        <v>2331</v>
       </c>
       <c r="B206">
         <v>-0.52600416740631895</v>
@@ -58161,7 +58154,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>2351</v>
+        <v>2332</v>
       </c>
       <c r="B207">
         <v>0.69660871488466403</v>
@@ -58205,7 +58198,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>2352</v>
+        <v>2333</v>
       </c>
       <c r="B211">
         <v>-1.29376996305431</v>
@@ -58216,7 +58209,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>2353</v>
+        <v>2334</v>
       </c>
       <c r="B212">
         <v>0.81083360754321698</v>
@@ -58227,7 +58220,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>2354</v>
+        <v>2335</v>
       </c>
       <c r="B213">
         <v>0.616751475215921</v>
@@ -58238,7 +58231,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>2355</v>
+        <v>2336</v>
       </c>
       <c r="B214">
         <v>-0.110461403663872</v>
@@ -58260,7 +58253,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>2356</v>
+        <v>2337</v>
       </c>
       <c r="B216">
         <v>-0.53075172064588905</v>
@@ -58271,7 +58264,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>2357</v>
+        <v>2338</v>
       </c>
       <c r="B217">
         <v>-1.3165484415167701</v>
@@ -58282,7 +58275,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>2358</v>
+        <v>2339</v>
       </c>
       <c r="B218">
         <v>0.65991477859006098</v>
@@ -58293,7 +58286,7 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>2359</v>
+        <v>2340</v>
       </c>
       <c r="B219">
         <v>0.524835513408482</v>
@@ -58304,7 +58297,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>2360</v>
+        <v>2341</v>
       </c>
       <c r="B220">
         <v>-1.33594240529243</v>
@@ -58315,7 +58308,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>2361</v>
+        <v>2342</v>
       </c>
       <c r="B221">
         <v>-0.39896919633219102</v>
@@ -58326,7 +58319,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>2362</v>
+        <v>2343</v>
       </c>
       <c r="B222">
         <v>-1.1459861650015299</v>
@@ -58392,7 +58385,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>2363</v>
+        <v>2344</v>
       </c>
       <c r="B228">
         <v>4.6555733687276897E-2</v>
@@ -58414,7 +58407,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>2364</v>
+        <v>2345</v>
       </c>
       <c r="B230">
         <v>-1.1917051319787599</v>
@@ -58436,7 +58429,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>2365</v>
+        <v>2346</v>
       </c>
       <c r="B232">
         <v>-4.38463726958793E-2</v>
@@ -58469,7 +58462,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>2366</v>
+        <v>2347</v>
       </c>
       <c r="B235">
         <v>0.74466923187026002</v>
@@ -58480,7 +58473,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>2367</v>
+        <v>2348</v>
       </c>
       <c r="B236">
         <v>-0.25416249658795498</v>
@@ -58502,7 +58495,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>2368</v>
+        <v>2349</v>
       </c>
       <c r="B238">
         <v>-1.47203267071197</v>
@@ -58513,7 +58506,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>2369</v>
+        <v>2350</v>
       </c>
       <c r="B239">
         <v>-0.95291643152001704</v>
@@ -58524,7 +58517,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>2370</v>
+        <v>2351</v>
       </c>
       <c r="B240">
         <v>-1.1606652983872701</v>
@@ -58557,7 +58550,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>2371</v>
+        <v>2352</v>
       </c>
       <c r="B243">
         <v>-0.49695576266953401</v>
@@ -58568,7 +58561,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>2372</v>
+        <v>2353</v>
       </c>
       <c r="B244">
         <v>-0.34405754769097002</v>
@@ -58579,7 +58572,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>2373</v>
+        <v>2354</v>
       </c>
       <c r="B245">
         <v>3.3285079818858698E-2</v>
@@ -58590,7 +58583,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>2374</v>
+        <v>2355</v>
       </c>
       <c r="B246">
         <v>0.80394514808290696</v>
@@ -58623,7 +58616,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>2375</v>
+        <v>2356</v>
       </c>
       <c r="B249">
         <v>-1.0747930592431501</v>
@@ -58634,7 +58627,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>2376</v>
+        <v>2357</v>
       </c>
       <c r="B250">
         <v>0.66586959784743005</v>
@@ -58645,7 +58638,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>2377</v>
+        <v>2358</v>
       </c>
       <c r="B251">
         <v>-0.45527374455698399</v>
@@ -58656,7 +58649,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>2378</v>
+        <v>2359</v>
       </c>
       <c r="B252">
         <v>0.56962652314708295</v>
@@ -58667,7 +58660,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>2379</v>
+        <v>2360</v>
       </c>
       <c r="B253">
         <v>-0.22799471115727299</v>
@@ -58689,7 +58682,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>2380</v>
+        <v>2361</v>
       </c>
       <c r="B255">
         <v>-1.0633653177568601</v>
@@ -58722,7 +58715,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>2381</v>
+        <v>2362</v>
       </c>
       <c r="B258">
         <v>-1.3552740188851</v>
@@ -58777,7 +58770,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>2382</v>
+        <v>2363</v>
       </c>
       <c r="B263">
         <v>-0.38325425153722997</v>
@@ -58799,7 +58792,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>2383</v>
+        <v>2364</v>
       </c>
       <c r="B265">
         <v>0.72676431312481704</v>
@@ -58832,7 +58825,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>2384</v>
+        <v>2365</v>
       </c>
       <c r="B268">
         <v>-0.116467825024808</v>
@@ -58843,7 +58836,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>2385</v>
+        <v>2366</v>
       </c>
       <c r="B269">
         <v>-1.1062084943653601</v>
@@ -58865,7 +58858,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>2386</v>
+        <v>2367</v>
       </c>
       <c r="B271">
         <v>-1.12940367668362</v>
@@ -58887,7 +58880,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>2387</v>
+        <v>2368</v>
       </c>
       <c r="B273">
         <v>-0.71948288341487998</v>
@@ -58964,7 +58957,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>2388</v>
+        <v>2369</v>
       </c>
       <c r="B280">
         <v>-0.84246754528317402</v>
@@ -58975,7 +58968,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>2389</v>
+        <v>2370</v>
       </c>
       <c r="B281">
         <v>0.73264679467886196</v>
@@ -58986,7 +58979,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>2390</v>
+        <v>2371</v>
       </c>
       <c r="B282">
         <v>-0.72212440582326998</v>
@@ -58997,7 +58990,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>2391</v>
+        <v>2372</v>
       </c>
       <c r="B283">
         <v>-1.1073164571409799</v>
@@ -59008,7 +59001,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>2392</v>
+        <v>2373</v>
       </c>
       <c r="B284">
         <v>0.70833729707791404</v>
@@ -59019,7 +59012,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>2393</v>
+        <v>2374</v>
       </c>
       <c r="B285">
         <v>0.120409852282632</v>
@@ -59041,7 +59034,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>2394</v>
+        <v>2375</v>
       </c>
       <c r="B287">
         <v>-1.1145133826032001</v>
@@ -59052,7 +59045,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>2395</v>
+        <v>2376</v>
       </c>
       <c r="B288">
         <v>0.58851515644318297</v>
@@ -59063,7 +59056,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>2396</v>
+        <v>2377</v>
       </c>
       <c r="B289">
         <v>0.71832209276803705</v>
@@ -59085,7 +59078,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>2397</v>
+        <v>2378</v>
       </c>
       <c r="B291">
         <v>-0.72826477748436502</v>
@@ -59096,7 +59089,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>2398</v>
+        <v>2379</v>
       </c>
       <c r="B292">
         <v>-1.2591440977502999</v>
@@ -59118,7 +59111,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>2399</v>
+        <v>2380</v>
       </c>
       <c r="B294">
         <v>-0.29681836845742399</v>
@@ -59129,7 +59122,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>2400</v>
+        <v>2381</v>
       </c>
       <c r="B295">
         <v>0.43968792506690502</v>
@@ -59151,7 +59144,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>2401</v>
+        <v>2382</v>
       </c>
       <c r="B297">
         <v>0.68611964625547905</v>
@@ -59173,7 +59166,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>2402</v>
+        <v>2383</v>
       </c>
       <c r="B299">
         <v>0.47656128908837297</v>
@@ -59184,7 +59177,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>2403</v>
+        <v>2384</v>
       </c>
       <c r="B300">
         <v>-0.51886887341451904</v>
@@ -59217,7 +59210,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>2404</v>
+        <v>2385</v>
       </c>
       <c r="B303">
         <v>0.57879735947454303</v>
@@ -59239,7 +59232,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>2405</v>
+        <v>2386</v>
       </c>
       <c r="B305">
         <v>-0.34920770193959499</v>
@@ -59250,7 +59243,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>2406</v>
+        <v>2387</v>
       </c>
       <c r="B306">
         <v>3.6957871420308701E-2</v>
@@ -59261,7 +59254,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>2407</v>
+        <v>2388</v>
       </c>
       <c r="B307">
         <v>0.53467333748006496</v>
@@ -59294,7 +59287,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>2408</v>
+        <v>2389</v>
       </c>
       <c r="B310">
         <v>-0.361522201856873</v>
@@ -59305,7 +59298,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>2409</v>
+        <v>2390</v>
       </c>
       <c r="B311">
         <v>-1.1073164571409799</v>
@@ -59316,7 +59309,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>2410</v>
+        <v>2391</v>
       </c>
       <c r="B312">
         <v>-1.1062084943653601</v>
@@ -59349,7 +59342,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>2411</v>
+        <v>2392</v>
       </c>
       <c r="B315">
         <v>-0.11017851114171801</v>
@@ -59382,7 +59375,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>2412</v>
+        <v>2393</v>
       </c>
       <c r="B318">
         <v>0.44551412698478199</v>
@@ -59437,7 +59430,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>2413</v>
+        <v>2394</v>
       </c>
       <c r="B323">
         <v>0.54448183402754502</v>
@@ -59448,7 +59441,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>2414</v>
+        <v>2395</v>
       </c>
       <c r="B324">
         <v>0.73496858225189798</v>
@@ -59459,7 +59452,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>2415</v>
+        <v>2396</v>
       </c>
       <c r="B325">
         <v>-1.1509803872433599</v>
@@ -59470,7 +59463,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>2416</v>
+        <v>2397</v>
       </c>
       <c r="B326">
         <v>-0.39115274230879399</v>
@@ -59481,7 +59474,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>2417</v>
+        <v>2398</v>
       </c>
       <c r="B327">
         <v>-0.49848725626141099</v>
@@ -59492,7 +59485,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>2418</v>
+        <v>2399</v>
       </c>
       <c r="B328">
         <v>0.66667506860521797</v>
@@ -59503,7 +59496,7 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>2419</v>
+        <v>2400</v>
       </c>
       <c r="B329">
         <v>-1.1024289553628699</v>
@@ -59525,7 +59518,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>2420</v>
+        <v>2401</v>
       </c>
       <c r="B331">
         <v>0.71534489990441896</v>
@@ -59547,7 +59540,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>2421</v>
+        <v>2402</v>
       </c>
       <c r="B333">
         <v>-1.26824503579849</v>
@@ -59558,7 +59551,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>2422</v>
+        <v>2403</v>
       </c>
       <c r="B334">
         <v>-1.1970826545597999</v>
@@ -59580,7 +59573,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>2423</v>
+        <v>2404</v>
       </c>
       <c r="B336">
         <v>-0.43956170818717699</v>
@@ -59591,7 +59584,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>2424</v>
+        <v>2405</v>
       </c>
       <c r="B337">
         <v>-0.43632371063450298</v>
@@ -59657,7 +59650,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>2425</v>
+        <v>2406</v>
       </c>
       <c r="B343">
         <v>-1.0661756736418599</v>
@@ -59679,7 +59672,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>2426</v>
+        <v>2407</v>
       </c>
       <c r="B345">
         <v>-1.0633653177568601</v>
@@ -59690,7 +59683,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>2427</v>
+        <v>2408</v>
       </c>
       <c r="B346">
         <v>0.53370560042022497</v>
@@ -59712,7 +59705,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>2428</v>
+        <v>2409</v>
       </c>
       <c r="B348">
         <v>-0.138555626792809</v>
@@ -59723,7 +59716,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>2429</v>
+        <v>2410</v>
       </c>
       <c r="B349">
         <v>-1.3165484415167701</v>
@@ -59734,7 +59727,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>2430</v>
+        <v>2411</v>
       </c>
       <c r="B350">
         <v>-0.70369864435302198</v>
@@ -59745,7 +59738,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>2431</v>
+        <v>2412</v>
       </c>
       <c r="B351">
         <v>-0.70322138280458102</v>
@@ -59767,7 +59760,7 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>2432</v>
+        <v>2413</v>
       </c>
       <c r="B353">
         <v>0.67034001641724295</v>
@@ -59789,7 +59782,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>2433</v>
+        <v>2414</v>
       </c>
       <c r="B355">
         <v>-0.40258573192656599</v>
@@ -59811,7 +59804,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>2434</v>
+        <v>2415</v>
       </c>
       <c r="B357">
         <v>0.67915655750806403</v>
@@ -59855,7 +59848,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>2435</v>
+        <v>2416</v>
       </c>
       <c r="B361">
         <v>7.8445222407563298E-2</v>
@@ -59866,7 +59859,7 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>2436</v>
+        <v>2417</v>
       </c>
       <c r="B362">
         <v>-0.38492248506320698</v>
@@ -59877,7 +59870,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>2437</v>
+        <v>2418</v>
       </c>
       <c r="B363">
         <v>-3.4393092024880501E-2</v>
@@ -59888,7 +59881,7 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>2438</v>
+        <v>2419</v>
       </c>
       <c r="B364">
         <v>0.82672795958165801</v>
@@ -59921,7 +59914,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>2439</v>
+        <v>2420</v>
       </c>
       <c r="B367">
         <v>0.168475561625482</v>
@@ -59965,7 +59958,7 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>2440</v>
+        <v>2421</v>
       </c>
       <c r="B371">
         <v>0.54869994387710896</v>
@@ -59976,7 +59969,7 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>2441</v>
+        <v>2422</v>
       </c>
       <c r="B372">
         <v>0.73102706594669997</v>
@@ -59998,7 +59991,7 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>2442</v>
+        <v>2423</v>
       </c>
       <c r="B374">
         <v>0.630644741296711</v>
@@ -60009,7 +60002,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>2443</v>
+        <v>2424</v>
       </c>
       <c r="B375">
         <v>-7.2094893642515201E-2</v>
@@ -60031,7 +60024,7 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>2444</v>
+        <v>2425</v>
       </c>
       <c r="B377">
         <v>-0.84246754528317402</v>
@@ -60042,7 +60035,7 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>2445</v>
+        <v>2426</v>
       </c>
       <c r="B378">
         <v>-1.0165679795845399</v>
@@ -60053,7 +60046,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>2446</v>
+        <v>2427</v>
       </c>
       <c r="B379">
         <v>-1.2102677297977</v>
@@ -60064,7 +60057,7 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>2447</v>
+        <v>2428</v>
       </c>
       <c r="B380">
         <v>-1.12890723352765</v>
@@ -60075,7 +60068,7 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>2448</v>
+        <v>2429</v>
       </c>
       <c r="B381">
         <v>-1.5242742955158399</v>
@@ -60086,7 +60079,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>2449</v>
+        <v>2430</v>
       </c>
       <c r="B382">
         <v>0.66223856798202296</v>
@@ -60097,7 +60090,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>2450</v>
+        <v>2431</v>
       </c>
       <c r="B383">
         <v>0.68067031719368598</v>
@@ -60108,7 +60101,7 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>2451</v>
+        <v>2432</v>
       </c>
       <c r="B384">
         <v>-1.27918029821088</v>
@@ -60119,7 +60112,7 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>2452</v>
+        <v>2433</v>
       </c>
       <c r="B385">
         <v>7.1780346557186098E-2</v>
@@ -60141,7 +60134,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>2453</v>
+        <v>2434</v>
       </c>
       <c r="B387">
         <v>-0.31899603764824003</v>
@@ -60152,7 +60145,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>2454</v>
+        <v>2435</v>
       </c>
       <c r="B388">
         <v>-1.17706472237271</v>
@@ -60174,7 +60167,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>2455</v>
+        <v>2436</v>
       </c>
       <c r="B390">
         <v>7.6138104046315797E-2</v>
@@ -60185,7 +60178,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>2456</v>
+        <v>2437</v>
       </c>
       <c r="B391">
         <v>-1.0416227507490201</v>
@@ -60218,7 +60211,7 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>2457</v>
+        <v>2438</v>
       </c>
       <c r="B394">
         <v>-0.323625377422809</v>
@@ -60229,7 +60222,7 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>2458</v>
+        <v>2439</v>
       </c>
       <c r="B395">
         <v>0.117441465724498</v>
@@ -60251,7 +60244,7 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>2459</v>
+        <v>2440</v>
       </c>
       <c r="B397">
         <v>-1.47201267326876</v>
@@ -60295,7 +60288,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>2460</v>
+        <v>2441</v>
       </c>
       <c r="B401">
         <v>-1.15792750591506</v>
@@ -60350,7 +60343,7 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>2461</v>
+        <v>2442</v>
       </c>
       <c r="B406">
         <v>-0.84246754528317402</v>
@@ -60372,7 +60365,7 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>2462</v>
+        <v>2443</v>
       </c>
       <c r="B408">
         <v>-1.2063189802901499</v>
@@ -60383,7 +60376,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>2463</v>
+        <v>2444</v>
       </c>
       <c r="B409">
         <v>-0.127483412736246</v>
@@ -60405,7 +60398,7 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>2464</v>
+        <v>2445</v>
       </c>
       <c r="B411">
         <v>0.49515267406396402</v>
@@ -60416,7 +60409,7 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>2465</v>
+        <v>2446</v>
       </c>
       <c r="B412">
         <v>-0.84246754528317402</v>
@@ -60449,7 +60442,7 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>2466</v>
+        <v>2447</v>
       </c>
       <c r="B415">
         <v>0.557162826116954</v>
@@ -60471,7 +60464,7 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>2467</v>
+        <v>2448</v>
       </c>
       <c r="B417">
         <v>-1.1002188913401101</v>
@@ -60482,7 +60475,7 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>2468</v>
+        <v>2449</v>
       </c>
       <c r="B418">
         <v>0.13477724196802601</v>
@@ -60504,7 +60497,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>2469</v>
+        <v>2450</v>
       </c>
       <c r="B420">
         <v>0.65721018567798395</v>
@@ -60515,7 +60508,7 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>2470</v>
+        <v>2451</v>
       </c>
       <c r="B421">
         <v>-1.34007417522257</v>
@@ -60526,7 +60519,7 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>2471</v>
+        <v>2452</v>
       </c>
       <c r="B422">
         <v>0.69516126877305595</v>
@@ -60537,7 +60530,7 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>2472</v>
+        <v>2453</v>
       </c>
       <c r="B423">
         <v>-0.50803481837989495</v>
@@ -60548,7 +60541,7 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>2473</v>
+        <v>2454</v>
       </c>
       <c r="B424">
         <v>0.66373405581179101</v>
@@ -60559,7 +60552,7 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>2474</v>
+        <v>2455</v>
       </c>
       <c r="B425">
         <v>-0.113370144213039</v>
@@ -60603,7 +60596,7 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>2475</v>
+        <v>2456</v>
       </c>
       <c r="B429">
         <v>-1.2751252348108699</v>
@@ -60625,7 +60618,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>2476</v>
+        <v>2457</v>
       </c>
       <c r="B431">
         <v>-1.4822281408661999</v>
@@ -60636,7 +60629,7 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>2477</v>
+        <v>2458</v>
       </c>
       <c r="B432">
         <v>0.52966861274980104</v>
@@ -60647,7 +60640,7 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>2478</v>
+        <v>2459</v>
       </c>
       <c r="B433">
         <v>-1.23854950711676</v>
@@ -60658,7 +60651,7 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>2479</v>
+        <v>2460</v>
       </c>
       <c r="B434">
         <v>-1.06410915461601</v>
@@ -60691,7 +60684,7 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>2480</v>
+        <v>2461</v>
       </c>
       <c r="B437">
         <v>-1.08232390593057</v>
@@ -60702,7 +60695,7 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>2481</v>
+        <v>2462</v>
       </c>
       <c r="B438">
         <v>-1.1427819333987901</v>
@@ -60713,7 +60706,7 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>2482</v>
+        <v>2463</v>
       </c>
       <c r="B439">
         <v>-0.58105083297140103</v>
@@ -60735,7 +60728,7 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>2483</v>
+        <v>2464</v>
       </c>
       <c r="B441">
         <v>-0.40760899194762201</v>
@@ -60757,7 +60750,7 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>2484</v>
+        <v>2465</v>
       </c>
       <c r="B443">
         <v>0.536353805573211</v>
@@ -60768,7 +60761,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>2485</v>
+        <v>2466</v>
       </c>
       <c r="B444">
         <v>-1.1859859902827701</v>
@@ -60790,7 +60783,7 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>2486</v>
+        <v>2467</v>
       </c>
       <c r="B446">
         <v>0.61669918717302696</v>
@@ -60812,7 +60805,7 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>2487</v>
+        <v>2468</v>
       </c>
       <c r="B448">
         <v>-1.0165679795845399</v>
@@ -60823,7 +60816,7 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>2488</v>
+        <v>2469</v>
       </c>
       <c r="B449">
         <v>0.51591265075413595</v>
@@ -60856,7 +60849,7 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>2489</v>
+        <v>2470</v>
       </c>
       <c r="B452">
         <v>0.76832084300985304</v>
@@ -60867,7 +60860,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>2490</v>
+        <v>2471</v>
       </c>
       <c r="B453">
         <v>4.9027626065973599E-2</v>
@@ -60878,7 +60871,7 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>2491</v>
+        <v>2472</v>
       </c>
       <c r="B454">
         <v>-0.32836081608961898</v>
@@ -60889,7 +60882,7 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>2492</v>
+        <v>2473</v>
       </c>
       <c r="B455">
         <v>-1.1334010627426301</v>
@@ -60900,7 +60893,7 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>2493</v>
+        <v>2474</v>
       </c>
       <c r="B456">
         <v>0.76119355464281402</v>
@@ -60922,7 +60915,7 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>2494</v>
+        <v>2475</v>
       </c>
       <c r="B458">
         <v>7.6138104046315797E-2</v>
@@ -60933,7 +60926,7 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>2495</v>
+        <v>2476</v>
       </c>
       <c r="B459">
         <v>-1.22659965720326</v>
@@ -60977,7 +60970,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>2496</v>
+        <v>2477</v>
       </c>
       <c r="B463">
         <v>-0.22799471115727299</v>
@@ -60988,7 +60981,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>2497</v>
+        <v>2478</v>
       </c>
       <c r="B464">
         <v>0.616373865053503</v>
@@ -61010,7 +61003,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>2498</v>
+        <v>2479</v>
       </c>
       <c r="B466">
         <v>-1.31234705943631</v>
@@ -61043,7 +61036,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>2499</v>
+        <v>2480</v>
       </c>
       <c r="B469">
         <v>-3.1066915304055801E-3</v>
@@ -61054,7 +61047,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>2500</v>
+        <v>2481</v>
       </c>
       <c r="B470">
         <v>-1.4236530472703599</v>
@@ -61120,7 +61113,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>2501</v>
+        <v>2482</v>
       </c>
       <c r="B476">
         <v>-1.2496416223822899</v>
@@ -61131,7 +61124,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>2502</v>
+        <v>2483</v>
       </c>
       <c r="B477">
         <v>0.50786242878838295</v>
@@ -61175,7 +61168,7 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>2503</v>
+        <v>2484</v>
       </c>
       <c r="B481">
         <v>0.67310970859130703</v>
@@ -61186,7 +61179,7 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>2504</v>
+        <v>2485</v>
       </c>
       <c r="B482">
         <v>-0.84134177947919297</v>
@@ -61197,7 +61190,7 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>2505</v>
+        <v>2486</v>
       </c>
       <c r="B483">
         <v>-0.20060113032881799</v>
@@ -61230,7 +61223,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>2506</v>
+        <v>2487</v>
       </c>
       <c r="B486">
         <v>-1.25854627560625</v>
@@ -61241,7 +61234,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>2507</v>
+        <v>2488</v>
       </c>
       <c r="B487">
         <v>-0.48798001541359198</v>
@@ -61252,7 +61245,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>2508</v>
+        <v>2489</v>
       </c>
       <c r="B488">
         <v>-1.34445470691266</v>
@@ -61263,7 +61256,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>2509</v>
+        <v>2490</v>
       </c>
       <c r="B489">
         <v>0.63559873976808501</v>
@@ -61274,7 +61267,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>2510</v>
+        <v>2491</v>
       </c>
       <c r="B490">
         <v>-0.25409339246161999</v>
@@ -61285,7 +61278,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>2511</v>
+        <v>2492</v>
       </c>
       <c r="B491">
         <v>-0.22032337482655401</v>
@@ -61296,7 +61289,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>2512</v>
+        <v>2493</v>
       </c>
       <c r="B492">
         <v>-1.2911258258149401</v>
@@ -61307,7 +61300,7 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>2513</v>
+        <v>2494</v>
       </c>
       <c r="B493">
         <v>-0.210322387066183</v>
@@ -61351,7 +61344,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>2514</v>
+        <v>2495</v>
       </c>
       <c r="B497">
         <v>0.47656128908837297</v>
@@ -61362,7 +61355,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>2515</v>
+        <v>2496</v>
       </c>
       <c r="B498">
         <v>-0.10847030413895201</v>
@@ -61395,7 +61388,7 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>2516</v>
+        <v>2497</v>
       </c>
       <c r="B501">
         <v>-0.14215954560392599</v>
@@ -61406,7 +61399,7 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>2517</v>
+        <v>2498</v>
       </c>
       <c r="B502">
         <v>0.64425548985794301</v>
@@ -61417,7 +61410,7 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>2518</v>
+        <v>2499</v>
       </c>
       <c r="B503">
         <v>-0.258157266397461</v>
@@ -61428,7 +61421,7 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>2519</v>
+        <v>2500</v>
       </c>
       <c r="B504">
         <v>-0.214746911807878</v>
@@ -61439,7 +61432,7 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>2520</v>
+        <v>2501</v>
       </c>
       <c r="B505">
         <v>0.67037750973547505</v>
@@ -61450,7 +61443,7 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>2521</v>
+        <v>2502</v>
       </c>
       <c r="B506">
         <v>0.77139591996879997</v>
@@ -61483,7 +61476,7 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>2522</v>
+        <v>2503</v>
       </c>
       <c r="B509">
         <v>-0.148446190847668</v>
@@ -61505,7 +61498,7 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>2523</v>
+        <v>2504</v>
       </c>
       <c r="B511">
         <v>0.78114009097373804</v>
@@ -61516,7 +61509,7 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>2524</v>
+        <v>2505</v>
       </c>
       <c r="B512">
         <v>-0.33816666548917101</v>
@@ -61527,7 +61520,7 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>2525</v>
+        <v>2506</v>
       </c>
       <c r="B513">
         <v>-0.119173872091473</v>
@@ -61571,7 +61564,7 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>2526</v>
+        <v>2507</v>
       </c>
       <c r="B517">
         <v>-1.01605415071946</v>
@@ -61593,7 +61586,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>2527</v>
+        <v>2508</v>
       </c>
       <c r="B519">
         <v>0.10281154218854401</v>
@@ -61604,7 +61597,7 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>2528</v>
+        <v>2509</v>
       </c>
       <c r="B520">
         <v>-0.38492248506320698</v>
@@ -61615,7 +61608,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>2529</v>
+        <v>2510</v>
       </c>
       <c r="B521">
         <v>0.475697459441426</v>
@@ -61626,7 +61619,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>2530</v>
+        <v>2511</v>
       </c>
       <c r="B522">
         <v>0.37734713149438498</v>
@@ -61637,7 +61630,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>2531</v>
+        <v>2512</v>
       </c>
       <c r="B523">
         <v>-0.34587592758995001</v>
@@ -61659,7 +61652,7 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>2532</v>
+        <v>2513</v>
       </c>
       <c r="B525">
         <v>-0.24777613720958899</v>
@@ -61670,7 +61663,7 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>2533</v>
+        <v>2514</v>
       </c>
       <c r="B526">
         <v>0.818625721459591</v>
@@ -61681,7 +61674,7 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>2534</v>
+        <v>2515</v>
       </c>
       <c r="B527">
         <v>-1.5052607385068699</v>
@@ -61692,7 +61685,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>2535</v>
+        <v>2516</v>
       </c>
       <c r="B528">
         <v>0.586741601533872</v>
@@ -61703,7 +61696,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>2536</v>
+        <v>2517</v>
       </c>
       <c r="B529">
         <v>-0.55748133623223595</v>
@@ -61725,7 +61718,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>2537</v>
+        <v>2518</v>
       </c>
       <c r="B531">
         <v>-1.14962811962145</v>
@@ -61769,7 +61762,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>2538</v>
+        <v>2519</v>
       </c>
       <c r="B535">
         <v>-0.425546429375457</v>
@@ -61780,7 +61773,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>2539</v>
+        <v>2520</v>
       </c>
       <c r="B536">
         <v>-0.311836690463696</v>
@@ -61791,7 +61784,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>2540</v>
+        <v>2521</v>
       </c>
       <c r="B537">
         <v>-0.48179869503615802</v>
@@ -61802,7 +61795,7 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>2541</v>
+        <v>2522</v>
       </c>
       <c r="B538">
         <v>0.55349323863101696</v>
@@ -61824,7 +61817,7 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>2542</v>
+        <v>2523</v>
       </c>
       <c r="B540">
         <v>0.64991339685483296</v>
@@ -61846,7 +61839,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>2543</v>
+        <v>2524</v>
       </c>
       <c r="B542">
         <v>0.65150891988182802</v>
@@ -61868,7 +61861,7 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>2544</v>
+        <v>2525</v>
       </c>
       <c r="B544">
         <v>-0.22799471115727299</v>
@@ -61890,7 +61883,7 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>2545</v>
+        <v>2526</v>
       </c>
       <c r="B546">
         <v>0.82672795958165801</v>
@@ -61912,7 +61905,7 @@
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>2546</v>
+        <v>2527</v>
       </c>
       <c r="B548">
         <v>0.71534489990441896</v>
@@ -61956,7 +61949,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>2547</v>
+        <v>2528</v>
       </c>
       <c r="B552">
         <v>0.23373759362178301</v>
@@ -61978,7 +61971,7 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>2548</v>
+        <v>2529</v>
       </c>
       <c r="B554">
         <v>-0.32777109189634102</v>
@@ -61989,7 +61982,7 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>2549</v>
+        <v>2530</v>
       </c>
       <c r="B555">
         <v>-0.89777403645601594</v>
@@ -62000,7 +61993,7 @@
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>2550</v>
+        <v>2531</v>
       </c>
       <c r="B556">
         <v>0.54765455989064904</v>
@@ -62011,7 +62004,7 @@
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>2551</v>
+        <v>2532</v>
       </c>
       <c r="B557">
         <v>0.73873328777855496</v>
@@ -62022,7 +62015,7 @@
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>2552</v>
+        <v>2533</v>
       </c>
       <c r="B558">
         <v>-1.3601602750402499</v>
@@ -62044,7 +62037,7 @@
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>2553</v>
+        <v>2534</v>
       </c>
       <c r="B560">
         <v>-1.0748807512540299</v>
@@ -62055,7 +62048,7 @@
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>2554</v>
+        <v>2535</v>
       </c>
       <c r="B561">
         <v>-1.18374972655177</v>
@@ -62077,7 +62070,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>2555</v>
+        <v>2536</v>
       </c>
       <c r="B563">
         <v>-1.1832410299605101</v>
@@ -62099,7 +62092,7 @@
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>2556</v>
+        <v>2537</v>
       </c>
       <c r="B565">
         <v>-0.28495231618560801</v>
@@ -62121,7 +62114,7 @@
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>2557</v>
+        <v>2538</v>
       </c>
       <c r="B567">
         <v>0.41938382501981403</v>
@@ -62132,7 +62125,7 @@
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>2558</v>
+        <v>2539</v>
       </c>
       <c r="B568">
         <v>-0.27911200879114401</v>
@@ -62176,7 +62169,7 @@
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>2559</v>
+        <v>2540</v>
       </c>
       <c r="B572">
         <v>0.41267332124416201</v>
@@ -62231,7 +62224,7 @@
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>2560</v>
+        <v>2541</v>
       </c>
       <c r="B577">
         <v>0.156370258158958</v>
@@ -62253,7 +62246,7 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>2561</v>
+        <v>2542</v>
       </c>
       <c r="B579">
         <v>-1.2658358866557899</v>
@@ -62264,7 +62257,7 @@
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>2562</v>
+        <v>2543</v>
       </c>
       <c r="B580">
         <v>-0.43040583507636099</v>
@@ -62275,7 +62268,7 @@
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>2563</v>
+        <v>2544</v>
       </c>
       <c r="B581">
         <v>-1.1366807719840599</v>
@@ -62330,7 +62323,7 @@
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>2564</v>
+        <v>2545</v>
       </c>
       <c r="B586">
         <v>-0.28547809523564899</v>
@@ -62352,7 +62345,7 @@
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>2565</v>
+        <v>2546</v>
       </c>
       <c r="B588">
         <v>-1.68324612484707</v>
@@ -62374,7 +62367,7 @@
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>2566</v>
+        <v>2547</v>
       </c>
       <c r="B590">
         <v>-1.4014067610255001</v>
@@ -62407,7 +62400,7 @@
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>2567</v>
+        <v>2548</v>
       </c>
       <c r="B593">
         <v>-0.28049664104661498</v>
@@ -62418,7 +62411,7 @@
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>2568</v>
+        <v>2549</v>
       </c>
       <c r="B594">
         <v>-0.355970483703762</v>
@@ -62429,7 +62422,7 @@
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>2569</v>
+        <v>2550</v>
       </c>
       <c r="B595">
         <v>-0.45497486775065199</v>
@@ -62440,7 +62433,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>2570</v>
+        <v>2551</v>
       </c>
       <c r="B596">
         <v>-1.6405590707411</v>
@@ -62451,7 +62444,7 @@
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>2571</v>
+        <v>2552</v>
       </c>
       <c r="B597">
         <v>0.66799428961094198</v>
@@ -62462,7 +62455,7 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>2572</v>
+        <v>2553</v>
       </c>
       <c r="B598">
         <v>-1.1427819333987901</v>
@@ -62473,7 +62466,7 @@
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>2573</v>
+        <v>2554</v>
       </c>
       <c r="B599">
         <v>-1.08232390593057</v>
@@ -62506,7 +62499,7 @@
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>2574</v>
+        <v>2555</v>
       </c>
       <c r="B602">
         <v>-1.1086191999699799</v>
@@ -62539,7 +62532,7 @@
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>2575</v>
+        <v>2556</v>
       </c>
       <c r="B605">
         <v>0.434220423094625</v>
@@ -62572,7 +62565,7 @@
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>2576</v>
+        <v>2557</v>
       </c>
       <c r="B608">
         <v>-0.66869750679619</v>
@@ -62594,7 +62587,7 @@
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>2577</v>
+        <v>2558</v>
       </c>
       <c r="B610">
         <v>-0.23870469205334399</v>
@@ -62605,7 +62598,7 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>2578</v>
+        <v>2559</v>
       </c>
       <c r="B611">
         <v>0.72288646720253302</v>
@@ -62627,7 +62620,7 @@
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>2579</v>
+        <v>2560</v>
       </c>
       <c r="B613">
         <v>-0.44523940087810798</v>
@@ -62638,7 +62631,7 @@
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>2580</v>
+        <v>2561</v>
       </c>
       <c r="B614">
         <v>0.90186859642708705</v>
@@ -62660,7 +62653,7 @@
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>2581</v>
+        <v>2562</v>
       </c>
       <c r="B616">
         <v>-1.0165679795845399</v>
@@ -62693,7 +62686,7 @@
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>2582</v>
+        <v>2563</v>
       </c>
       <c r="B619">
         <v>-0.48037151291248698</v>
@@ -62704,7 +62697,7 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>2583</v>
+        <v>2564</v>
       </c>
       <c r="B620">
         <v>-1.12940367668362</v>
@@ -62715,7 +62708,7 @@
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>2584</v>
+        <v>2565</v>
       </c>
       <c r="B621">
         <v>0.450564186421754</v>
@@ -62726,7 +62719,7 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>2585</v>
+        <v>2566</v>
       </c>
       <c r="B622">
         <v>0.18499558023458099</v>
@@ -62737,7 +62730,7 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>2586</v>
+        <v>2567</v>
       </c>
       <c r="B623">
         <v>-1.0909118750120801</v>
@@ -62814,7 +62807,7 @@
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>2587</v>
+        <v>2568</v>
       </c>
       <c r="B630">
         <v>-1.43519779700755</v>
@@ -62836,7 +62829,7 @@
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>2588</v>
+        <v>2569</v>
       </c>
       <c r="B632">
         <v>0.57879735947454303</v>
@@ -62847,7 +62840,7 @@
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>2589</v>
+        <v>2570</v>
       </c>
       <c r="B633">
         <v>0.90186859642708705</v>
@@ -62858,7 +62851,7 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>2590</v>
+        <v>2571</v>
       </c>
       <c r="B634">
         <v>-1.73774248874966</v>
@@ -62880,7 +62873,7 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>2591</v>
+        <v>2572</v>
       </c>
       <c r="B636">
         <v>-1.0165679795845399</v>
@@ -62891,7 +62884,7 @@
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>2592</v>
+        <v>2573</v>
       </c>
       <c r="B637">
         <v>9.9218950694444197E-2</v>
@@ -62902,7 +62895,7 @@
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>2593</v>
+        <v>2574</v>
       </c>
       <c r="B638">
         <v>-1.2861586649902701</v>
@@ -62946,7 +62939,7 @@
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>2594</v>
+        <v>2575</v>
       </c>
       <c r="B642">
         <v>-0.45327575381249302</v>
@@ -62957,7 +62950,7 @@
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>2595</v>
+        <v>2576</v>
       </c>
       <c r="B643">
         <v>-0.69082157816821099</v>
@@ -62968,7 +62961,7 @@
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>2596</v>
+        <v>2577</v>
       </c>
       <c r="B644">
         <v>-0.40283335867696202</v>
@@ -62979,7 +62972,7 @@
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>2597</v>
+        <v>2578</v>
       </c>
       <c r="B645">
         <v>-1.37415929509933</v>
@@ -63001,7 +62994,7 @@
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>2598</v>
+        <v>2579</v>
       </c>
       <c r="B647">
         <v>-1.2129112482651001</v>
@@ -63012,7 +63005,7 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>2599</v>
+        <v>2580</v>
       </c>
       <c r="B648">
         <v>-1.1006843667151001</v>

--- a/nmds_results.xlsx
+++ b/nmds_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drake\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95262361-ADE3-469D-BAAF-6F233E752D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8F2923-292B-4B88-AE16-4C9B8D04D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1170" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card_WA_Scores" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="662">
   <si>
     <t>NMDS1</t>
   </si>
@@ -911,9 +911,6 @@
     <t>Batterskull</t>
   </si>
   <si>
-    <t>Beanstalk Giant</t>
-  </si>
-  <si>
     <t>Blooming Marsh</t>
   </si>
   <si>
@@ -938,9 +935,6 @@
     <t>Carnage Tyrant</t>
   </si>
   <si>
-    <t>Cartographer's Survey</t>
-  </si>
-  <si>
     <t>Cephalid Coliseum</t>
   </si>
   <si>
@@ -959,9 +953,6 @@
     <t>Disciple of Freyalise</t>
   </si>
   <si>
-    <t>Dragonlord Atarka</t>
-  </si>
-  <si>
     <t>Dragonlord Dromoka</t>
   </si>
   <si>
@@ -989,9 +980,6 @@
     <t>Field of Ruin</t>
   </si>
   <si>
-    <t>Field Trip</t>
-  </si>
-  <si>
     <t>Finale of Devastation</t>
   </si>
   <si>
@@ -1025,9 +1013,6 @@
     <t>Halimar Depths</t>
   </si>
   <si>
-    <t>Hanweir Garrison</t>
-  </si>
-  <si>
     <t>Haywire Mite</t>
   </si>
   <si>
@@ -1199,9 +1184,6 @@
     <t>sb_Back to Nature</t>
   </si>
   <si>
-    <t>sb_Basic Conjuration</t>
-  </si>
-  <si>
     <t>sb_Batterskull</t>
   </si>
   <si>
@@ -1265,9 +1247,6 @@
     <t>sb_Consulate Crackdown</t>
   </si>
   <si>
-    <t>sb_Containment Breach</t>
-  </si>
-  <si>
     <t>sb_Courser of Kruphix</t>
   </si>
   <si>
@@ -1289,9 +1268,6 @@
     <t>sb_Damping Sphere</t>
   </si>
   <si>
-    <t>sb_Dead // Gone</t>
-  </si>
-  <si>
     <t>sb_Deafening Silence</t>
   </si>
   <si>
@@ -1322,9 +1298,6 @@
     <t>sb_Elixir of Immortality</t>
   </si>
   <si>
-    <t>sb_Environmental Sciences</t>
-  </si>
-  <si>
     <t>sb_Escape to the Wilds</t>
   </si>
   <si>
@@ -1436,9 +1409,6 @@
     <t>sb_Intervention Pact</t>
   </si>
   <si>
-    <t>sb_Introduction to Annihilation</t>
-  </si>
-  <si>
     <t>sb_Ipnu Rivulet</t>
   </si>
   <si>
@@ -1490,9 +1460,6 @@
     <t>sb_Mana Leak</t>
   </si>
   <si>
-    <t>sb_Mascot Exhibition</t>
-  </si>
-  <si>
     <t>sb_Meddling Mage</t>
   </si>
   <si>
@@ -1541,9 +1508,6 @@
     <t>sb_Omnath, Locus of Creation</t>
   </si>
   <si>
-    <t>sb_Overgrown Arch</t>
-  </si>
-  <si>
     <t>sb_Painful Truths</t>
   </si>
   <si>
@@ -1553,9 +1517,6 @@
     <t>sb_Pawpatch Formation</t>
   </si>
   <si>
-    <t>sb_Pest Summoning</t>
-  </si>
-  <si>
     <t>sb_Pit of Offerings</t>
   </si>
   <si>
@@ -1937,12 +1898,6 @@
     <t>Card</t>
   </si>
   <si>
-    <t>Up the Beanstalk</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>sb_Door to Nothingness</t>
   </si>
   <si>
@@ -1980,6 +1935,78 @@
   </si>
   <si>
     <t>sb_Zacama, Primal Calamity</t>
+  </si>
+  <si>
+    <t>Cascading Cataracts</t>
+  </si>
+  <si>
+    <t>Chromatic Sphere</t>
+  </si>
+  <si>
+    <t>Consecrated Sphinx</t>
+  </si>
+  <si>
+    <t>Fable of the Mirror-Breaker</t>
+  </si>
+  <si>
+    <t>Hallowed Fountain</t>
+  </si>
+  <si>
+    <t>sb_Boon of Boseiju</t>
+  </si>
+  <si>
+    <t>sb_Cloudstone Curio</t>
+  </si>
+  <si>
+    <t>sb_Colossal Dreadmaw</t>
+  </si>
+  <si>
+    <t>sb_Dead / Gone</t>
+  </si>
+  <si>
+    <t>sb_Deep Forest Hermit</t>
+  </si>
+  <si>
+    <t>sb_Fable of the Mirror-Breaker</t>
+  </si>
+  <si>
+    <t>sb_Filigree Sages</t>
+  </si>
+  <si>
+    <t>sb_Fracturing Gust</t>
+  </si>
+  <si>
+    <t>sb_Gut Shot</t>
+  </si>
+  <si>
+    <t>sb_Jegantha, the Wellspring</t>
+  </si>
+  <si>
+    <t>sb_The Filigree Sylex</t>
+  </si>
+  <si>
+    <t>sb_Timeless Lotus</t>
+  </si>
+  <si>
+    <t>sb_Timely Reinforcements</t>
+  </si>
+  <si>
+    <t>Storm the Festival</t>
+  </si>
+  <si>
+    <t>Tatyova, Benthic Druid</t>
+  </si>
+  <si>
+    <t>Timeless Lotus</t>
+  </si>
+  <si>
+    <t>Unknown Card</t>
+  </si>
+  <si>
+    <t>Vigor</t>
+  </si>
+  <si>
+    <t>Wrenn and Six</t>
   </si>
 </sst>
 </file>
@@ -2355,12 +2382,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C649"/>
+  <dimension ref="A1:C659"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2374,10 +2401,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>-0.54202244286493095</v>
+        <v>-0.54795730448574298</v>
       </c>
       <c r="C2">
-        <v>5.9477178598244702E-2</v>
+        <v>-4.4505557754270099E-2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2385,10 +2412,10 @@
         <v>289</v>
       </c>
       <c r="B3">
-        <v>-1.20362248086202</v>
+        <v>-1.2227447630778701</v>
       </c>
       <c r="C3">
-        <v>-0.43103906189473801</v>
+        <v>-0.41250362859502199</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2396,10 +2423,10 @@
         <v>290</v>
       </c>
       <c r="B4">
-        <v>-9.9463001601684795E-2</v>
+        <v>-9.3390628191401495E-2</v>
       </c>
       <c r="C4">
-        <v>0.16140525820500401</v>
+        <v>0.100780369626835</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2407,10 +2434,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>-1.06330155058013</v>
+        <v>-1.1798593778245501</v>
       </c>
       <c r="C5">
-        <v>-0.25748828523984302</v>
+        <v>-0.57427394448800595</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2418,10 +2445,10 @@
         <v>291</v>
       </c>
       <c r="B6">
-        <v>-1.1454839987858001</v>
+        <v>-1.1705422559471499</v>
       </c>
       <c r="C6">
-        <v>-1.0621093090007501</v>
+        <v>-1.0474082206172399</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2429,10 +2456,10 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>0.65822001386415296</v>
+        <v>0.67962330757760603</v>
       </c>
       <c r="C7">
-        <v>-0.18265400379330299</v>
+        <v>-0.22429536600315</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2440,10 +2467,10 @@
         <v>292</v>
       </c>
       <c r="B8">
-        <v>-0.309384553006263</v>
+        <v>-0.31427705693803198</v>
       </c>
       <c r="C8">
-        <v>0.30639278880342202</v>
+        <v>0.25933642997069101</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2451,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>-3.0837131266656901E-4</v>
+        <v>-2.62013609681693E-4</v>
       </c>
       <c r="C9" s="2">
-        <v>-4.44596622984826E-5</v>
+        <v>-6.2856667939504294E-5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2462,10 +2489,10 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>-1.28604997322514</v>
+        <v>-1.2911279145047101</v>
       </c>
       <c r="C10">
-        <v>-0.64047179115706898</v>
+        <v>-0.64396214829475895</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2473,10 +2500,10 @@
         <v>293</v>
       </c>
       <c r="B11">
-        <v>-1.13234650230461</v>
+        <v>-1.15814437045622</v>
       </c>
       <c r="C11">
-        <v>-1.4005894302280399</v>
+        <v>-1.38200420370414</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2484,10 +2511,10 @@
         <v>7</v>
       </c>
       <c r="B12">
-        <v>0.19205973664289799</v>
+        <v>0.18145658161949799</v>
       </c>
       <c r="C12">
-        <v>7.5512875190526699E-2</v>
+        <v>7.4349377073404305E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2495,10 +2522,10 @@
         <v>294</v>
       </c>
       <c r="B13">
-        <v>-0.41241793460991799</v>
+        <v>-0.43922381166353303</v>
       </c>
       <c r="C13">
-        <v>0.42933401355550399</v>
+        <v>0.26604923811979603</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2506,10 +2533,10 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-0.76354321096166</v>
+        <v>-0.74127642988256104</v>
       </c>
       <c r="C14">
-        <v>-9.6535849309889801E-2</v>
+        <v>-0.10429373568405401</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2517,10 +2544,10 @@
         <v>9</v>
       </c>
       <c r="B15">
-        <v>0.80363542255734399</v>
+        <v>0.82159749478000199</v>
       </c>
       <c r="C15">
-        <v>-0.49850131849229301</v>
+        <v>-0.545020052646494</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2528,32 +2555,32 @@
         <v>295</v>
       </c>
       <c r="B16">
-        <v>-1.29983655620397</v>
+        <v>-1.32571722281697</v>
       </c>
       <c r="C16">
-        <v>-0.88339985936349497</v>
+        <v>-0.86869562680928403</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>-0.98293899672748297</v>
+        <v>-0.82893595314801305</v>
       </c>
       <c r="C17">
-        <v>0.42103784826248702</v>
+        <v>9.0532559255122394E-3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>296</v>
       </c>
       <c r="B18">
-        <v>-0.84717891690880698</v>
+        <v>-1.5558742656072999</v>
       </c>
       <c r="C18">
-        <v>6.6099618791696901E-2</v>
+        <v>-0.79710738587186303</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2561,87 +2588,87 @@
         <v>297</v>
       </c>
       <c r="B19">
-        <v>-1.5255300008477299</v>
+        <v>0.91703736877801401</v>
       </c>
       <c r="C19">
-        <v>-0.82804141758409699</v>
+        <v>-0.16037233259369099</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>11</v>
       </c>
       <c r="B20">
-        <v>0.90133571895592701</v>
+        <v>-0.58404613915678405</v>
       </c>
       <c r="C20">
-        <v>-0.12772428727779001</v>
+        <v>1.19840178664178E-2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>298</v>
       </c>
       <c r="B21">
-        <v>-0.61143054101473804</v>
+        <v>-5.2727824915371098E-2</v>
       </c>
       <c r="C21">
-        <v>3.78677311202597E-2</v>
+        <v>0.66093556478443605</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>299</v>
+        <v>12</v>
       </c>
       <c r="B22">
-        <v>-4.1717848706752103E-2</v>
+        <v>-0.47232260987368102</v>
       </c>
       <c r="C22">
-        <v>0.70572453484640196</v>
+        <v>0.11409700383763501</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23">
-        <v>-0.51617221798746105</v>
+        <v>0.28244019739046</v>
       </c>
       <c r="C23">
-        <v>0.103534391236128</v>
+        <v>3.7045564750473901E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24">
-        <v>0.31252284839976002</v>
+        <v>-1.28238249266341</v>
       </c>
       <c r="C24">
-        <v>2.7350930294601498E-2</v>
+        <v>-0.82029249789292702</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25">
-        <v>-1.2604828547100799</v>
+        <v>-0.95631391525490295</v>
       </c>
       <c r="C25">
-        <v>-0.83222548741809099</v>
+        <v>9.1734045071359196E-3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="B26">
-        <v>-0.92069365004152204</v>
+        <v>0.81089090081215798</v>
       </c>
       <c r="C26">
-        <v>4.2470351025895199E-2</v>
+        <v>-0.19798549535286999</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -2649,10 +2676,10 @@
         <v>300</v>
       </c>
       <c r="B27">
-        <v>0.78801527250221703</v>
+        <v>0.46319844525097698</v>
       </c>
       <c r="C27">
-        <v>-0.163338795516138</v>
+        <v>-0.275261137255574</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2660,10 +2687,10 @@
         <v>301</v>
       </c>
       <c r="B28">
-        <v>0.45495090991140102</v>
+        <v>0.56304811386000098</v>
       </c>
       <c r="C28">
-        <v>-0.19165153533739601</v>
+        <v>0.30338749427351602</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2671,10 +2698,10 @@
         <v>302</v>
       </c>
       <c r="B29">
-        <v>0.54746703452005696</v>
+        <v>0.23725977286532601</v>
       </c>
       <c r="C29">
-        <v>0.33627180636916298</v>
+        <v>0.43700746213689501</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2682,65 +2709,65 @@
         <v>303</v>
       </c>
       <c r="B30">
-        <v>0.28025349394418902</v>
+        <v>-0.368595904736637</v>
       </c>
       <c r="C30">
-        <v>0.55160558356599698</v>
+        <v>-0.110841914467255</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>304</v>
+        <v>638</v>
       </c>
       <c r="B31">
-        <v>-0.36807318151080598</v>
+        <v>-0.21054867790587101</v>
       </c>
       <c r="C31">
-        <v>-7.9108270785752596E-2</v>
+        <v>-1.6086135631854299</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>305</v>
+        <v>16</v>
       </c>
       <c r="B32">
-        <v>-0.46952957021182201</v>
+        <v>-0.63416731336384602</v>
       </c>
       <c r="C32">
-        <v>0.16997980871437601</v>
+        <v>0.12778416177166499</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B33">
-        <v>-0.65072051674562004</v>
+        <v>-0.45812741551098102</v>
       </c>
       <c r="C33">
-        <v>0.169141900880693</v>
+        <v>6.8335956822971097E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>304</v>
       </c>
       <c r="B34">
-        <v>-0.47207407783444599</v>
+        <v>0.69036181651784101</v>
       </c>
       <c r="C34">
-        <v>0.10508816894593601</v>
+        <v>0.125303410986357</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>306</v>
+        <v>639</v>
       </c>
       <c r="B35">
-        <v>0.67119649672297299</v>
+        <v>-0.63061725517887701</v>
       </c>
       <c r="C35">
-        <v>0.155650125568387</v>
+        <v>0.112669721531703</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -2748,10 +2775,10 @@
         <v>18</v>
       </c>
       <c r="B36">
-        <v>-1.0983139967097399</v>
+        <v>-1.1281323913636001</v>
       </c>
       <c r="C36">
-        <v>-1.4970014521941399</v>
+        <v>-1.4771734764404401</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -2759,21 +2786,21 @@
         <v>19</v>
       </c>
       <c r="B37">
-        <v>-1.46610338194833</v>
+        <v>-1.49102160138823</v>
       </c>
       <c r="C37">
-        <v>-0.71287618533326003</v>
+        <v>-0.69004522128538803</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B38">
-        <v>0.85299124566499895</v>
+        <v>0.87240998711598805</v>
       </c>
       <c r="C38">
-        <v>-0.18857741149107299</v>
+        <v>-0.21391702931518899</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2781,142 +2808,142 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>0.49051570477982698</v>
+        <v>0.47989141900356902</v>
       </c>
       <c r="C39">
-        <v>0.20051456924141101</v>
+        <v>0.202520864190602</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B40">
-        <v>-1.10275307577409</v>
+        <v>-1.1339648919530401</v>
       </c>
       <c r="C40">
-        <v>-1.49806526804134</v>
+        <v>-1.4616957133019199</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>640</v>
       </c>
       <c r="B41">
-        <v>-1.1314636345585201</v>
+        <v>-1.17673414679627</v>
       </c>
       <c r="C41">
-        <v>-0.30552477578610199</v>
+        <v>-1.3118698236556601</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42">
-        <v>0.48587639694651102</v>
+        <v>-1.0595772365488201</v>
       </c>
       <c r="C42">
-        <v>-0.14302059994201</v>
+        <v>-0.45369187342749601</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43">
-        <v>2.9491867681630798E-2</v>
+        <v>0.48457731609441201</v>
       </c>
       <c r="C43">
-        <v>0.212166321984293</v>
+        <v>-0.15174170677728099</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>309</v>
+        <v>23</v>
       </c>
       <c r="B44">
-        <v>-1.7326282042389101</v>
+        <v>2.5789422481912901E-2</v>
       </c>
       <c r="C44">
-        <v>-0.13697415786339101</v>
+        <v>0.20741827628147599</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B45">
-        <v>-1.3093330574117701</v>
+        <v>-1.7506623372877199</v>
       </c>
       <c r="C45">
-        <v>0.32016698333900401</v>
+        <v>-0.12570859243025101</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B46">
-        <v>2.8251332606920799E-2</v>
+        <v>-1.33417703002549</v>
       </c>
       <c r="C46">
-        <v>0.64040979846868495</v>
+        <v>0.31027553890465998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>309</v>
       </c>
       <c r="B47">
-        <v>-0.79258379450071703</v>
+        <v>3.2336873762708399E-2</v>
       </c>
       <c r="C47">
-        <v>-0.353193712361215</v>
+        <v>0.59287462921490897</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>312</v>
+        <v>24</v>
       </c>
       <c r="B48">
-        <v>-1.1767143225765899</v>
+        <v>-0.88394721455119296</v>
       </c>
       <c r="C48">
-        <v>0.283449771596818</v>
+        <v>-0.25584050830076199</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B49">
-        <v>-1.22212737142085</v>
+        <v>-1.2484636793289301</v>
       </c>
       <c r="C49">
-        <v>-1.2395511278648901</v>
+        <v>-1.2282960484744401</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B50">
-        <v>-0.41241793460991799</v>
+        <v>-0.43922381166353303</v>
       </c>
       <c r="C50">
-        <v>0.42933401355550399</v>
+        <v>0.26604923811979603</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B51">
-        <v>-0.34858284014269397</v>
+        <v>-0.36389465619947298</v>
       </c>
       <c r="C51">
-        <v>0.747328088254122</v>
+        <v>0.68001645074077499</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2924,10 +2951,10 @@
         <v>25</v>
       </c>
       <c r="B52">
-        <v>0.65831385864431002</v>
+        <v>0.67918341844109797</v>
       </c>
       <c r="C52">
-        <v>-0.33102065639109801</v>
+        <v>-0.37041068580747299</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2935,10 +2962,10 @@
         <v>26</v>
       </c>
       <c r="B53">
-        <v>-0.21923922126479201</v>
+        <v>-0.18460785251113099</v>
       </c>
       <c r="C53">
-        <v>0.31440160101050502</v>
+        <v>0.302374236218029</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -2946,10 +2973,10 @@
         <v>27</v>
       </c>
       <c r="B54">
-        <v>0.64326453317331</v>
+        <v>0.66522563664900702</v>
       </c>
       <c r="C54">
-        <v>-0.207868723674411</v>
+        <v>-0.249427047449998</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -2957,21 +2984,21 @@
         <v>28</v>
       </c>
       <c r="B55">
-        <v>-1.0570998899587101</v>
+        <v>-0.99708560649898503</v>
       </c>
       <c r="C55">
-        <v>0.55898575891344005</v>
+        <v>0.29990854407626699</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B56">
-        <v>-0.92144839783500399</v>
+        <v>-0.94482996119407503</v>
       </c>
       <c r="C56">
-        <v>0.46559520720624897</v>
+        <v>0.42458482886300603</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -2979,10 +3006,10 @@
         <v>29</v>
       </c>
       <c r="B57">
-        <v>1.07711067734656E-2</v>
+        <v>-4.4733399388336703E-3</v>
       </c>
       <c r="C57">
-        <v>0.66837772699896303</v>
+        <v>0.63840202054102002</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -2990,21 +3017,21 @@
         <v>30</v>
       </c>
       <c r="B58">
-        <v>-0.80171461281525003</v>
+        <v>-0.63171733363475502</v>
       </c>
       <c r="C58">
-        <v>0.55883876533149002</v>
+        <v>0.43326674368642798</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B59">
-        <v>-0.41513126214657198</v>
+        <v>-0.46095999001375998</v>
       </c>
       <c r="C59">
-        <v>0.31275680238805698</v>
+        <v>0.32498047400773</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -3012,10 +3039,10 @@
         <v>31</v>
       </c>
       <c r="B60">
-        <v>-0.74495514058728096</v>
+        <v>-0.61439267703785205</v>
       </c>
       <c r="C60">
-        <v>-0.467112925038421</v>
+        <v>-0.82025316022516104</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -3023,10 +3050,10 @@
         <v>32</v>
       </c>
       <c r="B61">
-        <v>-0.118569999495708</v>
+        <v>-0.10152125376331</v>
       </c>
       <c r="C61">
-        <v>8.4025008143617894E-2</v>
+        <v>3.54140832003947E-2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -3034,21 +3061,21 @@
         <v>33</v>
       </c>
       <c r="B62">
-        <v>-1.2564444521624301</v>
+        <v>-1.29169757518269</v>
       </c>
       <c r="C62">
-        <v>-0.38206565795555297</v>
+        <v>-0.40642454942478701</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B63">
-        <v>-0.98146157947925805</v>
+        <v>-0.124737558557325</v>
       </c>
       <c r="C63">
-        <v>0.53340278084510595</v>
+        <v>-1.10234026220201</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3056,10 +3083,10 @@
         <v>34</v>
       </c>
       <c r="B64">
-        <v>1.02449775038742E-2</v>
+        <v>7.7447282863773103E-4</v>
       </c>
       <c r="C64">
-        <v>0.26235658704107201</v>
+        <v>0.257525375793006</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3067,54 +3094,54 @@
         <v>35</v>
       </c>
       <c r="B65">
-        <v>6.0651749996775702E-2</v>
+        <v>7.1050922180831602E-2</v>
       </c>
       <c r="C65">
-        <v>6.2479434732146399E-2</v>
+        <v>6.3270169110827099E-2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>319</v>
+        <v>641</v>
       </c>
       <c r="B66">
-        <v>0.57763837251911498</v>
+        <v>0.32545336014321302</v>
       </c>
       <c r="C66">
-        <v>-0.60049439498520896</v>
+        <v>1.3597113762378501</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B67">
-        <v>0.51241893718966303</v>
+        <v>0.59792292065795205</v>
       </c>
       <c r="C67">
-        <v>0.26130024857070799</v>
+        <v>-0.64222948711846595</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B68">
-        <v>-0.90837094598426404</v>
+        <v>0.51887691455988005</v>
       </c>
       <c r="C68">
-        <v>0.505877349403559</v>
+        <v>0.203980755982827</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B69">
-        <v>-1.3541246312009301</v>
+        <v>-1.3689237494570199</v>
       </c>
       <c r="C69">
-        <v>-0.56996290279605399</v>
+        <v>-0.57147931415463005</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3122,10 +3149,10 @@
         <v>36</v>
       </c>
       <c r="B70">
-        <v>-1.2070809734585799</v>
+        <v>-1.2538901365416</v>
       </c>
       <c r="C70">
-        <v>-2.7080678029201301E-2</v>
+        <v>-8.6321024445540295E-2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -3133,54 +3160,54 @@
         <v>37</v>
       </c>
       <c r="B71">
-        <v>-0.94085082186300695</v>
+        <v>-0.91828071381936804</v>
       </c>
       <c r="C71">
-        <v>0.36159074092404198</v>
+        <v>0.29411500285618503</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B72">
-        <v>-1.45191123105353</v>
+        <v>-1.46609667588786</v>
       </c>
       <c r="C72">
-        <v>-8.6886713736520196E-2</v>
+        <v>-8.8209787798195993E-2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B73">
-        <v>-1.16996845087402</v>
+        <v>-1.14596688416571</v>
       </c>
       <c r="C73">
-        <v>0.80821626752188902</v>
+        <v>0.83504339676693695</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B74">
-        <v>0.82508188080481004</v>
+        <v>0.85172899653860001</v>
       </c>
       <c r="C74">
-        <v>-0.42562342875034798</v>
+        <v>-0.46934656397511298</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B75">
-        <v>-0.25487017008898499</v>
+        <v>-0.27175441379619297</v>
       </c>
       <c r="C75">
-        <v>0.46081387156014397</v>
+        <v>0.398662139711218</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3188,10 +3215,10 @@
         <v>38</v>
       </c>
       <c r="B76">
-        <v>6.1241707997322899E-3</v>
+        <v>6.0434049706554801E-3</v>
       </c>
       <c r="C76">
-        <v>3.24444177380767E-2</v>
+        <v>2.7077381921135599E-2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3199,32 +3226,32 @@
         <v>39</v>
       </c>
       <c r="B77">
-        <v>0.617041563934983</v>
+        <v>0.631889912417824</v>
       </c>
       <c r="C77">
-        <v>-0.48597801631482301</v>
+        <v>-0.52602835389442004</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B78">
-        <v>0.78232663341321895</v>
+        <v>0.80231042906636996</v>
       </c>
       <c r="C78">
-        <v>-0.44205046436308798</v>
+        <v>-0.49229218302083599</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B79">
-        <v>-1.16660041700521</v>
+        <v>-1.20085867285184</v>
       </c>
       <c r="C79">
-        <v>-1.37798133373193</v>
+        <v>-1.34089385989829</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -3232,10 +3259,10 @@
         <v>40</v>
       </c>
       <c r="B80">
-        <v>-0.26136126418399303</v>
+        <v>-0.26768654866645802</v>
       </c>
       <c r="C80">
-        <v>0.25853491036991699</v>
+        <v>0.26394234387647503</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -3243,21 +3270,21 @@
         <v>41</v>
       </c>
       <c r="B81">
-        <v>-1.27763319510276</v>
+        <v>-1.2976680456035099</v>
       </c>
       <c r="C81">
-        <v>-0.75834951181580101</v>
+        <v>-0.75539696072587104</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B82">
-        <v>-0.225799801407152</v>
+        <v>-0.239120945290444</v>
       </c>
       <c r="C82">
-        <v>0.49184290134791298</v>
+        <v>0.43354420519961401</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -3265,32 +3292,32 @@
         <v>42</v>
       </c>
       <c r="B83">
-        <v>-0.96454726511145294</v>
+        <v>-0.99116440570269004</v>
       </c>
       <c r="C83">
-        <v>-0.247209240801854</v>
+        <v>-0.309178857487027</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B84">
-        <v>0.73209971640937499</v>
+        <v>0.76410996602947701</v>
       </c>
       <c r="C84">
-        <v>0.55821551512246803</v>
+        <v>0.52029225243392696</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B85">
-        <v>-1.1094473407227901</v>
+        <v>-1.13913722852627</v>
       </c>
       <c r="C85">
-        <v>-1.46653908266355</v>
+        <v>-1.44580919403583</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3298,10 +3325,10 @@
         <v>43</v>
       </c>
       <c r="B86">
-        <v>-0.24883759676673001</v>
+        <v>-0.22575237486296601</v>
       </c>
       <c r="C86">
-        <v>0.16319529790119999</v>
+        <v>0.166533453019306</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -3309,21 +3336,21 @@
         <v>44</v>
       </c>
       <c r="B87">
-        <v>-1.1689032447738701</v>
+        <v>-0.36181665847668798</v>
       </c>
       <c r="C87">
-        <v>-0.31041728644056699</v>
+        <v>-1.34906339577773</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B88">
-        <v>-1.4234846578425899</v>
+        <v>-1.4454434513155301</v>
       </c>
       <c r="C88">
-        <v>-0.61206966356197401</v>
+        <v>-0.59766642290536598</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -3331,10 +3358,10 @@
         <v>45</v>
       </c>
       <c r="B89">
-        <v>-0.293621052363568</v>
+        <v>-0.30647432814519199</v>
       </c>
       <c r="C89">
-        <v>0.76049796409088299</v>
+        <v>0.69985714172661395</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -3342,10 +3369,10 @@
         <v>46</v>
       </c>
       <c r="B90">
-        <v>0.67310938879279303</v>
+        <v>0.69447327611171195</v>
       </c>
       <c r="C90">
-        <v>-0.32341842761189599</v>
+        <v>-0.36683013992436297</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -3353,10 +3380,10 @@
         <v>47</v>
       </c>
       <c r="B91">
-        <v>-0.33267207992572201</v>
+        <v>-0.31099025429299498</v>
       </c>
       <c r="C91">
-        <v>0.28638674158170702</v>
+        <v>0.218209911578884</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -3364,10 +3391,10 @@
         <v>48</v>
       </c>
       <c r="B92">
-        <v>-1.34431968269795</v>
+        <v>-1.3635684082771899</v>
       </c>
       <c r="C92">
-        <v>-0.74018368096697795</v>
+        <v>-0.72146530514913298</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -3375,54 +3402,54 @@
         <v>49</v>
       </c>
       <c r="B93">
-        <v>0.13468739060632301</v>
+        <v>0.139786865578195</v>
       </c>
       <c r="C93">
-        <v>-4.0480231681730101E-2</v>
+        <v>-4.7852518617257499E-2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B94">
-        <v>-0.60215735556147298</v>
+        <v>-0.415220345748474</v>
       </c>
       <c r="C94">
-        <v>-0.39232274233238801</v>
+        <v>-8.4305903261313597E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>50</v>
+        <v>642</v>
       </c>
       <c r="B95">
-        <v>0.40030151384055201</v>
+        <v>-1.10755746664707</v>
       </c>
       <c r="C95">
-        <v>-7.8356427908148896E-2</v>
+        <v>0.81979381716452104</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>334</v>
+        <v>50</v>
       </c>
       <c r="B96">
-        <v>-0.169097809461693</v>
+        <v>0.419317134907288</v>
       </c>
       <c r="C96">
-        <v>0.33888194365139901</v>
+        <v>-9.5105258800695994E-2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B97">
-        <v>-0.27827285223017401</v>
+        <v>-0.32697675291896799</v>
       </c>
       <c r="C97">
-        <v>0.26080934887198798</v>
+        <v>0.21025375882164099</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -3430,10 +3457,10 @@
         <v>51</v>
       </c>
       <c r="B98">
-        <v>0.53671810696079703</v>
+        <v>0.51144444454451499</v>
       </c>
       <c r="C98">
-        <v>1.6008748181743498E-2</v>
+        <v>4.05171688601998E-2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -3441,21 +3468,21 @@
         <v>52</v>
       </c>
       <c r="B99">
-        <v>-1.17753106343259</v>
+        <v>-1.2032266987787801</v>
       </c>
       <c r="C99">
-        <v>-1.25796957496383</v>
+        <v>-1.2438737467630401</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B100">
-        <v>-1.4969748415634301</v>
+        <v>-1.5215120429278099</v>
       </c>
       <c r="C100">
-        <v>-0.72841069326254004</v>
+        <v>-0.69207012526915501</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -3463,10 +3490,10 @@
         <v>53</v>
       </c>
       <c r="B101">
-        <v>-1.3108596687838501</v>
+        <v>-1.33048539028307</v>
       </c>
       <c r="C101">
-        <v>-0.68497753847464904</v>
+        <v>-0.68103186672040095</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -3474,10 +3501,10 @@
         <v>54</v>
       </c>
       <c r="B102">
-        <v>-0.35195861495801101</v>
+        <v>-0.33355852131782499</v>
       </c>
       <c r="C102">
-        <v>0.30786326297321798</v>
+        <v>0.16721881995154</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -3485,43 +3512,43 @@
         <v>55</v>
       </c>
       <c r="B103">
-        <v>0.707161412160213</v>
+        <v>0.72636433264274802</v>
       </c>
       <c r="C103">
-        <v>-0.40328924857064002</v>
+        <v>-0.44758852167441499</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B104">
-        <v>-1.1167028626970401</v>
+        <v>-1.1492306733369499</v>
       </c>
       <c r="C104">
-        <v>-1.4931672597222201</v>
+        <v>-1.46200144251016</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B105">
-        <v>0.772426900278679</v>
+        <v>0.78398407914324597</v>
       </c>
       <c r="C105">
-        <v>-0.412440434487855</v>
+        <v>-0.47048952024153501</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B106">
-        <v>-0.21781504149734801</v>
+        <v>-0.241862921839512</v>
       </c>
       <c r="C106">
-        <v>1.2198217372244899</v>
+        <v>1.1535087211774999</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -3529,43 +3556,43 @@
         <v>56</v>
       </c>
       <c r="B107">
-        <v>-0.76880127433407297</v>
+        <v>-0.81196856112804305</v>
       </c>
       <c r="C107">
-        <v>-0.39085211389192098</v>
+        <v>-0.56659836525534502</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B108">
-        <v>-1.15591301788454</v>
+        <v>-1.17024477012565</v>
       </c>
       <c r="C108">
-        <v>-0.65650757728790998</v>
+        <v>-0.66517852333097605</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B109">
-        <v>-0.119576699007785</v>
+        <v>2.4556307124956399E-2</v>
       </c>
       <c r="C109">
-        <v>0.76336050417992096</v>
+        <v>0.75953275469164705</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B110">
-        <v>-0.29355906935738801</v>
+        <v>-0.28842278181180198</v>
       </c>
       <c r="C110">
-        <v>0.25744117874686001</v>
+        <v>0.13045814458625901</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -3573,10 +3600,10 @@
         <v>57</v>
       </c>
       <c r="B111">
-        <v>-1.2673024773386901</v>
+        <v>-1.3248779580108501</v>
       </c>
       <c r="C111">
-        <v>-0.70450803687953201</v>
+        <v>-0.74776480817633495</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -3584,10 +3611,10 @@
         <v>58</v>
       </c>
       <c r="B112">
-        <v>-0.78824045123217901</v>
+        <v>-0.77105050868838598</v>
       </c>
       <c r="C112">
-        <v>7.8158999262135195E-2</v>
+        <v>-3.2799665760710098E-2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -3595,10 +3622,10 @@
         <v>59</v>
       </c>
       <c r="B113">
-        <v>0.290135964470571</v>
+        <v>0.25847057100859</v>
       </c>
       <c r="C113">
-        <v>0.25330526641984202</v>
+        <v>0.27853653510397602</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -3606,10 +3633,10 @@
         <v>60</v>
       </c>
       <c r="B114">
-        <v>-0.99147162394829702</v>
+        <v>-0.92320847423207097</v>
       </c>
       <c r="C114">
-        <v>0.29840678109069602</v>
+        <v>0.120588638500064</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -3617,32 +3644,32 @@
         <v>61</v>
       </c>
       <c r="B115">
-        <v>-1.0155537335245</v>
+        <v>-1.00516803538207</v>
       </c>
       <c r="C115">
-        <v>-0.477056328457029</v>
+        <v>-0.490814100019213</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B116">
-        <v>-1.18254205385001</v>
+        <v>-1.20661506740142</v>
       </c>
       <c r="C116">
-        <v>0.33882653285449099</v>
+        <v>0.38698591685711597</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B117">
-        <v>-0.21781504149734801</v>
+        <v>-0.241862921839512</v>
       </c>
       <c r="C117">
-        <v>1.2198217372244899</v>
+        <v>1.1535087211774999</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -3650,10 +3677,10 @@
         <v>62</v>
       </c>
       <c r="B118">
-        <v>-0.40262323058868599</v>
+        <v>-0.37169221561257598</v>
       </c>
       <c r="C118">
-        <v>0.158243690296587</v>
+        <v>6.37991900466435E-2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -3661,10 +3688,10 @@
         <v>63</v>
       </c>
       <c r="B119">
-        <v>-1.3880437743947699E-2</v>
+        <v>1.3447237727188401E-2</v>
       </c>
       <c r="C119">
-        <v>0.46729024063952102</v>
+        <v>0.431658986767329</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -3672,21 +3699,21 @@
         <v>64</v>
       </c>
       <c r="B120">
-        <v>-1.16866235047718</v>
+        <v>-1.1927798570119399</v>
       </c>
       <c r="C120">
-        <v>-1.0127388809575399</v>
+        <v>-0.99777847390614405</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B121">
-        <v>-1.18556073912032</v>
+        <v>-1.20267219683201</v>
       </c>
       <c r="C121">
-        <v>-0.85562527072430805</v>
+        <v>-0.86258258109234298</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -3694,10 +3721,10 @@
         <v>65</v>
       </c>
       <c r="B122">
-        <v>0.63952974200124202</v>
+        <v>0.65658651209783403</v>
       </c>
       <c r="C122">
-        <v>-0.19467557970145699</v>
+        <v>-0.23630968791036699</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -3705,21 +3732,21 @@
         <v>66</v>
       </c>
       <c r="B123">
-        <v>0.65287370226632102</v>
+        <v>0.671684402136702</v>
       </c>
       <c r="C123">
-        <v>3.2765685321615501E-2</v>
+        <v>-6.0178768458360402E-3</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B124">
-        <v>0.69998324129085998</v>
+        <v>0.71772666379824501</v>
       </c>
       <c r="C124">
-        <v>1.75283708013667E-2</v>
+        <v>-2.2877657448826E-2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -3727,10 +3754,10 @@
         <v>67</v>
       </c>
       <c r="B125">
-        <v>0.112975370765522</v>
+        <v>0.10410658545384199</v>
       </c>
       <c r="C125">
-        <v>0.55218538539622597</v>
+        <v>0.55512654858300203</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -3738,10 +3765,10 @@
         <v>68</v>
       </c>
       <c r="B126">
-        <v>0.67168423896719298</v>
+        <v>0.69332733585344297</v>
       </c>
       <c r="C126">
-        <v>-0.263989547432812</v>
+        <v>-0.316376794990951</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -3749,43 +3776,43 @@
         <v>69</v>
       </c>
       <c r="B127">
-        <v>-1.1589620674332299</v>
+        <v>-1.1855017963799299</v>
       </c>
       <c r="C127">
-        <v>-1.3718105053937799</v>
+        <v>-1.3555214573345</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B128">
-        <v>-1.34890196634041</v>
+        <v>-1.37238643869498</v>
       </c>
       <c r="C128">
-        <v>-0.30642080930903098</v>
+        <v>-0.31506949936364698</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B129">
-        <v>-1.1290839225726601</v>
+        <v>-1.1611707952338</v>
       </c>
       <c r="C129">
-        <v>-1.4846215875814099</v>
+        <v>-1.4475761353072201</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B130">
-        <v>-0.16856041234187699</v>
+        <v>-0.17813349544843299</v>
       </c>
       <c r="C130">
-        <v>0.65215130990817705</v>
+        <v>0.60179429308550403</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -3793,10 +3820,10 @@
         <v>70</v>
       </c>
       <c r="B131">
-        <v>0.54918994235103902</v>
+        <v>0.538946199237614</v>
       </c>
       <c r="C131">
-        <v>-8.8965929242444799E-2</v>
+        <v>-8.5420450700207207E-2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -3804,76 +3831,76 @@
         <v>71</v>
       </c>
       <c r="B132">
-        <v>-0.123837789942442</v>
+        <v>-0.16810906092796701</v>
       </c>
       <c r="C132">
-        <v>0.104928275055197</v>
+        <v>6.6290920145107804E-2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B133">
-        <v>-0.50476834197776599</v>
+        <v>-0.389596368749837</v>
       </c>
       <c r="C133">
-        <v>6.7733934285393593E-2</v>
+        <v>0.223866333579753</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B134">
-        <v>0.40438432656166501</v>
+        <v>0.37584534494991401</v>
       </c>
       <c r="C134">
-        <v>0.69726729945434796</v>
+        <v>0.73879446284113104</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B135">
-        <v>-0.340311007981066</v>
+        <v>-0.32467947652288998</v>
       </c>
       <c r="C135">
-        <v>-7.8834262155072096E-2</v>
+        <v>-0.158985570783301</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B136">
-        <v>0.81023008354437298</v>
+        <v>0.83008884405870198</v>
       </c>
       <c r="C136">
-        <v>-0.43980979765925499</v>
+        <v>-0.48233966817334401</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B137">
-        <v>-1.43847023956195</v>
+        <v>-1.4656809837940199</v>
       </c>
       <c r="C137">
-        <v>-0.76579109347516505</v>
+        <v>-0.73621428927426302</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B138">
-        <v>-1.2940095600983199</v>
+        <v>-1.3153124123322499</v>
       </c>
       <c r="C138">
-        <v>-0.72221266830810904</v>
+        <v>-0.71791998967641801</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -3881,10 +3908,10 @@
         <v>72</v>
       </c>
       <c r="B139">
-        <v>-1.2864850266565999</v>
+        <v>-1.3069912736164</v>
       </c>
       <c r="C139">
-        <v>-0.297454383643531</v>
+        <v>-0.29872986036332599</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -3892,10 +3919,10 @@
         <v>73</v>
       </c>
       <c r="B140">
-        <v>-1.29671302257433</v>
+        <v>-1.3123643995943</v>
       </c>
       <c r="C140">
-        <v>-0.12641684748329299</v>
+        <v>-0.12499886707720199</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -3903,21 +3930,21 @@
         <v>74</v>
       </c>
       <c r="B141">
-        <v>-1.11058827151515</v>
+        <v>-1.1020491862183599</v>
       </c>
       <c r="C141">
-        <v>-1.5007380211472601</v>
+        <v>-1.3912686667679199</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B142">
-        <v>-0.80468593016755996</v>
+        <v>-0.81070757992446196</v>
       </c>
       <c r="C142">
-        <v>0.15399096463589601</v>
+        <v>0.112825100558957</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -3925,10 +3952,10 @@
         <v>75</v>
       </c>
       <c r="B143">
-        <v>0.20221624734650201</v>
+        <v>0.19490061976901699</v>
       </c>
       <c r="C143">
-        <v>0.47374621946661</v>
+        <v>0.44070211623387101</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -3936,21 +3963,21 @@
         <v>76</v>
       </c>
       <c r="B144">
-        <v>0.44966470645793</v>
+        <v>0.41852885259957201</v>
       </c>
       <c r="C144">
-        <v>-2.34656575266626E-2</v>
+        <v>-1.05310330994643E-2</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B145">
-        <v>-1.3461986332977001</v>
+        <v>-0.88195817341472105</v>
       </c>
       <c r="C145">
-        <v>5.8042296642601403E-2</v>
+        <v>0.36627345689847801</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -3958,32 +3985,32 @@
         <v>77</v>
       </c>
       <c r="B146">
-        <v>-1.2090170370934601</v>
+        <v>-1.22490935893471</v>
       </c>
       <c r="C146">
-        <v>-0.65157732369076704</v>
+        <v>-0.64769357556664797</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B147">
-        <v>-1.4950136178062601</v>
+        <v>-1.52481096076749</v>
       </c>
       <c r="C147">
-        <v>-0.76751481327764604</v>
+        <v>-0.71799337442219902</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B148">
-        <v>0.27087783446928898</v>
+        <v>0.304439647869235</v>
       </c>
       <c r="C148">
-        <v>0.82192074510385904</v>
+        <v>0.78911586640916997</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -3991,10 +4018,10 @@
         <v>78</v>
       </c>
       <c r="B149">
-        <v>-0.35506905743617201</v>
+        <v>-0.38105233162080798</v>
       </c>
       <c r="C149">
-        <v>0.55164015529458998</v>
+        <v>0.47901551663828201</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -4002,43 +4029,43 @@
         <v>79</v>
       </c>
       <c r="B150">
-        <v>0.73164468315605702</v>
+        <v>0.77540316643683505</v>
       </c>
       <c r="C150">
-        <v>-0.25517808159033301</v>
+        <v>-0.26447353402993001</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B151">
-        <v>-0.38678644260511202</v>
+        <v>-0.173325736864576</v>
       </c>
       <c r="C151">
-        <v>0.125910233728527</v>
+        <v>-0.80748217145617696</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B152">
-        <v>-0.44799415015970001</v>
+        <v>-0.48574823156758201</v>
       </c>
       <c r="C152">
-        <v>0.63169481437703101</v>
+        <v>0.62568494502663896</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B153">
-        <v>0.81526150240918704</v>
+        <v>0.83151445905639698</v>
       </c>
       <c r="C153">
-        <v>-1.81564523502772E-2</v>
+        <v>-5.4672525418671999E-2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -4046,10 +4073,10 @@
         <v>80</v>
       </c>
       <c r="B154">
-        <v>0.63516529776312602</v>
+        <v>0.30855667222142902</v>
       </c>
       <c r="C154">
-        <v>-0.60381776940171294</v>
+        <v>-0.26087793749849802</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -4057,10 +4084,10 @@
         <v>81</v>
       </c>
       <c r="B155">
-        <v>-1.1563313758592899</v>
+        <v>-1.26260033494039</v>
       </c>
       <c r="C155">
-        <v>-3.8495670842366402E-2</v>
+        <v>-0.128655635828404</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -4068,43 +4095,43 @@
         <v>82</v>
       </c>
       <c r="B156">
-        <v>-3.4337065381015602E-3</v>
+        <v>-3.2838157200440099E-3</v>
       </c>
       <c r="C156">
-        <v>1.0424220616531601E-3</v>
+        <v>2.9697966297482E-3</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B157">
-        <v>-0.580507442607192</v>
+        <v>-0.59650044847842998</v>
       </c>
       <c r="C157">
-        <v>0.59598747736684898</v>
+        <v>0.52979851339039596</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B158">
-        <v>-0.208411490658891</v>
+        <v>-0.21094046019293999</v>
       </c>
       <c r="C158">
-        <v>0.385942000657095</v>
+        <v>0.33431832533776301</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B159">
-        <v>-1.10461525832521</v>
+        <v>-1.13489524498618</v>
       </c>
       <c r="C159">
-        <v>-1.3639212671973</v>
+        <v>-1.3414140496121001</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -4112,43 +4139,43 @@
         <v>83</v>
       </c>
       <c r="B160">
-        <v>-0.73835243463338895</v>
+        <v>-0.70898145765131804</v>
       </c>
       <c r="C160">
-        <v>-1.8641112767480698E-2</v>
+        <v>-3.9033436764029601E-2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B161">
-        <v>-1.51801475782391</v>
+        <v>-1.54323009071141</v>
       </c>
       <c r="C161">
-        <v>-0.68912855835517395</v>
+        <v>-0.64974526536699295</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B162">
-        <v>0.80243528442620704</v>
+        <v>0.82642051549512197</v>
       </c>
       <c r="C162">
-        <v>0.50883205687687805</v>
+        <v>0.47035465517457598</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B163">
-        <v>-1.1866811851514301</v>
+        <v>-0.77843567335808195</v>
       </c>
       <c r="C163">
-        <v>-0.72076849893961104</v>
+        <v>-0.354663489953088</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -4156,21 +4183,21 @@
         <v>84</v>
       </c>
       <c r="B164">
-        <v>-1.3137292636081299</v>
+        <v>-1.3345663641619301</v>
       </c>
       <c r="C164">
-        <v>-0.43762507005941598</v>
+        <v>-0.44294978305800498</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B165">
-        <v>-1.1173400875866299</v>
+        <v>-1.1388724545002</v>
       </c>
       <c r="C165">
-        <v>-1.3944725283164101</v>
+        <v>-1.3854558988077501</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -4178,43 +4205,43 @@
         <v>85</v>
       </c>
       <c r="B166">
-        <v>-0.49614067202476703</v>
+        <v>-0.49435802373345999</v>
       </c>
       <c r="C166">
-        <v>9.0800395105175596E-2</v>
+        <v>5.0285132286288198E-2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B167">
-        <v>-0.1877980517002</v>
+        <v>-0.184611034320142</v>
       </c>
       <c r="C167">
-        <v>0.29232154411512201</v>
+        <v>0.25537979985132903</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B168">
-        <v>0.18201787977456699</v>
+        <v>0.15732879934628299</v>
       </c>
       <c r="C168">
-        <v>0.45977081039434903</v>
+        <v>0.44103642184148101</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B169">
-        <v>-1.20098535605715</v>
+        <v>-1.2274701745388601</v>
       </c>
       <c r="C169">
-        <v>-1.30976573843899</v>
+        <v>-1.29607052094177</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4222,10 +4249,10 @@
         <v>86</v>
       </c>
       <c r="B170">
-        <v>-0.59260018371175305</v>
+        <v>-0.60261141263598905</v>
       </c>
       <c r="C170">
-        <v>0.177891255197965</v>
+        <v>0.138052041572746</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -4233,5268 +4260,5378 @@
         <v>87</v>
       </c>
       <c r="B171">
-        <v>-1.2572904460613601</v>
+        <v>-1.2854973329069601</v>
       </c>
       <c r="C171">
-        <v>-0.287412279489693</v>
+        <v>-0.31485697944373198</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="B172">
-        <v>0.64713426202441404</v>
+        <v>-1.2821224230663999</v>
       </c>
       <c r="C172">
-        <v>-0.28045508275486097</v>
+        <v>-0.70806883247497399</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>598</v>
+        <v>368</v>
       </c>
       <c r="B173">
-        <v>-1.0788984140053799</v>
+        <v>-1.1138058441897001</v>
       </c>
       <c r="C173">
-        <v>-1.40805724208745</v>
+        <v>0.60752698287451801</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>599</v>
+        <v>369</v>
       </c>
       <c r="B174">
-        <v>-1.17697915791297</v>
+        <v>-0.75676490257291795</v>
       </c>
       <c r="C174">
-        <v>0.88960331255131397</v>
+        <v>-0.32542543224575399</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>89</v>
+        <v>370</v>
       </c>
       <c r="B175">
-        <v>-0.35272881475309997</v>
+        <v>-1.1347014976329</v>
       </c>
       <c r="C175">
-        <v>0.16705094233654899</v>
+        <v>-1.4824560209962701</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>90</v>
+        <v>371</v>
       </c>
       <c r="B176">
-        <v>-1.15856867227628</v>
+        <v>0.71134513012937595</v>
       </c>
       <c r="C176">
-        <v>-1.33277032980695</v>
+        <v>-0.43139419196567302</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>600</v>
+        <v>132</v>
       </c>
       <c r="B177">
-        <v>-0.27762933569316001</v>
+        <v>-1.1633367389184099</v>
       </c>
       <c r="C177">
-        <v>0.45669965775058202</v>
+        <v>0.164675661523672</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="B178">
-        <v>0.63793888214465699</v>
+        <v>0.69594592850758896</v>
       </c>
       <c r="C178">
-        <v>-0.156014641181699</v>
+        <v>-0.17311790549967099</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>601</v>
+        <v>372</v>
       </c>
       <c r="B179">
-        <v>0.43043897785278301</v>
+        <v>-1.1439744079033101</v>
       </c>
       <c r="C179">
-        <v>0.75769776892117802</v>
+        <v>-1.55480728039691</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>602</v>
+        <v>134</v>
       </c>
       <c r="B180">
-        <v>-0.27061248884329497</v>
+        <v>0.71517005917559195</v>
       </c>
       <c r="C180">
-        <v>0.51120087265524305</v>
+        <v>-0.19021091399551901</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>92</v>
+        <v>373</v>
       </c>
       <c r="B181">
-        <v>-1.12039786537027</v>
+        <v>-0.15614126495146999</v>
       </c>
       <c r="C181">
-        <v>-1.2558130056552901</v>
+        <v>0.165321598980846</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="B182">
-        <v>-6.1586434454348901E-2</v>
+        <v>-0.2410772253465</v>
       </c>
       <c r="C182">
-        <v>1.3132554077034999E-2</v>
+        <v>0.212243980218146</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>94</v>
+        <v>374</v>
       </c>
       <c r="B183">
-        <v>0.63748153465629398</v>
+        <v>-1.1115569750931</v>
       </c>
       <c r="C183">
-        <v>-0.31773695855474299</v>
+        <v>0.412703921454945</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>603</v>
+        <v>375</v>
       </c>
       <c r="B184">
-        <v>0.41547917956555303</v>
+        <v>-1.23070294182527</v>
       </c>
       <c r="C184">
-        <v>-0.66652041627497804</v>
+        <v>-0.81158145712504404</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="B185">
-        <v>-1.4283062776320301</v>
+        <v>-0.70778518775508503</v>
       </c>
       <c r="C185">
-        <v>-0.71351797974638598</v>
+        <v>-0.78713925142050301</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>96</v>
+        <v>377</v>
       </c>
       <c r="B186">
-        <v>-1.1599867541759401</v>
+        <v>-0.64554880082663002</v>
       </c>
       <c r="C186">
-        <v>-1.3119923416769399</v>
+        <v>0.292198657973398</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="B187">
-        <v>-0.51622078657178405</v>
+        <v>-0.65389817357506597</v>
       </c>
       <c r="C187">
-        <v>0.103266621001637</v>
+        <v>8.6006263272129693E-2</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>98</v>
+        <v>378</v>
       </c>
       <c r="B188">
-        <v>-1.1444813836405601</v>
+        <v>-0.14421437305374701</v>
       </c>
       <c r="C188">
-        <v>-1.3400302541318101</v>
+        <v>-0.159634621391639</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>604</v>
+        <v>379</v>
       </c>
       <c r="B189">
-        <v>0.16168274296428101</v>
+        <v>-1.3922404772811201</v>
       </c>
       <c r="C189">
-        <v>0.52089160658126799</v>
+        <v>-0.201499722591164</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>99</v>
+        <v>380</v>
       </c>
       <c r="B190">
-        <v>-1.0201652573187701</v>
+        <v>0.57117945264360404</v>
       </c>
       <c r="C190">
-        <v>1.7054766659207798E-2</v>
+        <v>0.19273584000006799</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="B191">
-        <v>-1.2586941048600999</v>
+        <v>-0.279042734024599</v>
       </c>
       <c r="C191">
-        <v>0.175005715689041</v>
+        <v>0.493185894129611</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>606</v>
+        <v>382</v>
       </c>
       <c r="B192">
-        <v>-0.42027754430406999</v>
+        <v>-1.10755746664707</v>
       </c>
       <c r="C192">
-        <v>-7.0004874781717505E-2</v>
+        <v>0.81979381716452104</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>607</v>
+        <v>383</v>
       </c>
       <c r="B193">
-        <v>-1.1365627305438799</v>
+        <v>-0.32608132406960599</v>
       </c>
       <c r="C193">
-        <v>-0.873285963917243</v>
+        <v>0.26219771823534999</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>100</v>
+        <v>384</v>
       </c>
       <c r="B194">
-        <v>0.62728803703004199</v>
+        <v>0.25153316012995203</v>
       </c>
       <c r="C194">
-        <v>-0.23436299950310199</v>
+        <v>0.14022778757841101</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>101</v>
+        <v>385</v>
       </c>
       <c r="B195">
-        <v>0.215902211064636</v>
+        <v>0.63032785085635701</v>
       </c>
       <c r="C195">
-        <v>0.42935050637153799</v>
+        <v>-0.35133644565341399</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="B196">
-        <v>0.67395001261016696</v>
+        <v>-0.191884510648961</v>
       </c>
       <c r="C196">
-        <v>-0.37056854543927098</v>
+        <v>0.52013605143618502</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="B197">
-        <v>-0.33769498080501298</v>
+        <v>-1.17350656383609</v>
       </c>
       <c r="C197">
-        <v>0.41910736690041001</v>
+        <v>-0.48833016148002401</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>608</v>
+        <v>388</v>
       </c>
       <c r="B198">
-        <v>-0.276921719257467</v>
+        <v>0.82201121223061402</v>
       </c>
       <c r="C198">
-        <v>0.78457927489927803</v>
+        <v>-0.15125710729859099</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="B199">
-        <v>-1.1453441740443999</v>
+        <v>-0.63321269464673902</v>
       </c>
       <c r="C199">
-        <v>-1.40817974357565</v>
+        <v>6.6427962411678407E-2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>105</v>
+        <v>389</v>
       </c>
       <c r="B200">
-        <v>-0.14293863560862499</v>
+        <v>0.36140410811352502</v>
       </c>
       <c r="C200">
-        <v>4.0590996957578902E-2</v>
+        <v>0.35963804045898801</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>106</v>
+        <v>390</v>
       </c>
       <c r="B201">
-        <v>-0.53564278709204705</v>
+        <v>-0.80864712283866202</v>
       </c>
       <c r="C201">
-        <v>8.6481101098573293E-2</v>
+        <v>-0.141754737518895</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>107</v>
+        <v>391</v>
       </c>
       <c r="B202">
-        <v>0.43277271460979999</v>
+        <v>-0.54332364269181899</v>
       </c>
       <c r="C202">
-        <v>0.27706216911618597</v>
+        <v>8.9485551869431607E-2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>609</v>
+        <v>392</v>
       </c>
       <c r="B203">
-        <v>-0.27184301199570599</v>
+        <v>0.69662392892796898</v>
       </c>
       <c r="C203">
-        <v>0.62261928553342805</v>
+        <v>-0.33721515792183698</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>610</v>
+        <v>138</v>
       </c>
       <c r="B204">
-        <v>-0.34815625006925899</v>
+        <v>-0.58231659897626098</v>
       </c>
       <c r="C204">
-        <v>0.32463020102846801</v>
+        <v>4.3411479012494897E-2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>611</v>
+        <v>139</v>
       </c>
       <c r="B205">
-        <v>-0.447603379858316</v>
+        <v>0.24316294840542901</v>
       </c>
       <c r="C205">
-        <v>0.39347256511626999</v>
+        <v>2.2230182605233501E-3</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>612</v>
+        <v>140</v>
       </c>
       <c r="B206">
-        <v>-1.60017450420244</v>
+        <v>3.5068713823416801E-2</v>
       </c>
       <c r="C206">
-        <v>-4.1288798997417301E-3</v>
+        <v>0.50871706471997102</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>613</v>
+        <v>393</v>
       </c>
       <c r="B207">
-        <v>0.67670133711914204</v>
+        <v>-1.3205338839246601</v>
       </c>
       <c r="C207">
-        <v>-0.39873317884266302</v>
+        <v>-0.88323765790888797</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>614</v>
+        <v>394</v>
       </c>
       <c r="B208">
-        <v>-1.18675894201167</v>
+        <v>0.83502424535090702</v>
       </c>
       <c r="C208">
-        <v>-1.12975491049054</v>
+        <v>-0.43428305046275301</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="B209">
-        <v>-1.0812940390005901</v>
+        <v>0.63540404736631395</v>
       </c>
       <c r="C209">
-        <v>-1.7506907253114301</v>
+        <v>-0.53477139405182195</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>108</v>
+        <v>395</v>
       </c>
       <c r="B210">
-        <v>-0.68614698150331599</v>
+        <v>-0.123709552257961</v>
       </c>
       <c r="C210">
-        <v>0.57449552399850001</v>
+        <v>0.90038058932477805</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="B211">
-        <v>-1.1615314103744301</v>
+        <v>9.3494709271733104E-2</v>
       </c>
       <c r="C211">
-        <v>-1.2172893154754001</v>
+        <v>0.139535105969507</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>616</v>
+        <v>396</v>
       </c>
       <c r="B212">
-        <v>-1.1136966615066</v>
+        <v>-1.33417703002549</v>
       </c>
       <c r="C212">
-        <v>-1.4639231567501001</v>
+        <v>0.31027553890465998</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>110</v>
+        <v>397</v>
       </c>
       <c r="B213">
-        <v>-1.1337066788283401</v>
+        <v>0.67467572459560698</v>
       </c>
       <c r="C213">
-        <v>-1.43100606017902</v>
+        <v>1.6317306003077001E-2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>111</v>
+        <v>398</v>
       </c>
       <c r="B214">
-        <v>8.9737143249263102E-2</v>
+        <v>0.53903383883945299</v>
       </c>
       <c r="C214">
-        <v>0.30867810533994</v>
+        <v>-7.1770369069487305E-2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>112</v>
+        <v>399</v>
       </c>
       <c r="B215">
-        <v>6.9427201389547694E-2</v>
+        <v>-1.35780360516111</v>
       </c>
       <c r="C215">
-        <v>0.43173879045444902</v>
+        <v>-0.74706887554690005</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>113</v>
+        <v>400</v>
       </c>
       <c r="B216">
-        <v>0.67037238510410901</v>
+        <v>-0.41282281077694999</v>
       </c>
       <c r="C216">
-        <v>-0.42030087986496401</v>
+        <v>5.6054118736589498E-2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>617</v>
+        <v>401</v>
       </c>
       <c r="B217">
-        <v>-0.66095826701929905</v>
+        <v>-1.1416370244107401</v>
       </c>
       <c r="C217">
-        <v>0.45322011622383301</v>
+        <v>-0.488226890337912</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="B218">
-        <v>-0.78467999552783296</v>
+        <v>0.24750695194668901</v>
       </c>
       <c r="C218">
-        <v>-0.466726881125825</v>
+        <v>0.27308596079870601</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>618</v>
+        <v>143</v>
       </c>
       <c r="B219">
-        <v>-0.238837178480822</v>
+        <v>-0.231699052437214</v>
       </c>
       <c r="C219">
-        <v>0.502378678523691</v>
+        <v>0.110367582240656</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>619</v>
+        <v>144</v>
       </c>
       <c r="B220">
-        <v>0.72711563690107095</v>
+        <v>-0.60723053740796695</v>
       </c>
       <c r="C220">
-        <v>-0.57481876800242704</v>
+        <v>0.37426780669411303</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="B221">
-        <v>-0.69829342725430499</v>
+        <v>-0.53331578278642</v>
       </c>
       <c r="C221">
-        <v>-0.17196446120778699</v>
+        <v>-0.30247580215807601</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>620</v>
+        <v>146</v>
       </c>
       <c r="B222">
-        <v>-0.437079790192345</v>
+        <v>-1.3613504695519001</v>
       </c>
       <c r="C222">
-        <v>0.29010130347542901</v>
+        <v>-0.451231116620948</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
       <c r="B223">
-        <v>-0.24963475302479801</v>
+        <v>6.18639515062104E-2</v>
       </c>
       <c r="C223">
-        <v>-1.5052014519102701E-2</v>
+        <v>-0.22516926517576699</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>621</v>
+        <v>147</v>
       </c>
       <c r="B224">
-        <v>-1.01923340143522</v>
+        <v>-0.41736764340961502</v>
       </c>
       <c r="C224">
-        <v>-1.55142040429275</v>
+        <v>-0.68118769443367999</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>117</v>
+        <v>403</v>
       </c>
       <c r="B225">
-        <v>-1.4124351275656599</v>
+        <v>-1.2216217715278599</v>
       </c>
       <c r="C225">
-        <v>-0.70616962568078001</v>
+        <v>-1.3387585261753601</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B226">
-        <v>-0.52181894077574298</v>
+        <v>-0.21228258426504101</v>
       </c>
       <c r="C226">
-        <v>0.185993870368897</v>
+        <v>0.212452071503891</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>622</v>
+        <v>404</v>
       </c>
       <c r="B227">
-        <v>-0.47296928684415801</v>
+        <v>-4.36927138077094E-2</v>
       </c>
       <c r="C227">
-        <v>0.52716538742020802</v>
+        <v>0.99396239326096203</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="B228">
-        <v>-1.13234650230461</v>
+        <v>-0.21054867790587101</v>
       </c>
       <c r="C228">
-        <v>-1.4005894302280399</v>
+        <v>-1.6086135631854299</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>624</v>
+        <v>149</v>
       </c>
       <c r="B229">
-        <v>0.45129762496922798</v>
+        <v>0.657487271180212</v>
       </c>
       <c r="C229">
-        <v>-0.68043566845499404</v>
+        <v>-0.33276191789680398</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="B230">
-        <v>0.19334955540177701</v>
+        <v>-0.15485742673669201</v>
       </c>
       <c r="C230">
-        <v>0.580018703093377</v>
+        <v>0.42746587125604601</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>638</v>
-      </c>
-      <c r="B231" t="s">
-        <v>639</v>
-      </c>
-      <c r="C231" t="s">
-        <v>639</v>
+        <v>150</v>
+      </c>
+      <c r="B231">
+        <v>0.60957084242070203</v>
+      </c>
+      <c r="C231">
+        <v>0.19993111272772199</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>119</v>
+        <v>405</v>
       </c>
       <c r="B232">
-        <v>-1.0682194548894499</v>
+        <v>0.77867598246647296</v>
       </c>
       <c r="C232">
-        <v>0.27855505009508102</v>
+        <v>-0.27781469507972101</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>120</v>
+        <v>406</v>
       </c>
       <c r="B233">
-        <v>0.66649116123978602</v>
+        <v>-0.25457427302824598</v>
       </c>
       <c r="C233">
-        <v>-0.21705468334744499</v>
+        <v>9.1346499530438205E-2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="B234">
-        <v>0.22594964023421599</v>
+        <v>0.65440419276461803</v>
       </c>
       <c r="C234">
-        <v>7.53602133355573E-2</v>
+        <v>-0.28061728499962901</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>122</v>
+        <v>407</v>
       </c>
       <c r="B235">
-        <v>-0.171115063112659</v>
+        <v>-1.49911202599159</v>
       </c>
       <c r="C235">
-        <v>0.27760753654640102</v>
+        <v>-0.669706372773203</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>123</v>
+        <v>408</v>
       </c>
       <c r="B236">
-        <v>-0.29136394784140301</v>
+        <v>-1.18869676104154</v>
       </c>
       <c r="C236">
-        <v>6.1798810537925297E-2</v>
+        <v>-0.73087356373974699</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B237">
-        <v>-1.1322439632639901E-2</v>
+        <v>-0.97671403812673396</v>
       </c>
       <c r="C237">
-        <v>2.14225516181147E-2</v>
+        <v>-1.3231973341098799</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="B238">
-        <v>0.71311504295129702</v>
+        <v>-1.3968525229156401</v>
       </c>
       <c r="C238">
-        <v>-0.373306379441603</v>
+        <v>-0.49444304235303899</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>626</v>
+        <v>409</v>
       </c>
       <c r="B239">
-        <v>0.57973374675405898</v>
+        <v>-0.50371020432584102</v>
       </c>
       <c r="C239">
-        <v>-0.38923731734662398</v>
+        <v>-9.3429931608359995E-2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>627</v>
+        <v>410</v>
       </c>
       <c r="B240">
-        <v>-1.7326282042389101</v>
+        <v>-0.33880238567841398</v>
       </c>
       <c r="C240">
-        <v>-0.13697415786339101</v>
+        <v>0.18083130637700701</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>126</v>
+        <v>411</v>
       </c>
       <c r="B241">
-        <v>-1.34720441454108</v>
+        <v>1.5790537923511101E-2</v>
       </c>
       <c r="C241">
-        <v>-0.67686700218220497</v>
+        <v>0.52234032769761296</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>628</v>
+        <v>412</v>
       </c>
       <c r="B242">
-        <v>-1.01923340143522</v>
+        <v>0.82112803363047704</v>
       </c>
       <c r="C242">
-        <v>-1.55142040429275</v>
+        <v>-0.56154178900233398</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>629</v>
+        <v>154</v>
       </c>
       <c r="B243">
-        <v>0.104233866041703</v>
+        <v>0.18501647823171</v>
       </c>
       <c r="C243">
-        <v>-2.9479299446637401E-2</v>
+        <v>5.02262021485066E-2</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>630</v>
+        <v>155</v>
       </c>
       <c r="B244">
-        <v>-1.30286533728041</v>
+        <v>-3.9225911197801701E-2</v>
       </c>
       <c r="C244">
-        <v>-0.88694233449024595</v>
+        <v>0.43465522574930099</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>127</v>
+        <v>413</v>
       </c>
       <c r="B245">
-        <v>-0.43385177841330003</v>
+        <v>-1.20085867285184</v>
       </c>
       <c r="C245">
-        <v>0.15671053155998399</v>
+        <v>-1.34089385989829</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>128</v>
+        <v>414</v>
       </c>
       <c r="B246">
-        <v>-0.61806837922161995</v>
+        <v>0.682361533808166</v>
       </c>
       <c r="C246">
-        <v>0.15565377813109299</v>
+        <v>-0.46678136383902302</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>129</v>
+        <v>646</v>
       </c>
       <c r="B247">
-        <v>0.13925006335836501</v>
+        <v>-0.45935124859391502</v>
       </c>
       <c r="C247">
-        <v>0.54734583243195201</v>
+        <v>0.212377760649618</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>631</v>
+        <v>415</v>
       </c>
       <c r="B248">
-        <v>-0.444093780907098</v>
+        <v>-0.18019900331931399</v>
       </c>
       <c r="C248">
-        <v>-0.10772176492319099</v>
+        <v>0.12986163610043899</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>632</v>
+        <v>416</v>
       </c>
       <c r="B249">
-        <v>-0.69773651967108097</v>
+        <v>-0.241862921839512</v>
       </c>
       <c r="C249">
-        <v>-0.36159872822511102</v>
+        <v>1.1535087211774999</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="B250">
-        <v>-0.396909733373082</v>
+        <v>-0.82016675877761203</v>
       </c>
       <c r="C250">
-        <v>0.51214638596691897</v>
+        <v>0.19405452972870599</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>634</v>
+        <v>156</v>
       </c>
       <c r="B251">
-        <v>-1.3756499630212</v>
+        <v>8.7085261855185905E-2</v>
       </c>
       <c r="C251">
-        <v>-0.792638055300527</v>
+        <v>0.37208167470214898</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>130</v>
+        <v>417</v>
       </c>
       <c r="B252">
-        <v>-0.51008512752827595</v>
+        <v>-0.94815718272085503</v>
       </c>
       <c r="C252">
-        <v>0.16645082780780299</v>
+        <v>0.67821394404990198</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>635</v>
+        <v>157</v>
       </c>
       <c r="B253">
-        <v>-1.2138670976918899</v>
+        <v>-1.39182105963787</v>
       </c>
       <c r="C253">
-        <v>-0.63225006347588597</v>
+        <v>-0.31722202859681098</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>636</v>
+        <v>158</v>
       </c>
       <c r="B254">
-        <v>-1.0936933303843099</v>
+        <v>9.6832974855728796E-2</v>
       </c>
       <c r="C254">
-        <v>0.58871222322731598</v>
+        <v>7.8065142416918398E-3</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>131</v>
+        <v>418</v>
       </c>
       <c r="B255">
-        <v>-1.26132751717225</v>
+        <v>-1.37284976547671</v>
       </c>
       <c r="C255">
-        <v>-0.66692744794616399</v>
+        <v>-0.29786611075441</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>373</v>
+        <v>159</v>
       </c>
       <c r="B256">
-        <v>-1.09322559501504</v>
+        <v>0.60943239835820995</v>
       </c>
       <c r="C256">
-        <v>0.63119795847686</v>
+        <v>-7.8544617637678601E-2</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>374</v>
+        <v>625</v>
       </c>
       <c r="B257">
-        <v>-0.74715928670783704</v>
+        <v>-8.6591453734509494E-2</v>
       </c>
       <c r="C257">
-        <v>-0.31608123105178298</v>
+        <v>-1.64595724416647</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>375</v>
+        <v>160</v>
       </c>
       <c r="B258">
-        <v>-1.1003101558924899</v>
+        <v>0.61752023262025901</v>
       </c>
       <c r="C258">
-        <v>-1.51272955272196</v>
+        <v>-0.36074374062164899</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>376</v>
+        <v>161</v>
       </c>
       <c r="B259">
-        <v>0.69082901553556297</v>
+        <v>-0.342263386934062</v>
       </c>
       <c r="C259">
-        <v>-0.39185876369442302</v>
+        <v>4.7562371695525803E-2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="B260">
-        <v>-1.14222427816781</v>
+        <v>-0.268725745815312</v>
       </c>
       <c r="C260">
-        <v>0.181645302270627</v>
+        <v>0.30596907432840598</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>133</v>
+        <v>419</v>
       </c>
       <c r="B261">
-        <v>0.665027400486781</v>
+        <v>-0.37184549509697601</v>
       </c>
       <c r="C261">
-        <v>-0.16466572639704199</v>
+        <v>0.172348091306884</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>377</v>
+        <v>163</v>
       </c>
       <c r="B262">
-        <v>-1.1113591899673501</v>
+        <v>0.61814392157118403</v>
       </c>
       <c r="C262">
-        <v>-1.5750188644825001</v>
+        <v>-0.30232409604469701</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>134</v>
+        <v>420</v>
       </c>
       <c r="B263">
-        <v>0.69875104851962799</v>
+        <v>0.74473054616155898</v>
       </c>
       <c r="C263">
-        <v>-0.15116126035347099</v>
+        <v>-0.42891388688179199</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>378</v>
+        <v>164</v>
       </c>
       <c r="B264">
-        <v>-0.16419249589012999</v>
+        <v>0.59760227377542796</v>
       </c>
       <c r="C264">
-        <v>0.220421964360135</v>
+        <v>-0.29171057229966701</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B265">
-        <v>-0.24813147024045801</v>
+        <v>5.1643309338649003E-2</v>
       </c>
       <c r="C265">
-        <v>0.27843494213637499</v>
+        <v>0.38034179491381698</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="B266">
-        <v>-1.09593149102747</v>
+        <v>-9.3545083318028202E-2</v>
       </c>
       <c r="C266">
-        <v>0.41544740337763603</v>
+        <v>0.63562706353784604</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="B267">
-        <v>-1.2110408975842399</v>
+        <v>-1.1439744079033101</v>
       </c>
       <c r="C267">
-        <v>-0.80920580794849195</v>
+        <v>-1.55480728039691</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>381</v>
+        <v>166</v>
       </c>
       <c r="B268">
-        <v>-0.691051594673048</v>
+        <v>0.67518695623014402</v>
       </c>
       <c r="C268">
-        <v>-0.78249758885546805</v>
+        <v>-0.27374098317378298</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="B269">
-        <v>-0.77240728237992495</v>
+        <v>-1.15814437045622</v>
       </c>
       <c r="C269">
-        <v>0.306563649969253</v>
+        <v>-1.38200420370414</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="B270">
-        <v>-0.71255576955174704</v>
+        <v>0.18380180862340301</v>
       </c>
       <c r="C270">
-        <v>0.23642701462708299</v>
+        <v>0.25965676725362902</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="B271">
-        <v>-0.34141151950536103</v>
+        <v>-0.46029664553917798</v>
       </c>
       <c r="C271">
-        <v>-5.9050376890591803E-2</v>
+        <v>0.432358699745506</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>384</v>
+        <v>168</v>
       </c>
       <c r="B272">
-        <v>-1.36761721388274</v>
+        <v>0.67526306373427603</v>
       </c>
       <c r="C272">
-        <v>-0.20725149783095301</v>
+        <v>-0.38665900046986901</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>385</v>
+        <v>169</v>
       </c>
       <c r="B273">
-        <v>0.54813822894613995</v>
+        <v>-0.380546882639893</v>
       </c>
       <c r="C273">
-        <v>0.25033857716276497</v>
+        <v>0.17036636870534599</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>386</v>
+        <v>170</v>
       </c>
       <c r="B274">
-        <v>-0.26515122496922899</v>
+        <v>-0.36902351294657199</v>
       </c>
       <c r="C274">
-        <v>0.53388751797306699</v>
+        <v>0.16924915870593599</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>387</v>
+        <v>171</v>
       </c>
       <c r="B275">
-        <v>-1.11131781018378</v>
+        <v>-0.116382635384592</v>
       </c>
       <c r="C275">
-        <v>0.67343045170420901</v>
+        <v>0.25678681433308398</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>388</v>
+        <v>172</v>
       </c>
       <c r="B276">
-        <v>-0.31758442322101599</v>
+        <v>-0.436361766058319</v>
       </c>
       <c r="C276">
-        <v>0.31687701591718098</v>
+        <v>0.174784261540987</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>389</v>
+        <v>173</v>
       </c>
       <c r="B277">
-        <v>0.242592860687318</v>
+        <v>-0.52858173140776898</v>
       </c>
       <c r="C277">
-        <v>0.16950880798220899</v>
+        <v>1.2458908443522499E-2</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="B278">
-        <v>0.61329841940871499</v>
+        <v>0.38424891275788198</v>
       </c>
       <c r="C278">
-        <v>-0.30631885986343099</v>
+        <v>0.37485069089062001</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="B279">
-        <v>-0.25137599580849901</v>
+        <v>-0.40826765289230299</v>
       </c>
       <c r="C279">
-        <v>0.41610314650679903</v>
+        <v>0.46686549112176601</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="B280">
-        <v>-0.94499329733430404</v>
+        <v>-1.1553909463943599</v>
       </c>
       <c r="C280">
-        <v>0.52119502362675096</v>
+        <v>-1.4462252426255799</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="B281">
-        <v>-1.1926179983409499</v>
+        <v>0.72340598800594103</v>
       </c>
       <c r="C281">
-        <v>-0.471766425207089</v>
+        <v>-0.54192732116965403</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="B282">
-        <v>0.80049322573305903</v>
+        <v>0.14049720083697401</v>
       </c>
       <c r="C282">
-        <v>-0.107940994629698</v>
+        <v>-0.29741662557360399</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="B283">
-        <v>-0.55118540198488197</v>
+        <v>-2.06392463551003E-2</v>
       </c>
       <c r="C283">
-        <v>6.7190366310122998E-2</v>
+        <v>0.46805929538422703</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>395</v>
+        <v>648</v>
       </c>
       <c r="B284">
-        <v>0.34495604077433301</v>
+        <v>0.117900509653352</v>
       </c>
       <c r="C284">
-        <v>0.39593522608174703</v>
+        <v>0.59791088924935598</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="B285">
-        <v>-0.70666259879930504</v>
+        <v>-1.16305031762311</v>
       </c>
       <c r="C285">
-        <v>-8.4872730292089596E-2</v>
+        <v>-1.4352316058928001</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="B286">
-        <v>-0.54394907532979597</v>
+        <v>0.605540994155915</v>
       </c>
       <c r="C286">
-        <v>0.14966440194514799</v>
+        <v>-0.51233800537688001</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="B287">
-        <v>0.69735073429583305</v>
+        <v>0.73812551193641496</v>
       </c>
       <c r="C287">
-        <v>-0.235786714827322</v>
+        <v>-0.45206454839007099</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="B288">
-        <v>-0.69755197407524605</v>
+        <v>0.63789866580002497</v>
       </c>
       <c r="C288">
-        <v>0.101906187177582</v>
+        <v>-8.8434460574456406E-2</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>139</v>
+        <v>433</v>
       </c>
       <c r="B289">
-        <v>0.25863427305293601</v>
+        <v>-0.76061602233144598</v>
       </c>
       <c r="C289">
-        <v>-5.3340029035353898E-3</v>
+        <v>0.21522763387725199</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>140</v>
+        <v>434</v>
       </c>
       <c r="B290">
-        <v>-3.5247828186437999E-2</v>
+        <v>-1.27231913418747</v>
       </c>
       <c r="C290">
-        <v>0.51936835221070898</v>
+        <v>-0.28788875760584398</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>399</v>
+        <v>176</v>
       </c>
       <c r="B291">
-        <v>-1.2954237779406901</v>
+        <v>-1.2731476854950201</v>
       </c>
       <c r="C291">
-        <v>-0.89255287315807097</v>
+        <v>-9.0205025360668906E-2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="B292">
-        <v>0.80983726554963098</v>
+        <v>-0.289833896320078</v>
       </c>
       <c r="C292">
-        <v>-0.38860130918734698</v>
+        <v>0.123485926425112</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>401</v>
+        <v>436</v>
       </c>
       <c r="B293">
-        <v>-0.102416783525018</v>
+        <v>0.44958759648692298</v>
       </c>
       <c r="C293">
-        <v>0.95045534253201303</v>
+        <v>0.24209168610651199</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>141</v>
+        <v>649</v>
       </c>
       <c r="B294">
-        <v>0.12237629241044699</v>
+        <v>-8.6591453734509494E-2</v>
       </c>
       <c r="C294">
-        <v>0.15658462629689099</v>
+        <v>-1.64595724416647</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>402</v>
+        <v>177</v>
       </c>
       <c r="B295">
-        <v>-1.3093330574117701</v>
+        <v>0.70625902356040005</v>
       </c>
       <c r="C295">
-        <v>0.32016698333900401</v>
+        <v>-0.37427301173581701</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="B296">
-        <v>0.66240660901246495</v>
+        <v>0.70294988841202</v>
       </c>
       <c r="C296">
-        <v>5.1722952034014801E-2</v>
+        <v>-0.44244290039819101</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>404</v>
+        <v>178</v>
       </c>
       <c r="B297">
-        <v>0.52846441050420601</v>
+        <v>0.27555776164180601</v>
       </c>
       <c r="C297">
-        <v>-3.2248997473636902E-2</v>
+        <v>-8.16972811895295E-2</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="B298">
-        <v>-1.33477782215861</v>
+        <v>0.53028785974328996</v>
       </c>
       <c r="C298">
-        <v>-0.74584985708361895</v>
+        <v>0.36473635966970203</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="B299">
-        <v>-0.39287147291356</v>
+        <v>-0.52766158798492002</v>
       </c>
       <c r="C299">
-        <v>3.2239696093737301E-2</v>
+        <v>0.38327763393997499</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>407</v>
+        <v>179</v>
       </c>
       <c r="B300">
-        <v>-1.12769256636691</v>
+        <v>0.134219581411857</v>
       </c>
       <c r="C300">
-        <v>-0.48797165360016098</v>
+        <v>-6.0636298477745001E-2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="B301">
-        <v>0.28704353879904698</v>
+        <v>0.44957758142354198</v>
       </c>
       <c r="C301">
-        <v>0.238747246574528</v>
+        <v>-9.40911126072842E-2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>143</v>
+        <v>440</v>
       </c>
       <c r="B302">
-        <v>-0.237773199384536</v>
+        <v>0.59897739915673398</v>
       </c>
       <c r="C302">
-        <v>0.13520713561376699</v>
+        <v>-0.43635566060200698</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="B303">
-        <v>-0.55632651095042795</v>
+        <v>-0.46509870123818398</v>
       </c>
       <c r="C303">
-        <v>0.25001599971372401</v>
+        <v>0.129962746214942</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>145</v>
+        <v>650</v>
       </c>
       <c r="B304">
-        <v>-0.55041499684151995</v>
+        <v>-0.41071845890304998</v>
       </c>
       <c r="C304">
-        <v>-0.25482945193458401</v>
+        <v>-0.169536806371791</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>146</v>
+        <v>441</v>
       </c>
       <c r="B305">
-        <v>-1.3212746187200499</v>
+        <v>-0.35817696496998402</v>
       </c>
       <c r="C305">
-        <v>-0.43349922084085701</v>
+        <v>0.179835263864732</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="B306">
-        <v>4.9725257865749502E-2</v>
+        <v>4.3792287061607399E-2</v>
       </c>
       <c r="C306">
-        <v>-0.166261767804433</v>
+        <v>-0.52439598690874101</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>147</v>
+        <v>443</v>
       </c>
       <c r="B307">
-        <v>-0.41085858525104701</v>
+        <v>0.56666573024012501</v>
       </c>
       <c r="C307">
-        <v>-0.67007069978632605</v>
+        <v>-0.22667433498395401</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>409</v>
+        <v>182</v>
       </c>
       <c r="B308">
-        <v>-1.19511434841357</v>
+        <v>0.33440914459974302</v>
       </c>
       <c r="C308">
-        <v>-1.35249710721897</v>
+        <v>-0.461802409545849</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="B309">
-        <v>-0.27708502800861901</v>
+        <v>-0.681458966180574</v>
       </c>
       <c r="C309">
-        <v>0.50852237291676405</v>
+        <v>0.17800554312505701</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="B310">
-        <v>-3.5910573053109698E-2</v>
+        <v>-0.347483294157446</v>
       </c>
       <c r="C310">
-        <v>1.0453914146348899</v>
+        <v>0.121283907464713</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>149</v>
+        <v>445</v>
       </c>
       <c r="B311">
-        <v>0.63371402317690995</v>
+        <v>-1.1553909463943599</v>
       </c>
       <c r="C311">
-        <v>-0.29247831745951303</v>
+        <v>-1.4462252426255799</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>150</v>
+        <v>446</v>
       </c>
       <c r="B312">
-        <v>0.59426848237748997</v>
+        <v>-1.1439744079033101</v>
       </c>
       <c r="C312">
-        <v>0.23457118659669901</v>
+        <v>-1.55480728039691</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>411</v>
+        <v>184</v>
       </c>
       <c r="B313">
-        <v>0.74496089289139</v>
+        <v>0.295117958909762</v>
       </c>
       <c r="C313">
-        <v>-0.202618553458565</v>
+        <v>0.13981409849812701</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>412</v>
+        <v>185</v>
       </c>
       <c r="B314">
-        <v>-0.26192603454880098</v>
+        <v>1.5783679422175401E-2</v>
       </c>
       <c r="C314">
-        <v>0.15266203339623199</v>
+        <v>0.42519268259341703</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>151</v>
+        <v>447</v>
       </c>
       <c r="B315">
-        <v>0.62261306788252901</v>
+        <v>-0.11463218051766</v>
       </c>
       <c r="C315">
-        <v>-0.26789169795638201</v>
+        <v>0.73837752609110197</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>413</v>
+        <v>186</v>
       </c>
       <c r="B316">
-        <v>-1.47266157710193</v>
+        <v>-0.42377738852858199</v>
       </c>
       <c r="C316">
-        <v>-0.69827301642830797</v>
+        <v>-0.44895615273598299</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>414</v>
+        <v>187</v>
       </c>
       <c r="B317">
-        <v>-0.94499329733430404</v>
+        <v>0.72964878437557601</v>
       </c>
       <c r="C317">
-        <v>0.52119502362675096</v>
+        <v>-0.29603372533998501</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="B318">
-        <v>-1.1698249519269499</v>
+        <v>0.46840713180850102</v>
       </c>
       <c r="C318">
-        <v>-0.72714865100066395</v>
+        <v>-0.24948884306772001</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="B319">
-        <v>-0.92649899080732101</v>
+        <v>-0.75658257497688297</v>
       </c>
       <c r="C319">
-        <v>-1.31992636690617</v>
+        <v>0.148421933737932</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B320">
-        <v>-1.3607755398077199</v>
+        <v>-0.26329247514932602</v>
       </c>
       <c r="C320">
-        <v>-0.450824262991392</v>
+        <v>0.33966792287541803</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>416</v>
+        <v>190</v>
       </c>
       <c r="B321">
-        <v>-0.49350951785303399</v>
+        <v>0.638899905232719</v>
       </c>
       <c r="C321">
-        <v>-6.6324189369035003E-2</v>
+        <v>-0.294115617295368</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>417</v>
+        <v>191</v>
       </c>
       <c r="B322">
-        <v>-0.33648324889428799</v>
+        <v>0.59844291858880305</v>
       </c>
       <c r="C322">
-        <v>0.23163363190885899</v>
+        <v>-0.26127815738125398</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="B323">
-        <v>4.0114145906793797E-2</v>
+        <v>0.56243334559402902</v>
       </c>
       <c r="C323">
-        <v>0.53497081818941405</v>
+        <v>-0.48385319774695801</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="B324">
-        <v>0.80612755673831404</v>
+        <v>0.77653409971021703</v>
       </c>
       <c r="C324">
-        <v>-0.51491253721163699</v>
+        <v>-0.18207100597418099</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>154</v>
+        <v>651</v>
       </c>
       <c r="B325">
-        <v>0.15823307007377699</v>
+        <v>-0.41071845890304998</v>
       </c>
       <c r="C325">
-        <v>6.1767632531797102E-2</v>
+        <v>-0.169536806371791</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>155</v>
+        <v>451</v>
       </c>
       <c r="B326">
-        <v>-3.0175555603365701E-2</v>
+        <v>-1.2030904096525199</v>
       </c>
       <c r="C326">
-        <v>0.45648357178009302</v>
+        <v>0.35029020522929699</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="B327">
-        <v>-1.0906579914177801</v>
+        <v>-0.33646017891223001</v>
       </c>
       <c r="C327">
-        <v>-0.70080483800353899</v>
+        <v>0.10626589438300001</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="B328">
-        <v>0.66647397584927903</v>
+        <v>-0.54737541314726101</v>
       </c>
       <c r="C328">
-        <v>-0.42061709544770698</v>
+        <v>0.78194476236404398</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="B329">
-        <v>-0.44970798380363203</v>
+        <v>0.68366255148843602</v>
       </c>
       <c r="C329">
-        <v>0.28451120355756798</v>
+        <v>-0.46303214441514301</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="B330">
-        <v>0.57078158716124805</v>
+        <v>-1.1473338302812901</v>
       </c>
       <c r="C330">
-        <v>-0.38442876725979902</v>
+        <v>-1.43180178719525</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>424</v>
+        <v>192</v>
       </c>
       <c r="B331">
-        <v>-0.21781504149734801</v>
+        <v>-0.15983729953242801</v>
       </c>
       <c r="C331">
-        <v>1.2198217372244899</v>
+        <v>0.23307168401005901</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>156</v>
+        <v>456</v>
       </c>
       <c r="B332">
-        <v>0.12655047141030401</v>
+        <v>0.73611976241805099</v>
       </c>
       <c r="C332">
-        <v>0.368081087930407</v>
+        <v>-1.6869240472807599E-2</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>425</v>
+        <v>193</v>
       </c>
       <c r="B333">
-        <v>-1.0548603513844199</v>
+        <v>0.643381896471661</v>
       </c>
       <c r="C333">
-        <v>0.56714804629632398</v>
+        <v>-0.30201715449796901</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>157</v>
+        <v>457</v>
       </c>
       <c r="B334">
-        <v>-1.36577715697627</v>
+        <v>-1.27234780823046</v>
       </c>
       <c r="C334">
-        <v>-0.315294072802768</v>
+        <v>-1.0388496693873801</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>158</v>
+        <v>458</v>
       </c>
       <c r="B335">
-        <v>0.10952126646787901</v>
+        <v>-1.21504357268739</v>
       </c>
       <c r="C335">
-        <v>1.0238278588921E-2</v>
+        <v>-0.75325120840454896</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>426</v>
+        <v>194</v>
       </c>
       <c r="B336">
-        <v>-1.3530658060646901</v>
+        <v>-1.304999060771</v>
       </c>
       <c r="C336">
-        <v>-0.30949472193361999</v>
+        <v>-0.75613828611629996</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>159</v>
+        <v>459</v>
       </c>
       <c r="B337">
-        <v>0.60396387753796099</v>
+        <v>-0.43287702489934499</v>
       </c>
       <c r="C337">
-        <v>-5.0976439534655901E-2</v>
+        <v>0.14515053291590499</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>640</v>
-      </c>
-      <c r="B338" t="s">
-        <v>639</v>
-      </c>
-      <c r="C338" t="s">
-        <v>639</v>
+        <v>460</v>
+      </c>
+      <c r="B338">
+        <v>-0.44028889229127899</v>
+      </c>
+      <c r="C338">
+        <v>-0.56754185099937804</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="B339">
-        <v>0.58563352021723103</v>
+        <v>0.22166035879148399</v>
       </c>
       <c r="C339">
-        <v>-0.28807823699478502</v>
+        <v>-0.34894908489509502</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="B340">
-        <v>-0.338653920070563</v>
+        <v>-0.30007429357274001</v>
       </c>
       <c r="C340">
-        <v>9.3150921067371606E-2</v>
+        <v>0.242135998298634</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="B341">
-        <v>-0.28810960363989802</v>
+        <v>0.73506376580118005</v>
       </c>
       <c r="C341">
-        <v>0.29542239458463498</v>
+        <v>-0.430023322950702</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>427</v>
+        <v>198</v>
       </c>
       <c r="B342">
-        <v>-0.38354907854755599</v>
+        <v>-0.34698311863333298</v>
       </c>
       <c r="C342">
-        <v>0.329866452068522</v>
+        <v>0.106864293408824</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="B343">
-        <v>0.58972603710693094</v>
+        <v>0.67883158969482704</v>
       </c>
       <c r="C343">
-        <v>-0.27572299007113699</v>
+        <v>-0.337755994336356</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="B344">
-        <v>0.72762253983583203</v>
+        <v>-1.1001843682558401</v>
       </c>
       <c r="C344">
-        <v>-0.37996789902431999</v>
+        <v>-1.4215123311025899</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="B345">
-        <v>0.58374396571093601</v>
+        <v>0.70917309276154805</v>
       </c>
       <c r="C345">
-        <v>-0.241830230998336</v>
+        <v>-1.89048939186168E-2</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>165</v>
+        <v>462</v>
       </c>
       <c r="B346">
-        <v>4.4270466522033897E-2</v>
+        <v>0.56157571463926004</v>
       </c>
       <c r="C346">
-        <v>0.417970671896704</v>
+        <v>0.142489611838994</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>429</v>
+        <v>201</v>
       </c>
       <c r="B347">
-        <v>-9.1366398204256197E-2</v>
+        <v>-0.34639514689863599</v>
       </c>
       <c r="C347">
-        <v>0.66253049943833697</v>
+        <v>0.16062322334093701</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="B348">
-        <v>-1.1113591899673501</v>
+        <v>-0.13186812384077201</v>
       </c>
       <c r="C348">
-        <v>-1.5750188644825001</v>
+        <v>0.412875735834007</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>166</v>
+        <v>464</v>
       </c>
       <c r="B349">
-        <v>0.621264274110649</v>
+        <v>-1.33417703002549</v>
       </c>
       <c r="C349">
-        <v>-0.214508562245006</v>
+        <v>0.31027553890465998</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>431</v>
+        <v>652</v>
       </c>
       <c r="B350">
-        <v>-1.13234650230461</v>
+        <v>-8.6591453734509494E-2</v>
       </c>
       <c r="C350">
-        <v>-1.4005894302280399</v>
+        <v>-1.64595724416647</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>167</v>
+        <v>465</v>
       </c>
       <c r="B351">
-        <v>0.25274015092687302</v>
+        <v>-0.41526826059147398</v>
       </c>
       <c r="C351">
-        <v>0.214963496465329</v>
+        <v>0.38541133644221598</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="B352">
-        <v>-0.72226125891453896</v>
+        <v>-0.55912328073930795</v>
       </c>
       <c r="C352">
-        <v>0.520148841062542</v>
+        <v>0.235884721360893</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B353">
-        <v>0.651527238227949</v>
+        <v>0.66469564285888105</v>
       </c>
       <c r="C353">
-        <v>-0.347588542287177</v>
+        <v>-0.328870645478337</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>169</v>
+        <v>467</v>
       </c>
       <c r="B354">
-        <v>-0.408058413216216</v>
+        <v>0.67621334971668701</v>
       </c>
       <c r="C354">
-        <v>0.209114822211352</v>
+        <v>-0.63339778334475805</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="B355">
-        <v>-0.36414042019172999</v>
+        <v>-0.15073554889802401</v>
       </c>
       <c r="C355">
-        <v>0.196305691271666</v>
+        <v>0.337504562353516</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>171</v>
+        <v>468</v>
       </c>
       <c r="B356">
-        <v>-0.115541981383456</v>
+        <v>-0.42892443351570397</v>
       </c>
       <c r="C356">
-        <v>0.28261763917580801</v>
+        <v>0.88119650199487298</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="B357">
-        <v>-0.48835642124683698</v>
+        <v>-0.203138670159169</v>
       </c>
       <c r="C357">
-        <v>0.18528961514756301</v>
+        <v>0.22646437370156</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>173</v>
+        <v>469</v>
       </c>
       <c r="B358">
-        <v>-0.63241121146672197</v>
+        <v>0.71442250869560098</v>
       </c>
       <c r="C358">
-        <v>0.15633393809655899</v>
+        <v>0.36963808544350102</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>433</v>
+        <v>206</v>
       </c>
       <c r="B359">
-        <v>-0.83512624328418394</v>
+        <v>-0.41791407051123303</v>
       </c>
       <c r="C359">
-        <v>0.475242000957177</v>
+        <v>0.15928104986817701</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>434</v>
+        <v>205</v>
       </c>
       <c r="B360">
-        <v>0.73300967053520005</v>
+        <v>-1.07758687439291</v>
       </c>
       <c r="C360">
-        <v>-0.38084380762272502</v>
+        <v>-0.72640919264667203</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>435</v>
+        <v>207</v>
       </c>
       <c r="B361">
-        <v>-0.71501616465599804</v>
+        <v>-0.27901915920956399</v>
       </c>
       <c r="C361">
-        <v>0.37755946776467902</v>
+        <v>0.19156916973551499</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="B362">
-        <v>-1.1236329943588099</v>
+        <v>3.2516959379490298E-2</v>
       </c>
       <c r="C362">
-        <v>-1.4847264839784899</v>
+        <v>0.61961690615803999</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="B363">
-        <v>0.70891264658027497</v>
+        <v>-0.37268331037734997</v>
       </c>
       <c r="C363">
-        <v>-0.49472817801799301</v>
+        <v>0.13975520343668901</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="B364">
-        <v>0.123397317029225</v>
+        <v>-2.65797514727951E-2</v>
       </c>
       <c r="C364">
-        <v>-0.24062144314325201</v>
+        <v>0.51499074580464899</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>174</v>
+        <v>473</v>
       </c>
       <c r="B365">
-        <v>-9.8706883180252405E-3</v>
+        <v>0.85172899653860001</v>
       </c>
       <c r="C365">
-        <v>0.399590344269591</v>
+        <v>-0.46934656397511298</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>439</v>
+        <v>208</v>
       </c>
       <c r="B366">
-        <v>-1.13086057332156</v>
+        <v>-1.13821059824485</v>
       </c>
       <c r="C366">
-        <v>-1.47448914884621</v>
+        <v>-1.22613589798544</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>440</v>
+        <v>209</v>
       </c>
       <c r="B367">
-        <v>0.58980735063789902</v>
+        <v>-0.48283778266441102</v>
       </c>
       <c r="C367">
-        <v>-0.47035669579581602</v>
+        <v>4.51564105033272E-2</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="B368">
-        <v>0.718913545423703</v>
+        <v>-4.5989507050032102E-2</v>
       </c>
       <c r="C368">
-        <v>-0.40722106377735201</v>
+        <v>3.3317888005661198E-2</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="B369">
-        <v>0.58347214371265299</v>
+        <v>-1.0630699069962599</v>
       </c>
       <c r="C369">
-        <v>3.9219633366448001E-2</v>
+        <v>0.373166516114804</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>442</v>
+        <v>211</v>
       </c>
       <c r="B370">
-        <v>-0.72085811180080195</v>
+        <v>-0.66098196592931302</v>
       </c>
       <c r="C370">
-        <v>0.22937302954409</v>
+        <v>9.8592149658742106E-2</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>443</v>
+        <v>212</v>
       </c>
       <c r="B371">
-        <v>-1.2549959582922501</v>
+        <v>0.74562933917973095</v>
       </c>
       <c r="C371">
-        <v>-0.28590862454041599</v>
+        <v>-0.40582973463334798</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>176</v>
+        <v>475</v>
       </c>
       <c r="B372">
-        <v>-1.22758401363536</v>
+        <v>0.570393214806583</v>
       </c>
       <c r="C372">
-        <v>-5.7535744472409597E-2</v>
+        <v>-0.30899467119217799</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="B373">
-        <v>-0.28987995780743803</v>
+        <v>0.70599673021817</v>
       </c>
       <c r="C373">
-        <v>0.17446216804739201</v>
+        <v>-0.332837279249033</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>445</v>
+        <v>213</v>
       </c>
       <c r="B374">
-        <v>0.44450634422802199</v>
+        <v>0.60085653453481602</v>
       </c>
       <c r="C374">
-        <v>0.26601623456655299</v>
+        <v>0.135999457130283</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>177</v>
+        <v>477</v>
       </c>
       <c r="B375">
-        <v>0.67411421434970598</v>
+        <v>0.65212909675661201</v>
       </c>
       <c r="C375">
-        <v>-0.34346902824491099</v>
+        <v>-0.43602462478780601</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="B376">
-        <v>0.68589327860539595</v>
+        <v>-0.12950176833322699</v>
       </c>
       <c r="C376">
-        <v>-0.40080561084973898</v>
+        <v>-0.40289890185812499</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="B377">
-        <v>0.26142291859953798</v>
+        <v>-1.3530591493158</v>
       </c>
       <c r="C377">
-        <v>-7.7962844334204098E-2</v>
+        <v>-0.33237061531297701</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>447</v>
+        <v>626</v>
       </c>
       <c r="B378">
-        <v>0.48244005006389401</v>
+        <v>-0.21054867790587101</v>
       </c>
       <c r="C378">
-        <v>0.41556374824841402</v>
+        <v>-1.6086135631854299</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="B379">
-        <v>-0.51183163420450895</v>
+        <v>-1.0482606741878</v>
       </c>
       <c r="C379">
-        <v>0.455242056747516</v>
+        <v>-1.5235775960073099</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>179</v>
+        <v>480</v>
       </c>
       <c r="B380">
-        <v>0.123055863695176</v>
+        <v>-1.23135621472707</v>
       </c>
       <c r="C380">
-        <v>-2.3204076174457602E-2</v>
+        <v>-1.02646908123078</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>180</v>
+        <v>481</v>
       </c>
       <c r="B381">
-        <v>0.44746318244479699</v>
+        <v>-1.17836906008061</v>
       </c>
       <c r="C381">
-        <v>-7.7011288214437104E-2</v>
+        <v>-1.4132443324272399</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="B382">
-        <v>0.57973374675405898</v>
+        <v>-1.5558742656072999</v>
       </c>
       <c r="C382">
-        <v>-0.38923731734662398</v>
+        <v>-0.79710738587186303</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>181</v>
+        <v>483</v>
       </c>
       <c r="B383">
-        <v>-0.46992627601832099</v>
+        <v>0.68058209316621598</v>
       </c>
       <c r="C383">
-        <v>0.204111305887023</v>
+        <v>-0.40581673787487998</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="B384">
-        <v>-0.34443189708294297</v>
+        <v>0.69891660777482201</v>
       </c>
       <c r="C384">
-        <v>0.18035857161386401</v>
+        <v>6.4723726688819594E-2</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="B385">
-        <v>3.81183909243911E-2</v>
+        <v>-1.3016407907118099</v>
       </c>
       <c r="C385">
-        <v>-0.48521414246509098</v>
+        <v>-0.89455742772715796</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="B386">
-        <v>0.54238834233144995</v>
+        <v>7.6094381599708799E-2</v>
       </c>
       <c r="C386">
-        <v>-0.18376537107125401</v>
+        <v>0.740494218313002</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="B387">
-        <v>0.323421056608654</v>
+        <v>-1.43754985186335</v>
       </c>
       <c r="C387">
-        <v>-0.43293867689858401</v>
+        <v>-0.560056653528473</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>183</v>
+        <v>487</v>
       </c>
       <c r="B388">
-        <v>-0.78404686234412402</v>
+        <v>-0.32009674479246503</v>
       </c>
       <c r="C388">
-        <v>0.242474692437677</v>
+        <v>0.51391193649359801</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>453</v>
+        <v>488</v>
       </c>
       <c r="B389">
-        <v>-0.35450521873242002</v>
+        <v>-0.93313455775225196</v>
       </c>
       <c r="C389">
-        <v>0.17327860914361301</v>
+        <v>0.40675869696867401</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>454</v>
+        <v>216</v>
       </c>
       <c r="B390">
-        <v>-1.1236329943588099</v>
+        <v>-2.94375275210478E-2</v>
       </c>
       <c r="C390">
-        <v>-1.4847264839784899</v>
+        <v>-8.5835514976845394E-3</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="B391">
-        <v>-1.1113591899673501</v>
+        <v>8.2616402872568495E-2</v>
       </c>
       <c r="C391">
-        <v>-1.5750188644825001</v>
+        <v>0.79809678613747903</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>184</v>
+        <v>490</v>
       </c>
       <c r="B392">
-        <v>0.31097113357410899</v>
+        <v>-1.06031557427927</v>
       </c>
       <c r="C392">
-        <v>0.1461201255706</v>
+        <v>-0.39800422326163998</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="B393">
-        <v>2.9138404691086799E-2</v>
+        <v>-1.02572891600534</v>
       </c>
       <c r="C393">
-        <v>0.42988885549275702</v>
+        <v>-0.88480597863150101</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>456</v>
+        <v>218</v>
       </c>
       <c r="B394">
-        <v>-0.103007874464215</v>
+        <v>-1.4075362540643801</v>
       </c>
       <c r="C394">
-        <v>0.77648773254021497</v>
+        <v>-0.53839028424531099</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>186</v>
+        <v>491</v>
       </c>
       <c r="B395">
-        <v>-0.43134756746180802</v>
+        <v>-0.35023249300205</v>
       </c>
       <c r="C395">
-        <v>-0.39008192421840499</v>
+        <v>0.83779607875268902</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>187</v>
+        <v>492</v>
       </c>
       <c r="B396">
-        <v>0.71227269938174897</v>
+        <v>0.126412266387773</v>
       </c>
       <c r="C396">
-        <v>-0.23580127527789599</v>
+        <v>0.35626893798390602</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>457</v>
+        <v>219</v>
       </c>
       <c r="B397">
-        <v>0.44862483415659099</v>
+        <v>0.73467326634498598</v>
       </c>
       <c r="C397">
-        <v>-0.21210604992448201</v>
+        <v>-0.444533218875103</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>188</v>
+        <v>493</v>
       </c>
       <c r="B398">
-        <v>-0.77367817791099003</v>
+        <v>-0.92793724170007297</v>
       </c>
       <c r="C398">
-        <v>0.23305309648685599</v>
+        <v>-0.30812310600570297</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="B399">
-        <v>-0.33216462721542001</v>
+        <v>-0.30240857883410299</v>
       </c>
       <c r="C399">
-        <v>0.319162228169516</v>
+        <v>0.34902501148320703</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="B400">
-        <v>0.61257478676691202</v>
+        <v>-1.2467113277652599</v>
       </c>
       <c r="C400">
-        <v>-0.26320824261280701</v>
+        <v>-0.36595797635963701</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>458</v>
+        <v>222</v>
       </c>
       <c r="B401">
-        <v>0.54576305490535604</v>
+        <v>-1.42180643190759</v>
       </c>
       <c r="C401">
-        <v>-0.44368095022950799</v>
+        <v>-0.31141723588683101</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>191</v>
+        <v>494</v>
       </c>
       <c r="B402">
-        <v>0.58499567252761597</v>
+        <v>-1.16801897631134</v>
       </c>
       <c r="C402">
-        <v>-0.21872583501092799</v>
+        <v>0.103538822477609</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>459</v>
+        <v>223</v>
       </c>
       <c r="B403">
-        <v>0.76327633205574197</v>
+        <v>0.558981940343101</v>
       </c>
       <c r="C403">
-        <v>-0.156783594404411</v>
+        <v>0.17891595626182599</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>460</v>
+        <v>224</v>
       </c>
       <c r="B404">
-        <v>-1.1437067104012999</v>
+        <v>-0.39630066472772002</v>
       </c>
       <c r="C404">
-        <v>0.32933035986384201</v>
+        <v>0.31394234022210799</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>461</v>
+        <v>225</v>
       </c>
       <c r="B405">
-        <v>-0.38951513369391599</v>
+        <v>0.59256262236087398</v>
       </c>
       <c r="C405">
-        <v>0.41063757660096101</v>
+        <v>-0.248365973019194</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>462</v>
+        <v>226</v>
       </c>
       <c r="B406">
-        <v>-0.49339969684488399</v>
+        <v>-0.241076903966744</v>
       </c>
       <c r="C406">
-        <v>0.69722675808674495</v>
+        <v>6.4457372391519899E-2</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>463</v>
+        <v>227</v>
       </c>
       <c r="B407">
-        <v>0.66809715652746504</v>
+        <v>-0.527484958014377</v>
       </c>
       <c r="C407">
-        <v>-0.41795635080598897</v>
+        <v>0.11417586410443099</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="B408">
-        <v>-1.11586219581188</v>
+        <v>-1.24143505672814</v>
       </c>
       <c r="C408">
-        <v>-1.46837931061507</v>
+        <v>-1.3034157348086499</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>192</v>
+        <v>496</v>
       </c>
       <c r="B409">
-        <v>-0.15853419595587601</v>
+        <v>-0.134525359288348</v>
       </c>
       <c r="C409">
-        <v>0.38261362329224602</v>
+        <v>0.71502486901505002</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>465</v>
+        <v>228</v>
       </c>
       <c r="B410">
-        <v>0.71824192727974501</v>
+        <v>-1.5079657210419899</v>
       </c>
       <c r="C410">
-        <v>1.01352879683804E-2</v>
+        <v>-0.591923611562989</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>193</v>
+        <v>497</v>
       </c>
       <c r="B411">
-        <v>0.62332473839473002</v>
+        <v>0.55474086337710704</v>
       </c>
       <c r="C411">
-        <v>-0.26196008163245699</v>
+        <v>0.89631658509239798</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>466</v>
+        <v>229</v>
       </c>
       <c r="B412">
-        <v>-1.26984156299854</v>
+        <v>-0.24400016043148401</v>
       </c>
       <c r="C412">
-        <v>-0.98554819958297102</v>
+        <v>0.282888165442995</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>467</v>
+        <v>230</v>
       </c>
       <c r="B413">
-        <v>-1.19527235050335</v>
+        <v>8.7532184685108205E-2</v>
       </c>
       <c r="C413">
-        <v>-0.74940942333309002</v>
+        <v>0.51047361794087098</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>194</v>
+        <v>498</v>
       </c>
       <c r="B414">
-        <v>-1.2924144757101399</v>
+        <v>0.54926121470238198</v>
       </c>
       <c r="C414">
-        <v>-0.77716145551368099</v>
+        <v>-0.32050541666249399</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>468</v>
+        <v>231</v>
       </c>
       <c r="B415">
-        <v>-0.43201712165862299</v>
+        <v>-0.32927784048293901</v>
       </c>
       <c r="C415">
-        <v>0.22438576937926499</v>
+        <v>-0.14191677302314001</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="B416">
-        <v>-0.43711127510908498</v>
+        <v>-1.1138058441897001</v>
       </c>
       <c r="C416">
-        <v>-0.56313916933802199</v>
+        <v>0.60752698287451801</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>195</v>
+        <v>500</v>
       </c>
       <c r="B417">
-        <v>0.20971152634109599</v>
+        <v>-1.07793626414261E-2</v>
       </c>
       <c r="C417">
-        <v>-0.321376752711445</v>
+        <v>0.53421547971526895</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="B418">
-        <v>-0.30451149343175499</v>
+        <v>0.62833434340576799</v>
       </c>
       <c r="C418">
-        <v>0.289397780970437</v>
+        <v>0.223738741219595</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>197</v>
+        <v>501</v>
       </c>
       <c r="B419">
-        <v>0.71386103820887803</v>
+        <v>0.67094814833518801</v>
       </c>
       <c r="C419">
-        <v>-0.38649148513325898</v>
+        <v>0.244900544395632</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>198</v>
+        <v>502</v>
       </c>
       <c r="B420">
-        <v>-0.35980406825606698</v>
+        <v>-1.5438793495265499</v>
       </c>
       <c r="C420">
-        <v>0.22857730918576799</v>
+        <v>-0.64098362965174405</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>199</v>
+        <v>503</v>
       </c>
       <c r="B421">
-        <v>0.65277979814327103</v>
+        <v>0.71855991451317203</v>
       </c>
       <c r="C421">
-        <v>-0.28977008022369</v>
+        <v>-0.22266509428190001</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="B422">
-        <v>-1.0708670632828099</v>
+        <v>-0.283861536564044</v>
       </c>
       <c r="C422">
-        <v>-1.4500497959216301</v>
+        <v>-7.2149732734953495E-2</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>200</v>
+        <v>505</v>
       </c>
       <c r="B423">
-        <v>0.67952585089726503</v>
+        <v>0.68797877864776702</v>
       </c>
       <c r="C423">
-        <v>1.39841714478596E-2</v>
+        <v>-0.20842812904302499</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>471</v>
+        <v>506</v>
       </c>
       <c r="B424">
-        <v>-1.0548603513844199</v>
+        <v>-9.4632707181924097E-2</v>
       </c>
       <c r="C424">
-        <v>0.56714804629632398</v>
+        <v>0.43002291993361302</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="B425">
-        <v>0.53566775612879802</v>
+        <v>0.10816073833267</v>
       </c>
       <c r="C425">
-        <v>0.17521187725978299</v>
+        <v>-0.48422798915126802</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="B426">
-        <v>-0.35120180303494403</v>
+        <v>-0.202674613601286</v>
       </c>
       <c r="C426">
-        <v>0.24762142487171801</v>
+        <v>0.365713500403474</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>473</v>
+        <v>235</v>
       </c>
       <c r="B427">
-        <v>-0.13409052380309</v>
+        <v>-3.43790366747668E-2</v>
       </c>
       <c r="C427">
-        <v>0.45125440233651098</v>
+        <v>0.30936514492439998</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
       <c r="B428">
-        <v>-1.3093330574117701</v>
+        <v>-1.2948342059666</v>
       </c>
       <c r="C428">
-        <v>0.32016698333900401</v>
+        <v>-0.75509836435556998</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>475</v>
+        <v>236</v>
       </c>
       <c r="B429">
-        <v>-0.696604864737848</v>
+        <v>-1.3269394720411101</v>
       </c>
       <c r="C429">
-        <v>0.196374622389342</v>
+        <v>-0.37498485511181601</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="B430">
-        <v>-0.71397734753055797</v>
+        <v>-1.47168090654507</v>
       </c>
       <c r="C430">
-        <v>0.25194877564301899</v>
+        <v>-0.179385319050685</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>202</v>
+        <v>509</v>
       </c>
       <c r="B431">
-        <v>0.64499000217740199</v>
+        <v>0.54824446001784699</v>
       </c>
       <c r="C431">
-        <v>-0.28588726555899102</v>
+        <v>-2.34658923737248E-2</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="B432">
-        <v>0.65691473512827003</v>
+        <v>-1.26999312045621</v>
       </c>
       <c r="C432">
-        <v>-0.59509629000493802</v>
+        <v>-1.2249263929334699</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>203</v>
+        <v>511</v>
       </c>
       <c r="B433">
-        <v>-0.15583645626464299</v>
+        <v>-1.0898415678868101</v>
       </c>
       <c r="C433">
-        <v>0.377491214481254</v>
+        <v>-1.2039766222310799</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>478</v>
+        <v>237</v>
       </c>
       <c r="B434">
-        <v>-0.39665768858584899</v>
+        <v>-1.2016804693901999</v>
       </c>
       <c r="C434">
-        <v>0.93480805946421297</v>
+        <v>-0.24185385918013699</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="B435">
-        <v>-0.20089005935528201</v>
+        <v>-0.24076950681838799</v>
       </c>
       <c r="C435">
-        <v>0.29203746661248597</v>
+        <v>0.205474930760631</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="B436">
-        <v>0.684041110668828</v>
+        <v>-1.1093719914759901</v>
       </c>
       <c r="C436">
-        <v>0.41613307620128498</v>
+        <v>-1.7292295115340499</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>205</v>
+        <v>513</v>
       </c>
       <c r="B437">
-        <v>-1.1156327872515801</v>
+        <v>-1.1941933735586501</v>
       </c>
       <c r="C437">
-        <v>-0.80532018095281299</v>
+        <v>-1.2217414050021</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>206</v>
+        <v>514</v>
       </c>
       <c r="B438">
-        <v>-0.47734734502940801</v>
+        <v>-0.65792408095529198</v>
       </c>
       <c r="C438">
-        <v>0.20297451791576199</v>
+        <v>0.48518069394996499</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="B439">
-        <v>-0.29159425745787299</v>
+        <v>0.21936858363119699</v>
       </c>
       <c r="C439">
-        <v>0.25447337451222202</v>
+        <v>0.34777683097432299</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>480</v>
+        <v>515</v>
       </c>
       <c r="B440">
-        <v>8.6195405448937598E-2</v>
+        <v>-0.45926489325143199</v>
       </c>
       <c r="C440">
-        <v>0.66174959174055104</v>
+        <v>-0.136978160353978</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>481</v>
+        <v>240</v>
       </c>
       <c r="B441">
-        <v>-0.37598687717936002</v>
+        <v>-1.2220337086689601</v>
       </c>
       <c r="C441">
-        <v>0.180641435663047</v>
+        <v>-0.61984888690020701</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="B442">
-        <v>-2.7775843104527499E-2</v>
+        <v>0.55273564099678396</v>
       </c>
       <c r="C442">
-        <v>0.56498406356678499</v>
+        <v>-0.346420390758168</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="B443">
-        <v>0.82508188080481004</v>
+        <v>-1.20267219683201</v>
       </c>
       <c r="C443">
-        <v>-0.42562342875034798</v>
+        <v>-0.86258258109234298</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="B444">
-        <v>-1.1201054802822801</v>
+        <v>0.27216952091382401</v>
       </c>
       <c r="C444">
-        <v>-1.25170688100835</v>
+        <v>0.17634411941110001</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>209</v>
+        <v>518</v>
       </c>
       <c r="B445">
-        <v>-0.56773699347072504</v>
+        <v>0.61083888107008499</v>
       </c>
       <c r="C445">
-        <v>-7.5303296869248304E-2</v>
+        <v>-0.26520744747865899</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>484</v>
+        <v>242</v>
       </c>
       <c r="B446">
-        <v>0.17131407059472101</v>
+        <v>0.59087416324840902</v>
       </c>
       <c r="C446">
-        <v>-2.61479464378724E-2</v>
+        <v>-0.19505557575051699</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>210</v>
+        <v>519</v>
       </c>
       <c r="B447">
-        <v>-1.13434762151883</v>
+        <v>-1.0482606741878</v>
       </c>
       <c r="C447">
-        <v>0.398506407441517</v>
+        <v>-1.5235775960073099</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>211</v>
+        <v>520</v>
       </c>
       <c r="B448">
-        <v>-0.69918530957230995</v>
+        <v>0.54019969915133004</v>
       </c>
       <c r="C448">
-        <v>0.181148201239306</v>
+        <v>-0.34125672802069001</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="B449">
-        <v>0.72049251147902404</v>
+        <v>-1.1246738949728301</v>
       </c>
       <c r="C449">
-        <v>-0.36500650888974601</v>
+        <v>-1.2873528439278401</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>485</v>
+        <v>244</v>
       </c>
       <c r="B450">
-        <v>0.55067758881637296</v>
+        <v>0.71124181805384401</v>
       </c>
       <c r="C450">
-        <v>-0.27243883749675202</v>
+        <v>-0.27309456454286302</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="B451">
-        <v>0.736264024060859</v>
+        <v>0.789299139863338</v>
       </c>
       <c r="C451">
-        <v>-0.20418762236785501</v>
+        <v>-8.9230767109803405E-2</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>213</v>
+        <v>522</v>
       </c>
       <c r="B452">
-        <v>0.58419202581303697</v>
+        <v>8.3916184508420102E-2</v>
       </c>
       <c r="C452">
-        <v>0.17525424069348999</v>
+        <v>0.66081984008292205</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>487</v>
+        <v>523</v>
       </c>
       <c r="B453">
-        <v>0.63314620301125701</v>
+        <v>-0.31712095886298303</v>
       </c>
       <c r="C453">
-        <v>-0.38905572250011</v>
+        <v>0.13906886114263001</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="B454">
-        <v>-7.0090283442285004E-2</v>
+        <v>-1.1555152999465901</v>
       </c>
       <c r="C454">
-        <v>-0.37712268261204102</v>
+        <v>-1.1855806023809099</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>214</v>
+        <v>525</v>
       </c>
       <c r="B455">
-        <v>-1.3336384742115199</v>
+        <v>0.77433505806274505</v>
       </c>
       <c r="C455">
-        <v>-0.330110942445068</v>
+        <v>-0.55910171109061502</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>641</v>
-      </c>
-      <c r="B456" t="s">
-        <v>639</v>
-      </c>
-      <c r="C456" t="s">
-        <v>639</v>
+        <v>245</v>
+      </c>
+      <c r="B456">
+        <v>0.55447924494821998</v>
+      </c>
+      <c r="C456">
+        <v>-0.13971846263153501</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="B457">
-        <v>-0.83512624328418394</v>
+        <v>0.20907590073994001</v>
       </c>
       <c r="C457">
-        <v>0.475242000957177</v>
+        <v>0.84057806371578903</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="B458">
-        <v>-1.01923340143522</v>
+        <v>-1.2364141992364199</v>
       </c>
       <c r="C458">
-        <v>-1.55142040429275</v>
+        <v>-0.50977246867806802</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>491</v>
+        <v>246</v>
       </c>
       <c r="B459">
-        <v>-1.2123470567700201</v>
+        <v>-1.2904555156200901</v>
       </c>
       <c r="C459">
-        <v>-1.11829229105299</v>
+        <v>-1.1438689843062999</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>492</v>
+        <v>247</v>
       </c>
       <c r="B460">
-        <v>-1.1453157312470701</v>
+        <v>-0.20818931035313001</v>
       </c>
       <c r="C460">
-        <v>-1.45401447858166</v>
+        <v>0.57694683329697505</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>493</v>
+        <v>248</v>
       </c>
       <c r="B461">
-        <v>-1.5255300008477299</v>
+        <v>0.67765310580574001</v>
       </c>
       <c r="C461">
-        <v>-0.82804141758409699</v>
+        <v>-0.33028921344432499</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="B462">
-        <v>0.66282198876590503</v>
+        <v>-0.241862921839512</v>
       </c>
       <c r="C462">
-        <v>-0.38476390382662101</v>
+        <v>1.1535087211774999</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="B463">
-        <v>0.68382681570913395</v>
+        <v>0.64095508947483704</v>
       </c>
       <c r="C463">
-        <v>8.4627456122570194E-2</v>
+        <v>0.380566386724776</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>496</v>
+        <v>249</v>
       </c>
       <c r="B464">
-        <v>-1.2793092979084799</v>
+        <v>0.77661014852027499</v>
       </c>
       <c r="C464">
-        <v>-0.89852326677190697</v>
+        <v>-0.42404823051678497</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="B465">
-        <v>7.9673041272032799E-2</v>
+        <v>-1.33113230188233</v>
       </c>
       <c r="C465">
-        <v>0.78141318159472295</v>
+        <v>-0.37028359190621701</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="B466">
-        <v>-1.41439460559033</v>
+        <v>-0.65292421887528895</v>
       </c>
       <c r="C466">
-        <v>-0.56453392772384403</v>
+        <v>0.169256524258658</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>498</v>
+        <v>251</v>
       </c>
       <c r="B467">
-        <v>-0.311630637568866</v>
+        <v>-1.08944920982299</v>
       </c>
       <c r="C467">
-        <v>0.57201179375911804</v>
+        <v>-1.18583696632076</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B468">
-        <v>-1.16996845087402</v>
+        <v>8.7875350846187896E-4</v>
       </c>
       <c r="C468">
-        <v>0.80821626752188902</v>
+        <v>-0.66973996003897596</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>216</v>
+        <v>532</v>
       </c>
       <c r="B469">
-        <v>3.7139822379038998E-2</v>
+        <v>-1.4452691367359101</v>
       </c>
       <c r="C469">
-        <v>4.6658539391769803E-3</v>
+        <v>-0.62237165185592902</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>500</v>
+        <v>252</v>
       </c>
       <c r="B470">
-        <v>8.4660764033205105E-2</v>
+        <v>0.56309809169692004</v>
       </c>
       <c r="C470">
-        <v>0.82913825889888404</v>
+        <v>-0.26114657429706201</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>501</v>
+        <v>253</v>
       </c>
       <c r="B471">
-        <v>-1.0404745768489401</v>
+        <v>0.73101812158614499</v>
       </c>
       <c r="C471">
-        <v>-0.38122130299243201</v>
+        <v>-0.34253369187503702</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="B472">
-        <v>-1.0126523975060699</v>
+        <v>-1.2571277912621199</v>
       </c>
       <c r="C472">
-        <v>-0.87055194155573901</v>
+        <v>-0.62360069845256605</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="B473">
-        <v>-1.37874457751813</v>
+        <v>-1.0613025528649001</v>
       </c>
       <c r="C473">
-        <v>-0.54212335312594695</v>
+        <v>-0.47783997150333901</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>502</v>
+        <v>256</v>
       </c>
       <c r="B474">
-        <v>-0.31583645081876699</v>
+        <v>4.8787918754373799E-2</v>
       </c>
       <c r="C474">
-        <v>0.89793170168088199</v>
+        <v>0.45022830046217599</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="B475">
-        <v>0.119898721527065</v>
+        <v>-1.2756217857513801</v>
       </c>
       <c r="C475">
-        <v>0.38989628727938302</v>
+        <v>0.271525283607921</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>219</v>
+        <v>534</v>
       </c>
       <c r="B476">
-        <v>0.71663550844984303</v>
+        <v>0.52286017974800603</v>
       </c>
       <c r="C476">
-        <v>-0.399696076874479</v>
+        <v>-0.51048387272340001</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>504</v>
+        <v>257</v>
       </c>
       <c r="B477">
-        <v>-1.47360344480126</v>
+        <v>0.70967397728170201</v>
       </c>
       <c r="C477">
-        <v>-0.66540877486195005</v>
+        <v>-0.38721421100652098</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="B478">
-        <v>-0.29256215916497902</v>
+        <v>0.37914770866021302</v>
       </c>
       <c r="C478">
-        <v>0.39212010831550498</v>
+        <v>0.28429574142936498</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="B479">
-        <v>-1.1895995847749501</v>
+        <v>-0.106599622458001</v>
       </c>
       <c r="C479">
-        <v>-0.28324369853938602</v>
+        <v>0.43742004990484701</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>222</v>
+        <v>535</v>
       </c>
       <c r="B480">
-        <v>-1.3997058548049901</v>
+        <v>0.71195027403906597</v>
       </c>
       <c r="C480">
-        <v>-0.30628818407519598</v>
+        <v>5.6234953353468599E-2</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="B481">
-        <v>-1.1515170312362999</v>
+        <v>-0.85455482800018501</v>
       </c>
       <c r="C481">
-        <v>0.105246832422787</v>
+        <v>-0.46738105451990802</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>223</v>
+        <v>537</v>
       </c>
       <c r="B482">
-        <v>0.61539871414972702</v>
+        <v>-0.17486662088215399</v>
       </c>
       <c r="C482">
-        <v>0.14501084619147001</v>
+        <v>0.351216903117617</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="B483">
-        <v>-0.37318157398805002</v>
+        <v>7.6620979928140306E-2</v>
       </c>
       <c r="C483">
-        <v>0.44866956847871697</v>
+        <v>0.49210089415622899</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="B484">
-        <v>0.60153371806835099</v>
+        <v>0.63060875553568996</v>
       </c>
       <c r="C484">
-        <v>-0.24343091703561401</v>
+        <v>-0.45112090912997199</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>226</v>
+        <v>538</v>
       </c>
       <c r="B485">
-        <v>-0.26588600498071402</v>
+        <v>-1.27697185036093</v>
       </c>
       <c r="C485">
-        <v>0.120741298256063</v>
+        <v>-0.81637131756579795</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="B486">
-        <v>-0.83512624328418394</v>
+        <v>-0.507288320559801</v>
       </c>
       <c r="C486">
-        <v>0.475242000957177</v>
+        <v>0.34405859134622502</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>227</v>
+        <v>540</v>
       </c>
       <c r="B487">
-        <v>-0.56661364555875204</v>
+        <v>-1.3608194452695801</v>
       </c>
       <c r="C487">
-        <v>0.14345705650285301</v>
+        <v>0.17954247101902901</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="B488">
-        <v>-1.20795491746071</v>
+        <v>0.64619664715773295</v>
       </c>
       <c r="C488">
-        <v>-1.3369677280658701</v>
+        <v>-0.59513998659918399</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="B489">
-        <v>-0.119576699007785</v>
+        <v>-0.23393573920921101</v>
       </c>
       <c r="C489">
-        <v>0.76336050417992096</v>
+        <v>-2.2787105369271199E-2</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>228</v>
+        <v>543</v>
       </c>
       <c r="B490">
-        <v>-1.48509632095039</v>
+        <v>-0.20274019372498001</v>
       </c>
       <c r="C490">
-        <v>-0.60345163198278096</v>
+        <v>0.51598862351518104</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="B491">
-        <v>0.50860293172613702</v>
+        <v>-1.32334909812219</v>
       </c>
       <c r="C491">
-        <v>0.93898917732166798</v>
+        <v>-0.98745404571467799</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="B492">
-        <v>-0.83512624328418394</v>
+        <v>-0.212400941082769</v>
       </c>
       <c r="C492">
-        <v>0.475242000957177</v>
+        <v>0.58965973595124099</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="B493">
-        <v>-0.24896244835717801</v>
+        <v>0.62187032173719903</v>
       </c>
       <c r="C493">
-        <v>0.41167250852124898</v>
+        <v>-5.9364408060479303E-2</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="B494">
-        <v>8.98631822977876E-2</v>
+        <v>-0.54255393497750004</v>
       </c>
       <c r="C494">
-        <v>0.53429850509161003</v>
+        <v>-9.5051541618249094E-2</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>511</v>
+        <v>264</v>
       </c>
       <c r="B495">
-        <v>0.55409338016113296</v>
+        <v>0.60973484391511801</v>
       </c>
       <c r="C495">
-        <v>-0.33209828574695599</v>
+        <v>-0.27221736302544303</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>231</v>
+        <v>546</v>
       </c>
       <c r="B496">
-        <v>-0.34593240472384401</v>
+        <v>8.7804630693936195E-2</v>
       </c>
       <c r="C496">
-        <v>-6.0749665951130197E-2</v>
+        <v>0.118137673697226</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>512</v>
+        <v>547</v>
       </c>
       <c r="B497">
-        <v>-1.09322559501504</v>
+        <v>-2.95365186066853E-2</v>
       </c>
       <c r="C497">
-        <v>0.63119795847686</v>
+        <v>0.59129812051511299</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>513</v>
+        <v>265</v>
       </c>
       <c r="B498">
-        <v>0.15238954046028</v>
+        <v>-0.10619130868007499</v>
       </c>
       <c r="C498">
-        <v>0.48718830774196298</v>
+        <v>0.388138373464394</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="B499">
-        <v>0.61476458665738398</v>
+        <v>-1.2611112017500701</v>
       </c>
       <c r="C499">
-        <v>0.25295011479839402</v>
+        <v>-0.14732651340581299</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="B500">
-        <v>0.65974608342681496</v>
+        <v>-0.14857287845794701</v>
       </c>
       <c r="C500">
-        <v>0.25812247584347398</v>
+        <v>0.33964321659674002</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="B501">
-        <v>-1.33836488861216</v>
+        <v>0.67056049812626195</v>
       </c>
       <c r="C501">
-        <v>-0.47946020474277801</v>
+        <v>-5.21569104243172E-2</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="B502">
-        <v>0.69733781685320995</v>
+        <v>-0.25524914473349503</v>
       </c>
       <c r="C502">
-        <v>-0.203439377343172</v>
+        <v>0.381202896204347</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="B503">
-        <v>-0.50114306025172795</v>
+        <v>-0.21176026933467201</v>
       </c>
       <c r="C503">
-        <v>0.27882893013709797</v>
+        <v>0.35270442432813798</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>518</v>
+        <v>653</v>
       </c>
       <c r="B504">
-        <v>0.66625181159353697</v>
+        <v>3.7365770436852401E-2</v>
       </c>
       <c r="C504">
-        <v>-0.19396311283368001</v>
+        <v>-1.68330092514751</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="B505">
-        <v>-0.1062428780616</v>
+        <v>0.69087878047800799</v>
       </c>
       <c r="C505">
-        <v>0.44342543531719197</v>
+        <v>-0.39128148829413001</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>233</v>
+        <v>553</v>
       </c>
       <c r="B506">
-        <v>0.130483432227749</v>
+        <v>0.79774257007999205</v>
       </c>
       <c r="C506">
-        <v>-0.44912453648011502</v>
+        <v>-0.20992854779668599</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="B507">
-        <v>-0.202986047685488</v>
+        <v>-5.76448283419526E-2</v>
       </c>
       <c r="C507">
-        <v>0.41729376879812002</v>
+        <v>0.25505148431807301</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="B508">
-        <v>-4.8660237516916602E-2</v>
+        <v>-9.1389987847245793E-2</v>
       </c>
       <c r="C508">
-        <v>0.31473382862299798</v>
+        <v>0.46471250276883203</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
       <c r="B509">
-        <v>-1.2752347713315499</v>
+        <v>-0.154066440901795</v>
       </c>
       <c r="C509">
-        <v>-0.74973476560355401</v>
+        <v>0.47226285157793402</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="B510">
-        <v>-1.2816401120913801</v>
+        <v>0.75247998780797998</v>
       </c>
       <c r="C510">
-        <v>-0.358944058748772</v>
+        <v>-0.42288486430031802</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
       <c r="B511">
-        <v>-1.4595976439960401</v>
+        <v>0.79925371807928203</v>
       </c>
       <c r="C511">
-        <v>-0.16645695003316699</v>
+        <v>-0.50898384466213997</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="B512">
-        <v>0.53310091462644404</v>
+        <v>-0.35580902078632798</v>
       </c>
       <c r="C512">
-        <v>4.7499402178139598E-3</v>
+        <v>0.45183077449936099</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
       <c r="B513">
-        <v>-1.2413174890762799</v>
+        <v>-8.2510961899354696E-2</v>
       </c>
       <c r="C513">
-        <v>-1.2331133484563801</v>
+        <v>0.50296978386533697</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>524</v>
+        <v>270</v>
       </c>
       <c r="B514">
-        <v>-1.0654187766012</v>
+        <v>7.3169944198632195E-2</v>
       </c>
       <c r="C514">
-        <v>-1.2132917715230001</v>
+        <v>-0.22940292543468099</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="B515">
-        <v>-1.1364881609652999</v>
+        <v>-0.52320229054432399</v>
       </c>
       <c r="C515">
-        <v>-0.17465066291949199</v>
+        <v>-0.28567329937416902</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="B516">
-        <v>-0.31312528104155402</v>
+        <v>0.113962020162683</v>
       </c>
       <c r="C516">
-        <v>0.21384583341526001</v>
+        <v>5.6415364895407501E-2</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>525</v>
+        <v>558</v>
       </c>
       <c r="B517">
-        <v>-1.0812940390005901</v>
+        <v>-1.0337172906579</v>
       </c>
       <c r="C517">
-        <v>-1.7506907253114301</v>
+        <v>-0.44129230593002</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>526</v>
+        <v>654</v>
       </c>
       <c r="B518">
-        <v>-1.18675894201167</v>
+        <v>3.7365770436852401E-2</v>
       </c>
       <c r="C518">
-        <v>-1.12975491049054</v>
+        <v>-1.68330092514751</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>527</v>
+        <v>655</v>
       </c>
       <c r="B519">
-        <v>-0.57549947014649405</v>
+        <v>-0.94815718272085503</v>
       </c>
       <c r="C519">
-        <v>0.37746637944198203</v>
+        <v>0.67821394404990198</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="B520">
-        <v>0.210728428290784</v>
+        <v>-0.26401657896415798</v>
       </c>
       <c r="C520">
-        <v>0.35007678392207398</v>
+        <v>-6.7871425005546507E-2</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="B521">
-        <v>-0.39964747169141501</v>
+        <v>0.123074893288913</v>
       </c>
       <c r="C521">
-        <v>-1.5983026784080801E-2</v>
+        <v>0.63774019131411597</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="B522">
-        <v>-1.2038075972597799</v>
+        <v>-0.37268331037734997</v>
       </c>
       <c r="C522">
-        <v>-0.61892346680335997</v>
+        <v>0.13975520343668901</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="B523">
-        <v>0.53806520708291095</v>
+        <v>0.49684817986952001</v>
       </c>
       <c r="C523">
-        <v>-0.31310863963587499</v>
+        <v>0.18076969753057101</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="B524">
-        <v>-1.18556073912032</v>
+        <v>8.3280676111545604E-2</v>
       </c>
       <c r="C524">
-        <v>-0.85562527072430805</v>
+        <v>-0.24771779255609</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>241</v>
+        <v>563</v>
       </c>
       <c r="B525">
-        <v>0.312652893938273</v>
+        <v>-0.32467947652288998</v>
       </c>
       <c r="C525">
-        <v>0.110722258695601</v>
+        <v>-0.158985570783301</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>531</v>
+        <v>274</v>
       </c>
       <c r="B526">
-        <v>0.61701781326037997</v>
+        <v>-0.60369560583433401</v>
       </c>
       <c r="C526">
-        <v>-0.2275211740951</v>
+        <v>-4.39447329726666E-2</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>242</v>
+        <v>564</v>
       </c>
       <c r="B527">
-        <v>0.58266382223480795</v>
+        <v>0.44572555579794598</v>
       </c>
       <c r="C527">
-        <v>-0.14028784093187499</v>
+        <v>-0.29266494396962001</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>532</v>
+        <v>565</v>
       </c>
       <c r="B528">
-        <v>-1.01923340143522</v>
+        <v>0.83835540071551395</v>
       </c>
       <c r="C528">
-        <v>-1.55142040429275</v>
+        <v>-0.28219598102752202</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>533</v>
+        <v>566</v>
       </c>
       <c r="B529">
-        <v>0.51677147449841798</v>
+        <v>-1.5469651544760501</v>
       </c>
       <c r="C529">
-        <v>-0.29629110742841203</v>
+        <v>-0.68685394030383695</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>243</v>
+        <v>567</v>
       </c>
       <c r="B530">
-        <v>-1.09917405271089</v>
+        <v>0.60574413714332898</v>
       </c>
       <c r="C530">
-        <v>-1.30367570540346</v>
+        <v>-0.43580119304948001</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>244</v>
+        <v>568</v>
       </c>
       <c r="B531">
-        <v>0.68951336670298902</v>
+        <v>-0.74769334230589701</v>
       </c>
       <c r="C531">
-        <v>-0.238654826550181</v>
+        <v>0.33681628957020399</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>534</v>
+        <v>275</v>
       </c>
       <c r="B532">
-        <v>0.76974729434283196</v>
+        <v>0.70374495465206</v>
       </c>
       <c r="C532">
-        <v>-5.5843913850905903E-2</v>
+        <v>-0.33417758801990899</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="B533">
-        <v>6.3273716180196005E-2</v>
+        <v>-1.18289412448975</v>
       </c>
       <c r="C533">
-        <v>0.67990951902868002</v>
+        <v>-1.3030251586725801</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>536</v>
+        <v>276</v>
       </c>
       <c r="B534">
-        <v>-0.320631255984001</v>
+        <v>3.9445984269936799E-2</v>
       </c>
       <c r="C534">
-        <v>0.19809421289250501</v>
+        <v>0.61878594867035197</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>537</v>
+        <v>277</v>
       </c>
       <c r="B535">
-        <v>-1.1361213630545599</v>
+        <v>4.8176685897115303E-2</v>
       </c>
       <c r="C535">
-        <v>-1.1910946356624501</v>
+        <v>0.47603351254501303</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>538</v>
+        <v>278</v>
       </c>
       <c r="B536">
-        <v>0.76143431591562005</v>
+        <v>-0.29131560932085598</v>
       </c>
       <c r="C536">
-        <v>-0.51508960932581904</v>
+        <v>0.31259721499466497</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>245</v>
+        <v>570</v>
       </c>
       <c r="B537">
-        <v>0.54365084944023201</v>
+        <v>-0.36238949672104798</v>
       </c>
       <c r="C537">
-        <v>-8.6102928739849094E-2</v>
+        <v>-5.81737678981053E-2</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="B538">
-        <v>8.4660764033205105E-2</v>
+        <v>-0.29099506999973401</v>
       </c>
       <c r="C538">
-        <v>0.82913825889888404</v>
+        <v>-2.51834711813512E-2</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="B539">
-        <v>-1.2227293086172599</v>
+        <v>-0.430014897205372</v>
       </c>
       <c r="C539">
-        <v>-0.50673837484240702</v>
+        <v>-7.6751778270812407E-2</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>246</v>
+        <v>573</v>
       </c>
       <c r="B540">
-        <v>-1.2684682126337301</v>
+        <v>0.57459231391529597</v>
       </c>
       <c r="C540">
-        <v>-1.1554370635684099</v>
+        <v>-0.39880694890186102</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="B541">
-        <v>-0.19616254417171899</v>
+        <v>-0.325197397217803</v>
       </c>
       <c r="C541">
-        <v>0.61948752201990998</v>
+        <v>0.16318451002721901</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>248</v>
+        <v>574</v>
       </c>
       <c r="B542">
-        <v>0.65447306183499399</v>
+        <v>0.67914991045202799</v>
       </c>
       <c r="C542">
-        <v>-0.28996229278124902</v>
+        <v>-0.165071460958225</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>541</v>
+        <v>280</v>
       </c>
       <c r="B543">
-        <v>-0.21781504149734801</v>
+        <v>-1.1617973480014101</v>
       </c>
       <c r="C543">
-        <v>1.2198217372244899</v>
+        <v>0.19573943252421</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>542</v>
+        <v>575</v>
       </c>
       <c r="B544">
-        <v>0.62312981803245404</v>
+        <v>0.66467479162961896</v>
       </c>
       <c r="C544">
-        <v>0.41329150543059801</v>
+        <v>-0.27549161959226798</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B545">
-        <v>0.75491987902267699</v>
+        <v>7.6410307568087393E-2</v>
       </c>
       <c r="C545">
-        <v>-0.37928752643223101</v>
+        <v>-0.23117462777508699</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="B546">
-        <v>-1.3082153726727901</v>
+        <v>-0.241862921839512</v>
       </c>
       <c r="C546">
-        <v>-0.36944973479467202</v>
+        <v>1.1535087211774999</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="B547">
-        <v>-0.70520245635520995</v>
+        <v>0.67104115231125805</v>
       </c>
       <c r="C547">
-        <v>0.26905092077325599</v>
+        <v>-0.24499032005563201</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>251</v>
+        <v>577</v>
       </c>
       <c r="B548">
-        <v>-1.0663947157747</v>
+        <v>0.85172899653860001</v>
       </c>
       <c r="C548">
-        <v>-1.19536042439779</v>
+        <v>-0.46934656397511298</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>544</v>
+        <v>283</v>
       </c>
       <c r="B549">
-        <v>-4.33211880012992E-3</v>
+        <v>-0.49269102987032598</v>
       </c>
       <c r="C549">
-        <v>-0.65300581264003899</v>
+        <v>0.139734301233468</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>545</v>
+        <v>578</v>
       </c>
       <c r="B550">
-        <v>-1.4241148226425999</v>
+        <v>0.73611976241805099</v>
       </c>
       <c r="C550">
-        <v>-0.64045577377259599</v>
+        <v>-1.6869240472807599E-2</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="B551">
-        <v>0.57654112758656095</v>
+        <v>0.68725649846128301</v>
       </c>
       <c r="C551">
-        <v>-0.24825237923211199</v>
+        <v>-0.30295877349356798</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="B552">
-        <v>0.71043916673684404</v>
+        <v>5.2225096790569601E-2</v>
       </c>
       <c r="C552">
-        <v>-0.29273191594889297</v>
+        <v>0.28286883038666299</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="B553">
-        <v>-1.2344984543228501</v>
+        <v>0.75754267483929005</v>
       </c>
       <c r="C553">
-        <v>-0.61656387050985995</v>
+        <v>-0.418119063530483</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>255</v>
+        <v>579</v>
       </c>
       <c r="B554">
-        <v>-1.0501288590290401</v>
+        <v>0.25705837333761999</v>
       </c>
       <c r="C554">
-        <v>-0.40049467205628198</v>
+        <v>-0.31943218364987502</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B555">
-        <v>7.6732112183917497E-2</v>
+        <v>-0.71035210816071004</v>
       </c>
       <c r="C555">
-        <v>0.46106572517968902</v>
+        <v>1.8213603905379499E-2</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="B556">
-        <v>-1.25865502542656</v>
+        <v>-0.30175564367060997</v>
       </c>
       <c r="C556">
-        <v>0.28902712765862199</v>
+        <v>-0.257273114908528</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
       <c r="B557">
-        <v>0.50723457129866201</v>
+        <v>-0.93401747203002095</v>
       </c>
       <c r="C557">
-        <v>-0.46880538093298901</v>
+        <v>7.6255411576698101E-2</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>257</v>
+        <v>582</v>
       </c>
       <c r="B558">
-        <v>0.68818998815677901</v>
+        <v>0.57994245505229103</v>
       </c>
       <c r="C558">
-        <v>-0.34573105595862802</v>
+        <v>0.41924497721976201</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>258</v>
+        <v>627</v>
       </c>
       <c r="B559">
-        <v>0.51618533289374202</v>
+        <v>-4.7144783509839097E-2</v>
       </c>
       <c r="C559">
-        <v>0.14854065541810499</v>
+        <v>-1.8301038842261901</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>548</v>
+        <v>583</v>
       </c>
       <c r="B560">
-        <v>0.67421056314509498</v>
+        <v>0.752010413490799</v>
       </c>
       <c r="C560">
-        <v>9.44829113781952E-2</v>
+        <v>-0.64995161174006999</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>259</v>
+        <v>584</v>
       </c>
       <c r="B561">
-        <v>-0.102638665039484</v>
+        <v>-1.38491045626701</v>
       </c>
       <c r="C561">
-        <v>0.43838150065849402</v>
+        <v>-0.80075026051619602</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>549</v>
+        <v>628</v>
       </c>
       <c r="B562">
-        <v>-0.84050911244205395</v>
+        <v>-0.32391203879466401</v>
       </c>
       <c r="C562">
-        <v>-0.48392374812571098</v>
+        <v>2.6395715492607E-2</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>260</v>
+        <v>629</v>
       </c>
       <c r="B563">
-        <v>6.0688163732660998E-2</v>
+        <v>-0.53068342002212499</v>
       </c>
       <c r="C563">
-        <v>0.52251062289551897</v>
+        <v>-1.4032618102054801E-2</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>550</v>
+        <v>630</v>
       </c>
       <c r="B564">
-        <v>-0.19517151070486999</v>
+        <v>2.4057344721291899E-2</v>
       </c>
       <c r="C564">
-        <v>0.39458428363480802</v>
+        <v>0.62139271593011702</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>261</v>
+        <v>631</v>
       </c>
       <c r="B565">
-        <v>0.61496325071885505</v>
+        <v>-1.2116526003210299</v>
       </c>
       <c r="C565">
-        <v>-0.42993217125990002</v>
+        <v>-1.13161298634854</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>551</v>
+        <v>632</v>
       </c>
       <c r="B566">
-        <v>-1.2589007076251499</v>
+        <v>-0.191344494665003</v>
       </c>
       <c r="C566">
-        <v>-0.82045222493585002</v>
+        <v>0.54762682847745503</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>552</v>
+        <v>633</v>
       </c>
       <c r="B567">
-        <v>-0.48264362840993102</v>
+        <v>0.74500885362619795</v>
       </c>
       <c r="C567">
-        <v>0.43764421661658998</v>
+        <v>0.28203486337424499</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>553</v>
+        <v>634</v>
       </c>
       <c r="B568">
-        <v>-1.3389044252198801</v>
+        <v>-0.41049671964951001</v>
       </c>
       <c r="C568">
-        <v>0.186097126274507</v>
+        <v>0.18509417028681099</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>554</v>
+        <v>635</v>
       </c>
       <c r="B569">
-        <v>0.63797592772795297</v>
+        <v>3.04749759261639E-2</v>
       </c>
       <c r="C569">
-        <v>-0.55852792043160104</v>
+        <v>0.56890202826173597</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>555</v>
+        <v>636</v>
       </c>
       <c r="B570">
-        <v>-0.248112522031327</v>
+        <v>0.77136598451572203</v>
       </c>
       <c r="C570">
-        <v>3.51807451159405E-2</v>
+        <v>-3.6069576534292297E-2</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>556</v>
+        <v>637</v>
       </c>
       <c r="B571">
-        <v>-0.214295461005966</v>
+        <v>-1.55295942338985</v>
       </c>
       <c r="C571">
-        <v>0.46955933002869399</v>
+        <v>-0.78180439298368198</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>557</v>
+        <v>88</v>
       </c>
       <c r="B572">
-        <v>-1.2945792800859599</v>
+        <v>0.671337328675778</v>
       </c>
       <c r="C572">
-        <v>-1.01162276121776</v>
+        <v>-0.32019655600886598</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
       <c r="B573">
-        <v>-0.20298794555982</v>
+        <v>-1.1036984000082599</v>
       </c>
       <c r="C573">
-        <v>0.64230730178326001</v>
+        <v>-1.39480947456717</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>262</v>
+        <v>586</v>
       </c>
       <c r="B574">
-        <v>0.73026750902870496</v>
+        <v>-1.1971794408572201</v>
       </c>
       <c r="C574">
-        <v>-0.130696114699732</v>
+        <v>0.85537616957015805</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>263</v>
+        <v>89</v>
       </c>
       <c r="B575">
-        <v>-0.56002175876466498</v>
+        <v>-0.32245927923852702</v>
       </c>
       <c r="C575">
-        <v>-0.119278588576441</v>
+        <v>0.174162915350975</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>264</v>
+        <v>90</v>
       </c>
       <c r="B576">
-        <v>0.58780831998518102</v>
+        <v>-1.18528728582426</v>
       </c>
       <c r="C576">
-        <v>-0.24238468027477</v>
+        <v>-1.3161718320824201</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="B577">
-        <v>0.48244005006389401</v>
+        <v>-0.28372378099038498</v>
       </c>
       <c r="C577">
-        <v>0.41556374824841402</v>
+        <v>0.403332960721759</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>560</v>
+        <v>91</v>
       </c>
       <c r="B578">
-        <v>-0.101439422571801</v>
+        <v>0.65953393829148899</v>
       </c>
       <c r="C578">
-        <v>0.49595709477711702</v>
+        <v>-0.19812776830848899</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>265</v>
+        <v>588</v>
       </c>
       <c r="B579">
-        <v>-0.10523609581129501</v>
+        <v>0.42056922455671197</v>
       </c>
       <c r="C579">
-        <v>0.43097745818148597</v>
+        <v>0.77817499340394702</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>266</v>
+        <v>589</v>
       </c>
       <c r="B580">
-        <v>-1.23807330913032</v>
+        <v>-0.27675182741847199</v>
       </c>
       <c r="C580">
-        <v>-0.150535827192846</v>
+        <v>0.457267412356548</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>561</v>
+        <v>92</v>
       </c>
       <c r="B581">
-        <v>-0.13535271755285899</v>
+        <v>-1.1562363100700701</v>
       </c>
       <c r="C581">
-        <v>0.379317654312117</v>
+        <v>-1.3537215817748001</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>562</v>
+        <v>93</v>
       </c>
       <c r="B582">
-        <v>0.64119426276611302</v>
+        <v>-5.90133862528898E-2</v>
       </c>
       <c r="C582">
-        <v>-1.57797262354165E-2</v>
+        <v>1.4745991751789001E-2</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>563</v>
+        <v>94</v>
       </c>
       <c r="B583">
-        <v>-0.250394977135795</v>
+        <v>0.65531875037195897</v>
       </c>
       <c r="C583">
-        <v>0.43006259979216699</v>
+        <v>-0.29769862412022202</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="B584">
-        <v>-0.20722293734786101</v>
+        <v>0.42655046044814798</v>
       </c>
       <c r="C584">
-        <v>0.40269996091938898</v>
+        <v>-0.69283388519696698</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>565</v>
+        <v>95</v>
       </c>
       <c r="B585">
-        <v>0.67114037411881</v>
+        <v>-1.4527740986013</v>
       </c>
       <c r="C585">
-        <v>-0.34887736006478998</v>
+        <v>-0.69159793497278299</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>566</v>
+        <v>96</v>
       </c>
       <c r="B586">
-        <v>0.77296929056755603</v>
+        <v>-1.1860050704098599</v>
       </c>
       <c r="C586">
-        <v>-0.17577466171043801</v>
+        <v>-1.2973119420559101</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="B587">
-        <v>6.9200252834661705E-2</v>
+        <v>-0.47291772259965098</v>
       </c>
       <c r="C587">
-        <v>0.35290317771734098</v>
+        <v>0.11296429055660299</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>268</v>
+        <v>98</v>
       </c>
       <c r="B588">
-        <v>-6.6170665988569799E-2</v>
+        <v>-1.1708405408383999</v>
       </c>
       <c r="C588">
-        <v>0.55130919168019799</v>
+        <v>-1.3222998023189401</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="B589">
-        <v>-0.141169067844367</v>
+        <v>4.9089905282595103E-2</v>
       </c>
       <c r="C589">
-        <v>0.47719108687691297</v>
+        <v>0.52605347953366699</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="B590">
-        <v>0.72118567932714805</v>
+        <v>-1.03772340868916</v>
       </c>
       <c r="C590">
-        <v>-0.37882358467896099</v>
+        <v>-3.5417686777287502E-2</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="B591">
-        <v>0.78330987568246502</v>
+        <v>-1.2735983225665599</v>
       </c>
       <c r="C591">
-        <v>-0.46189971944914898</v>
+        <v>0.18190033526805999</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="B592">
-        <v>-0.331998906063177</v>
+        <v>-0.408824161559106</v>
       </c>
       <c r="C592">
-        <v>0.526352809604822</v>
+        <v>-0.16000874893005901</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="B593">
-        <v>-0.11212300201990801</v>
+        <v>-1.15645961806272</v>
       </c>
       <c r="C593">
-        <v>0.448994077699021</v>
+        <v>-0.86009608244846403</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="B594">
-        <v>-0.174365956437015</v>
+        <v>0.64158807917013305</v>
       </c>
       <c r="C594">
-        <v>-4.03364646055238E-2</v>
+        <v>-0.26787526074747597</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="B595">
-        <v>-0.64921537627120396</v>
+        <v>0.160963433269147</v>
       </c>
       <c r="C595">
-        <v>-0.46484572273671598</v>
+        <v>0.35972468955993098</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>272</v>
+        <v>102</v>
       </c>
       <c r="B596">
-        <v>0.10550509118005801</v>
+        <v>0.69336773691883702</v>
       </c>
       <c r="C596">
-        <v>0.10921635308802299</v>
+        <v>-0.39749170038683401</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>571</v>
+        <v>103</v>
       </c>
       <c r="B597">
-        <v>-1.0190129468725799</v>
+        <v>-0.11331993784303</v>
       </c>
       <c r="C597">
-        <v>-0.42258328959042801</v>
+        <v>0.436402782469546</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>273</v>
+        <v>656</v>
       </c>
       <c r="B598">
-        <v>-0.29506234335138298</v>
+        <v>-4.7144783509839097E-2</v>
       </c>
       <c r="C598">
-        <v>-2.1414646102129401E-2</v>
+        <v>-1.8301038842261901</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="B599">
-        <v>0.112534411576519</v>
+        <v>-0.297112957753147</v>
       </c>
       <c r="C599">
-        <v>0.680742242361834</v>
+        <v>0.72003897424150298</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>573</v>
+        <v>104</v>
       </c>
       <c r="B600">
-        <v>-0.37598687717936002</v>
+        <v>-1.1727770624493301</v>
       </c>
       <c r="C600">
-        <v>0.180641435663047</v>
+        <v>-1.39023002551668</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>574</v>
+        <v>105</v>
       </c>
       <c r="B601">
-        <v>0.48063006344467402</v>
+        <v>-0.13295726221649301</v>
       </c>
       <c r="C601">
-        <v>0.21568159294560299</v>
+        <v>4.4613047598032599E-2</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>575</v>
+        <v>106</v>
       </c>
       <c r="B602">
-        <v>0.38029605373340603</v>
+        <v>-0.49789195380810602</v>
       </c>
       <c r="C602">
-        <v>-0.357558500626801</v>
+        <v>9.0532891918262207E-2</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>576</v>
+        <v>107</v>
       </c>
       <c r="B603">
-        <v>-0.340311007981066</v>
+        <v>0.391751039290408</v>
       </c>
       <c r="C603">
-        <v>-7.8834262155072096E-2</v>
+        <v>0.25261910494338602</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>274</v>
+        <v>596</v>
       </c>
       <c r="B604">
-        <v>-0.66660853650699903</v>
+        <v>-0.28093583235144098</v>
       </c>
       <c r="C604">
-        <v>-3.5642299577084299E-2</v>
+        <v>0.56539062168271303</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="B605">
-        <v>-0.25516403321694298</v>
+        <v>-0.35490715912799697</v>
       </c>
       <c r="C605">
-        <v>0.209438444616173</v>
+        <v>0.26810802524135402</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="B606">
-        <v>0.81790816879064099</v>
+        <v>-0.46114648363177002</v>
       </c>
       <c r="C606">
-        <v>-0.264302946531905</v>
+        <v>0.31899626444525803</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="B607">
-        <v>-1.5194962871009601</v>
+        <v>-1.5992075314724501</v>
       </c>
       <c r="C607">
-        <v>-0.72078418881470396</v>
+        <v>-1.9834039759392099E-2</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B608">
-        <v>0.58715664031593595</v>
+        <v>0.69576198446517401</v>
       </c>
       <c r="C608">
-        <v>-0.40237720821376599</v>
+        <v>-0.43884661709398898</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>581</v>
+        <v>657</v>
       </c>
       <c r="B609">
-        <v>-0.55420685342887299</v>
+        <v>-1.0360125548667101</v>
       </c>
       <c r="C609">
-        <v>0.22787879505674799</v>
+        <v>0.106773614099248</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>275</v>
+        <v>601</v>
       </c>
       <c r="B610">
-        <v>0.68090617761763905</v>
+        <v>-1.2116526003210299</v>
       </c>
       <c r="C610">
-        <v>-0.29175341017262502</v>
+        <v>-1.13161298634854</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="B611">
-        <v>-1.1571708376659999</v>
+        <v>-1.1093719914759901</v>
       </c>
       <c r="C611">
-        <v>-1.30829018875201</v>
+        <v>-1.7292295115340499</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="B612">
-        <v>1.34753867218946E-2</v>
+        <v>-0.57530160541771302</v>
       </c>
       <c r="C612">
-        <v>0.70497703336375905</v>
+        <v>0.50246933378430603</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="B613">
-        <v>2.5175689801801598E-2</v>
+        <v>-1.1874621246702901</v>
       </c>
       <c r="C613">
-        <v>0.46361730692477399</v>
+        <v>-1.1968853164837301</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>278</v>
+        <v>603</v>
       </c>
       <c r="B614">
-        <v>-0.27584372458908402</v>
+        <v>-1.1403539294426099</v>
       </c>
       <c r="C614">
-        <v>0.36953792537100599</v>
+        <v>-1.4527916466508699</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>583</v>
+        <v>110</v>
       </c>
       <c r="B615">
-        <v>-0.42265217226024399</v>
+        <v>-1.1623062887570601</v>
       </c>
       <c r="C615">
-        <v>-0.191453619658603</v>
+        <v>-1.4122861490534</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>584</v>
+        <v>111</v>
       </c>
       <c r="B616">
-        <v>-0.30486511306880099</v>
+        <v>5.20740114919837E-2</v>
       </c>
       <c r="C616">
-        <v>3.2776430293160498E-2</v>
+        <v>0.310701790649974</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>585</v>
+        <v>112</v>
       </c>
       <c r="B617">
-        <v>-0.48022322182121602</v>
+        <v>4.4374281234797301E-2</v>
       </c>
       <c r="C617">
-        <v>0.42883366051893101</v>
+        <v>0.416891306863166</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>586</v>
+        <v>113</v>
       </c>
       <c r="B618">
-        <v>0.55557777024325306</v>
+        <v>0.69208439686148004</v>
       </c>
       <c r="C618">
-        <v>-0.37476343288123898</v>
+        <v>-0.452111991700751</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>279</v>
+        <v>604</v>
       </c>
       <c r="B619">
-        <v>-0.326152796817053</v>
+        <v>-0.25524914473349503</v>
       </c>
       <c r="C619">
-        <v>0.20297915457228799</v>
+        <v>0.381202896204347</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>587</v>
+        <v>114</v>
       </c>
       <c r="B620">
-        <v>0.65158838824199705</v>
+        <v>-0.74252075751759194</v>
       </c>
       <c r="C620">
-        <v>-0.131549015962138</v>
+        <v>-0.66804595867256</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>280</v>
+        <v>605</v>
       </c>
       <c r="B621">
-        <v>-1.14266051889704</v>
+        <v>-0.25378417287411598</v>
       </c>
       <c r="C621">
-        <v>0.20878041114092699</v>
+        <v>0.440869201352801</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="B622">
-        <v>0.65240547514548397</v>
+        <v>0.75542703764677299</v>
       </c>
       <c r="C622">
-        <v>-0.24939038123245799</v>
+        <v>-0.61094130771663202</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>281</v>
+        <v>658</v>
       </c>
       <c r="B623">
-        <v>0.12912161790693399</v>
+        <v>-8.3516048577480503E-2</v>
       </c>
       <c r="C623">
-        <v>-0.223151031561719</v>
+        <v>-1.7095247786444501</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>589</v>
+        <v>115</v>
       </c>
       <c r="B624">
-        <v>-0.21781504149734801</v>
+        <v>-0.700644848448298</v>
       </c>
       <c r="C624">
-        <v>1.2198217372244899</v>
+        <v>-9.5388551490347404E-2</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>282</v>
+        <v>607</v>
       </c>
       <c r="B625">
-        <v>0.64968329223486998</v>
+        <v>-0.44028141764092399</v>
       </c>
       <c r="C625">
-        <v>-0.19421677104617699</v>
+        <v>0.236517632750224</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>590</v>
+        <v>116</v>
       </c>
       <c r="B626">
-        <v>0.82508188080481004</v>
+        <v>-0.23589965441874999</v>
       </c>
       <c r="C626">
-        <v>-0.42562342875034798</v>
+        <v>-8.9766228233822097E-3</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>283</v>
+        <v>608</v>
       </c>
       <c r="B627">
-        <v>-0.46037015035942003</v>
+        <v>-1.0482606741878</v>
       </c>
       <c r="C627">
-        <v>0.16712207980701599</v>
+        <v>-1.5235775960073099</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>591</v>
+        <v>117</v>
       </c>
       <c r="B628">
-        <v>0.71824192727974501</v>
+        <v>-1.4356197859509801</v>
       </c>
       <c r="C628">
-        <v>1.01352879683804E-2</v>
+        <v>-0.68757291479168103</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>284</v>
+        <v>118</v>
       </c>
       <c r="B629">
-        <v>0.66394729770633198</v>
+        <v>-0.43069255208818502</v>
       </c>
       <c r="C629">
-        <v>-0.258828219693166</v>
+        <v>0.12931396545913301</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>285</v>
+        <v>609</v>
       </c>
       <c r="B630">
-        <v>4.5437618655068499E-2</v>
+        <v>-0.49549758692664703</v>
       </c>
       <c r="C630">
-        <v>0.32129093339582598</v>
+        <v>0.45992318545773803</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>286</v>
+        <v>610</v>
       </c>
       <c r="B631">
-        <v>0.72632697122257095</v>
+        <v>-1.15814437045622</v>
       </c>
       <c r="C631">
-        <v>-0.39352033600761299</v>
+        <v>-1.38200420370414</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="B632">
-        <v>0.23785832631887099</v>
+        <v>0.46279452986244202</v>
       </c>
       <c r="C632">
-        <v>-0.272356171616494</v>
+        <v>-0.706910527119744</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>287</v>
+        <v>612</v>
       </c>
       <c r="B633">
-        <v>-0.73931787870162602</v>
+        <v>0.20123886416700901</v>
       </c>
       <c r="C633">
-        <v>0.10315161926201501</v>
+        <v>0.54696841289542197</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>593</v>
+        <v>659</v>
       </c>
       <c r="B634">
-        <v>-0.32149317506441599</v>
+        <v>-1.1217031484992499</v>
       </c>
       <c r="C634">
-        <v>-0.17316740889483301</v>
+        <v>-1.48071804486904</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>594</v>
+        <v>119</v>
       </c>
       <c r="B635">
-        <v>-0.89889429188122205</v>
+        <v>-1.1185188032409199</v>
       </c>
       <c r="C635">
-        <v>7.8240224128400995E-2</v>
+        <v>0.19420406503283899</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="B636">
-        <v>0.55318338353815699</v>
+        <v>0.68996696912645605</v>
       </c>
       <c r="C636">
-        <v>0.45105131456338299</v>
+        <v>-0.25814512919020499</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>642</v>
-      </c>
-      <c r="B637" t="s">
-        <v>639</v>
-      </c>
-      <c r="C637" t="s">
-        <v>639</v>
+        <v>121</v>
+      </c>
+      <c r="B637">
+        <v>0.204383669370272</v>
+      </c>
+      <c r="C637">
+        <v>7.6565395959690793E-2</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>596</v>
+        <v>122</v>
       </c>
       <c r="B638">
-        <v>0.74229293245958405</v>
+        <v>-0.14688452350418599</v>
       </c>
       <c r="C638">
-        <v>-0.60187962850024201</v>
+        <v>0.26543311776379602</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>597</v>
+        <v>123</v>
       </c>
       <c r="B639">
-        <v>-1.36195564587555</v>
+        <v>-0.27200334487574301</v>
       </c>
       <c r="C639">
-        <v>-0.80060198432378704</v>
+        <v>0.120724570435067</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>643</v>
+        <v>124</v>
       </c>
       <c r="B640">
-        <v>-0.296015751784037</v>
+        <v>-1.2581174008749099E-2</v>
       </c>
       <c r="C640">
-        <v>0.121785733919552</v>
+        <v>3.3225300085588397E-2</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>644</v>
+        <v>125</v>
       </c>
       <c r="B641">
-        <v>-0.61379557914357297</v>
+        <v>0.73468261065019902</v>
       </c>
       <c r="C641">
-        <v>0.132763928279371</v>
+        <v>-0.41344144443803399</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>645</v>
+        <v>613</v>
       </c>
       <c r="B642">
-        <v>1.426495023619E-2</v>
+        <v>0.59897739915673398</v>
       </c>
       <c r="C642">
-        <v>0.66359279253067505</v>
+        <v>-0.43635566060200698</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="B643">
-        <v>-1.18675894201167</v>
+        <v>0.89000614952137402</v>
       </c>
       <c r="C643">
-        <v>-1.12975491049054</v>
+        <v>-0.24216815421941201</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="B644">
-        <v>-0.18570785632358999</v>
+        <v>-1.7506623372877199</v>
       </c>
       <c r="C644">
-        <v>0.59878095492736205</v>
+        <v>-0.12570859243025101</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>648</v>
+        <v>126</v>
       </c>
       <c r="B645">
-        <v>0.72430160441428104</v>
+        <v>-1.3563635736759601</v>
       </c>
       <c r="C645">
-        <v>0.31263366590430902</v>
+        <v>-0.65953984015276901</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>649</v>
+        <v>615</v>
       </c>
       <c r="B646">
-        <v>-0.45903943310253997</v>
+        <v>-1.0482606741878</v>
       </c>
       <c r="C646">
-        <v>0.19197741774268801</v>
+        <v>-1.5235775960073099</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>650</v>
+        <v>616</v>
       </c>
       <c r="B647">
-        <v>7.3369532102355098E-3</v>
+        <v>-0.19991535887115999</v>
       </c>
       <c r="C647">
-        <v>0.56795595507111496</v>
+        <v>-0.151681061994001</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>651</v>
+        <v>617</v>
       </c>
       <c r="B648">
-        <v>0.77864566864387896</v>
+        <v>-1.32728537490281</v>
       </c>
       <c r="C648">
-        <v>1.32703693032186E-2</v>
+        <v>-0.87128157180993304</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>652</v>
+        <v>127</v>
       </c>
       <c r="B649">
-        <v>-1.5214604674087699</v>
+        <v>-0.37533004098302097</v>
       </c>
       <c r="C649">
-        <v>-0.82295233577918103</v>
+        <v>0.101964686537519</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>128</v>
+      </c>
+      <c r="B650">
+        <v>-0.56591212899068699</v>
+      </c>
+      <c r="C650">
+        <v>0.14415870828664901</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>129</v>
+      </c>
+      <c r="B651">
+        <v>0.136143868226557</v>
+      </c>
+      <c r="C651">
+        <v>0.51719589619621098</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>618</v>
+      </c>
+      <c r="B652">
+        <v>-0.43104158129116699</v>
+      </c>
+      <c r="C652">
+        <v>-0.19855631656286499</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>661</v>
+      </c>
+      <c r="B653">
+        <v>0.32545336014321302</v>
+      </c>
+      <c r="C653">
+        <v>1.3597113762378501</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>619</v>
+      </c>
+      <c r="B654">
+        <v>-0.72520671222222399</v>
+      </c>
+      <c r="C654">
+        <v>-0.37462081481210902</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>620</v>
+      </c>
+      <c r="B655">
+        <v>-0.48112781956858303</v>
+      </c>
+      <c r="C655">
+        <v>0.62662226633774598</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>621</v>
+      </c>
+      <c r="B656">
+        <v>-1.4004934811448999</v>
+      </c>
+      <c r="C656">
+        <v>-0.78856068405762303</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>130</v>
+      </c>
+      <c r="B657">
+        <v>-0.50137693585284704</v>
+      </c>
+      <c r="C657">
+        <v>0.12962230824193899</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>622</v>
+      </c>
+      <c r="B658">
+        <v>-1.23210057645153</v>
+      </c>
+      <c r="C658">
+        <v>-0.64118282398485305</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>623</v>
+      </c>
+      <c r="B659">
+        <v>-1.11207621955779</v>
+      </c>
+      <c r="C659">
+        <v>0.5480535887279</v>
       </c>
     </row>
   </sheetData>

--- a/nmds_results.xlsx
+++ b/nmds_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drake\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8F2923-292B-4B88-AE16-4C9B8D04D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F10045-0D9B-4C5B-80FB-585746336DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3072" yWindow="3072" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card_WA_Scores" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="695">
   <si>
     <t>NMDS1</t>
   </si>
@@ -1385,9 +1385,6 @@
     <t>sb_Hallowed Moonlight</t>
   </si>
   <si>
-    <t>sb_Hanweir Garrison</t>
-  </si>
-  <si>
     <t>sb_Harmonic Sliver</t>
   </si>
   <si>
@@ -1985,9 +1982,6 @@
     <t>sb_The Filigree Sylex</t>
   </si>
   <si>
-    <t>sb_Timeless Lotus</t>
-  </si>
-  <si>
     <t>sb_Timely Reinforcements</t>
   </si>
   <si>
@@ -1997,9 +1991,6 @@
     <t>Tatyova, Benthic Druid</t>
   </si>
   <si>
-    <t>Timeless Lotus</t>
-  </si>
-  <si>
     <t>Unknown Card</t>
   </si>
   <si>
@@ -2007,6 +1998,114 @@
   </si>
   <si>
     <t>Wrenn and Six</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Cavalier of Thorns</t>
+  </si>
+  <si>
+    <t>Emeritus of Abundance</t>
+  </si>
+  <si>
+    <t>Ephemerate</t>
+  </si>
+  <si>
+    <t>Gitaxian Probe</t>
+  </si>
+  <si>
+    <t>Leyline of the Guildpact</t>
+  </si>
+  <si>
+    <t>Nykthos, Shrine to Nyx</t>
+  </si>
+  <si>
+    <t>Petrified Hamlet</t>
+  </si>
+  <si>
+    <t>Scavenger Grounds</t>
+  </si>
+  <si>
+    <t>See Beyond</t>
+  </si>
+  <si>
+    <t>Summon the Pack</t>
+  </si>
+  <si>
+    <t>Sylvan Safekeeper</t>
+  </si>
+  <si>
+    <t>The Mycotyrant</t>
+  </si>
+  <si>
+    <t>Up the Beanstalk</t>
+  </si>
+  <si>
+    <t>Zuran Orb</t>
+  </si>
+  <si>
+    <t>sb_Abstergo Entertainment</t>
+  </si>
+  <si>
+    <t>sb_Avengers Disassembled</t>
+  </si>
+  <si>
+    <t>sb_Call the Skybreaker</t>
+  </si>
+  <si>
+    <t>sb_Captain Marvel, Earth's Protector</t>
+  </si>
+  <si>
+    <t>sb_Erode</t>
+  </si>
+  <si>
+    <t>sb_Eternal Witness</t>
+  </si>
+  <si>
+    <t>sb_Guerrilla Gorilla</t>
+  </si>
+  <si>
+    <t>sb_Hanweir Battlements</t>
+  </si>
+  <si>
+    <t>sb_High Noon</t>
+  </si>
+  <si>
+    <t>sb_Krosan Grip</t>
+  </si>
+  <si>
+    <t>sb_MjÃ¶lnir, Hammer of Thor</t>
+  </si>
+  <si>
+    <t>sb_Monastery Siege</t>
+  </si>
+  <si>
+    <t>sb_Oracle of Mul Daya</t>
+  </si>
+  <si>
+    <t>sb_Rampaging Baloths</t>
+  </si>
+  <si>
+    <t>sb_Scavenger Grounds</t>
+  </si>
+  <si>
+    <t>sb_Sixth Sense</t>
+  </si>
+  <si>
+    <t>sb_The Wandering Rescuer</t>
+  </si>
+  <si>
+    <t>sb_Unknown Card</t>
+  </si>
+  <si>
+    <t>sb_Voice of Victory</t>
+  </si>
+  <si>
+    <t>sb_Welding Jar</t>
+  </si>
+  <si>
+    <t>sb_Wolverine, Fierce Fighter</t>
   </si>
 </sst>
 </file>
@@ -2071,12 +2170,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2382,12 +2480,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C659"/>
+  <dimension ref="A1:C691"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2401,10 +2502,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>-0.54795730448574298</v>
+        <v>-0.49994402099422902</v>
       </c>
       <c r="C2">
-        <v>-4.4505557754270099E-2</v>
+        <v>7.7670540663729706E-2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2412,10 +2513,10 @@
         <v>289</v>
       </c>
       <c r="B3">
-        <v>-1.2227447630778701</v>
+        <v>-1.2097665047220301</v>
       </c>
       <c r="C3">
-        <v>-0.41250362859502199</v>
+        <v>-6.32636645554812E-2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2423,10 +2524,10 @@
         <v>290</v>
       </c>
       <c r="B4">
-        <v>-9.3390628191401495E-2</v>
+        <v>-3.4922247071445603E-2</v>
       </c>
       <c r="C4">
-        <v>0.100780369626835</v>
+        <v>0.10696959652367299</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2434,10 +2535,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>-1.1798593778245501</v>
+        <v>-1.1943078959137701</v>
       </c>
       <c r="C5">
-        <v>-0.57427394448800595</v>
+        <v>-0.18666129215188901</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2445,10 +2546,10 @@
         <v>291</v>
       </c>
       <c r="B6">
-        <v>-1.1705422559471499</v>
+        <v>-1.22261782133285</v>
       </c>
       <c r="C6">
-        <v>-1.0474082206172399</v>
+        <v>-0.69034279397904497</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2456,10 +2557,10 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>0.67962330757760603</v>
+        <v>0.650388045704409</v>
       </c>
       <c r="C7">
-        <v>-0.22429536600315</v>
+        <v>-0.21786005035367201</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2467,10 +2568,10 @@
         <v>292</v>
       </c>
       <c r="B8">
-        <v>-0.31427705693803198</v>
+        <v>-0.15428094140433399</v>
       </c>
       <c r="C8">
-        <v>0.25933642997069101</v>
+        <v>0.20208554596044401</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2478,10 +2579,10 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>-2.62013609681693E-4</v>
-      </c>
-      <c r="C9" s="2">
-        <v>-6.2856667939504294E-5</v>
+        <v>-3.6464901190345097E-4</v>
+      </c>
+      <c r="C9">
+        <v>-2.2526694096608701E-4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2489,10 +2590,10 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>-1.2911279145047101</v>
+        <v>-1.29367014505343</v>
       </c>
       <c r="C10">
-        <v>-0.64396214829475895</v>
+        <v>-0.47449135165633399</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2500,10 +2601,10 @@
         <v>293</v>
       </c>
       <c r="B11">
-        <v>-1.15814437045622</v>
+        <v>-1.25057759449405</v>
       </c>
       <c r="C11">
-        <v>-1.38200420370414</v>
+        <v>-1.04933521376224</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2511,10 +2612,10 @@
         <v>7</v>
       </c>
       <c r="B12">
-        <v>0.18145658161949799</v>
+        <v>0.22480072393671699</v>
       </c>
       <c r="C12">
-        <v>7.4349377073404305E-2</v>
+        <v>6.9069057049762003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2522,10 +2623,10 @@
         <v>294</v>
       </c>
       <c r="B13">
-        <v>-0.43922381166353303</v>
+        <v>-0.38340264051602502</v>
       </c>
       <c r="C13">
-        <v>0.26604923811979603</v>
+        <v>0.26853400760650098</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2533,10 +2634,10 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-0.74127642988256104</v>
+        <v>-0.75600512363387795</v>
       </c>
       <c r="C14">
-        <v>-0.10429373568405401</v>
+        <v>-3.6529448566888299E-2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2544,10 +2645,10 @@
         <v>9</v>
       </c>
       <c r="B15">
-        <v>0.82159749478000199</v>
+        <v>0.76350822959897502</v>
       </c>
       <c r="C15">
-        <v>-0.545020052646494</v>
+        <v>-0.51450155649988605</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2555,10 +2656,10 @@
         <v>295</v>
       </c>
       <c r="B16">
-        <v>-1.32571722281697</v>
+        <v>-1.3439727688443699</v>
       </c>
       <c r="C16">
-        <v>-0.86869562680928403</v>
+        <v>-0.50744730295882001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2566,10 +2667,10 @@
         <v>10</v>
       </c>
       <c r="B17">
-        <v>-0.82893595314801305</v>
+        <v>-0.76596607443542697</v>
       </c>
       <c r="C17">
-        <v>9.0532559255122394E-3</v>
+        <v>0.195056763522441</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2577,10 +2678,10 @@
         <v>296</v>
       </c>
       <c r="B18">
-        <v>-1.5558742656072999</v>
+        <v>-1.5673506953502101</v>
       </c>
       <c r="C18">
-        <v>-0.79710738587186303</v>
+        <v>-0.33880569983488401</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2588,10 +2689,10 @@
         <v>297</v>
       </c>
       <c r="B19">
-        <v>0.91703736877801401</v>
+        <v>0.870321643969028</v>
       </c>
       <c r="C19">
-        <v>-0.16037233259369099</v>
+        <v>-0.14932142398488599</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2599,10 +2700,10 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>-0.58404613915678405</v>
+        <v>-0.54902167935085899</v>
       </c>
       <c r="C20">
-        <v>1.19840178664178E-2</v>
+        <v>0.132921707381319</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2610,10 +2711,10 @@
         <v>298</v>
       </c>
       <c r="B21">
-        <v>-5.2727824915371098E-2</v>
+        <v>6.1775611717393803E-3</v>
       </c>
       <c r="C21">
-        <v>0.66093556478443605</v>
+        <v>0.63812258081718698</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2621,10 +2722,10 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>-0.47232260987368102</v>
+        <v>-0.50129333259524</v>
       </c>
       <c r="C22">
-        <v>0.11409700383763501</v>
+        <v>0.101357923220195</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -2632,10 +2733,10 @@
         <v>13</v>
       </c>
       <c r="B23">
-        <v>0.28244019739046</v>
+        <v>0.31316547507364201</v>
       </c>
       <c r="C23">
-        <v>3.7045564750473901E-2</v>
+        <v>2.5427274414825E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2643,10 +2744,10 @@
         <v>14</v>
       </c>
       <c r="B24">
-        <v>-1.28238249266341</v>
+        <v>-1.30302181236323</v>
       </c>
       <c r="C24">
-        <v>-0.82029249789292702</v>
+        <v>-0.45392483752129198</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2654,10 +2755,10 @@
         <v>15</v>
       </c>
       <c r="B25">
-        <v>-0.95631391525490295</v>
+        <v>-0.87495097827781199</v>
       </c>
       <c r="C25">
-        <v>9.1734045071359196E-3</v>
+        <v>0.23332445699493701</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -2665,10 +2766,10 @@
         <v>299</v>
       </c>
       <c r="B26">
-        <v>0.81089090081215798</v>
+        <v>0.75984752003823897</v>
       </c>
       <c r="C26">
-        <v>-0.19798549535286999</v>
+        <v>-0.16610166235416701</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -2676,10 +2777,10 @@
         <v>300</v>
       </c>
       <c r="B27">
-        <v>0.46319844525097698</v>
+        <v>0.43755024646601598</v>
       </c>
       <c r="C27">
-        <v>-0.275261137255574</v>
+        <v>-0.30811953233553802</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2687,10 +2788,10 @@
         <v>301</v>
       </c>
       <c r="B28">
-        <v>0.56304811386000098</v>
+        <v>0.59147789460976397</v>
       </c>
       <c r="C28">
-        <v>0.30338749427351602</v>
+        <v>0.196838767250026</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2698,10 +2799,10 @@
         <v>302</v>
       </c>
       <c r="B29">
-        <v>0.23725977286532601</v>
+        <v>0.242171737931095</v>
       </c>
       <c r="C29">
-        <v>0.43700746213689501</v>
+        <v>0.37138726319015403</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2709,21 +2810,21 @@
         <v>303</v>
       </c>
       <c r="B30">
-        <v>-0.368595904736637</v>
+        <v>-0.34146687576884699</v>
       </c>
       <c r="C30">
-        <v>-0.110841914467255</v>
+        <v>1.8600804376609902E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>638</v>
-      </c>
-      <c r="B31">
-        <v>-0.21054867790587101</v>
-      </c>
-      <c r="C31">
-        <v>-1.6086135631854299</v>
+        <v>637</v>
+      </c>
+      <c r="B31" t="s">
+        <v>659</v>
+      </c>
+      <c r="C31" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -2731,6907 +2832,7259 @@
         <v>16</v>
       </c>
       <c r="B32">
-        <v>-0.63416731336384602</v>
+        <v>-0.55894986795994195</v>
       </c>
       <c r="C32">
-        <v>0.12778416177166499</v>
+        <v>0.275673660200566</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33">
-        <v>-0.45812741551098102</v>
-      </c>
-      <c r="C33">
-        <v>6.8335956822971097E-2</v>
+        <v>660</v>
+      </c>
+      <c r="B33" t="s">
+        <v>659</v>
+      </c>
+      <c r="C33" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="B34">
-        <v>0.69036181651784101</v>
+        <v>-0.46794028054542203</v>
       </c>
       <c r="C34">
-        <v>0.125303410986357</v>
+        <v>9.31634369490804E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>639</v>
+        <v>304</v>
       </c>
       <c r="B35">
-        <v>-0.63061725517887701</v>
+        <v>0.71172614089175201</v>
       </c>
       <c r="C35">
-        <v>0.112669721531703</v>
+        <v>-0.19580791826923799</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>638</v>
       </c>
       <c r="B36">
-        <v>-1.1281323913636001</v>
+        <v>-0.56108354159812901</v>
       </c>
       <c r="C36">
-        <v>-1.4771734764404401</v>
+        <v>0.33393989845376199</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37">
-        <v>-1.49102160138823</v>
+        <v>-1.27513452655085</v>
       </c>
       <c r="C37">
-        <v>-0.69004522128538803</v>
+        <v>-1.0506228733949601</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>305</v>
+        <v>19</v>
       </c>
       <c r="B38">
-        <v>0.87240998711598805</v>
+        <v>-1.48964557917263</v>
       </c>
       <c r="C38">
-        <v>-0.21391702931518899</v>
+        <v>-0.27516455012041502</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="B39">
-        <v>0.47989141900356902</v>
+        <v>0.81744993890067896</v>
       </c>
       <c r="C39">
-        <v>0.202520864190602</v>
+        <v>-0.20494918020393699</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="B40">
-        <v>-1.1339648919530401</v>
+        <v>0.46760861562139999</v>
       </c>
       <c r="C40">
-        <v>-1.4616957133019199</v>
+        <v>0.203762094469746</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>640</v>
+        <v>306</v>
       </c>
       <c r="B41">
-        <v>-1.17673414679627</v>
+        <v>-1.23374758169757</v>
       </c>
       <c r="C41">
-        <v>-1.3118698236556601</v>
+        <v>-1.1400912538200101</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>639</v>
       </c>
       <c r="B42">
-        <v>-1.0595772365488201</v>
+        <v>-1.25809578849633</v>
       </c>
       <c r="C42">
-        <v>-0.45369187342749601</v>
+        <v>-0.96846930428606204</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B43">
-        <v>0.48457731609441201</v>
+        <v>-1.07483409768523</v>
       </c>
       <c r="C43">
-        <v>-0.15174170677728099</v>
+        <v>-0.234178082326126</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B44">
-        <v>2.5789422481912901E-2</v>
+        <v>0.49402936853950402</v>
       </c>
       <c r="C44">
-        <v>0.20741827628147599</v>
+        <v>-0.15447145880549801</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>307</v>
+        <v>23</v>
       </c>
       <c r="B45">
-        <v>-1.7506623372877199</v>
+        <v>0.106449010596834</v>
       </c>
       <c r="C45">
-        <v>-0.12570859243025101</v>
+        <v>0.174947975928579</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B46">
-        <v>-1.33417703002549</v>
+        <v>-1.65024264604958</v>
       </c>
       <c r="C46">
-        <v>0.31027553890465998</v>
+        <v>0.292049639249641</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B47">
-        <v>3.2336873762708399E-2</v>
+        <v>-1.1865220532340901</v>
       </c>
       <c r="C47">
-        <v>0.59287462921490897</v>
+        <v>0.64116295637285803</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>309</v>
       </c>
       <c r="B48">
-        <v>-0.88394721455119296</v>
+        <v>7.3196076285590203E-2</v>
       </c>
       <c r="C48">
-        <v>-0.25584050830076199</v>
+        <v>0.56013859105368802</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>310</v>
+        <v>24</v>
       </c>
       <c r="B49">
-        <v>-1.2484636793289301</v>
+        <v>-0.85783737382498604</v>
       </c>
       <c r="C49">
-        <v>-1.2282960484744401</v>
+        <v>-2.0770448179424399E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B50">
-        <v>-0.43922381166353303</v>
+        <v>-1.2235734215852301</v>
       </c>
       <c r="C50">
-        <v>0.26604923811979603</v>
+        <v>-0.77111520749463702</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B51">
-        <v>-0.36389465619947298</v>
+        <v>-0.38340264051602602</v>
       </c>
       <c r="C51">
-        <v>0.68001645074077499</v>
+        <v>0.26853400760650098</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
       <c r="B52">
-        <v>0.67918341844109797</v>
+        <v>-0.29807038821376602</v>
       </c>
       <c r="C52">
-        <v>-0.37041068580747299</v>
+        <v>0.68132207356603003</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53">
-        <v>-0.18460785251113099</v>
+        <v>0.66780355325418905</v>
       </c>
       <c r="C53">
-        <v>0.302374236218029</v>
+        <v>-0.34793945855719399</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54">
-        <v>0.66522563664900702</v>
+        <v>-0.13435693918963901</v>
       </c>
       <c r="C54">
-        <v>-0.249427047449998</v>
+        <v>0.331968396458868</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B55">
-        <v>-0.99708560649898503</v>
+        <v>0.64015365174670102</v>
       </c>
       <c r="C55">
-        <v>0.29990854407626699</v>
+        <v>-0.24172223479048099</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>313</v>
+        <v>28</v>
       </c>
       <c r="B56">
-        <v>-0.94482996119407503</v>
+        <v>-0.89443053671431705</v>
       </c>
       <c r="C56">
-        <v>0.42458482886300603</v>
+        <v>0.48687007015314099</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>313</v>
       </c>
       <c r="B57">
-        <v>-4.4733399388336703E-3</v>
+        <v>-0.79836027744883198</v>
       </c>
       <c r="C57">
-        <v>0.63840202054102002</v>
+        <v>0.66094644620589504</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58">
-        <v>-0.63171733363475502</v>
+        <v>5.2842444391104901E-2</v>
       </c>
       <c r="C58">
-        <v>0.43326674368642798</v>
+        <v>0.62703339946903802</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>314</v>
+        <v>30</v>
       </c>
       <c r="B59">
-        <v>-0.46095999001375998</v>
+        <v>-0.46655705041407097</v>
       </c>
       <c r="C59">
-        <v>0.32498047400773</v>
+        <v>0.49757411030973397</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>314</v>
       </c>
       <c r="B60">
-        <v>-0.61439267703785205</v>
+        <v>-0.38921922093420103</v>
       </c>
       <c r="C60">
-        <v>-0.82025316022516104</v>
+        <v>0.36442834200440299</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>32</v>
+        <v>661</v>
       </c>
       <c r="B61">
-        <v>-0.10152125376331</v>
+        <v>0.78824975728001301</v>
       </c>
       <c r="C61">
-        <v>3.54140832003947E-2</v>
+        <v>-0.28600065277780401</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B62">
-        <v>-1.29169757518269</v>
+        <v>-0.67711401476354804</v>
       </c>
       <c r="C62">
-        <v>-0.40642454942478701</v>
+        <v>8.43379771657084E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>315</v>
+        <v>32</v>
       </c>
       <c r="B63">
-        <v>-0.124737558557325</v>
+        <v>-3.2640840209479799E-2</v>
       </c>
       <c r="C63">
-        <v>-1.10234026220201</v>
+        <v>5.8980438379467197E-2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64">
-        <v>7.7447282863773103E-4</v>
+        <v>-1.2556330101914499</v>
       </c>
       <c r="C64">
-        <v>0.257525375793006</v>
+        <v>-0.141043225066834</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>662</v>
       </c>
       <c r="B65">
-        <v>7.1050922180831602E-2</v>
+        <v>-0.33572192701902198</v>
       </c>
       <c r="C65">
-        <v>6.3270169110827099E-2</v>
+        <v>0.46628039004737398</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>641</v>
+        <v>315</v>
       </c>
       <c r="B66">
-        <v>0.32545336014321302</v>
+        <v>-0.28302646916678498</v>
       </c>
       <c r="C66">
-        <v>1.3597113762378501</v>
+        <v>0.65329989070217498</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>316</v>
+        <v>34</v>
       </c>
       <c r="B67">
-        <v>0.59792292065795205</v>
+        <v>2.9577749415158699E-2</v>
       </c>
       <c r="C67">
-        <v>-0.64222948711846595</v>
+        <v>0.272691914500508</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>317</v>
+        <v>35</v>
       </c>
       <c r="B68">
-        <v>0.51887691455988005</v>
+        <v>8.2098287671732495E-2</v>
       </c>
       <c r="C68">
-        <v>0.203980755982827</v>
+        <v>0.114328843361025</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>318</v>
+        <v>640</v>
       </c>
       <c r="B69">
-        <v>-1.3689237494570199</v>
+        <v>0.34534996394138501</v>
       </c>
       <c r="C69">
-        <v>-0.57147931415463005</v>
+        <v>1.30300288088899</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>36</v>
+        <v>316</v>
       </c>
       <c r="B70">
-        <v>-1.2538901365416</v>
+        <v>0.59061209247698299</v>
       </c>
       <c r="C70">
-        <v>-8.6321024445540295E-2</v>
+        <v>-0.385155136858011</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>317</v>
       </c>
       <c r="B71">
-        <v>-0.91828071381936804</v>
+        <v>0.50037574257585404</v>
       </c>
       <c r="C71">
-        <v>0.29411500285618503</v>
+        <v>0.18631122084072399</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B72">
-        <v>-1.46609667588786</v>
+        <v>-1.3608946386324099</v>
       </c>
       <c r="C72">
-        <v>-8.8209787798195993E-2</v>
+        <v>-0.15546417225894599</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>320</v>
+        <v>36</v>
       </c>
       <c r="B73">
-        <v>-1.14596688416571</v>
+        <v>-1.17012708912946</v>
       </c>
       <c r="C73">
-        <v>0.83504339676693695</v>
+        <v>0.22302208540972601</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>321</v>
+        <v>37</v>
       </c>
       <c r="B74">
-        <v>0.85172899653860001</v>
+        <v>-0.81160088451036705</v>
       </c>
       <c r="C74">
-        <v>-0.46934656397511298</v>
+        <v>0.48151597185001999</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B75">
-        <v>-0.27175441379619297</v>
+        <v>-1.3754799438212</v>
       </c>
       <c r="C75">
-        <v>0.398662139711218</v>
+        <v>0.253569257950646</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="B76">
-        <v>6.0434049706554801E-3</v>
+        <v>-0.95882183192327197</v>
       </c>
       <c r="C76">
-        <v>2.7077381921135599E-2</v>
+        <v>1.0292624705431299</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>321</v>
       </c>
       <c r="B77">
-        <v>0.631889912417824</v>
+        <v>0.78848297479330798</v>
       </c>
       <c r="C77">
-        <v>-0.52602835389442004</v>
+        <v>-0.45775476661069697</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B78">
-        <v>0.80231042906636996</v>
+        <v>-0.21471803998790001</v>
       </c>
       <c r="C78">
-        <v>-0.49229218302083599</v>
+        <v>0.34904903183582497</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="B79">
-        <v>-1.20085867285184</v>
+        <v>4.9863688959670097E-2</v>
       </c>
       <c r="C79">
-        <v>-1.34089385989829</v>
+        <v>3.94501707392092E-2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B80">
-        <v>-0.26768654866645802</v>
+        <v>0.56489036707808704</v>
       </c>
       <c r="C80">
-        <v>0.26394234387647503</v>
+        <v>-0.447959431513269</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>41</v>
+        <v>323</v>
       </c>
       <c r="B81">
-        <v>-1.2976680456035099</v>
+        <v>0.730790158802336</v>
       </c>
       <c r="C81">
-        <v>-0.75539696072587104</v>
+        <v>-0.48614967688452798</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B82">
-        <v>-0.239120945290444</v>
+        <v>-1.33286136604385</v>
       </c>
       <c r="C82">
-        <v>0.43354420519961401</v>
+        <v>-0.94375488850262201</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B83">
-        <v>-0.99116440570269004</v>
+        <v>-0.15837989526827201</v>
       </c>
       <c r="C83">
-        <v>-0.309178857487027</v>
+        <v>0.25814190753689298</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>326</v>
+        <v>41</v>
       </c>
       <c r="B84">
-        <v>0.76410996602947701</v>
+        <v>-1.2984441129566899</v>
       </c>
       <c r="C84">
-        <v>0.52029225243392696</v>
+        <v>-0.58567128314504902</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B85">
-        <v>-1.13913722852627</v>
+        <v>-0.177174854959853</v>
       </c>
       <c r="C85">
-        <v>-1.44580919403583</v>
+        <v>0.43779046476817801</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B86">
-        <v>-0.22575237486296601</v>
+        <v>-0.98791038712910295</v>
       </c>
       <c r="C86">
-        <v>0.166533453019306</v>
+        <v>-0.13424314484536301</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>44</v>
+        <v>326</v>
       </c>
       <c r="B87">
-        <v>-0.36181665847668798</v>
+        <v>0.73051812959250595</v>
       </c>
       <c r="C87">
-        <v>-1.34906339577773</v>
+        <v>0.497445238524096</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>328</v>
+        <v>663</v>
       </c>
       <c r="B88">
-        <v>-1.4454434513155301</v>
+        <v>-1.3261930071077901</v>
       </c>
       <c r="C88">
-        <v>-0.59766642290536598</v>
+        <v>-1.08916376797845</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>327</v>
       </c>
       <c r="B89">
-        <v>-0.30647432814519199</v>
+        <v>-1.28756658212858</v>
       </c>
       <c r="C89">
-        <v>0.69985714172661395</v>
+        <v>-1.05602273589976</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B90">
-        <v>0.69447327611171195</v>
+        <v>-0.26657224394417101</v>
       </c>
       <c r="C90">
-        <v>-0.36683013992436297</v>
+        <v>0.13589054378707499</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B91">
-        <v>-0.31099025429299498</v>
+        <v>-1.16230414227967</v>
       </c>
       <c r="C91">
-        <v>0.218209911578884</v>
+        <v>-2.98043103648124E-2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="B92">
-        <v>-1.3635684082771899</v>
+        <v>-1.4309983426930999</v>
       </c>
       <c r="C92">
-        <v>-0.72146530514913298</v>
+        <v>-0.190644924351346</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B93">
-        <v>0.139786865578195</v>
+        <v>-0.21096601373950299</v>
       </c>
       <c r="C93">
-        <v>-4.7852518617257499E-2</v>
+        <v>0.693322687987731</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>329</v>
+        <v>46</v>
       </c>
       <c r="B94">
-        <v>-0.415220345748474</v>
+        <v>0.66274601020926305</v>
       </c>
       <c r="C94">
-        <v>-8.4305903261313597E-2</v>
+        <v>-0.34310955825640099</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>642</v>
+        <v>47</v>
       </c>
       <c r="B95">
-        <v>-1.10755746664707</v>
+        <v>-0.24763545988708399</v>
       </c>
       <c r="C95">
-        <v>0.81979381716452104</v>
+        <v>0.285930564981209</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B96">
-        <v>0.419317134907288</v>
+        <v>-1.371675186304</v>
       </c>
       <c r="C96">
-        <v>-9.5105258800695994E-2</v>
+        <v>-0.32163758397529701</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>330</v>
+        <v>49</v>
       </c>
       <c r="B97">
-        <v>-0.32697675291896799</v>
+        <v>0.113496559369568</v>
       </c>
       <c r="C97">
-        <v>0.21025375882164099</v>
+        <v>-6.0875556641356902E-2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>51</v>
+        <v>329</v>
       </c>
       <c r="B98">
-        <v>0.51144444454451499</v>
+        <v>-0.61889530492415401</v>
       </c>
       <c r="C98">
-        <v>4.05171688601998E-2</v>
+        <v>-0.233785774089389</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>52</v>
+        <v>641</v>
       </c>
       <c r="B99">
-        <v>-1.2032266987787801</v>
+        <v>-0.91627770118819896</v>
       </c>
       <c r="C99">
-        <v>-1.2438737467630401</v>
+        <v>1.01432799194129</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>331</v>
+        <v>50</v>
       </c>
       <c r="B100">
-        <v>-1.5215120429278099</v>
+        <v>0.43825674779127</v>
       </c>
       <c r="C100">
-        <v>-0.69207012526915501</v>
+        <v>-8.5840710571990303E-2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="B101">
-        <v>-1.33048539028307</v>
+        <v>-0.26859622096143898</v>
       </c>
       <c r="C101">
-        <v>-0.68103186672040095</v>
+        <v>0.22126188529642399</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B102">
-        <v>-0.33355852131782499</v>
+        <v>0.49496003654107201</v>
       </c>
       <c r="C102">
-        <v>0.16721881995154</v>
+        <v>5.2228686708113703E-2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B103">
-        <v>0.72636433264274802</v>
+        <v>-1.27822061888344</v>
       </c>
       <c r="C103">
-        <v>-0.44758852167441499</v>
+        <v>-0.96374536155041202</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B104">
-        <v>-1.1492306733369499</v>
+        <v>-1.5201112408600299</v>
       </c>
       <c r="C104">
-        <v>-1.46200144251016</v>
+        <v>-0.25196413307259402</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="B105">
-        <v>0.78398407914324597</v>
+        <v>-1.3313978332845999</v>
       </c>
       <c r="C105">
-        <v>-0.47048952024153501</v>
+        <v>-0.29769107199518402</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>334</v>
+        <v>54</v>
       </c>
       <c r="B106">
-        <v>-0.241862921839512</v>
+        <v>-0.27364861942157298</v>
       </c>
       <c r="C106">
-        <v>1.1535087211774999</v>
+        <v>0.21997158384736601</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B107">
-        <v>-0.81196856112804305</v>
+        <v>0.66919592384314597</v>
       </c>
       <c r="C107">
-        <v>-0.56659836525534502</v>
+        <v>-0.42543175400494099</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B108">
-        <v>-1.17024477012565</v>
+        <v>-1.26073668581775</v>
       </c>
       <c r="C108">
-        <v>-0.66517852333097605</v>
+        <v>-1.08812533662988</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B109">
-        <v>2.4556307124956399E-2</v>
+        <v>0.73193904114489305</v>
       </c>
       <c r="C109">
-        <v>0.75953275469164705</v>
+        <v>-0.43738797365091397</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B110">
-        <v>-0.28842278181180198</v>
+        <v>-0.13792923684307701</v>
       </c>
       <c r="C110">
-        <v>0.13045814458625901</v>
+        <v>1.1326597436760699</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B111">
-        <v>-1.3248779580108501</v>
+        <v>-0.97220200660554501</v>
       </c>
       <c r="C111">
-        <v>-0.74776480817633495</v>
+        <v>-0.561818801728724</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="B112">
-        <v>-0.77105050868838598</v>
+        <v>-1.1695029983315399</v>
       </c>
       <c r="C112">
-        <v>-3.2799665760710098E-2</v>
+        <v>-0.35222641838501101</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>59</v>
+        <v>336</v>
       </c>
       <c r="B113">
-        <v>0.25847057100859</v>
+        <v>7.0311921874817898E-2</v>
       </c>
       <c r="C113">
-        <v>0.27853653510397602</v>
+        <v>0.72700063072250498</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>60</v>
+        <v>337</v>
       </c>
       <c r="B114">
-        <v>-0.92320847423207097</v>
+        <v>-0.24685645679694801</v>
       </c>
       <c r="C114">
-        <v>0.120588638500064</v>
+        <v>0.14567668751951801</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B115">
-        <v>-1.00516803538207</v>
+        <v>-1.3117846759838101</v>
       </c>
       <c r="C115">
-        <v>-0.490814100019213</v>
+        <v>-0.62622646004715798</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>338</v>
+        <v>58</v>
       </c>
       <c r="B116">
-        <v>-1.20661506740142</v>
+        <v>-0.73518287464390097</v>
       </c>
       <c r="C116">
-        <v>0.38698591685711597</v>
+        <v>0.203950950493478</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>339</v>
+        <v>59</v>
       </c>
       <c r="B117">
-        <v>-0.241862921839512</v>
+        <v>0.22452235549146601</v>
       </c>
       <c r="C117">
-        <v>1.1535087211774999</v>
+        <v>0.25328278041671998</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B118">
-        <v>-0.37169221561257598</v>
+        <v>-0.82366351992675102</v>
       </c>
       <c r="C118">
-        <v>6.37991900466435E-2</v>
+        <v>0.62720011640206197</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B119">
-        <v>1.3447237727188401E-2</v>
+        <v>-1.08189769974345</v>
       </c>
       <c r="C119">
-        <v>0.431658986767329</v>
+        <v>-0.43782298188275298</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>64</v>
+        <v>338</v>
       </c>
       <c r="B120">
-        <v>-1.1927798570119399</v>
+        <v>-1.06132371378559</v>
       </c>
       <c r="C120">
-        <v>-0.99777847390614405</v>
+        <v>0.66110733943332001</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B121">
-        <v>-1.20267219683201</v>
+        <v>-0.13792923684307701</v>
       </c>
       <c r="C121">
-        <v>-0.86258258109234298</v>
+        <v>1.1326597436760699</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B122">
-        <v>0.65658651209783403</v>
+        <v>-0.25342769739034399</v>
       </c>
       <c r="C122">
-        <v>-0.23630968791036699</v>
+        <v>0.133797356130857</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>66</v>
+        <v>664</v>
       </c>
       <c r="B123">
-        <v>0.671684402136702</v>
+        <v>0.20751003950164501</v>
       </c>
       <c r="C123">
-        <v>-6.0178768458360402E-3</v>
+        <v>-1.1088279380352699</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>341</v>
+        <v>63</v>
       </c>
       <c r="B124">
-        <v>0.71772666379824501</v>
+        <v>4.8754570333099802E-2</v>
       </c>
       <c r="C124">
-        <v>-2.2877657448826E-2</v>
+        <v>0.42630803049152799</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B125">
-        <v>0.10410658545384199</v>
+        <v>-1.2352591319436099</v>
       </c>
       <c r="C125">
-        <v>0.55512654858300203</v>
+        <v>-0.64926178856862704</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>68</v>
+        <v>340</v>
       </c>
       <c r="B126">
-        <v>0.69332733585344297</v>
+        <v>-1.24432826899878</v>
       </c>
       <c r="C126">
-        <v>-0.316376794990951</v>
+        <v>-0.46733542636973202</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B127">
-        <v>-1.1855017963799299</v>
+        <v>0.62308645336430402</v>
       </c>
       <c r="C127">
-        <v>-1.3555214573345</v>
+        <v>-0.21301422634487699</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>342</v>
+        <v>66</v>
       </c>
       <c r="B128">
-        <v>-1.37238643869498</v>
+        <v>0.63330734471399297</v>
       </c>
       <c r="C128">
-        <v>-0.31506949936364698</v>
+        <v>2.8641781467555801E-3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B129">
-        <v>-1.1611707952338</v>
+        <v>0.67448967277483196</v>
       </c>
       <c r="C129">
-        <v>-1.4475761353072201</v>
+        <v>-2.03484026085522E-2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>344</v>
+        <v>67</v>
       </c>
       <c r="B130">
-        <v>-0.17813349544843299</v>
+        <v>0.191669541812519</v>
       </c>
       <c r="C130">
-        <v>0.60179429308550403</v>
+        <v>0.46873353228303799</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B131">
-        <v>0.538946199237614</v>
+        <v>0.67326968500497697</v>
       </c>
       <c r="C131">
-        <v>-8.5420450700207207E-2</v>
+        <v>-0.305761860638463</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B132">
-        <v>-0.16810906092796701</v>
+        <v>-1.2732361557858001</v>
       </c>
       <c r="C132">
-        <v>6.6290920145107804E-2</v>
+        <v>-1.0006827301869201</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B133">
-        <v>-0.389596368749837</v>
+        <v>-1.31385579822344</v>
       </c>
       <c r="C133">
-        <v>0.223866333579753</v>
+        <v>1.21871263689279E-2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B134">
-        <v>0.37584534494991401</v>
+        <v>-1.2576998537015001</v>
       </c>
       <c r="C134">
-        <v>0.73879446284113104</v>
+        <v>-1.1206101685377801</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B135">
-        <v>-0.32467947652288998</v>
+        <v>0.37291606346169098</v>
       </c>
       <c r="C135">
-        <v>-0.158985570783301</v>
+        <v>0.13238411191295299</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>348</v>
+        <v>70</v>
       </c>
       <c r="B136">
-        <v>0.83008884405870198</v>
+        <v>0.53787330889930096</v>
       </c>
       <c r="C136">
-        <v>-0.48233966817334401</v>
+        <v>-9.9809935302360597E-2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>349</v>
+        <v>71</v>
       </c>
       <c r="B137">
-        <v>-1.4656809837940199</v>
+        <v>-0.125631729336772</v>
       </c>
       <c r="C137">
-        <v>-0.73621428927426302</v>
+        <v>0.14386269904554999</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B138">
-        <v>-1.3153124123322499</v>
+        <v>-0.35043630851758201</v>
       </c>
       <c r="C138">
-        <v>-0.71791998967641801</v>
+        <v>0.28314727114732802</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>72</v>
+        <v>346</v>
       </c>
       <c r="B139">
-        <v>-1.3069912736164</v>
+        <v>0.38053079219879998</v>
       </c>
       <c r="C139">
-        <v>-0.29872986036332599</v>
+        <v>0.67760736743403904</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="B140">
-        <v>-1.3123643995943</v>
+        <v>-0.27789593412340402</v>
       </c>
       <c r="C140">
-        <v>-0.12499886707720199</v>
+        <v>-8.1789281311300505E-2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>74</v>
+        <v>348</v>
       </c>
       <c r="B141">
-        <v>-1.1020491862183599</v>
+        <v>0.70883225970207697</v>
       </c>
       <c r="C141">
-        <v>-1.3912686667679199</v>
+        <v>-0.36139215857853202</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>351</v>
+        <v>665</v>
       </c>
       <c r="B142">
-        <v>-0.81070757992446196</v>
+        <v>0.20751003950164501</v>
       </c>
       <c r="C142">
-        <v>0.112825100558957</v>
+        <v>-1.1088279380352699</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="B143">
-        <v>0.19490061976901699</v>
+        <v>-1.47366926962893</v>
       </c>
       <c r="C143">
-        <v>0.44070211623387101</v>
+        <v>-0.28197316784215998</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>76</v>
+        <v>350</v>
       </c>
       <c r="B144">
-        <v>0.41852885259957201</v>
+        <v>-1.3164946184808399</v>
       </c>
       <c r="C144">
-        <v>-1.05310330994643E-2</v>
+        <v>-0.35966564091673697</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>352</v>
+        <v>72</v>
       </c>
       <c r="B145">
-        <v>-0.88195817341472105</v>
+        <v>-1.24693649654172</v>
       </c>
       <c r="C145">
-        <v>0.36627345689847801</v>
+        <v>3.1561226113135301E-3</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B146">
-        <v>-1.22490935893471</v>
+        <v>-1.22885767382563</v>
       </c>
       <c r="C146">
-        <v>-0.64769357556664797</v>
+        <v>0.19144030270915299</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>353</v>
+        <v>74</v>
       </c>
       <c r="B147">
-        <v>-1.52481096076749</v>
+        <v>-1.1954443237363801</v>
       </c>
       <c r="C147">
-        <v>-0.71799337442219902</v>
+        <v>-1.0863544753869401</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B148">
-        <v>0.304439647869235</v>
+        <v>-0.73852352643307295</v>
       </c>
       <c r="C148">
-        <v>0.78911586640916997</v>
+        <v>0.286228561025407</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B149">
-        <v>-0.38105233162080798</v>
+        <v>0.222501276280827</v>
       </c>
       <c r="C149">
-        <v>0.47901551663828201</v>
+        <v>0.40611029178883201</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B150">
-        <v>0.77540316643683505</v>
+        <v>0.43519852316452301</v>
       </c>
       <c r="C150">
-        <v>-0.26447353402993001</v>
+        <v>-2.8338105643542399E-2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B151">
-        <v>-0.173325736864576</v>
+        <v>-0.79384377968111797</v>
       </c>
       <c r="C151">
-        <v>-0.80748217145617696</v>
+        <v>0.56635017237546303</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="B152">
-        <v>-0.48574823156758201</v>
+        <v>-1.2410594056244599</v>
       </c>
       <c r="C152">
-        <v>0.62568494502663896</v>
+        <v>-0.56918339901063897</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B153">
-        <v>0.83151445905639698</v>
+        <v>-1.52882143252891</v>
       </c>
       <c r="C153">
-        <v>-5.4672525418671999E-2</v>
+        <v>-0.25899789301892201</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="B154">
-        <v>0.30855667222142902</v>
+        <v>0.32354378471650902</v>
       </c>
       <c r="C154">
-        <v>-0.26087793749849802</v>
+        <v>0.73646926873809004</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>81</v>
+        <v>666</v>
       </c>
       <c r="B155">
-        <v>-1.26260033494039</v>
+        <v>-3.2581403732515599E-2</v>
       </c>
       <c r="C155">
-        <v>-0.128655635828404</v>
+        <v>7.1102179397439402E-2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B156">
-        <v>-3.2838157200440099E-3</v>
+        <v>-0.31384888661794602</v>
       </c>
       <c r="C156">
-        <v>2.9697966297482E-3</v>
+        <v>0.46559558862482098</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="B157">
-        <v>-0.59650044847842998</v>
+        <v>0.70549647342203103</v>
       </c>
       <c r="C157">
-        <v>0.52979851339039596</v>
+        <v>-0.268665838076732</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B158">
-        <v>-0.21094046019293999</v>
+        <v>-0.33128501256436299</v>
       </c>
       <c r="C158">
-        <v>0.33431832533776301</v>
+        <v>0.142635784496811</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B159">
-        <v>-1.13489524498618</v>
+        <v>-0.38685499111300498</v>
       </c>
       <c r="C159">
-        <v>-1.3414140496121001</v>
+        <v>0.65825288496673695</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="B160">
-        <v>-0.70898145765131804</v>
+        <v>0.78405336135935899</v>
       </c>
       <c r="C160">
-        <v>-3.9033436764029601E-2</v>
+        <v>-5.0191910570196702E-2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>361</v>
+        <v>80</v>
       </c>
       <c r="B161">
-        <v>-1.54323009071141</v>
+        <v>0.30049360213979898</v>
       </c>
       <c r="C161">
-        <v>-0.64974526536699295</v>
+        <v>-0.23959447783500101</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="B162">
-        <v>0.82642051549512197</v>
+        <v>-1.2029353109271399</v>
       </c>
       <c r="C162">
-        <v>0.47035465517457598</v>
+        <v>0.178403127472406</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="B163">
-        <v>-0.77843567335808195</v>
+        <v>-1.0974458306011899E-2</v>
       </c>
       <c r="C163">
-        <v>-0.354663489953088</v>
+        <v>4.7678712617336702E-3</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="B164">
-        <v>-1.3345663641619301</v>
+        <v>-0.50890073875730901</v>
       </c>
       <c r="C164">
-        <v>-0.44294978305800498</v>
+        <v>0.55476143679965595</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B165">
-        <v>-1.1388724545002</v>
+        <v>-0.156035751479428</v>
       </c>
       <c r="C165">
-        <v>-1.3854558988077501</v>
+        <v>0.337222208076218</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>85</v>
+        <v>360</v>
       </c>
       <c r="B166">
-        <v>-0.49435802373345999</v>
+        <v>-1.2140360693597501</v>
       </c>
       <c r="C166">
-        <v>5.0285132286288198E-2</v>
+        <v>-1.02071949557065</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="B167">
-        <v>-0.184611034320142</v>
+        <v>-0.71235185400590495</v>
       </c>
       <c r="C167">
-        <v>0.25537979985132903</v>
+        <v>3.5283222665380198E-2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B168">
-        <v>0.15732879934628299</v>
+        <v>-1.5327733176938001</v>
       </c>
       <c r="C168">
-        <v>0.44103642184148101</v>
+        <v>-0.20977863838315799</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B169">
-        <v>-1.2274701745388601</v>
+        <v>0.79272109798545098</v>
       </c>
       <c r="C169">
-        <v>-1.29607052094177</v>
+        <v>0.43546458309863501</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>86</v>
+        <v>363</v>
       </c>
       <c r="B170">
-        <v>-0.60261141263598905</v>
+        <v>-0.76000406251362296</v>
       </c>
       <c r="C170">
-        <v>0.138052041572746</v>
+        <v>-0.15822581921783199</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B171">
-        <v>-1.2854973329069601</v>
+        <v>-1.2956126368435401</v>
       </c>
       <c r="C171">
-        <v>-0.31485697944373198</v>
+        <v>-0.10912225284233799</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>131</v>
+        <v>364</v>
       </c>
       <c r="B172">
-        <v>-1.2821224230663999</v>
+        <v>-1.2322413790476201</v>
       </c>
       <c r="C172">
-        <v>-0.70806883247497399</v>
+        <v>-1.05375225796028</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>368</v>
+        <v>85</v>
       </c>
       <c r="B173">
-        <v>-1.1138058441897001</v>
+        <v>-0.420922385722096</v>
       </c>
       <c r="C173">
-        <v>0.60752698287451801</v>
+        <v>0.14044002480911699</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B174">
-        <v>-0.75676490257291795</v>
+        <v>-0.149342349853336</v>
       </c>
       <c r="C174">
-        <v>-0.32542543224575399</v>
+        <v>0.24466641420240701</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B175">
-        <v>-1.1347014976329</v>
+        <v>0.18133931426525901</v>
       </c>
       <c r="C175">
-        <v>-1.4824560209962701</v>
+        <v>0.44142568371537599</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B176">
-        <v>0.71134513012937595</v>
+        <v>-1.31140528634317</v>
       </c>
       <c r="C176">
-        <v>-0.43139419196567302</v>
+        <v>-0.94325979111608804</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="B177">
-        <v>-1.1633367389184099</v>
+        <v>-0.53168584075066305</v>
       </c>
       <c r="C177">
-        <v>0.164675661523672</v>
+        <v>0.24512570132959299</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="B178">
-        <v>0.69594592850758896</v>
+        <v>-1.23564806439004</v>
       </c>
       <c r="C178">
-        <v>-0.17311790549967099</v>
+        <v>1.1626762306950001E-2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>372</v>
+        <v>88</v>
       </c>
       <c r="B179">
-        <v>-1.1439744079033101</v>
+        <v>0.64975087829158895</v>
       </c>
       <c r="C179">
-        <v>-1.55480728039691</v>
+        <v>-0.30423427512802897</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>134</v>
+        <v>667</v>
       </c>
       <c r="B180">
-        <v>0.71517005917559195</v>
+        <v>0.747169102513353</v>
       </c>
       <c r="C180">
-        <v>-0.19021091399551901</v>
+        <v>-0.47371259116694803</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>373</v>
+        <v>584</v>
       </c>
       <c r="B181">
-        <v>-0.15614126495146999</v>
+        <v>-1.1840508832749199</v>
       </c>
       <c r="C181">
-        <v>0.165321598980846</v>
+        <v>-1.08549215892603</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>135</v>
+        <v>668</v>
       </c>
       <c r="B182">
-        <v>-0.2410772253465</v>
+        <v>-1.27047368374627</v>
       </c>
       <c r="C182">
-        <v>0.212243980218146</v>
+        <v>-1.4050042945749801</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>374</v>
+        <v>585</v>
       </c>
       <c r="B183">
-        <v>-1.1115569750931</v>
+        <v>-1.0155473395700301</v>
       </c>
       <c r="C183">
-        <v>0.412703921454945</v>
+        <v>1.04917510867893</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>375</v>
+        <v>89</v>
       </c>
       <c r="B184">
-        <v>-1.23070294182527</v>
+        <v>-0.31277396363480497</v>
       </c>
       <c r="C184">
-        <v>-0.81158145712504404</v>
+        <v>0.19123984273208899</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>376</v>
+        <v>90</v>
       </c>
       <c r="B185">
-        <v>-0.70778518775508503</v>
+        <v>-1.2759141260808899</v>
       </c>
       <c r="C185">
-        <v>-0.78713925142050301</v>
+        <v>-0.99010178699204698</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>377</v>
+        <v>586</v>
       </c>
       <c r="B186">
-        <v>-0.64554880082663002</v>
+        <v>-0.22725223332076999</v>
       </c>
       <c r="C186">
-        <v>0.292198657973398</v>
+        <v>0.39606626710096399</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="B187">
-        <v>-0.65389817357506597</v>
+        <v>0.63542514164350306</v>
       </c>
       <c r="C187">
-        <v>8.6006263272129693E-2</v>
+        <v>-0.196622457048335</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>378</v>
+        <v>587</v>
       </c>
       <c r="B188">
-        <v>-0.14421437305374701</v>
+        <v>0.42553363131342897</v>
       </c>
       <c r="C188">
-        <v>-0.159634621391639</v>
+        <v>0.71566783652142096</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>379</v>
+        <v>588</v>
       </c>
       <c r="B189">
-        <v>-1.3922404772811201</v>
+        <v>-0.22038288059362901</v>
       </c>
       <c r="C189">
-        <v>-0.201499722591164</v>
+        <v>0.454642995363645</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>92</v>
       </c>
       <c r="B190">
-        <v>0.57117945264360404</v>
+        <v>-1.2594510152720799</v>
       </c>
       <c r="C190">
-        <v>0.19273584000006799</v>
+        <v>-1.0331008941705999</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>93</v>
       </c>
       <c r="B191">
-        <v>-0.279042734024599</v>
+        <v>-5.96100041982092E-2</v>
       </c>
       <c r="C191">
-        <v>0.493185894129611</v>
+        <v>1.56348090487709E-2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>382</v>
+        <v>94</v>
       </c>
       <c r="B192">
-        <v>-1.10755746664707</v>
+        <v>0.62459219005964595</v>
       </c>
       <c r="C192">
-        <v>0.81979381716452104</v>
+        <v>-0.29002083857068001</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>383</v>
+        <v>589</v>
       </c>
       <c r="B193">
-        <v>-0.32608132406960599</v>
+        <v>0.68610844087088196</v>
       </c>
       <c r="C193">
-        <v>0.26219771823534999</v>
+        <v>-0.50138321570059796</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>384</v>
+        <v>95</v>
       </c>
       <c r="B194">
-        <v>0.25153316012995203</v>
+        <v>-1.46214251509754</v>
       </c>
       <c r="C194">
-        <v>0.14022778757841101</v>
+        <v>-0.28103484053606698</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>96</v>
       </c>
       <c r="B195">
-        <v>0.63032785085635701</v>
+        <v>-1.2756960084575999</v>
       </c>
       <c r="C195">
-        <v>-0.35133644565341399</v>
+        <v>-0.98374934244722401</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>386</v>
+        <v>97</v>
       </c>
       <c r="B196">
-        <v>-0.191884510648961</v>
+        <v>-0.50203089949378099</v>
       </c>
       <c r="C196">
-        <v>0.52013605143618502</v>
+        <v>0.100387735445109</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>387</v>
+        <v>98</v>
       </c>
       <c r="B197">
-        <v>-1.17350656383609</v>
+        <v>-1.2657437937835201</v>
       </c>
       <c r="C197">
-        <v>-0.48833016148002401</v>
+        <v>-0.99541619064361497</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>388</v>
+        <v>590</v>
       </c>
       <c r="B198">
-        <v>0.82201121223061402</v>
+        <v>8.6973249802213395E-2</v>
       </c>
       <c r="C198">
-        <v>-0.15125710729859099</v>
+        <v>0.50885568478633403</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="B199">
-        <v>-0.63321269464673902</v>
+        <v>-0.93361529659381404</v>
       </c>
       <c r="C199">
-        <v>6.6427962411678407E-2</v>
+        <v>0.21647077149629601</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>389</v>
+        <v>591</v>
       </c>
       <c r="B200">
-        <v>0.36140410811352502</v>
+        <v>-1.16256094862715</v>
       </c>
       <c r="C200">
-        <v>0.35963804045898801</v>
+        <v>0.41500608761919799</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>390</v>
+        <v>592</v>
       </c>
       <c r="B201">
-        <v>-0.80864712283866202</v>
+        <v>-0.36787551296737497</v>
       </c>
       <c r="C201">
-        <v>-0.141754737518895</v>
+        <v>-3.9864252037009801E-2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>391</v>
+        <v>593</v>
       </c>
       <c r="B202">
-        <v>-0.54332364269181899</v>
+        <v>-1.1670662712548301</v>
       </c>
       <c r="C202">
-        <v>8.9485551869431607E-2</v>
+        <v>-0.58918972868356201</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>392</v>
+        <v>100</v>
       </c>
       <c r="B203">
-        <v>0.69662392892796898</v>
+        <v>0.62044313807156704</v>
       </c>
       <c r="C203">
-        <v>-0.33721515792183698</v>
+        <v>-0.25809010150114797</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="B204">
-        <v>-0.58231659897626098</v>
+        <v>0.205987139450311</v>
       </c>
       <c r="C204">
-        <v>4.3411479012494897E-2</v>
+        <v>0.30668203806185401</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="B205">
-        <v>0.24316294840542901</v>
+        <v>0.64901200619988997</v>
       </c>
       <c r="C205">
-        <v>2.2230182605233501E-3</v>
+        <v>-0.36325328772993798</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="B206">
-        <v>3.5068713823416801E-2</v>
+        <v>-6.6389842025134996E-2</v>
       </c>
       <c r="C206">
-        <v>0.50871706471997102</v>
+        <v>0.50777127903929997</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>393</v>
-      </c>
-      <c r="B207">
-        <v>-1.3205338839246601</v>
-      </c>
-      <c r="C207">
-        <v>-0.88323765790888797</v>
+        <v>654</v>
+      </c>
+      <c r="B207" t="s">
+        <v>659</v>
+      </c>
+      <c r="C207" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>394</v>
+        <v>594</v>
       </c>
       <c r="B208">
-        <v>0.83502424535090702</v>
+        <v>-0.22989949543159399</v>
       </c>
       <c r="C208">
-        <v>-0.43428305046275301</v>
+        <v>0.71582072241099903</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>643</v>
+        <v>104</v>
       </c>
       <c r="B209">
-        <v>0.63540404736631395</v>
+        <v>-1.27611143616425</v>
       </c>
       <c r="C209">
-        <v>-0.53477139405182195</v>
+        <v>-1.01501418007707</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>395</v>
+        <v>669</v>
       </c>
       <c r="B210">
-        <v>-0.123709552257961</v>
+        <v>-1.74482128015309</v>
       </c>
       <c r="C210">
-        <v>0.90038058932477805</v>
+        <v>-0.283064773469548</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="B211">
-        <v>9.3494709271733104E-2</v>
+        <v>-0.13827359539100501</v>
       </c>
       <c r="C211">
-        <v>0.139535105969507</v>
+        <v>4.6520954499521601E-2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
       <c r="B212">
-        <v>-1.33417703002549</v>
+        <v>-0.52768189256278197</v>
       </c>
       <c r="C212">
-        <v>0.31027553890465998</v>
+        <v>7.9318116654576304E-2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>397</v>
+        <v>107</v>
       </c>
       <c r="B213">
-        <v>0.67467572459560698</v>
+        <v>0.35728211534290999</v>
       </c>
       <c r="C213">
-        <v>1.6317306003077001E-2</v>
+        <v>0.27212092415551498</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>398</v>
+        <v>595</v>
       </c>
       <c r="B214">
-        <v>0.53903383883945299</v>
+        <v>-0.223873072640313</v>
       </c>
       <c r="C214">
-        <v>-7.1770369069487305E-2</v>
+        <v>0.55648213884204201</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>399</v>
+        <v>596</v>
       </c>
       <c r="B215">
-        <v>-1.35780360516111</v>
+        <v>-0.28938223883325398</v>
       </c>
       <c r="C215">
-        <v>-0.74706887554690005</v>
+        <v>0.28285652831306402</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>400</v>
+        <v>670</v>
       </c>
       <c r="B216">
-        <v>-0.41282281077694999</v>
+        <v>0.64879154393291105</v>
       </c>
       <c r="C216">
-        <v>5.6054118736589498E-2</v>
+        <v>-0.35914460808721499</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>401</v>
+        <v>597</v>
       </c>
       <c r="B217">
-        <v>-1.1416370244107401</v>
+        <v>-0.384601350011268</v>
       </c>
       <c r="C217">
-        <v>-0.488226890337912</v>
+        <v>0.36818967063548702</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>142</v>
+        <v>598</v>
       </c>
       <c r="B218">
-        <v>0.24750695194668901</v>
+        <v>-1.492167200516</v>
       </c>
       <c r="C218">
-        <v>0.27308596079870601</v>
+        <v>0.35119173291355998</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>143</v>
+        <v>599</v>
       </c>
       <c r="B219">
-        <v>-0.231699052437214</v>
+        <v>0.64907166935278804</v>
       </c>
       <c r="C219">
-        <v>0.110367582240656</v>
+        <v>-0.39958990203647399</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>144</v>
+        <v>655</v>
       </c>
       <c r="B220">
-        <v>-0.60723053740796695</v>
+        <v>-0.93281227029191505</v>
       </c>
       <c r="C220">
-        <v>0.37426780669411303</v>
+        <v>0.37462435891031798</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>145</v>
+        <v>600</v>
       </c>
       <c r="B221">
-        <v>-0.53331578278642</v>
+        <v>-1.0414985189107699</v>
       </c>
       <c r="C221">
-        <v>-0.30247580215807601</v>
+        <v>-1.1364312074966201</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>146</v>
+        <v>601</v>
       </c>
       <c r="B222">
-        <v>-1.3613504695519001</v>
+        <v>-1.2339363730128501</v>
       </c>
       <c r="C222">
-        <v>-0.451231116620948</v>
+        <v>-1.41776199581864</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>402</v>
+        <v>108</v>
       </c>
       <c r="B223">
-        <v>6.18639515062104E-2</v>
+        <v>-0.45553382340724702</v>
       </c>
       <c r="C223">
-        <v>-0.22516926517576699</v>
+        <v>0.53501224014776105</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="B224">
-        <v>-0.41736764340961502</v>
+        <v>-1.26419190540461</v>
       </c>
       <c r="C224">
-        <v>-0.68118769443367999</v>
+        <v>-0.962934121644899</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>403</v>
+        <v>602</v>
       </c>
       <c r="B225">
-        <v>-1.2216217715278599</v>
+        <v>-1.2437956610725101</v>
       </c>
       <c r="C225">
-        <v>-1.3387585261753601</v>
+        <v>-1.11771011292022</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="B226">
-        <v>-0.21228258426504101</v>
+        <v>-1.2708888853276501</v>
       </c>
       <c r="C226">
-        <v>0.212452071503891</v>
+        <v>-1.03142453535276</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>404</v>
+        <v>111</v>
       </c>
       <c r="B227">
-        <v>-4.36927138077094E-2</v>
+        <v>0.12395710941742701</v>
       </c>
       <c r="C227">
-        <v>0.99396239326096203</v>
+        <v>0.26890164794146798</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="B228">
-        <v>-0.21054867790587101</v>
+        <v>0.43755024646601598</v>
       </c>
       <c r="C228">
-        <v>-1.6086135631854299</v>
+        <v>-0.30811953233553802</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="B229">
-        <v>0.657487271180212</v>
+        <v>7.5489953651712405E-2</v>
       </c>
       <c r="C229">
-        <v>-0.33276191789680398</v>
+        <v>0.40909789680751402</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>645</v>
+        <v>113</v>
       </c>
       <c r="B230">
-        <v>-0.15485742673669201</v>
+        <v>0.646662636793226</v>
       </c>
       <c r="C230">
-        <v>0.42746587125604601</v>
+        <v>-0.41891899799480298</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>150</v>
+        <v>603</v>
       </c>
       <c r="B231">
-        <v>0.60957084242070203</v>
+        <v>-0.94924129433737503</v>
       </c>
       <c r="C231">
-        <v>0.19993111272772199</v>
+        <v>-0.55980183768606995</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>405</v>
+        <v>114</v>
       </c>
       <c r="B232">
-        <v>0.77867598246647296</v>
+        <v>-0.70036015337161595</v>
       </c>
       <c r="C232">
-        <v>-0.27781469507972101</v>
+        <v>3.79830376925408E-2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>406</v>
+        <v>604</v>
       </c>
       <c r="B233">
-        <v>-0.25457427302824598</v>
+        <v>-0.188077161967903</v>
       </c>
       <c r="C233">
-        <v>9.1346499530438205E-2</v>
+        <v>0.44781780599564902</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>151</v>
+        <v>605</v>
       </c>
       <c r="B234">
-        <v>0.65440419276461803</v>
+        <v>0.67442812724886103</v>
       </c>
       <c r="C234">
-        <v>-0.28061728499962901</v>
+        <v>-0.59831291042237</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="B235">
-        <v>-1.49911202599159</v>
+        <v>-0.64804384395153702</v>
       </c>
       <c r="C235">
-        <v>-0.669706372773203</v>
+        <v>9.0552305420983706E-2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>408</v>
+        <v>606</v>
       </c>
       <c r="B236">
-        <v>-1.18869676104154</v>
+        <v>-0.37450480316436502</v>
       </c>
       <c r="C236">
-        <v>-0.73087356373974699</v>
+        <v>0.29439385839204801</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="B237">
-        <v>-0.97671403812673396</v>
+        <v>-0.258708985571515</v>
       </c>
       <c r="C237">
-        <v>-1.3231973341098799</v>
+        <v>-8.9913207742272801E-3</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>153</v>
+        <v>607</v>
       </c>
       <c r="B238">
-        <v>-1.3968525229156401</v>
+        <v>-1.2017387207697501</v>
       </c>
       <c r="C238">
-        <v>-0.49444304235303899</v>
+        <v>-1.1079695883479901</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>409</v>
+        <v>117</v>
       </c>
       <c r="B239">
-        <v>-0.50371020432584102</v>
+        <v>-1.4376505761337399</v>
       </c>
       <c r="C239">
-        <v>-9.3429931608359995E-2</v>
+        <v>-0.26898104670233403</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>410</v>
+        <v>118</v>
       </c>
       <c r="B240">
-        <v>-0.33880238567841398</v>
+        <v>-0.36700925898695003</v>
       </c>
       <c r="C240">
-        <v>0.18083130637700701</v>
+        <v>0.24038045920110199</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>411</v>
+        <v>608</v>
       </c>
       <c r="B241">
-        <v>1.5790537923511101E-2</v>
+        <v>-0.412379951779351</v>
       </c>
       <c r="C241">
-        <v>0.52234032769761296</v>
+        <v>0.48990176491189402</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>412</v>
+        <v>609</v>
       </c>
       <c r="B242">
-        <v>0.82112803363047704</v>
+        <v>-1.2563938192466499</v>
       </c>
       <c r="C242">
-        <v>-0.56154178900233398</v>
+        <v>-0.94670776568161696</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>154</v>
+        <v>610</v>
       </c>
       <c r="B243">
-        <v>0.18501647823171</v>
+        <v>0.41656341412575598</v>
       </c>
       <c r="C243">
-        <v>5.02262021485066E-2</v>
+        <v>-0.64774559292620804</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>155</v>
+        <v>611</v>
       </c>
       <c r="B244">
-        <v>-3.9225911197801701E-2</v>
+        <v>0.224947999931255</v>
       </c>
       <c r="C244">
-        <v>0.43465522574930099</v>
+        <v>0.53325752989712205</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>413</v>
+        <v>656</v>
       </c>
       <c r="B245">
-        <v>-1.20085867285184</v>
+        <v>-1.2716659299408</v>
       </c>
       <c r="C245">
-        <v>-1.34089385989829</v>
+        <v>-1.01796835707106</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>414</v>
-      </c>
-      <c r="B246">
-        <v>0.682361533808166</v>
-      </c>
-      <c r="C246">
-        <v>-0.46678136383902302</v>
+        <v>672</v>
+      </c>
+      <c r="B246" t="s">
+        <v>659</v>
+      </c>
+      <c r="C246" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>646</v>
+        <v>119</v>
       </c>
       <c r="B247">
-        <v>-0.45935124859391502</v>
+        <v>-1.0076633282890799</v>
       </c>
       <c r="C247">
-        <v>0.212377760649618</v>
+        <v>0.450906449433155</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>415</v>
+        <v>120</v>
       </c>
       <c r="B248">
-        <v>-0.18019900331931399</v>
+        <v>0.65398530983558401</v>
       </c>
       <c r="C248">
-        <v>0.12986163610043899</v>
+        <v>-0.24529602903902001</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>416</v>
+        <v>121</v>
       </c>
       <c r="B249">
-        <v>-0.241862921839512</v>
+        <v>0.24455685005043501</v>
       </c>
       <c r="C249">
-        <v>1.1535087211774999</v>
+        <v>6.7536637254334494E-2</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>647</v>
+        <v>122</v>
       </c>
       <c r="B250">
-        <v>-0.82016675877761203</v>
+        <v>-0.10108583749830199</v>
       </c>
       <c r="C250">
-        <v>0.19405452972870599</v>
+        <v>0.29813767986969503</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="B251">
-        <v>8.7085261855185905E-2</v>
+        <v>-0.2349881672845</v>
       </c>
       <c r="C251">
-        <v>0.37208167470214898</v>
+        <v>0.21647829993335299</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>417</v>
+        <v>124</v>
       </c>
       <c r="B252">
-        <v>-0.94815718272085503</v>
+        <v>-3.2703963957477197E-2</v>
       </c>
       <c r="C252">
-        <v>0.67821394404990198</v>
+        <v>3.4704513609443099E-2</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="B253">
-        <v>-1.39182105963787</v>
+        <v>0.68293712261195405</v>
       </c>
       <c r="C253">
-        <v>-0.31722202859681098</v>
+        <v>-0.380270390820794</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>158</v>
+        <v>612</v>
       </c>
       <c r="B254">
-        <v>9.6832974855728796E-2</v>
+        <v>0.56073590979325105</v>
       </c>
       <c r="C254">
-        <v>7.8065142416918398E-3</v>
+        <v>-0.39208192581556101</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>418</v>
+        <v>657</v>
       </c>
       <c r="B255">
-        <v>-1.37284976547671</v>
+        <v>0.84170693457013002</v>
       </c>
       <c r="C255">
-        <v>-0.29786611075441</v>
+        <v>-0.20251395424695001</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>159</v>
+        <v>613</v>
       </c>
       <c r="B256">
-        <v>0.60943239835820995</v>
+        <v>-1.65024264604958</v>
       </c>
       <c r="C256">
-        <v>-7.8544617637678601E-2</v>
+        <v>0.292049639249641</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>625</v>
+        <v>126</v>
       </c>
       <c r="B257">
-        <v>-8.6591453734509494E-2</v>
+        <v>-1.3550246935949199</v>
       </c>
       <c r="C257">
-        <v>-1.64595724416647</v>
+        <v>-0.27578149745233999</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>160</v>
+        <v>614</v>
       </c>
       <c r="B258">
-        <v>0.61752023262025901</v>
+        <v>-1.2106115794341401</v>
       </c>
       <c r="C258">
-        <v>-0.36074374062164899</v>
+        <v>-1.3164064099594499</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>161</v>
+        <v>615</v>
       </c>
       <c r="B259">
-        <v>-0.342263386934062</v>
+        <v>1.95896973210644E-2</v>
       </c>
       <c r="C259">
-        <v>4.7562371695525803E-2</v>
+        <v>2.36784871185272E-2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>162</v>
+        <v>616</v>
       </c>
       <c r="B260">
-        <v>-0.268725745815312</v>
+        <v>-1.2652954967907699</v>
       </c>
       <c r="C260">
-        <v>0.30596907432840598</v>
+        <v>-0.62443962676721498</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>419</v>
+        <v>127</v>
       </c>
       <c r="B261">
-        <v>-0.37184549509697601</v>
+        <v>-0.28419560627207802</v>
       </c>
       <c r="C261">
-        <v>0.172348091306884</v>
+        <v>0.20630274755884301</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="B262">
-        <v>0.61814392157118403</v>
+        <v>-0.47968829958738302</v>
       </c>
       <c r="C262">
-        <v>-0.30232409604469701</v>
+        <v>0.31689921989497299</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>420</v>
+        <v>129</v>
       </c>
       <c r="B263">
-        <v>0.74473054616155898</v>
+        <v>0.16026762120993299</v>
       </c>
       <c r="C263">
-        <v>-0.42891388688179199</v>
+        <v>0.49037458867285399</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>164</v>
+        <v>617</v>
       </c>
       <c r="B264">
-        <v>0.59760227377542796</v>
+        <v>-0.39273814489780601</v>
       </c>
       <c r="C264">
-        <v>-0.29171057229966701</v>
+        <v>-8.5486687011860005E-2</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>165</v>
+        <v>658</v>
       </c>
       <c r="B265">
-        <v>5.1643309338649003E-2</v>
+        <v>0.34534996394138501</v>
       </c>
       <c r="C265">
-        <v>0.38034179491381698</v>
+        <v>1.30300288088899</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>421</v>
+        <v>618</v>
       </c>
       <c r="B266">
-        <v>-9.3545083318028202E-2</v>
+        <v>-0.71218515587229603</v>
       </c>
       <c r="C266">
-        <v>0.63562706353784604</v>
+        <v>-0.187806502283937</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>422</v>
+        <v>619</v>
       </c>
       <c r="B267">
-        <v>-1.1439744079033101</v>
+        <v>-0.37082440345853102</v>
       </c>
       <c r="C267">
-        <v>-1.55480728039691</v>
+        <v>0.622351622916681</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>166</v>
+        <v>620</v>
       </c>
       <c r="B268">
-        <v>0.67518695623014402</v>
+        <v>-1.3737068761403499</v>
       </c>
       <c r="C268">
-        <v>-0.27374098317378298</v>
+        <v>-0.70693441420946002</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>423</v>
+        <v>130</v>
       </c>
       <c r="B269">
-        <v>-1.15814437045622</v>
+        <v>-0.163360903835302</v>
       </c>
       <c r="C269">
-        <v>-1.38200420370414</v>
+        <v>0.11660458390245</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>167</v>
+        <v>621</v>
       </c>
       <c r="B270">
-        <v>0.18380180862340301</v>
+        <v>-1.2383240567864</v>
       </c>
       <c r="C270">
-        <v>0.25965676725362902</v>
+        <v>-0.27803152791575803</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>424</v>
+        <v>622</v>
       </c>
       <c r="B271">
-        <v>-0.46029664553917798</v>
+        <v>-0.952606263750437</v>
       </c>
       <c r="C271">
-        <v>0.432358699745506</v>
+        <v>0.77683858865925204</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>168</v>
+        <v>673</v>
       </c>
       <c r="B272">
-        <v>0.67526306373427603</v>
+        <v>0.74462167468641405</v>
       </c>
       <c r="C272">
-        <v>-0.38665900046986901</v>
+        <v>-0.33994057927892701</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="B273">
-        <v>-0.380546882639893</v>
+        <v>-1.2874640584552</v>
       </c>
       <c r="C273">
-        <v>0.17036636870534599</v>
+        <v>-0.32987805000631498</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>170</v>
+        <v>368</v>
       </c>
       <c r="B274">
-        <v>-0.36902351294657199</v>
+        <v>-0.94557593680206797</v>
       </c>
       <c r="C274">
-        <v>0.16924915870593599</v>
+        <v>0.83262579928571701</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>171</v>
+        <v>674</v>
       </c>
       <c r="B275">
-        <v>-0.116382635384592</v>
+        <v>0.73000335126714999</v>
       </c>
       <c r="C275">
-        <v>0.25678681433308398</v>
+        <v>-0.435516728643767</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>172</v>
+        <v>369</v>
       </c>
       <c r="B276">
-        <v>-0.436361766058319</v>
+        <v>-0.74902827353761603</v>
       </c>
       <c r="C276">
-        <v>0.174784261540987</v>
+        <v>-9.9360781182014302E-2</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>173</v>
+        <v>370</v>
       </c>
       <c r="B277">
-        <v>-0.52858173140776898</v>
+        <v>-1.22750567353651</v>
       </c>
       <c r="C277">
-        <v>1.2458908443522499E-2</v>
+        <v>-1.1451035579670801</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>425</v>
+        <v>371</v>
       </c>
       <c r="B278">
-        <v>0.38424891275788198</v>
+        <v>0.66190240145655599</v>
       </c>
       <c r="C278">
-        <v>0.37485069089062001</v>
+        <v>-0.40228494929923198</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="B279">
-        <v>-0.40826765289230299</v>
+        <v>-1.04665817802275</v>
       </c>
       <c r="C279">
-        <v>0.46686549112176601</v>
+        <v>0.453264733606626</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>427</v>
+        <v>133</v>
       </c>
       <c r="B280">
-        <v>-1.1553909463943599</v>
+        <v>0.64382757023522996</v>
       </c>
       <c r="C280">
-        <v>-1.4462252426255799</v>
+        <v>-0.158358809464863</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="B281">
-        <v>0.72340598800594103</v>
+        <v>-1.25551643948393</v>
       </c>
       <c r="C281">
-        <v>-0.54192732116965403</v>
+        <v>-1.2193650831413301</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>429</v>
+        <v>134</v>
       </c>
       <c r="B282">
-        <v>0.14049720083697401</v>
+        <v>0.66947292493452804</v>
       </c>
       <c r="C282">
-        <v>-0.29741662557360399</v>
+        <v>-0.14032179296153499</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>174</v>
+        <v>373</v>
       </c>
       <c r="B283">
-        <v>-2.06392463551003E-2</v>
+        <v>-0.106652909764472</v>
       </c>
       <c r="C283">
-        <v>0.46805929538422703</v>
+        <v>0.20588053686264701</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>648</v>
+        <v>135</v>
       </c>
       <c r="B284">
-        <v>0.117900509653352</v>
+        <v>-0.19683607235889</v>
       </c>
       <c r="C284">
-        <v>0.59791088924935598</v>
+        <v>0.234356682438256</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="B285">
-        <v>-1.16305031762311</v>
+        <v>-0.97525291253021895</v>
       </c>
       <c r="C285">
-        <v>-1.4352316058928001</v>
+        <v>0.63013771822915499</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="B286">
-        <v>0.605540994155915</v>
+        <v>-1.2534238855027799</v>
       </c>
       <c r="C286">
-        <v>-0.51233800537688001</v>
+        <v>-0.60024209342241797</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="B287">
-        <v>0.73812551193641496</v>
+        <v>-0.82413556359851003</v>
       </c>
       <c r="C287">
-        <v>-0.45206454839007099</v>
+        <v>-0.62083926124381805</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>175</v>
+        <v>377</v>
       </c>
       <c r="B288">
-        <v>0.63789866580002497</v>
+        <v>-0.55574487451138599</v>
       </c>
       <c r="C288">
-        <v>-8.8434460574456406E-2</v>
+        <v>0.404424240639152</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>433</v>
+        <v>136</v>
       </c>
       <c r="B289">
-        <v>-0.76061602233144598</v>
+        <v>-0.58900522990448301</v>
       </c>
       <c r="C289">
-        <v>0.21522763387725199</v>
+        <v>0.23081721572705899</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>434</v>
+        <v>378</v>
       </c>
       <c r="B290">
-        <v>-1.27231913418747</v>
+        <v>-0.11971536439342199</v>
       </c>
       <c r="C290">
-        <v>-0.28788875760584398</v>
+        <v>-2.3003045077055199E-2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>176</v>
+        <v>379</v>
       </c>
       <c r="B291">
-        <v>-1.2731476854950201</v>
+        <v>-1.32524970356154</v>
       </c>
       <c r="C291">
-        <v>-9.0205025360668906E-2</v>
+        <v>0.158326477971382</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>435</v>
+        <v>380</v>
       </c>
       <c r="B292">
-        <v>-0.289833896320078</v>
+        <v>0.29516805631382198</v>
       </c>
       <c r="C292">
-        <v>0.123485926425112</v>
+        <v>-0.39245515337572001</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>436</v>
+        <v>381</v>
       </c>
       <c r="B293">
-        <v>0.44958759648692298</v>
+        <v>-0.215647231900289</v>
       </c>
       <c r="C293">
-        <v>0.24209168610651199</v>
+        <v>0.495137631662533</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>649</v>
+        <v>382</v>
       </c>
       <c r="B294">
-        <v>-8.6591453734509494E-2</v>
+        <v>-0.91627770118819896</v>
       </c>
       <c r="C294">
-        <v>-1.64595724416647</v>
+        <v>1.01432799194129</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>177</v>
+        <v>675</v>
       </c>
       <c r="B295">
-        <v>0.70625902356040005</v>
+        <v>0.68045728276768103</v>
       </c>
       <c r="C295">
-        <v>-0.37427301173581701</v>
+        <v>-0.102262397984569</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>437</v>
+        <v>383</v>
       </c>
       <c r="B296">
-        <v>0.70294988841202</v>
+        <v>-0.26851689858379102</v>
       </c>
       <c r="C296">
-        <v>-0.44244290039819101</v>
+        <v>0.257815288416959</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>178</v>
+        <v>384</v>
       </c>
       <c r="B297">
-        <v>0.27555776164180601</v>
+        <v>0.249338943833701</v>
       </c>
       <c r="C297">
-        <v>-8.16972811895295E-2</v>
+        <v>0.17531371221087699</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>438</v>
+        <v>385</v>
       </c>
       <c r="B298">
-        <v>0.53028785974328996</v>
+        <v>0.595955351532931</v>
       </c>
       <c r="C298">
-        <v>0.36473635966970203</v>
+        <v>-0.31615989381682902</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="B299">
-        <v>-0.52766158798492002</v>
+        <v>-0.13428624900300601</v>
       </c>
       <c r="C299">
-        <v>0.38327763393997499</v>
+        <v>0.50733626519514896</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>179</v>
+        <v>387</v>
       </c>
       <c r="B300">
-        <v>0.134219581411857</v>
+        <v>-1.1510477239253201</v>
       </c>
       <c r="C300">
-        <v>-6.0636298477745001E-2</v>
+        <v>-0.13479425892274599</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="B301">
-        <v>0.44957758142354198</v>
+        <v>0.777853362177506</v>
       </c>
       <c r="C301">
-        <v>-9.40911126072842E-2</v>
+        <v>-0.13455693886582901</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>440</v>
+        <v>137</v>
       </c>
       <c r="B302">
-        <v>0.59897739915673398</v>
+        <v>-0.58070360466943005</v>
       </c>
       <c r="C302">
-        <v>-0.43635566060200698</v>
+        <v>0.20832763422471601</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="B303">
-        <v>-0.46509870123818398</v>
+        <v>0.35575925159250199</v>
       </c>
       <c r="C303">
-        <v>0.129962746214942</v>
+        <v>0.36006905568872499</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>650</v>
+        <v>390</v>
       </c>
       <c r="B304">
-        <v>-0.41071845890304998</v>
+        <v>-0.76200019688506004</v>
       </c>
       <c r="C304">
-        <v>-0.169536806371791</v>
+        <v>5.2539545008862903E-2</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="B305">
-        <v>-0.35817696496998402</v>
+        <v>-0.48503085572874899</v>
       </c>
       <c r="C305">
-        <v>0.179835263864732</v>
+        <v>0.182028215385898</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
       <c r="B306">
-        <v>4.3792287061607399E-2</v>
+        <v>0.646165848214316</v>
       </c>
       <c r="C306">
-        <v>-0.52439598690874101</v>
+        <v>-0.30929246224016899</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>443</v>
+        <v>138</v>
       </c>
       <c r="B307">
-        <v>0.56666573024012501</v>
+        <v>-0.84860292183199004</v>
       </c>
       <c r="C307">
-        <v>-0.22667433498395401</v>
+        <v>-0.226673435008511</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="B308">
-        <v>0.33440914459974302</v>
+        <v>0.22424828568629801</v>
       </c>
       <c r="C308">
-        <v>-0.461802409545849</v>
+        <v>-2.1977039640515901E-2</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="B309">
-        <v>-0.681458966180574</v>
+        <v>6.7139529747347798E-2</v>
       </c>
       <c r="C309">
-        <v>0.17800554312505701</v>
+        <v>0.49150804117791502</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="B310">
-        <v>-0.347483294157446</v>
+        <v>-1.3593094655654701</v>
       </c>
       <c r="C310">
-        <v>0.121283907464713</v>
+        <v>-0.46442817801500902</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="B311">
-        <v>-1.1553909463943599</v>
+        <v>0.75797014979807598</v>
       </c>
       <c r="C311">
-        <v>-1.4462252426255799</v>
+        <v>-0.45190870872386901</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>446</v>
+        <v>642</v>
       </c>
       <c r="B312">
-        <v>-1.1439744079033101</v>
+        <v>0.58267384312896697</v>
       </c>
       <c r="C312">
-        <v>-1.55480728039691</v>
+        <v>-0.495986893656581</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>184</v>
+        <v>395</v>
       </c>
       <c r="B313">
-        <v>0.295117958909762</v>
+        <v>-4.7211734832428902E-2</v>
       </c>
       <c r="C313">
-        <v>0.13981409849812701</v>
+        <v>0.86716814746662996</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="B314">
-        <v>1.5783679422175401E-2</v>
+        <v>0.14143833143074</v>
       </c>
       <c r="C314">
-        <v>0.42519268259341703</v>
+        <v>0.13494843781728399</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B315">
-        <v>-0.11463218051766</v>
+        <v>-1.1865220532340901</v>
       </c>
       <c r="C315">
-        <v>0.73837752609110197</v>
+        <v>0.64116295637285803</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>186</v>
+        <v>397</v>
       </c>
       <c r="B316">
-        <v>-0.42377738852858199</v>
+        <v>0.65062489361240605</v>
       </c>
       <c r="C316">
-        <v>-0.44895615273598299</v>
+        <v>6.3079555878709406E-2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>187</v>
+        <v>398</v>
       </c>
       <c r="B317">
-        <v>0.72964878437557601</v>
+        <v>0.53962566514764598</v>
       </c>
       <c r="C317">
-        <v>-0.29603372533998501</v>
+        <v>-3.7704976680788503E-2</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>448</v>
+        <v>399</v>
       </c>
       <c r="B318">
-        <v>0.46840713180850102</v>
+        <v>-1.36949745660745</v>
       </c>
       <c r="C318">
-        <v>-0.24948884306772001</v>
+        <v>-0.33896271007626799</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="B319">
-        <v>-0.75658257497688297</v>
+        <v>-0.36341454108839999</v>
       </c>
       <c r="C319">
-        <v>0.148421933737932</v>
+        <v>0.125222847305997</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>189</v>
+        <v>676</v>
       </c>
       <c r="B320">
-        <v>-0.26329247514932602</v>
+        <v>-1.27884814295923</v>
       </c>
       <c r="C320">
-        <v>0.33966792287541803</v>
+        <v>-0.93573092969663996</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>190</v>
+        <v>677</v>
       </c>
       <c r="B321">
-        <v>0.638899905232719</v>
+        <v>0.55430539399357903</v>
       </c>
       <c r="C321">
-        <v>-0.294115617295368</v>
+        <v>-0.17335241997585199</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>191</v>
+        <v>401</v>
       </c>
       <c r="B322">
-        <v>0.59844291858880305</v>
+        <v>-1.15421020132323</v>
       </c>
       <c r="C322">
-        <v>-0.26127815738125398</v>
+        <v>-0.18370654880012</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="B323">
-        <v>0.56243334559402902</v>
+        <v>0.26016767316394501</v>
       </c>
       <c r="C323">
-        <v>-0.48385319774695801</v>
+        <v>0.27673535616650802</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>450</v>
+        <v>143</v>
       </c>
       <c r="B324">
-        <v>0.77653409971021703</v>
+        <v>-0.217562067813623</v>
       </c>
       <c r="C324">
-        <v>-0.18207100597418099</v>
+        <v>0.15523792350537</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>651</v>
+        <v>144</v>
       </c>
       <c r="B325">
-        <v>-0.41071845890304998</v>
+        <v>-0.52331107686400102</v>
       </c>
       <c r="C325">
-        <v>-0.169536806371791</v>
+        <v>0.48630239263490699</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>451</v>
+        <v>145</v>
       </c>
       <c r="B326">
-        <v>-1.2030904096525199</v>
+        <v>-0.94602478787740896</v>
       </c>
       <c r="C326">
-        <v>0.35029020522929699</v>
+        <v>-0.60802307998847005</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>452</v>
+        <v>146</v>
       </c>
       <c r="B327">
-        <v>-0.33646017891223001</v>
+        <v>-1.32927469652213</v>
       </c>
       <c r="C327">
-        <v>0.10626589438300001</v>
+        <v>-9.3262820445469102E-2</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="B328">
-        <v>-0.54737541314726101</v>
+        <v>8.7458475927081294E-2</v>
       </c>
       <c r="C328">
-        <v>0.78194476236404398</v>
+        <v>-0.16083372515292299</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>454</v>
+        <v>147</v>
       </c>
       <c r="B329">
-        <v>0.68366255148843602</v>
+        <v>-0.717599204354749</v>
       </c>
       <c r="C329">
-        <v>-0.46303214441514301</v>
+        <v>-0.62873161388431698</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>455</v>
+        <v>403</v>
       </c>
       <c r="B330">
-        <v>-1.1473338302812901</v>
+        <v>-1.31380794919291</v>
       </c>
       <c r="C330">
-        <v>-1.43180178719525</v>
+        <v>-0.99153217123885395</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="B331">
-        <v>-0.15983729953242801</v>
+        <v>-0.17401842342812501</v>
       </c>
       <c r="C331">
-        <v>0.23307168401005901</v>
+        <v>0.51352290776482401</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>456</v>
+        <v>404</v>
       </c>
       <c r="B332">
-        <v>0.73611976241805099</v>
+        <v>3.12684857560954E-2</v>
       </c>
       <c r="C332">
-        <v>-1.6869240472807599E-2</v>
+        <v>0.95793669192007103</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>193</v>
-      </c>
-      <c r="B333">
-        <v>0.643381896471661</v>
-      </c>
-      <c r="C333">
-        <v>-0.30201715449796901</v>
+        <v>643</v>
+      </c>
+      <c r="B333" t="s">
+        <v>659</v>
+      </c>
+      <c r="C333" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>457</v>
+        <v>149</v>
       </c>
       <c r="B334">
-        <v>-1.27234780823046</v>
+        <v>0.62620028812731499</v>
       </c>
       <c r="C334">
-        <v>-1.0388496693873801</v>
+        <v>-0.30812581811706502</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>458</v>
+        <v>644</v>
       </c>
       <c r="B335">
-        <v>-1.21504357268739</v>
+        <v>-0.102939838550097</v>
       </c>
       <c r="C335">
-        <v>-0.75325120840454896</v>
+        <v>0.42062712362166799</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>194</v>
+        <v>150</v>
       </c>
       <c r="B336">
-        <v>-1.304999060771</v>
+        <v>0.58583457111137105</v>
       </c>
       <c r="C336">
-        <v>-0.75613828611629996</v>
+        <v>0.20541117427129099</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="B337">
-        <v>-0.43287702489934499</v>
+        <v>0.70505451767471805</v>
       </c>
       <c r="C337">
-        <v>0.14515053291590499</v>
+        <v>-0.29825275032239201</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>460</v>
+        <v>406</v>
       </c>
       <c r="B338">
-        <v>-0.44028889229127899</v>
+        <v>-0.20356449018627901</v>
       </c>
       <c r="C338">
-        <v>-0.56754185099937804</v>
+        <v>0.14975205417485701</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="B339">
-        <v>0.22166035879148399</v>
+        <v>0.61018905755471398</v>
       </c>
       <c r="C339">
-        <v>-0.34894908489509502</v>
+        <v>-0.25324619643790902</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>196</v>
+        <v>407</v>
       </c>
       <c r="B340">
-        <v>-0.30007429357274001</v>
+        <v>-1.4919964182941601</v>
       </c>
       <c r="C340">
-        <v>0.242135998298634</v>
+        <v>-0.24045672516029001</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="B341">
-        <v>0.73506376580118005</v>
+        <v>-1.10117034392472</v>
       </c>
       <c r="C341">
-        <v>-0.430023322950702</v>
+        <v>-0.27297320108103001</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="B342">
-        <v>-0.34698311863333298</v>
+        <v>-1.21839361204038</v>
       </c>
       <c r="C342">
-        <v>0.106864293408824</v>
+        <v>-1.0176500855539901</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="B343">
-        <v>0.67883158969482704</v>
+        <v>-1.36834814273998</v>
       </c>
       <c r="C343">
-        <v>-0.337755994336356</v>
+        <v>-0.120989260080219</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>461</v>
+        <v>409</v>
       </c>
       <c r="B344">
-        <v>-1.1001843682558401</v>
+        <v>-0.49302163305750701</v>
       </c>
       <c r="C344">
-        <v>-1.4215123311025899</v>
+        <v>1.07836772795927E-2</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="B345">
-        <v>0.70917309276154805</v>
+        <v>-0.28142208507461303</v>
       </c>
       <c r="C345">
-        <v>-1.89048939186168E-2</v>
+        <v>0.228088592554933</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="B346">
-        <v>0.56157571463926004</v>
+        <v>4.6362293046166202E-2</v>
       </c>
       <c r="C346">
-        <v>0.142489611838994</v>
+        <v>0.49689823041454001</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>201</v>
+        <v>412</v>
       </c>
       <c r="B347">
-        <v>-0.34639514689863599</v>
+        <v>0.77018679478337904</v>
       </c>
       <c r="C347">
-        <v>0.16062322334093701</v>
+        <v>-0.50966335405644403</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>463</v>
+        <v>154</v>
       </c>
       <c r="B348">
-        <v>-0.13186812384077201</v>
+        <v>0.18533389593604499</v>
       </c>
       <c r="C348">
-        <v>0.412875735834007</v>
+        <v>8.3921848425967394E-2</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>464</v>
+        <v>155</v>
       </c>
       <c r="B349">
-        <v>-1.33417703002549</v>
+        <v>-1.6458519921931901E-3</v>
       </c>
       <c r="C349">
-        <v>0.31027553890465998</v>
+        <v>0.42387487006146901</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>652</v>
+        <v>413</v>
       </c>
       <c r="B350">
-        <v>-8.6591453734509494E-2</v>
+        <v>-1.3211147952910001</v>
       </c>
       <c r="C350">
-        <v>-1.64595724416647</v>
+        <v>-0.97276848024823903</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="B351">
-        <v>-0.41526826059147398</v>
+        <v>0.63457502591094295</v>
       </c>
       <c r="C351">
-        <v>0.38541133644221598</v>
+        <v>-0.43110685780505098</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>466</v>
+        <v>645</v>
       </c>
       <c r="B352">
-        <v>-0.55912328073930795</v>
+        <v>-0.39154543005721698</v>
       </c>
       <c r="C352">
-        <v>0.235884721360893</v>
+        <v>0.27304588785469103</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>202</v>
+        <v>415</v>
       </c>
       <c r="B353">
-        <v>0.66469564285888105</v>
+        <v>-0.125032389690485</v>
       </c>
       <c r="C353">
-        <v>-0.328870645478337</v>
+        <v>0.228810833687387</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="B354">
-        <v>0.67621334971668701</v>
+        <v>-0.13792923684307701</v>
       </c>
       <c r="C354">
-        <v>-0.63339778334475805</v>
+        <v>1.1326597436760699</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>203</v>
+        <v>646</v>
       </c>
       <c r="B355">
-        <v>-0.15073554889802401</v>
+        <v>-0.69575677187270402</v>
       </c>
       <c r="C355">
-        <v>0.337504562353516</v>
+        <v>0.55098855524435297</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>468</v>
+        <v>156</v>
       </c>
       <c r="B356">
-        <v>-0.42892443351570397</v>
+        <v>0.110841276536902</v>
       </c>
       <c r="C356">
-        <v>0.88119650199487298</v>
+        <v>0.35852960631456499</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>204</v>
+        <v>417</v>
       </c>
       <c r="B357">
-        <v>-0.203138670159169</v>
+        <v>-0.81309706343243204</v>
       </c>
       <c r="C357">
-        <v>0.22646437370156</v>
+        <v>0.819296067166009</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>469</v>
+        <v>157</v>
       </c>
       <c r="B358">
-        <v>0.71442250869560098</v>
+        <v>-1.33097566416179</v>
       </c>
       <c r="C358">
-        <v>0.36963808544350102</v>
+        <v>6.5798131807659E-3</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="B359">
-        <v>-0.41791407051123303</v>
+        <v>0.14174402481891599</v>
       </c>
       <c r="C359">
-        <v>0.15928104986817701</v>
+        <v>2.67507221819131E-2</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>205</v>
+        <v>418</v>
       </c>
       <c r="B360">
-        <v>-1.07758687439291</v>
+        <v>-1.3209194715844499</v>
       </c>
       <c r="C360">
-        <v>-0.72640919264667203</v>
+        <v>6.10868451540095E-2</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="B361">
-        <v>-0.27901915920956399</v>
+        <v>0.55011915106077003</v>
       </c>
       <c r="C361">
-        <v>0.19156916973551499</v>
+        <v>-5.8588280854855103E-2</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>470</v>
-      </c>
-      <c r="B362">
-        <v>3.2516959379490298E-2</v>
-      </c>
-      <c r="C362">
-        <v>0.61961690615803999</v>
+        <v>624</v>
+      </c>
+      <c r="B362" t="s">
+        <v>659</v>
+      </c>
+      <c r="C362" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>471</v>
+        <v>160</v>
       </c>
       <c r="B363">
-        <v>-0.37268331037734997</v>
+        <v>0.598461162953005</v>
       </c>
       <c r="C363">
-        <v>0.13975520343668901</v>
+        <v>-0.33311046560003699</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>472</v>
+        <v>161</v>
       </c>
       <c r="B364">
-        <v>-2.65797514727951E-2</v>
+        <v>-0.41279075142871902</v>
       </c>
       <c r="C364">
-        <v>0.51499074580464899</v>
+        <v>-7.1454589217288299E-3</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>473</v>
+        <v>162</v>
       </c>
       <c r="B365">
-        <v>0.85172899653860001</v>
+        <v>-0.23499631725593501</v>
       </c>
       <c r="C365">
-        <v>-0.46934656397511298</v>
+        <v>0.32680840102412201</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>208</v>
+        <v>419</v>
       </c>
       <c r="B366">
-        <v>-1.13821059824485</v>
+        <v>-0.104862136065971</v>
       </c>
       <c r="C366">
-        <v>-1.22613589798544</v>
+        <v>0.126266837164379</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="B367">
-        <v>-0.48283778266441102</v>
+        <v>0.60622844542073895</v>
       </c>
       <c r="C367">
-        <v>4.51564105033272E-2</v>
+        <v>-0.30908202482180203</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="B368">
-        <v>-4.5989507050032102E-2</v>
+        <v>0.69383698885110201</v>
       </c>
       <c r="C368">
-        <v>3.3317888005661198E-2</v>
+        <v>-0.40174526540620498</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="B369">
-        <v>-1.0630699069962599</v>
+        <v>0.58256094967364802</v>
       </c>
       <c r="C369">
-        <v>0.373166516114804</v>
+        <v>-0.22868224775474999</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="B370">
-        <v>-0.66098196592931302</v>
+        <v>7.8292459339458803E-2</v>
       </c>
       <c r="C370">
-        <v>9.8592149658742106E-2</v>
+        <v>0.36680288896963198</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>212</v>
+        <v>421</v>
       </c>
       <c r="B371">
-        <v>0.74562933917973095</v>
+        <v>-3.7458849593068402E-2</v>
       </c>
       <c r="C371">
-        <v>-0.40582973463334798</v>
+        <v>0.60817334179381199</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>475</v>
+        <v>422</v>
       </c>
       <c r="B372">
-        <v>0.570393214806583</v>
+        <v>-1.25551643948393</v>
       </c>
       <c r="C372">
-        <v>-0.30899467119217799</v>
+        <v>-1.2193650831413301</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>476</v>
+        <v>166</v>
       </c>
       <c r="B373">
-        <v>0.70599673021817</v>
+        <v>0.63446331638755205</v>
       </c>
       <c r="C373">
-        <v>-0.332837279249033</v>
+        <v>-0.257045723267329</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>213</v>
+        <v>423</v>
       </c>
       <c r="B374">
-        <v>0.60085653453481602</v>
+        <v>-1.25057759449405</v>
       </c>
       <c r="C374">
-        <v>0.135999457130283</v>
+        <v>-1.04933521376224</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>477</v>
+        <v>167</v>
       </c>
       <c r="B375">
-        <v>0.65212909675661201</v>
+        <v>0.22374480248534501</v>
       </c>
       <c r="C375">
-        <v>-0.43602462478780601</v>
+        <v>0.27391036231634103</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>478</v>
+        <v>424</v>
       </c>
       <c r="B376">
-        <v>-0.12950176833322699</v>
+        <v>-0.3756426442934</v>
       </c>
       <c r="C376">
-        <v>-0.40289890185812499</v>
+        <v>0.42840346592098799</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="B377">
-        <v>-1.3530591493158</v>
+        <v>0.64178537602185304</v>
       </c>
       <c r="C377">
-        <v>-0.33237061531297701</v>
+        <v>-0.346616620972932</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>626</v>
+        <v>169</v>
       </c>
       <c r="B378">
-        <v>-0.21054867790587101</v>
+        <v>-0.33037548969337099</v>
       </c>
       <c r="C378">
-        <v>-1.6086135631854299</v>
+        <v>0.22643974774897199</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>479</v>
+        <v>170</v>
       </c>
       <c r="B379">
-        <v>-1.0482606741878</v>
+        <v>-0.32240249992618097</v>
       </c>
       <c r="C379">
-        <v>-1.5235775960073099</v>
+        <v>0.23459249430731199</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>480</v>
+        <v>171</v>
       </c>
       <c r="B380">
-        <v>-1.23135621472707</v>
+        <v>-7.2130609465897402E-2</v>
       </c>
       <c r="C380">
-        <v>-1.02646908123078</v>
+        <v>0.27101985688916103</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="B381">
-        <v>-1.17836906008061</v>
+        <v>-0.42211283899357799</v>
       </c>
       <c r="C381">
-        <v>-1.4132443324272399</v>
+        <v>0.209685455082285</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>482</v>
+        <v>173</v>
       </c>
       <c r="B382">
-        <v>-1.5558742656072999</v>
+        <v>-0.54049031518778301</v>
       </c>
       <c r="C382">
-        <v>-0.79710738587186303</v>
+        <v>0.31628416776871698</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>483</v>
+        <v>678</v>
       </c>
       <c r="B383">
-        <v>0.68058209316621598</v>
+        <v>0.96649813966019504</v>
       </c>
       <c r="C383">
-        <v>-0.40581673787487998</v>
+        <v>-0.32683960851451399</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>484</v>
+        <v>425</v>
       </c>
       <c r="B384">
-        <v>0.69891660777482201</v>
+        <v>0.42295834449106801</v>
       </c>
       <c r="C384">
-        <v>6.4723726688819594E-2</v>
+        <v>0.18778461982420899</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>485</v>
+        <v>426</v>
       </c>
       <c r="B385">
-        <v>-1.3016407907118099</v>
+        <v>-0.36695084718184201</v>
       </c>
       <c r="C385">
-        <v>-0.89455742772715796</v>
+        <v>0.48937649358420199</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>486</v>
+        <v>679</v>
       </c>
       <c r="B386">
-        <v>7.6094381599708799E-2</v>
+        <v>-1.2766224939508499</v>
       </c>
       <c r="C386">
-        <v>0.740494218313002</v>
+        <v>-0.99750863154674196</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>215</v>
+        <v>427</v>
       </c>
       <c r="B387">
-        <v>-1.43754985186335</v>
+        <v>-1.2444787558599399</v>
       </c>
       <c r="C387">
-        <v>-0.560056653528473</v>
+        <v>-1.1355403631243399</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
       <c r="B388">
-        <v>-0.32009674479246503</v>
+        <v>0.67874505142470798</v>
       </c>
       <c r="C388">
-        <v>0.51391193649359801</v>
+        <v>-0.49489882647535399</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>488</v>
+        <v>429</v>
       </c>
       <c r="B389">
-        <v>-0.93313455775225196</v>
+        <v>0.13815110766062499</v>
       </c>
       <c r="C389">
-        <v>0.40675869696867401</v>
+        <v>-0.24263512697731901</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="B390">
-        <v>-2.94375275210478E-2</v>
+        <v>2.1198681255458901E-2</v>
       </c>
       <c r="C390">
-        <v>-8.5835514976845394E-3</v>
+        <v>0.46212268747419999</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>489</v>
+        <v>647</v>
       </c>
       <c r="B391">
-        <v>8.2616402872568495E-2</v>
+        <v>0.25937201402552401</v>
       </c>
       <c r="C391">
-        <v>0.79809678613747903</v>
+        <v>0.41580938195571798</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="B392">
-        <v>-1.06031557427927</v>
+        <v>-1.2941190195954999</v>
       </c>
       <c r="C392">
-        <v>-0.39800422326163998</v>
+        <v>-1.03045402040571</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>217</v>
+        <v>431</v>
       </c>
       <c r="B393">
-        <v>-1.02572891600534</v>
+        <v>0.56789101028101296</v>
       </c>
       <c r="C393">
-        <v>-0.88480597863150101</v>
+        <v>-0.47311767772274799</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>218</v>
+        <v>432</v>
       </c>
       <c r="B394">
-        <v>-1.4075362540643801</v>
+        <v>0.685551546041271</v>
       </c>
       <c r="C394">
-        <v>-0.53839028424531099</v>
+        <v>-0.42162482643043497</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>491</v>
+        <v>175</v>
       </c>
       <c r="B395">
-        <v>-0.35023249300205</v>
+        <v>0.59191478939813102</v>
       </c>
       <c r="C395">
-        <v>0.83779607875268902</v>
+        <v>-9.6952792761892601E-2</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>492</v>
+        <v>433</v>
       </c>
       <c r="B396">
-        <v>0.126412266387773</v>
+        <v>-0.68304270883060203</v>
       </c>
       <c r="C396">
-        <v>0.35626893798390602</v>
+        <v>0.35522961701767902</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>219</v>
+        <v>434</v>
       </c>
       <c r="B397">
-        <v>0.73467326634498598</v>
+        <v>-1.2180774347833301</v>
       </c>
       <c r="C397">
-        <v>-0.444533218875103</v>
+        <v>3.7886125609775702E-2</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>493</v>
+        <v>176</v>
       </c>
       <c r="B398">
-        <v>-0.92793724170007297</v>
+        <v>-1.18676775718099</v>
       </c>
       <c r="C398">
-        <v>-0.30812310600570297</v>
+        <v>0.22383866784329601</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>220</v>
+        <v>435</v>
       </c>
       <c r="B399">
-        <v>-0.30240857883410299</v>
+        <v>-0.24640210318273301</v>
       </c>
       <c r="C399">
-        <v>0.34902501148320703</v>
+        <v>0.15996022410716301</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>221</v>
+        <v>436</v>
       </c>
       <c r="B400">
-        <v>-1.2467113277652599</v>
+        <v>0.44021284742629602</v>
       </c>
       <c r="C400">
-        <v>-0.36595797635963701</v>
+        <v>0.241099046768909</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>222</v>
-      </c>
-      <c r="B401">
-        <v>-1.42180643190759</v>
-      </c>
-      <c r="C401">
-        <v>-0.31141723588683101</v>
+        <v>648</v>
+      </c>
+      <c r="B401" t="s">
+        <v>659</v>
+      </c>
+      <c r="C401" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>494</v>
+        <v>177</v>
       </c>
       <c r="B402">
-        <v>-1.16801897631134</v>
+        <v>0.67908187566586398</v>
       </c>
       <c r="C402">
-        <v>0.103538822477609</v>
+        <v>-0.354140113061579</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>223</v>
+        <v>437</v>
       </c>
       <c r="B403">
-        <v>0.558981940343101</v>
+        <v>0.65870541268291405</v>
       </c>
       <c r="C403">
-        <v>0.17891595626182599</v>
+        <v>-0.40544746435658802</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="B404">
-        <v>-0.39630066472772002</v>
+        <v>0.196421422220911</v>
       </c>
       <c r="C404">
-        <v>0.31394234022210799</v>
+        <v>-9.8009324674933604E-2</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>225</v>
+        <v>438</v>
       </c>
       <c r="B405">
-        <v>0.59256262236087398</v>
+        <v>0.51446837880110396</v>
       </c>
       <c r="C405">
-        <v>-0.248365973019194</v>
+        <v>0.32799960569066899</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>226</v>
+        <v>439</v>
       </c>
       <c r="B406">
-        <v>-0.241076903966744</v>
+        <v>-0.44385988489003297</v>
       </c>
       <c r="C406">
-        <v>6.4457372391519899E-2</v>
+        <v>0.48536349956588598</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="B407">
-        <v>-0.527484958014377</v>
+        <v>0.19502027093107299</v>
       </c>
       <c r="C407">
-        <v>0.11417586410443099</v>
+        <v>-3.7663259115734003E-2</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>495</v>
+        <v>180</v>
       </c>
       <c r="B408">
-        <v>-1.24143505672814</v>
+        <v>0.38338689357755901</v>
       </c>
       <c r="C408">
-        <v>-1.3034157348086499</v>
+        <v>-9.5911449538162899E-2</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>496</v>
+        <v>440</v>
       </c>
       <c r="B409">
-        <v>-0.134525359288348</v>
+        <v>0.56073590979325105</v>
       </c>
       <c r="C409">
-        <v>0.71502486901505002</v>
+        <v>-0.39208192581556101</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B410">
-        <v>-1.5079657210419899</v>
+        <v>-0.40958380085926099</v>
       </c>
       <c r="C410">
-        <v>-0.591923611562989</v>
+        <v>0.211033437566647</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>497</v>
+        <v>649</v>
       </c>
       <c r="B411">
-        <v>0.55474086337710704</v>
+        <v>-0.81412854135576596</v>
       </c>
       <c r="C411">
-        <v>0.89631658509239798</v>
+        <v>-0.57685943034313003</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>229</v>
+        <v>441</v>
       </c>
       <c r="B412">
-        <v>-0.24400016043148401</v>
+        <v>-0.296923664338125</v>
       </c>
       <c r="C412">
-        <v>0.282888165442995</v>
+        <v>0.230338590186837</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>230</v>
+        <v>442</v>
       </c>
       <c r="B413">
-        <v>8.7532184685108205E-2</v>
+        <v>8.4357428572792003E-3</v>
       </c>
       <c r="C413">
-        <v>0.51047361794087098</v>
+        <v>-0.39114423574969798</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>498</v>
+        <v>443</v>
       </c>
       <c r="B414">
-        <v>0.54926121470238198</v>
+        <v>0.53238589759199095</v>
       </c>
       <c r="C414">
-        <v>-0.32050541666249399</v>
+        <v>-0.22501111437752</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="B415">
-        <v>-0.32927784048293901</v>
+        <v>0.34606148068127301</v>
       </c>
       <c r="C415">
-        <v>-0.14191677302314001</v>
+        <v>-0.38131103140613098</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>499</v>
+        <v>183</v>
       </c>
       <c r="B416">
-        <v>-1.1138058441897001</v>
+        <v>-0.608362251546818</v>
       </c>
       <c r="C416">
-        <v>0.60752698287451801</v>
+        <v>0.29677876015069998</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>500</v>
+        <v>444</v>
       </c>
       <c r="B417">
-        <v>-1.07793626414261E-2</v>
+        <v>-0.29314193332306898</v>
       </c>
       <c r="C417">
-        <v>0.53421547971526895</v>
+        <v>0.19665843393629701</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>232</v>
+        <v>445</v>
       </c>
       <c r="B418">
-        <v>0.62833434340576799</v>
+        <v>-1.2444787558599399</v>
       </c>
       <c r="C418">
-        <v>0.223738741219595</v>
+        <v>-1.1355403631243399</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>501</v>
+        <v>446</v>
       </c>
       <c r="B419">
-        <v>0.67094814833518801</v>
+        <v>-1.25551643948393</v>
       </c>
       <c r="C419">
-        <v>0.244900544395632</v>
+        <v>-1.2193650831413301</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>502</v>
+        <v>184</v>
       </c>
       <c r="B420">
-        <v>-1.5438793495265499</v>
+        <v>0.32314719546234899</v>
       </c>
       <c r="C420">
-        <v>-0.64098362965174405</v>
+        <v>0.12867974678050501</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>503</v>
+        <v>185</v>
       </c>
       <c r="B421">
-        <v>0.71855991451317203</v>
+        <v>4.8429095974000899E-2</v>
       </c>
       <c r="C421">
-        <v>-0.22266509428190001</v>
+        <v>0.41466918907038902</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>504</v>
+        <v>447</v>
       </c>
       <c r="B422">
-        <v>-0.283861536564044</v>
+        <v>-4.2573642565390299E-2</v>
       </c>
       <c r="C422">
-        <v>-7.2149732734953495E-2</v>
+        <v>0.71228346287038002</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>505</v>
+        <v>186</v>
       </c>
       <c r="B423">
-        <v>0.68797877864776702</v>
+        <v>-0.62441747339043996</v>
       </c>
       <c r="C423">
-        <v>-0.20842812904302499</v>
+        <v>-0.44225993854991602</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>506</v>
+        <v>187</v>
       </c>
       <c r="B424">
-        <v>-9.4632707181924097E-2</v>
+        <v>0.68347073279084503</v>
       </c>
       <c r="C424">
-        <v>0.43002291993361302</v>
+        <v>-0.24980031347676199</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>233</v>
+        <v>448</v>
       </c>
       <c r="B425">
-        <v>0.10816073833267</v>
+        <v>0.44812972165324</v>
       </c>
       <c r="C425">
-        <v>-0.48422798915126802</v>
+        <v>-0.21019139923654501</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="B426">
-        <v>-0.202674613601286</v>
+        <v>-0.70633541640598296</v>
       </c>
       <c r="C426">
-        <v>0.365713500403474</v>
+        <v>0.30638643926583398</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="B427">
-        <v>-3.43790366747668E-2</v>
+        <v>-0.22756460578263299</v>
       </c>
       <c r="C427">
-        <v>0.30936514492439998</v>
+        <v>0.37213994558336999</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>507</v>
+        <v>190</v>
       </c>
       <c r="B428">
-        <v>-1.2948342059666</v>
+        <v>0.60283051204275695</v>
       </c>
       <c r="C428">
-        <v>-0.75509836435556998</v>
+        <v>-0.26291614038397398</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>236</v>
+        <v>449</v>
       </c>
       <c r="B429">
-        <v>-1.3269394720411101</v>
+        <v>0.51622592280953095</v>
       </c>
       <c r="C429">
-        <v>-0.37498485511181601</v>
+        <v>-0.44041208392365999</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>508</v>
+        <v>191</v>
       </c>
       <c r="B430">
-        <v>-1.47168090654507</v>
+        <v>0.57264653012183098</v>
       </c>
       <c r="C430">
-        <v>-0.179385319050685</v>
+        <v>-0.22104564669541901</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>509</v>
+        <v>450</v>
       </c>
       <c r="B431">
-        <v>0.54824446001784699</v>
+        <v>0.73012620722728605</v>
       </c>
       <c r="C431">
-        <v>-2.34658923737248E-2</v>
+        <v>-0.16662163033330801</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>510</v>
+        <v>680</v>
       </c>
       <c r="B432">
-        <v>-1.26999312045621</v>
+        <v>0.76493887830881502</v>
       </c>
       <c r="C432">
-        <v>-1.2249263929334699</v>
+        <v>-0.35709564497502599</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>511</v>
+        <v>650</v>
       </c>
       <c r="B433">
-        <v>-1.0898415678868101</v>
+        <v>-0.82596283953970995</v>
       </c>
       <c r="C433">
-        <v>-1.2039766222310799</v>
+        <v>-0.72832483202140696</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>237</v>
+        <v>451</v>
       </c>
       <c r="B434">
-        <v>-1.2016804693901999</v>
+        <v>-1.0625512051219701</v>
       </c>
       <c r="C434">
-        <v>-0.24185385918013699</v>
+        <v>0.61767403769669504</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>238</v>
+        <v>452</v>
       </c>
       <c r="B435">
-        <v>-0.24076950681838799</v>
+        <v>-0.27721495819810898</v>
       </c>
       <c r="C435">
-        <v>0.205474930760631</v>
+        <v>0.15972102193887799</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="B436">
-        <v>-1.1093719914759901</v>
+        <v>-0.40569980886720503</v>
       </c>
       <c r="C436">
-        <v>-1.7292295115340499</v>
+        <v>0.74613146728109303</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>513</v>
+        <v>681</v>
       </c>
       <c r="B437">
-        <v>-1.1941933735586501</v>
+        <v>0.63843027922950502</v>
       </c>
       <c r="C437">
-        <v>-1.2217414050021</v>
+        <v>-0.42383703701981201</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>514</v>
+        <v>454</v>
       </c>
       <c r="B438">
-        <v>-0.65792408095529198</v>
+        <v>-1.2298401298828601</v>
       </c>
       <c r="C438">
-        <v>0.48518069394996499</v>
+        <v>-1.08314790536743</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="B439">
-        <v>0.21936858363119699</v>
+        <v>-0.114910546682169</v>
       </c>
       <c r="C439">
-        <v>0.34777683097432299</v>
+        <v>0.35603379211937602</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>515</v>
+        <v>455</v>
       </c>
       <c r="B440">
-        <v>-0.45926489325143199</v>
+        <v>0.73492711874999705</v>
       </c>
       <c r="C440">
-        <v>-0.136978160353978</v>
+        <v>-0.17312305459491401</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="B441">
-        <v>-1.2220337086689601</v>
+        <v>0.60566928962259403</v>
       </c>
       <c r="C441">
-        <v>-0.61984888690020701</v>
+        <v>-0.27192296496188201</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>516</v>
+        <v>682</v>
       </c>
       <c r="B442">
-        <v>0.55273564099678396</v>
+        <v>0.85807126820897395</v>
       </c>
       <c r="C442">
-        <v>-0.346420390758168</v>
+        <v>-0.43855222701747898</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="B443">
-        <v>-1.20267219683201</v>
+        <v>-1.31105210073116</v>
       </c>
       <c r="C443">
-        <v>-0.86258258109234298</v>
+        <v>-0.83196659013760899</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>241</v>
+        <v>457</v>
       </c>
       <c r="B444">
-        <v>0.27216952091382401</v>
+        <v>-1.22922010008814</v>
       </c>
       <c r="C444">
-        <v>0.17634411941110001</v>
+        <v>-0.40493441729136198</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>518</v>
+        <v>194</v>
       </c>
       <c r="B445">
-        <v>0.61083888107008499</v>
+        <v>-1.3050912471729299</v>
       </c>
       <c r="C445">
-        <v>-0.26520744747865899</v>
+        <v>-0.52388633564550202</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>242</v>
+        <v>458</v>
       </c>
       <c r="B446">
-        <v>0.59087416324840902</v>
+        <v>-0.37034619458971502</v>
       </c>
       <c r="C446">
-        <v>-0.19505557575051699</v>
+        <v>0.262122415748405</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>519</v>
+        <v>459</v>
       </c>
       <c r="B447">
-        <v>-1.0482606741878</v>
+        <v>-0.46288110875240102</v>
       </c>
       <c r="C447">
-        <v>-1.5235775960073099</v>
+        <v>-0.31046055793709898</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>520</v>
+        <v>195</v>
       </c>
       <c r="B448">
-        <v>0.54019969915133004</v>
+        <v>0.30139160347967597</v>
       </c>
       <c r="C448">
-        <v>-0.34125672802069001</v>
+        <v>-0.275514686539022</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="B449">
-        <v>-1.1246738949728301</v>
+        <v>-0.24411114180386401</v>
       </c>
       <c r="C449">
-        <v>-1.2873528439278401</v>
+        <v>0.27552602334309101</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
       <c r="B450">
-        <v>0.71124181805384401</v>
+        <v>0.67989736324235095</v>
       </c>
       <c r="C450">
-        <v>-0.27309456454286302</v>
+        <v>-0.39925470804027502</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>521</v>
+        <v>198</v>
       </c>
       <c r="B451">
-        <v>0.789299139863338</v>
+        <v>-0.29298354722853898</v>
       </c>
       <c r="C451">
-        <v>-8.9230767109803405E-2</v>
+        <v>0.14176683682896099</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>522</v>
+        <v>199</v>
       </c>
       <c r="B452">
-        <v>8.3916184508420102E-2</v>
+        <v>0.64014390328875503</v>
       </c>
       <c r="C452">
-        <v>0.66081984008292205</v>
+        <v>-0.30863359242119498</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>523</v>
+        <v>460</v>
       </c>
       <c r="B453">
-        <v>-0.31712095886298303</v>
+        <v>-1.2653060472745401</v>
       </c>
       <c r="C453">
-        <v>0.13906886114263001</v>
+        <v>-1.13642021364743</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>524</v>
+        <v>200</v>
       </c>
       <c r="B454">
-        <v>-1.1555152999465901</v>
+        <v>0.65493436929956805</v>
       </c>
       <c r="C454">
-        <v>-1.1855806023809099</v>
+        <v>-2.0743950073692001E-2</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>525</v>
+        <v>461</v>
       </c>
       <c r="B455">
-        <v>0.77433505806274505</v>
+        <v>0.53255687580336397</v>
       </c>
       <c r="C455">
-        <v>-0.55910171109061502</v>
+        <v>0.15681978085689399</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="B456">
-        <v>0.55447924494821998</v>
+        <v>-0.28747823361297098</v>
       </c>
       <c r="C456">
-        <v>-0.13971846263153501</v>
+        <v>0.19340914784032201</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>526</v>
+        <v>462</v>
       </c>
       <c r="B457">
-        <v>0.20907590073994001</v>
+        <v>-8.7554012283952001E-2</v>
       </c>
       <c r="C457">
-        <v>0.84057806371578903</v>
+        <v>0.40374420292063101</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>527</v>
+        <v>463</v>
       </c>
       <c r="B458">
-        <v>-1.2364141992364199</v>
+        <v>-1.1865220532340901</v>
       </c>
       <c r="C458">
-        <v>-0.50977246867806802</v>
+        <v>0.64116295637285803</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>246</v>
-      </c>
-      <c r="B459">
-        <v>-1.2904555156200901</v>
-      </c>
-      <c r="C459">
-        <v>-1.1438689843062999</v>
+        <v>651</v>
+      </c>
+      <c r="B459" t="s">
+        <v>659</v>
+      </c>
+      <c r="C459" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>247</v>
+        <v>464</v>
       </c>
       <c r="B460">
-        <v>-0.20818931035313001</v>
+        <v>-0.370876243298148</v>
       </c>
       <c r="C460">
-        <v>0.57694683329697505</v>
+        <v>0.489595099406824</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>248</v>
+        <v>465</v>
       </c>
       <c r="B461">
-        <v>0.67765310580574001</v>
+        <v>-0.48870948035192402</v>
       </c>
       <c r="C461">
-        <v>-0.33028921344432499</v>
+        <v>0.35263694489703801</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>528</v>
+        <v>202</v>
       </c>
       <c r="B462">
-        <v>-0.241862921839512</v>
+        <v>0.63783001356454905</v>
       </c>
       <c r="C462">
-        <v>1.1535087211774999</v>
+        <v>-0.31032447485345899</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>529</v>
+        <v>466</v>
       </c>
       <c r="B463">
-        <v>0.64095508947483704</v>
+        <v>0.61366507158019901</v>
       </c>
       <c r="C463">
-        <v>0.380566386724776</v>
+        <v>-0.59329950720708302</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="B464">
-        <v>0.77661014852027499</v>
+        <v>-0.107660107189926</v>
       </c>
       <c r="C464">
-        <v>-0.42404823051678497</v>
+        <v>0.34134822808388898</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>530</v>
+        <v>467</v>
       </c>
       <c r="B465">
-        <v>-1.33113230188233</v>
+        <v>-0.26788726181351902</v>
       </c>
       <c r="C465">
-        <v>-0.37028359190621701</v>
+        <v>0.92118797209653502</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="B466">
-        <v>-0.65292421887528895</v>
+        <v>-0.15881163016054101</v>
       </c>
       <c r="C466">
-        <v>0.169256524258658</v>
+        <v>0.24370667871777901</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>251</v>
+        <v>468</v>
       </c>
       <c r="B467">
-        <v>-1.08944920982299</v>
+        <v>0.67791138660453798</v>
       </c>
       <c r="C467">
-        <v>-1.18583696632076</v>
+        <v>0.358571483737543</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>531</v>
+        <v>205</v>
       </c>
       <c r="B468">
-        <v>8.7875350846187896E-4</v>
+        <v>-1.0933802653985301</v>
       </c>
       <c r="C468">
-        <v>-0.66973996003897596</v>
+        <v>-0.40923837901354698</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>532</v>
+        <v>206</v>
       </c>
       <c r="B469">
-        <v>-1.4452691367359101</v>
+        <v>-0.35129133531475698</v>
       </c>
       <c r="C469">
-        <v>-0.62237165185592902</v>
+        <v>0.26001506868286001</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>252</v>
+        <v>683</v>
       </c>
       <c r="B470">
-        <v>0.56309809169692004</v>
+        <v>-1.2665989360262599</v>
       </c>
       <c r="C470">
-        <v>-0.26114657429706201</v>
+        <v>-1.07937822358951</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="B471">
-        <v>0.73101812158614499</v>
+        <v>-0.22807384540180001</v>
       </c>
       <c r="C471">
-        <v>-0.34253369187503702</v>
+        <v>0.22910750771306301</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>254</v>
+        <v>469</v>
       </c>
       <c r="B472">
-        <v>-1.2571277912621199</v>
+        <v>8.4060936014676194E-2</v>
       </c>
       <c r="C472">
-        <v>-0.62360069845256605</v>
+        <v>0.60400959444774605</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>255</v>
+        <v>470</v>
       </c>
       <c r="B473">
-        <v>-1.0613025528649001</v>
+        <v>-0.32437786381014</v>
       </c>
       <c r="C473">
-        <v>-0.47783997150333901</v>
+        <v>0.19564634085838301</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>256</v>
+        <v>471</v>
       </c>
       <c r="B474">
-        <v>4.8787918754373799E-2</v>
+        <v>2.2276543255837E-2</v>
       </c>
       <c r="C474">
-        <v>0.45022830046217599</v>
+        <v>0.50683337239503701</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>533</v>
+        <v>472</v>
       </c>
       <c r="B475">
-        <v>-1.2756217857513801</v>
+        <v>0.773261230706346</v>
       </c>
       <c r="C475">
-        <v>0.271525283607921</v>
+        <v>-0.30660690006541602</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>534</v>
+        <v>208</v>
       </c>
       <c r="B476">
-        <v>0.52286017974800603</v>
+        <v>-1.2629836441345901</v>
       </c>
       <c r="C476">
-        <v>-0.51048387272340001</v>
+        <v>-0.95326011895310703</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="B477">
-        <v>0.70967397728170201</v>
+        <v>-0.64089203751872303</v>
       </c>
       <c r="C477">
-        <v>-0.38721421100652098</v>
+        <v>-0.13153049983229301</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>258</v>
+        <v>473</v>
       </c>
       <c r="B478">
-        <v>0.37914770866021302</v>
+        <v>-2.2543485397431E-2</v>
       </c>
       <c r="C478">
-        <v>0.28429574142936498</v>
+        <v>0.111375457376982</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="B479">
-        <v>-0.106599622458001</v>
+        <v>-0.93050604633270395</v>
       </c>
       <c r="C479">
-        <v>0.43742004990484701</v>
+        <v>0.60737438998565496</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>535</v>
+        <v>211</v>
       </c>
       <c r="B480">
-        <v>0.71195027403906597</v>
+        <v>-0.61208369810753904</v>
       </c>
       <c r="C480">
-        <v>5.6234953353468599E-2</v>
+        <v>0.28191639393745299</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>536</v>
+        <v>212</v>
       </c>
       <c r="B481">
-        <v>-0.85455482800018501</v>
+        <v>0.69087245861149305</v>
       </c>
       <c r="C481">
-        <v>-0.46738105451990802</v>
+        <v>-0.38548623802845799</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>537</v>
+        <v>474</v>
       </c>
       <c r="B482">
-        <v>-0.17486662088215399</v>
+        <v>0.60071549595792095</v>
       </c>
       <c r="C482">
-        <v>0.351216903117617</v>
+        <v>-0.22767189584276301</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>260</v>
+        <v>475</v>
       </c>
       <c r="B483">
-        <v>7.6620979928140306E-2</v>
+        <v>0.72548044858174199</v>
       </c>
       <c r="C483">
-        <v>0.49210089415622899</v>
+        <v>-0.18193914976660799</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="B484">
-        <v>0.63060875553568996</v>
+        <v>0.54333944756838104</v>
       </c>
       <c r="C484">
-        <v>-0.45112090912997199</v>
+        <v>8.8353990709222993E-2</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>538</v>
+        <v>476</v>
       </c>
       <c r="B485">
-        <v>-1.27697185036093</v>
+        <v>0.61045915117221605</v>
       </c>
       <c r="C485">
-        <v>-0.81637131756579795</v>
+        <v>-0.39419626767759602</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>539</v>
+        <v>477</v>
       </c>
       <c r="B486">
-        <v>-0.507288320559801</v>
+        <v>-0.13040605146100101</v>
       </c>
       <c r="C486">
-        <v>0.34405859134622502</v>
+        <v>-0.24919653838515099</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>540</v>
+        <v>214</v>
       </c>
       <c r="B487">
-        <v>-1.3608194452695801</v>
+        <v>-1.29499405826933</v>
       </c>
       <c r="C487">
-        <v>0.17954247101902901</v>
+        <v>-2.0452921155005899E-2</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>541</v>
-      </c>
-      <c r="B488">
-        <v>0.64619664715773295</v>
-      </c>
-      <c r="C488">
-        <v>-0.59513998659918399</v>
+        <v>625</v>
+      </c>
+      <c r="B488" t="s">
+        <v>659</v>
+      </c>
+      <c r="C488" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>542</v>
+        <v>478</v>
       </c>
       <c r="B489">
-        <v>-0.23393573920921101</v>
+        <v>-1.15074947512201</v>
       </c>
       <c r="C489">
-        <v>-2.2787105369271199E-2</v>
+        <v>-1.2278085253439199</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>543</v>
+        <v>479</v>
       </c>
       <c r="B490">
-        <v>-0.20274019372498001</v>
+        <v>-1.27457121320864</v>
       </c>
       <c r="C490">
-        <v>0.51598862351518104</v>
+        <v>-0.74402836514302095</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>544</v>
+        <v>480</v>
       </c>
       <c r="B491">
-        <v>-1.32334909812219</v>
+        <v>-1.2651190717503999</v>
       </c>
       <c r="C491">
-        <v>-0.98745404571467799</v>
+        <v>-1.0923419145867499</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>545</v>
+        <v>481</v>
       </c>
       <c r="B492">
-        <v>-0.212400941082769</v>
+        <v>-1.5673506953502101</v>
       </c>
       <c r="C492">
-        <v>0.58965973595124099</v>
+        <v>-0.33880569983488401</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>262</v>
+        <v>482</v>
       </c>
       <c r="B493">
-        <v>0.62187032173719903</v>
+        <v>0.61264013224908198</v>
       </c>
       <c r="C493">
-        <v>-5.9364408060479303E-2</v>
+        <v>-0.403237977880535</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>263</v>
+        <v>483</v>
       </c>
       <c r="B494">
-        <v>-0.54255393497750004</v>
+        <v>0.66711892885435597</v>
       </c>
       <c r="C494">
-        <v>-9.5051541618249094E-2</v>
+        <v>7.3241387227861804E-2</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>264</v>
+        <v>684</v>
       </c>
       <c r="B495">
-        <v>0.60973484391511801</v>
+        <v>0.74215480124724997</v>
       </c>
       <c r="C495">
-        <v>-0.27221736302544303</v>
+        <v>-0.38465000458535298</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>546</v>
+        <v>685</v>
       </c>
       <c r="B496">
-        <v>8.7804630693936195E-2</v>
+        <v>-1.27884814295923</v>
       </c>
       <c r="C496">
-        <v>0.118137673697226</v>
+        <v>-0.93573092969663996</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>547</v>
+        <v>484</v>
       </c>
       <c r="B497">
-        <v>-2.95365186066853E-2</v>
+        <v>-1.3242415006022801</v>
       </c>
       <c r="C497">
-        <v>0.59129812051511299</v>
+        <v>-0.55668454658299804</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>265</v>
+        <v>485</v>
       </c>
       <c r="B498">
-        <v>-0.10619130868007499</v>
+        <v>0.118094932819037</v>
       </c>
       <c r="C498">
-        <v>0.388138373464394</v>
+        <v>0.69015226184155598</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="B499">
-        <v>-1.2611112017500701</v>
+        <v>-1.4144972525974999</v>
       </c>
       <c r="C499">
-        <v>-0.14732651340581299</v>
+        <v>-0.17819950559011299</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>548</v>
+        <v>486</v>
       </c>
       <c r="B500">
-        <v>-0.14857287845794701</v>
+        <v>-0.250440736442332</v>
       </c>
       <c r="C500">
-        <v>0.33964321659674002</v>
+        <v>0.52262882716011705</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>549</v>
+        <v>487</v>
       </c>
       <c r="B501">
-        <v>0.67056049812626195</v>
+        <v>-0.81549102091147596</v>
       </c>
       <c r="C501">
-        <v>-5.21569104243172E-2</v>
+        <v>0.77922761591266598</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>550</v>
+        <v>216</v>
       </c>
       <c r="B502">
-        <v>-0.25524914473349503</v>
+        <v>2.9190380973390701E-3</v>
       </c>
       <c r="C502">
-        <v>0.381202896204347</v>
+        <v>0.11326424802124301</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>551</v>
+        <v>488</v>
       </c>
       <c r="B503">
-        <v>-0.21176026933467201</v>
+        <v>0.151110965138331</v>
       </c>
       <c r="C503">
-        <v>0.35270442432813798</v>
+        <v>0.75389742912664903</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>653</v>
+        <v>489</v>
       </c>
       <c r="B504">
-        <v>3.7365770436852401E-2</v>
+        <v>-1.0577905734366</v>
       </c>
       <c r="C504">
-        <v>-1.68330092514751</v>
+        <v>-0.101760887759816</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>552</v>
+        <v>217</v>
       </c>
       <c r="B505">
-        <v>0.69087878047800799</v>
+        <v>-1.11693894362823</v>
       </c>
       <c r="C505">
-        <v>-0.39128148829413001</v>
+        <v>-0.68421953775190303</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>553</v>
+        <v>218</v>
       </c>
       <c r="B506">
-        <v>0.79774257007999205</v>
+        <v>-1.38611145417578</v>
       </c>
       <c r="C506">
-        <v>-0.20992854779668599</v>
+        <v>-0.15820122438253501</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>267</v>
+        <v>490</v>
       </c>
       <c r="B507">
-        <v>-5.76448283419526E-2</v>
+        <v>-0.234195297046529</v>
       </c>
       <c r="C507">
-        <v>0.25505148431807301</v>
+        <v>0.84272049828233797</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>268</v>
+        <v>491</v>
       </c>
       <c r="B508">
-        <v>-9.1389987847245793E-2</v>
+        <v>0.1505722279102</v>
       </c>
       <c r="C508">
-        <v>0.46471250276883203</v>
+        <v>0.34631662775010802</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>554</v>
+        <v>219</v>
       </c>
       <c r="B509">
-        <v>-0.154066440901795</v>
+        <v>0.63637362316826696</v>
       </c>
       <c r="C509">
-        <v>0.47226285157793402</v>
+        <v>-0.39984739340486602</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>269</v>
+        <v>492</v>
       </c>
       <c r="B510">
-        <v>0.75247998780797998</v>
+        <v>-0.89933514310512397</v>
       </c>
       <c r="C510">
-        <v>-0.42288486430031802</v>
+        <v>-6.2730000246493597E-2</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>555</v>
+        <v>220</v>
       </c>
       <c r="B511">
-        <v>0.79925371807928203</v>
+        <v>-0.243961758223944</v>
       </c>
       <c r="C511">
-        <v>-0.50898384466213997</v>
+        <v>0.36551412401616201</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>556</v>
+        <v>221</v>
       </c>
       <c r="B512">
-        <v>-0.35580902078632798</v>
+        <v>-1.20423917169723</v>
       </c>
       <c r="C512">
-        <v>0.45183077449936099</v>
+        <v>-5.3054693675740401E-2</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>557</v>
+        <v>222</v>
       </c>
       <c r="B513">
-        <v>-8.2510961899354696E-2</v>
+        <v>-1.35911977050113</v>
       </c>
       <c r="C513">
-        <v>0.50296978386533697</v>
+        <v>1.9649885582383401E-2</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>270</v>
+        <v>493</v>
       </c>
       <c r="B514">
-        <v>7.3169944198632195E-2</v>
+        <v>-1.06845132274007</v>
       </c>
       <c r="C514">
-        <v>-0.22940292543468099</v>
+        <v>0.32067697503852399</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>271</v>
+        <v>686</v>
       </c>
       <c r="B515">
-        <v>-0.52320229054432399</v>
+        <v>-1.2580857873661899</v>
       </c>
       <c r="C515">
-        <v>-0.28567329937416902</v>
+        <v>-1.00189528931303</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="B516">
-        <v>0.113962020162683</v>
+        <v>0.55532158872739801</v>
       </c>
       <c r="C516">
-        <v>5.6415364895407501E-2</v>
+        <v>0.19165798153067901</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>558</v>
+        <v>224</v>
       </c>
       <c r="B517">
-        <v>-1.0337172906579</v>
+        <v>-0.33485985954502201</v>
       </c>
       <c r="C517">
-        <v>-0.44129230593002</v>
+        <v>0.33023573350096902</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>654</v>
+        <v>225</v>
       </c>
       <c r="B518">
-        <v>3.7365770436852401E-2</v>
+        <v>0.556182506696136</v>
       </c>
       <c r="C518">
-        <v>-1.68330092514751</v>
+        <v>-0.22553425362415599</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>655</v>
+        <v>226</v>
       </c>
       <c r="B519">
-        <v>-0.94815718272085503</v>
+        <v>-0.20551817389749999</v>
       </c>
       <c r="C519">
-        <v>0.67821394404990198</v>
+        <v>0.12800410529847001</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="B520">
-        <v>-0.26401657896415798</v>
+        <v>-0.51149520989409303</v>
       </c>
       <c r="C520">
-        <v>-6.7871425005546507E-2</v>
+        <v>0.166625339009905</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>559</v>
+        <v>494</v>
       </c>
       <c r="B521">
-        <v>0.123074893288913</v>
+        <v>-1.32980183516446</v>
       </c>
       <c r="C521">
-        <v>0.63774019131411597</v>
+        <v>-0.94014216450832699</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>560</v>
+        <v>495</v>
       </c>
       <c r="B522">
-        <v>-0.37268331037734997</v>
+        <v>-6.2536459805933406E-2</v>
       </c>
       <c r="C522">
-        <v>0.13975520343668901</v>
+        <v>0.68934663928700202</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>561</v>
+        <v>228</v>
       </c>
       <c r="B523">
-        <v>0.49684817986952001</v>
+        <v>-1.4949289708828</v>
       </c>
       <c r="C523">
-        <v>0.18076969753057101</v>
+        <v>-0.17716553161500301</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>562</v>
+        <v>496</v>
       </c>
       <c r="B524">
-        <v>8.3280676111545604E-2</v>
+        <v>0.560542148657315</v>
       </c>
       <c r="C524">
-        <v>-0.24771779255609</v>
+        <v>0.82984924378356595</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>563</v>
+        <v>229</v>
       </c>
       <c r="B525">
-        <v>-0.32467947652288998</v>
+        <v>-0.197051753858864</v>
       </c>
       <c r="C525">
-        <v>-0.158985570783301</v>
+        <v>0.392920443041685</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="B526">
-        <v>-0.60369560583433401</v>
+        <v>0.123996825035149</v>
       </c>
       <c r="C526">
-        <v>-4.39447329726666E-2</v>
+        <v>0.50067935098323302</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>564</v>
+        <v>497</v>
       </c>
       <c r="B527">
-        <v>0.44572555579794598</v>
+        <v>0.55114493512364804</v>
       </c>
       <c r="C527">
-        <v>-0.29266494396962001</v>
+        <v>-0.18018054013894999</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>565</v>
+        <v>231</v>
       </c>
       <c r="B528">
-        <v>0.83835540071551395</v>
+        <v>-0.50313609839913598</v>
       </c>
       <c r="C528">
-        <v>-0.28219598102752202</v>
+        <v>-0.20707368880098501</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>566</v>
+        <v>498</v>
       </c>
       <c r="B529">
-        <v>-1.5469651544760501</v>
+        <v>-0.94557593680206797</v>
       </c>
       <c r="C529">
-        <v>-0.68685394030383695</v>
+        <v>0.83262579928571701</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>567</v>
+        <v>499</v>
       </c>
       <c r="B530">
-        <v>0.60574413714332898</v>
+        <v>0.27167775957370399</v>
       </c>
       <c r="C530">
-        <v>-0.43580119304948001</v>
+        <v>0.30993122524685901</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>568</v>
+        <v>232</v>
       </c>
       <c r="B531">
-        <v>-0.74769334230589701</v>
+        <v>0.601831408357694</v>
       </c>
       <c r="C531">
-        <v>0.33681628957020399</v>
+        <v>0.22310775786190301</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>275</v>
+        <v>500</v>
       </c>
       <c r="B532">
-        <v>0.70374495465206</v>
+        <v>0.66551749243437397</v>
       </c>
       <c r="C532">
-        <v>-0.33417758801990899</v>
+        <v>0.29525667877905298</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>569</v>
+        <v>501</v>
       </c>
       <c r="B533">
-        <v>-1.18289412448975</v>
+        <v>-1.52978174219999</v>
       </c>
       <c r="C533">
-        <v>-1.3030251586725801</v>
+        <v>-0.20056324712292101</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>276</v>
+        <v>502</v>
       </c>
       <c r="B534">
-        <v>3.9445984269936799E-2</v>
+        <v>0.67559867122643102</v>
       </c>
       <c r="C534">
-        <v>0.61878594867035197</v>
+        <v>-0.42630935350244697</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>277</v>
+        <v>503</v>
       </c>
       <c r="B535">
-        <v>4.8176685897115303E-2</v>
+        <v>-1.4900435637533601E-2</v>
       </c>
       <c r="C535">
-        <v>0.47603351254501303</v>
+        <v>-0.54828976346846303</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>278</v>
+        <v>504</v>
       </c>
       <c r="B536">
-        <v>-0.29131560932085598</v>
+        <v>0.64317547538795405</v>
       </c>
       <c r="C536">
-        <v>0.31259721499466497</v>
+        <v>-0.19469914122627299</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>570</v>
+        <v>505</v>
       </c>
       <c r="B537">
-        <v>-0.36238949672104798</v>
+        <v>-5.5259644867955801E-2</v>
       </c>
       <c r="C537">
-        <v>-5.81737678981053E-2</v>
+        <v>0.41063803636923901</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>571</v>
+        <v>233</v>
       </c>
       <c r="B538">
-        <v>-0.29099506999973401</v>
+        <v>-0.414014181054497</v>
       </c>
       <c r="C538">
-        <v>-2.51834711813512E-2</v>
+        <v>-0.60081386683465798</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>572</v>
+        <v>234</v>
       </c>
       <c r="B539">
-        <v>-0.430014897205372</v>
+        <v>-0.14933224876290199</v>
       </c>
       <c r="C539">
-        <v>-7.6751778270812407E-2</v>
+        <v>0.37171901739126301</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>573</v>
+        <v>235</v>
       </c>
       <c r="B540">
-        <v>0.57459231391529597</v>
+        <v>-3.2863895399755801E-3</v>
       </c>
       <c r="C540">
-        <v>-0.39880694890186102</v>
+        <v>0.33877424184681398</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>279</v>
+        <v>506</v>
       </c>
       <c r="B541">
-        <v>-0.325197397217803</v>
+        <v>-1.313079896611</v>
       </c>
       <c r="C541">
-        <v>0.16318451002721901</v>
+        <v>-0.34241272045348897</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>574</v>
+        <v>687</v>
       </c>
       <c r="B542">
-        <v>0.67914991045202799</v>
+        <v>-1.27047368374627</v>
       </c>
       <c r="C542">
-        <v>-0.165071460958225</v>
+        <v>-1.4050042945749801</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="B543">
-        <v>-1.1617973480014101</v>
+        <v>-1.2713115654109699</v>
       </c>
       <c r="C543">
-        <v>0.19573943252421</v>
+        <v>-4.0667870843500202E-2</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>575</v>
+        <v>507</v>
       </c>
       <c r="B544">
-        <v>0.66467479162961896</v>
+        <v>-1.38790517478802</v>
       </c>
       <c r="C544">
-        <v>-0.27549161959226798</v>
+        <v>0.160381416446886</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>281</v>
+        <v>508</v>
       </c>
       <c r="B545">
-        <v>7.6410307568087393E-2</v>
+        <v>0.51918639594918303</v>
       </c>
       <c r="C545">
-        <v>-0.23117462777508699</v>
+        <v>-1.5798674447185499E-2</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>576</v>
+        <v>509</v>
       </c>
       <c r="B546">
-        <v>-0.241862921839512</v>
+        <v>-1.3393655800489299</v>
       </c>
       <c r="C546">
-        <v>1.1535087211774999</v>
+        <v>-0.87501666442609904</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>282</v>
+        <v>510</v>
       </c>
       <c r="B547">
-        <v>0.67104115231125805</v>
+        <v>-1.1403066223657301</v>
       </c>
       <c r="C547">
-        <v>-0.24499032005563201</v>
+        <v>-0.89372631265914104</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>577</v>
+        <v>237</v>
       </c>
       <c r="B548">
-        <v>0.85172899653860001</v>
+        <v>-1.1467393415551299</v>
       </c>
       <c r="C548">
-        <v>-0.46934656397511298</v>
+        <v>7.42623298490903E-2</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>283</v>
+        <v>238</v>
       </c>
       <c r="B549">
-        <v>-0.49269102987032598</v>
+        <v>-0.15900415915671601</v>
       </c>
       <c r="C549">
-        <v>0.139734301233468</v>
+        <v>0.24680696547488901</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>578</v>
+        <v>511</v>
       </c>
       <c r="B550">
-        <v>0.73611976241805099</v>
+        <v>-1.2339363730128501</v>
       </c>
       <c r="C550">
-        <v>-1.6869240472807599E-2</v>
+        <v>-1.41776199581864</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>284</v>
+        <v>512</v>
       </c>
       <c r="B551">
-        <v>0.68725649846128301</v>
+        <v>-1.209880955349</v>
       </c>
       <c r="C551">
-        <v>-0.30295877349356798</v>
+        <v>-1.0538278053341801</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>285</v>
+        <v>513</v>
       </c>
       <c r="B552">
-        <v>5.2225096790569601E-2</v>
+        <v>-0.55300856333496196</v>
       </c>
       <c r="C552">
-        <v>0.28286883038666299</v>
+        <v>8.6159353679703607E-2</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="B553">
-        <v>0.75754267483929005</v>
+        <v>0.237557875463661</v>
       </c>
       <c r="C553">
-        <v>-0.418119063530483</v>
+        <v>0.34779632101790497</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>579</v>
+        <v>514</v>
       </c>
       <c r="B554">
-        <v>0.25705837333761999</v>
+        <v>-0.40671474198249802</v>
       </c>
       <c r="C554">
-        <v>-0.31943218364987502</v>
+        <v>0.28600746407633698</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="B555">
-        <v>-0.71035210816071004</v>
+        <v>-1.1728291554880199</v>
       </c>
       <c r="C555">
-        <v>1.8213603905379499E-2</v>
+        <v>-0.48946271478121001</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>580</v>
+        <v>515</v>
       </c>
       <c r="B556">
-        <v>-0.30175564367060997</v>
+        <v>0.52814538242690301</v>
       </c>
       <c r="C556">
-        <v>-0.257273114908528</v>
+        <v>-0.30710437783136701</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>581</v>
+        <v>516</v>
       </c>
       <c r="B557">
-        <v>-0.93401747203002095</v>
+        <v>-1.24432826899878</v>
       </c>
       <c r="C557">
-        <v>7.6255411576698101E-2</v>
+        <v>-0.46733542636973202</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>582</v>
+        <v>241</v>
       </c>
       <c r="B558">
-        <v>0.57994245505229103</v>
+        <v>0.27146786990051303</v>
       </c>
       <c r="C558">
-        <v>0.41924497721976201</v>
+        <v>0.16189643783365901</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>627</v>
+        <v>517</v>
       </c>
       <c r="B559">
-        <v>-4.7144783509839097E-2</v>
+        <v>0.58243924332372199</v>
       </c>
       <c r="C559">
-        <v>-1.8301038842261901</v>
+        <v>-0.220743107147895</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>583</v>
+        <v>242</v>
       </c>
       <c r="B560">
-        <v>0.752010413490799</v>
+        <v>0.55455317553021599</v>
       </c>
       <c r="C560">
-        <v>-0.64995161174006999</v>
+        <v>-0.17087690113891299</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>584</v>
+        <v>688</v>
       </c>
       <c r="B561">
-        <v>-1.38491045626701</v>
+        <v>0.75082407380564897</v>
       </c>
       <c r="C561">
-        <v>-0.80075026051619602</v>
+        <v>-0.40789043470984998</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>628</v>
+        <v>518</v>
       </c>
       <c r="B562">
-        <v>-0.32391203879466401</v>
+        <v>-1.15074947512201</v>
       </c>
       <c r="C562">
-        <v>2.6395715492607E-2</v>
+        <v>-1.2278085253439199</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>629</v>
+        <v>519</v>
       </c>
       <c r="B563">
-        <v>-0.53068342002212499</v>
+        <v>0.51799358254547501</v>
       </c>
       <c r="C563">
-        <v>-1.4032618102054801E-2</v>
+        <v>-0.29543886486272403</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>630</v>
+        <v>243</v>
       </c>
       <c r="B564">
-        <v>2.4057344721291899E-2</v>
+        <v>-1.25819818485927</v>
       </c>
       <c r="C564">
-        <v>0.62139271593011702</v>
+        <v>-0.99138100762735404</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>631</v>
+        <v>244</v>
       </c>
       <c r="B565">
-        <v>-1.2116526003210299</v>
+        <v>0.65681122981835105</v>
       </c>
       <c r="C565">
-        <v>-1.13161298634854</v>
+        <v>-0.27045548241942402</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>632</v>
+        <v>520</v>
       </c>
       <c r="B566">
-        <v>-0.191344494665003</v>
+        <v>0.74673356847111705</v>
       </c>
       <c r="C566">
-        <v>0.54762682847745503</v>
+        <v>-8.5507288462598002E-2</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>633</v>
+        <v>521</v>
       </c>
       <c r="B567">
-        <v>0.74500885362619795</v>
+        <v>0.122478087496045</v>
       </c>
       <c r="C567">
-        <v>0.28203486337424499</v>
+        <v>0.62989986730355196</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>634</v>
+        <v>522</v>
       </c>
       <c r="B568">
-        <v>-0.41049671964951001</v>
+        <v>-0.26628496717765998</v>
       </c>
       <c r="C568">
-        <v>0.18509417028681099</v>
+        <v>0.17677472605361699</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>635</v>
+        <v>523</v>
       </c>
       <c r="B569">
-        <v>3.04749759261639E-2</v>
+        <v>-1.22192861835579</v>
       </c>
       <c r="C569">
-        <v>0.56890202826173597</v>
+        <v>-0.85598786218138601</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>636</v>
+        <v>524</v>
       </c>
       <c r="B570">
-        <v>0.77136598451572203</v>
+        <v>0.72886399819796799</v>
       </c>
       <c r="C570">
-        <v>-3.6069576534292297E-2</v>
+        <v>-0.51577788625680099</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>637</v>
+        <v>245</v>
       </c>
       <c r="B571">
-        <v>-1.55295942338985</v>
+        <v>0.53420448126855402</v>
       </c>
       <c r="C571">
-        <v>-0.78180439298368198</v>
+        <v>-0.10783690177682</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>88</v>
+        <v>525</v>
       </c>
       <c r="B572">
-        <v>0.671337328675778</v>
+        <v>0.24499472757316099</v>
       </c>
       <c r="C572">
-        <v>-0.32019655600886598</v>
+        <v>0.79274151222752298</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
       <c r="B573">
-        <v>-1.1036984000082599</v>
+        <v>-1.2118940497302999</v>
       </c>
       <c r="C573">
-        <v>-1.39480947456717</v>
+        <v>-0.20410086815187101</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>586</v>
+        <v>246</v>
       </c>
       <c r="B574">
-        <v>-1.1971794408572201</v>
+        <v>-1.3369092005832199</v>
       </c>
       <c r="C574">
-        <v>0.85537616957015805</v>
+        <v>-0.84952473794843597</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="B575">
-        <v>-0.32245927923852702</v>
+        <v>-0.144728958898039</v>
       </c>
       <c r="C575">
-        <v>0.174162915350975</v>
+        <v>0.56782502245047795</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>90</v>
+        <v>248</v>
       </c>
       <c r="B576">
-        <v>-1.18528728582426</v>
+        <v>0.65145221886149995</v>
       </c>
       <c r="C576">
-        <v>-1.3161718320824201</v>
+        <v>-0.31354783785635398</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>587</v>
+        <v>689</v>
       </c>
       <c r="B577">
-        <v>-0.28372378099038498</v>
+        <v>0.86390793681998301</v>
       </c>
       <c r="C577">
-        <v>0.403332960721759</v>
+        <v>-0.32493387741532498</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>91</v>
+        <v>527</v>
       </c>
       <c r="B578">
-        <v>0.65953393829148899</v>
+        <v>-0.13792923684307701</v>
       </c>
       <c r="C578">
-        <v>-0.19812776830848899</v>
+        <v>1.1326597436760699</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="B579">
-        <v>0.42056922455671197</v>
+        <v>0.61355140017534504</v>
       </c>
       <c r="C579">
-        <v>0.77817499340394702</v>
+        <v>0.36686032612784902</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>589</v>
+        <v>249</v>
       </c>
       <c r="B580">
-        <v>-0.27675182741847199</v>
+        <v>0.72426791825860504</v>
       </c>
       <c r="C580">
-        <v>0.457267412356548</v>
+        <v>-0.38099072990684002</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>92</v>
+        <v>529</v>
       </c>
       <c r="B581">
-        <v>-1.1562363100700701</v>
+        <v>-1.27632800588467</v>
       </c>
       <c r="C581">
-        <v>-1.3537215817748001</v>
+        <v>-7.1611378635206002E-2</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="B582">
-        <v>-5.90133862528898E-2</v>
+        <v>-0.59832991878418995</v>
       </c>
       <c r="C582">
-        <v>1.4745991751789001E-2</v>
+        <v>0.30976570675359699</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>94</v>
+        <v>251</v>
       </c>
       <c r="B583">
-        <v>0.65531875037195897</v>
+        <v>-1.23323933793574</v>
       </c>
       <c r="C583">
-        <v>-0.29769862412022202</v>
+        <v>-0.96597891503947497</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="B584">
-        <v>0.42655046044814798</v>
+        <v>-5.6279754547774799E-2</v>
       </c>
       <c r="C584">
-        <v>-0.69283388519696698</v>
+        <v>-0.53448640132715697</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>95</v>
+        <v>531</v>
       </c>
       <c r="B585">
-        <v>-1.4527740986013</v>
+        <v>-1.4310425103348401</v>
       </c>
       <c r="C585">
-        <v>-0.69159793497278299</v>
+        <v>-0.24551944246143001</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="B586">
-        <v>-1.1860050704098599</v>
+        <v>0.57382709467652204</v>
       </c>
       <c r="C586">
-        <v>-1.2973119420559101</v>
+        <v>-0.25308385515332499</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="B587">
-        <v>-0.47291772259965098</v>
+        <v>0.67955801851502196</v>
       </c>
       <c r="C587">
-        <v>0.11296429055660299</v>
+        <v>-0.30736402086958597</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>98</v>
+        <v>254</v>
       </c>
       <c r="B588">
-        <v>-1.1708405408383999</v>
+        <v>-1.25273503468268</v>
       </c>
       <c r="C588">
-        <v>-1.3222998023189401</v>
+        <v>-0.27538328601791401</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>591</v>
+        <v>255</v>
       </c>
       <c r="B589">
-        <v>4.9089905282595103E-2</v>
+        <v>-1.10583557490996</v>
       </c>
       <c r="C589">
-        <v>0.52605347953366699</v>
+        <v>-0.40410561537407402</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>99</v>
+        <v>256</v>
       </c>
       <c r="B590">
-        <v>-1.03772340868916</v>
+        <v>8.0117036870752695E-2</v>
       </c>
       <c r="C590">
-        <v>-3.5417686777287502E-2</v>
+        <v>0.43695400920233501</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>592</v>
+        <v>532</v>
       </c>
       <c r="B591">
-        <v>-1.2735983225665599</v>
+        <v>-1.1397475851691199</v>
       </c>
       <c r="C591">
-        <v>0.18190033526805999</v>
+        <v>0.59260839369797602</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>593</v>
+        <v>533</v>
       </c>
       <c r="B592">
-        <v>-0.408824161559106</v>
+        <v>0.49096110125814002</v>
       </c>
       <c r="C592">
-        <v>-0.16000874893005901</v>
+        <v>-0.45459917827094198</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>594</v>
+        <v>257</v>
       </c>
       <c r="B593">
-        <v>-1.15645961806272</v>
+        <v>0.68839540383743403</v>
       </c>
       <c r="C593">
-        <v>-0.86009608244846403</v>
+        <v>-0.36331955082769102</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>100</v>
+        <v>258</v>
       </c>
       <c r="B594">
-        <v>0.64158807917013305</v>
+        <v>0.37772591098300401</v>
       </c>
       <c r="C594">
-        <v>-0.26787526074747597</v>
+        <v>0.27946239610999002</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>101</v>
+        <v>534</v>
       </c>
       <c r="B595">
-        <v>0.160963433269147</v>
+        <v>0.68844109897085304</v>
       </c>
       <c r="C595">
-        <v>0.35972468955993098</v>
+        <v>8.8172214588453604E-2</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>102</v>
+        <v>259</v>
       </c>
       <c r="B596">
-        <v>0.69336773691883702</v>
+        <v>-6.67075526918465E-2</v>
       </c>
       <c r="C596">
-        <v>-0.39749170038683401</v>
+        <v>0.41519847630411899</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>103</v>
+        <v>535</v>
       </c>
       <c r="B597">
-        <v>-0.11331993784303</v>
+        <v>-1.0886338887098299</v>
       </c>
       <c r="C597">
-        <v>0.436402782469546</v>
+        <v>-0.63258171678928599</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>656</v>
+        <v>260</v>
       </c>
       <c r="B598">
-        <v>-4.7144783509839097E-2</v>
+        <v>0.105044400740821</v>
       </c>
       <c r="C598">
-        <v>-1.8301038842261901</v>
+        <v>0.47243952470093398</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>595</v>
+        <v>536</v>
       </c>
       <c r="B599">
-        <v>-0.297112957753147</v>
+        <v>-0.13127600800654399</v>
       </c>
       <c r="C599">
-        <v>0.72003897424150298</v>
+        <v>0.34696786544271802</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="B600">
-        <v>-1.1727770624493301</v>
+        <v>0.58935573654498097</v>
       </c>
       <c r="C600">
-        <v>-1.39023002551668</v>
+        <v>-0.41102835307729702</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>105</v>
+        <v>537</v>
       </c>
       <c r="B601">
-        <v>-0.13295726221649301</v>
+        <v>-1.3338712975325799</v>
       </c>
       <c r="C601">
-        <v>4.4613047598032599E-2</v>
+        <v>-0.30650824616640998</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>106</v>
+        <v>538</v>
       </c>
       <c r="B602">
-        <v>-0.49789195380810602</v>
+        <v>-0.41679221572713798</v>
       </c>
       <c r="C602">
-        <v>9.0532891918262207E-2</v>
+        <v>0.44214671312691101</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>107</v>
+        <v>539</v>
       </c>
       <c r="B603">
-        <v>0.391751039290408</v>
+        <v>-1.2353703737330901</v>
       </c>
       <c r="C603">
-        <v>0.25261910494338602</v>
+        <v>0.50159468608900404</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>596</v>
+        <v>540</v>
       </c>
       <c r="B604">
-        <v>-0.28093583235144098</v>
+        <v>0.59722160990211604</v>
       </c>
       <c r="C604">
-        <v>0.56539062168271303</v>
+        <v>-0.54912043209065398</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>597</v>
+        <v>541</v>
       </c>
       <c r="B605">
-        <v>-0.35490715912799697</v>
+        <v>-0.19997167181626899</v>
       </c>
       <c r="C605">
-        <v>0.26810802524135402</v>
+        <v>3.0458990766584801E-2</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>598</v>
+        <v>542</v>
       </c>
       <c r="B606">
-        <v>-0.46114648363177002</v>
+        <v>-0.14193367220643499</v>
       </c>
       <c r="C606">
-        <v>0.31899626444525803</v>
+        <v>0.51254487038674901</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>599</v>
+        <v>543</v>
       </c>
       <c r="B607">
-        <v>-1.5992075314724501</v>
+        <v>-1.3710667206632901</v>
       </c>
       <c r="C607">
-        <v>-1.9834039759392099E-2</v>
+        <v>-0.59379874724583603</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>600</v>
+        <v>544</v>
       </c>
       <c r="B608">
-        <v>0.69576198446517401</v>
+        <v>-0.153341564144505</v>
       </c>
       <c r="C608">
-        <v>-0.43884661709398898</v>
+        <v>0.57862878044150101</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>657</v>
+        <v>262</v>
       </c>
       <c r="B609">
-        <v>-1.0360125548667101</v>
+        <v>0.65349715087517901</v>
       </c>
       <c r="C609">
-        <v>0.106773614099248</v>
+        <v>-0.154946937409674</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>601</v>
+        <v>263</v>
       </c>
       <c r="B610">
-        <v>-1.2116526003210299</v>
+        <v>-0.71767731458855599</v>
       </c>
       <c r="C610">
-        <v>-1.13161298634854</v>
+        <v>-0.25706046496429202</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>602</v>
+        <v>264</v>
       </c>
       <c r="B611">
-        <v>-1.1093719914759901</v>
+        <v>0.58287799340492996</v>
       </c>
       <c r="C611">
-        <v>-1.7292295115340499</v>
+        <v>-0.23414424711012699</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>108</v>
+        <v>545</v>
       </c>
       <c r="B612">
-        <v>-0.57530160541771302</v>
+        <v>9.0206476088278906E-2</v>
       </c>
       <c r="C612">
-        <v>0.50246933378430603</v>
+        <v>0.122275712762855</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>109</v>
+        <v>546</v>
       </c>
       <c r="B613">
-        <v>-1.1874621246702901</v>
+        <v>1.25139394982633E-2</v>
       </c>
       <c r="C613">
-        <v>-1.1968853164837301</v>
+        <v>0.56958452487200995</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>603</v>
+        <v>265</v>
       </c>
       <c r="B614">
-        <v>-1.1403539294426099</v>
+        <v>-6.6965631580309604E-2</v>
       </c>
       <c r="C614">
-        <v>-1.4527916466508699</v>
+        <v>0.381236232304904</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>110</v>
+        <v>266</v>
       </c>
       <c r="B615">
-        <v>-1.1623062887570601</v>
+        <v>-1.18907752513925</v>
       </c>
       <c r="C615">
-        <v>-1.4122861490534</v>
+        <v>0.170770332661241</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>111</v>
+        <v>547</v>
       </c>
       <c r="B616">
-        <v>5.20740114919837E-2</v>
+        <v>-9.7940148400486607E-2</v>
       </c>
       <c r="C616">
-        <v>0.310701790649974</v>
+        <v>0.34404693676370601</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>112</v>
+        <v>548</v>
       </c>
       <c r="B617">
-        <v>4.4374281234797301E-2</v>
+        <v>0.65242795424302502</v>
       </c>
       <c r="C617">
-        <v>0.416891306863166</v>
+        <v>-2.6079212140880999E-2</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>113</v>
+        <v>549</v>
       </c>
       <c r="B618">
-        <v>0.69208439686148004</v>
+        <v>-0.20711898636149101</v>
       </c>
       <c r="C618">
-        <v>-0.452111991700751</v>
+        <v>0.36208810944571701</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="B619">
-        <v>-0.25524914473349503</v>
+        <v>-0.15771026514876199</v>
       </c>
       <c r="C619">
-        <v>0.381202896204347</v>
+        <v>0.357246160078524</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>114</v>
-      </c>
-      <c r="B620">
-        <v>-0.74252075751759194</v>
-      </c>
-      <c r="C620">
-        <v>-0.66804595867256</v>
+        <v>652</v>
+      </c>
+      <c r="B620" t="s">
+        <v>659</v>
+      </c>
+      <c r="C620" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>605</v>
+        <v>551</v>
       </c>
       <c r="B621">
-        <v>-0.25378417287411598</v>
+        <v>0.63941859783252997</v>
       </c>
       <c r="C621">
-        <v>0.440869201352801</v>
+        <v>-0.36594170153449601</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>606</v>
+        <v>552</v>
       </c>
       <c r="B622">
-        <v>0.75542703764677299</v>
+        <v>0.74942538862371399</v>
       </c>
       <c r="C622">
-        <v>-0.61094130771663202</v>
+        <v>-0.17861383076019799</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>658</v>
+        <v>267</v>
       </c>
       <c r="B623">
-        <v>-8.3516048577480503E-2</v>
+        <v>-2.1291274352873701E-2</v>
       </c>
       <c r="C623">
-        <v>-1.7095247786444501</v>
+        <v>0.31491466363202802</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="B624">
-        <v>-0.700644848448298</v>
+        <v>-5.03885247155288E-2</v>
       </c>
       <c r="C624">
-        <v>-9.5388551490347404E-2</v>
+        <v>0.48117197099008702</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>607</v>
+        <v>553</v>
       </c>
       <c r="B625">
-        <v>-0.44028141764092399</v>
+        <v>-0.10361939354883599</v>
       </c>
       <c r="C625">
-        <v>0.236517632750224</v>
+        <v>0.46193337834355802</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>116</v>
+        <v>269</v>
       </c>
       <c r="B626">
-        <v>-0.23589965441874999</v>
+        <v>0.711415292376394</v>
       </c>
       <c r="C626">
-        <v>-8.9766228233822097E-3</v>
+        <v>-0.37300935668530999</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>608</v>
+        <v>690</v>
       </c>
       <c r="B627">
-        <v>-1.0482606741878</v>
+        <v>0.86390793681998301</v>
       </c>
       <c r="C627">
-        <v>-1.5235775960073099</v>
+        <v>-0.32493387741532498</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>117</v>
+        <v>554</v>
       </c>
       <c r="B628">
-        <v>-1.4356197859509801</v>
+        <v>0.74972755417733505</v>
       </c>
       <c r="C628">
-        <v>-0.68757291479168103</v>
+        <v>-0.477262262828341</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>118</v>
+        <v>555</v>
       </c>
       <c r="B629">
-        <v>-0.43069255208818502</v>
+        <v>-0.28532213965723102</v>
       </c>
       <c r="C629">
-        <v>0.12931396545913301</v>
+        <v>0.46686651794702799</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>609</v>
+        <v>556</v>
       </c>
       <c r="B630">
-        <v>-0.49549758692664703</v>
+        <v>-4.3844382075098401E-2</v>
       </c>
       <c r="C630">
-        <v>0.45992318545773803</v>
+        <v>0.489055187947535</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>610</v>
+        <v>270</v>
       </c>
       <c r="B631">
-        <v>-1.15814437045622</v>
+        <v>7.2427671743960295E-2</v>
       </c>
       <c r="C631">
-        <v>-1.38200420370414</v>
+        <v>-0.104071087107849</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>611</v>
+        <v>271</v>
       </c>
       <c r="B632">
-        <v>0.46279452986244202</v>
+        <v>-0.81100271524024503</v>
       </c>
       <c r="C632">
-        <v>-0.706910527119744</v>
+        <v>-0.43825752355793901</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>612</v>
+        <v>272</v>
       </c>
       <c r="B633">
-        <v>0.20123886416700901</v>
+        <v>0.106962504507225</v>
       </c>
       <c r="C633">
-        <v>0.54696841289542197</v>
+        <v>2.86729154191613E-2</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>659</v>
+        <v>557</v>
       </c>
       <c r="B634">
-        <v>-1.1217031484992499</v>
+        <v>-1.01526435681517</v>
       </c>
       <c r="C634">
-        <v>-1.48071804486904</v>
+        <v>-0.164411288783162</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>119</v>
+        <v>653</v>
       </c>
       <c r="B635">
-        <v>-1.1185188032409199</v>
+        <v>-0.81309706343243204</v>
       </c>
       <c r="C635">
-        <v>0.19420406503283899</v>
+        <v>0.819296067166009</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>120</v>
+        <v>273</v>
       </c>
       <c r="B636">
-        <v>0.68996696912645605</v>
+        <v>-0.20639714066970999</v>
       </c>
       <c r="C636">
-        <v>-0.25814512919020499</v>
+        <v>3.3261673135659697E-2</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>121</v>
+        <v>558</v>
       </c>
       <c r="B637">
-        <v>0.204383669370272</v>
+        <v>0.15497988753331701</v>
       </c>
       <c r="C637">
-        <v>7.6565395959690793E-2</v>
+        <v>0.61202445625675705</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>122</v>
+        <v>559</v>
       </c>
       <c r="B638">
-        <v>-0.14688452350418599</v>
+        <v>-0.32437786381014</v>
       </c>
       <c r="C638">
-        <v>0.26543311776379602</v>
+        <v>0.19564634085838301</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>123</v>
+        <v>560</v>
       </c>
       <c r="B639">
-        <v>-0.27200334487574301</v>
+        <v>0.61800062828664004</v>
       </c>
       <c r="C639">
-        <v>0.120724570435067</v>
+        <v>-0.188638583616523</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>124</v>
+        <v>561</v>
       </c>
       <c r="B640">
-        <v>-1.2581174008749099E-2</v>
+        <v>-0.249015909310461</v>
       </c>
       <c r="C640">
-        <v>3.3225300085588397E-2</v>
+        <v>-0.46569408476458601</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>125</v>
+        <v>562</v>
       </c>
       <c r="B641">
-        <v>0.73468261065019902</v>
+        <v>-0.27789593412340402</v>
       </c>
       <c r="C641">
-        <v>-0.41344144443803399</v>
+        <v>-8.1789281311300505E-2</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>613</v>
+        <v>274</v>
       </c>
       <c r="B642">
-        <v>0.59897739915673398</v>
+        <v>-0.57514542678509495</v>
       </c>
       <c r="C642">
-        <v>-0.43635566060200698</v>
+        <v>0.115927477799715</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>660</v>
+        <v>563</v>
       </c>
       <c r="B643">
-        <v>0.89000614952137402</v>
+        <v>0.43382768145505302</v>
       </c>
       <c r="C643">
-        <v>-0.24216815421941201</v>
+        <v>-0.22997828287288</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="B644">
-        <v>-1.7506623372877199</v>
+        <v>0.79619300524595804</v>
       </c>
       <c r="C644">
-        <v>-0.12570859243025101</v>
+        <v>-0.24346571974921</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>126</v>
+        <v>565</v>
       </c>
       <c r="B645">
-        <v>-1.3563635736759601</v>
+        <v>-1.5432746833784201</v>
       </c>
       <c r="C645">
-        <v>-0.65953984015276901</v>
+        <v>-0.224405838333087</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="B646">
-        <v>-1.0482606741878</v>
+        <v>0.55423985659414199</v>
       </c>
       <c r="C646">
-        <v>-1.5235775960073099</v>
+        <v>-0.40347608253416201</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>616</v>
+        <v>567</v>
       </c>
       <c r="B647">
-        <v>-0.19991535887115999</v>
+        <v>-0.5574736863966</v>
       </c>
       <c r="C647">
-        <v>-0.151681061994001</v>
+        <v>0.41583189482697303</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>617</v>
+        <v>275</v>
       </c>
       <c r="B648">
-        <v>-1.32728537490281</v>
+        <v>0.70420105144334799</v>
       </c>
       <c r="C648">
-        <v>-0.87128157180993304</v>
+        <v>-0.34248279208119897</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>127</v>
+        <v>568</v>
       </c>
       <c r="B649">
-        <v>-0.37533004098302097</v>
+        <v>-1.24986116060932</v>
       </c>
       <c r="C649">
-        <v>0.101964686537519</v>
+        <v>-0.98214629488956096</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>128</v>
+        <v>276</v>
       </c>
       <c r="B650">
-        <v>-0.56591212899068699</v>
+        <v>7.8375203800964299E-2</v>
       </c>
       <c r="C650">
-        <v>0.14415870828664901</v>
+        <v>0.59218923645155896</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="B651">
-        <v>0.136143868226557</v>
+        <v>8.5545355640758602E-2</v>
       </c>
       <c r="C651">
-        <v>0.51719589619621098</v>
+        <v>0.469226798486437</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>618</v>
+        <v>278</v>
       </c>
       <c r="B652">
-        <v>-0.43104158129116699</v>
+        <v>-0.238459524095648</v>
       </c>
       <c r="C652">
-        <v>-0.19855631656286499</v>
+        <v>0.32009641365527902</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>661</v>
+        <v>569</v>
       </c>
       <c r="B653">
-        <v>0.32545336014321302</v>
+        <v>-0.54545423387705505</v>
       </c>
       <c r="C653">
-        <v>1.3597113762378501</v>
+        <v>-0.17296644656096999</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>619</v>
+        <v>570</v>
       </c>
       <c r="B654">
-        <v>-0.72520671222222399</v>
+        <v>-0.244408353557314</v>
       </c>
       <c r="C654">
-        <v>-0.37462081481210902</v>
+        <v>4.4007214873052397E-2</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>620</v>
+        <v>571</v>
       </c>
       <c r="B655">
-        <v>-0.48112781956858303</v>
+        <v>-0.39128628514612801</v>
       </c>
       <c r="C655">
-        <v>0.62662226633774598</v>
+        <v>0.55034799562494796</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>621</v>
+        <v>572</v>
       </c>
       <c r="B656">
-        <v>-1.4004934811448999</v>
+        <v>0.537793767677057</v>
       </c>
       <c r="C656">
-        <v>-0.78856068405762303</v>
+        <v>-0.358103970528516</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>130</v>
+        <v>691</v>
       </c>
       <c r="B657">
-        <v>-0.50137693585284704</v>
+        <v>-1.30556980029975</v>
       </c>
       <c r="C657">
-        <v>0.12962230824193899</v>
+        <v>-1.05637306985751</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>622</v>
+        <v>279</v>
       </c>
       <c r="B658">
-        <v>-1.23210057645153</v>
+        <v>-0.27066885662665202</v>
       </c>
       <c r="C658">
-        <v>-0.64118282398485305</v>
+        <v>0.212573935687805</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>623</v>
+        <v>573</v>
       </c>
       <c r="B659">
-        <v>-1.11207621955779</v>
+        <v>0.75176080434161097</v>
       </c>
       <c r="C659">
-        <v>0.5480535887279</v>
+        <v>-0.250937066819027</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>280</v>
+      </c>
+      <c r="B660">
+        <v>-1.0547699327834901</v>
+      </c>
+      <c r="C660">
+        <v>0.43084781312160503</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>574</v>
+      </c>
+      <c r="B661">
+        <v>0.62441218683622202</v>
+      </c>
+      <c r="C661">
+        <v>-0.24597176915399299</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>281</v>
+      </c>
+      <c r="B662">
+        <v>8.7893035371629805E-2</v>
+      </c>
+      <c r="C662">
+        <v>-0.116815612556043</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>575</v>
+      </c>
+      <c r="B663">
+        <v>-0.13792923684307701</v>
+      </c>
+      <c r="C663">
+        <v>1.1326597436760699</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>282</v>
+      </c>
+      <c r="B664">
+        <v>0.63883079346122296</v>
+      </c>
+      <c r="C664">
+        <v>-0.225486425409408</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>576</v>
+      </c>
+      <c r="B665">
+        <v>0.78848297479330798</v>
+      </c>
+      <c r="C665">
+        <v>-0.45775476661069697</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>283</v>
+      </c>
+      <c r="B666">
+        <v>-0.42951388680453301</v>
+      </c>
+      <c r="C666">
+        <v>0.25913738645207401</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>577</v>
+      </c>
+      <c r="B667">
+        <v>0.69482842411300905</v>
+      </c>
+      <c r="C667">
+        <v>1.8226610418192401E-3</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>284</v>
+      </c>
+      <c r="B668">
+        <v>0.65234130984104299</v>
+      </c>
+      <c r="C668">
+        <v>-0.28666420377157797</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>692</v>
+      </c>
+      <c r="B669">
+        <v>0.69423600651779405</v>
+      </c>
+      <c r="C669">
+        <v>-0.38398718543429</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>285</v>
+      </c>
+      <c r="B670">
+        <v>7.71650649653947E-2</v>
+      </c>
+      <c r="C670">
+        <v>0.27833089502387998</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A671" t="s">
+        <v>286</v>
+      </c>
+      <c r="B671">
+        <v>0.68094561427593803</v>
+      </c>
+      <c r="C671">
+        <v>-0.42499589504236401</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>578</v>
+      </c>
+      <c r="B672">
+        <v>0.26700388044725598</v>
+      </c>
+      <c r="C672">
+        <v>-0.24295760437129399</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>287</v>
+      </c>
+      <c r="B673">
+        <v>-0.66467259568975701</v>
+      </c>
+      <c r="C673">
+        <v>0.20083789512154701</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>579</v>
+      </c>
+      <c r="B674">
+        <v>-0.26203811105248198</v>
+      </c>
+      <c r="C674">
+        <v>-0.15695512308437001</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>580</v>
+      </c>
+      <c r="B675">
+        <v>-0.85749217638561404</v>
+      </c>
+      <c r="C675">
+        <v>0.30496802142222901</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>693</v>
+      </c>
+      <c r="B676" t="s">
+        <v>659</v>
+      </c>
+      <c r="C676" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>581</v>
+      </c>
+      <c r="B677">
+        <v>0.56254488732548902</v>
+      </c>
+      <c r="C677">
+        <v>0.426835499201355</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>626</v>
+      </c>
+      <c r="B678" t="s">
+        <v>659</v>
+      </c>
+      <c r="C678" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>582</v>
+      </c>
+      <c r="B679">
+        <v>0.689468266745345</v>
+      </c>
+      <c r="C679">
+        <v>-0.62143771880062104</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>583</v>
+      </c>
+      <c r="B680">
+        <v>-1.4004189674508301</v>
+      </c>
+      <c r="C680">
+        <v>-0.38820155820775998</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>694</v>
+      </c>
+      <c r="B681">
+        <v>0.645014087135382</v>
+      </c>
+      <c r="C681">
+        <v>-0.35524084411706203</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>627</v>
+      </c>
+      <c r="B682">
+        <v>-0.257870539799194</v>
+      </c>
+      <c r="C682">
+        <v>7.5919348095542599E-2</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>628</v>
+      </c>
+      <c r="B683">
+        <v>-0.47967359447265001</v>
+      </c>
+      <c r="C683">
+        <v>9.9344785624933499E-2</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>629</v>
+      </c>
+      <c r="B684">
+        <v>6.1734717304568199E-2</v>
+      </c>
+      <c r="C684">
+        <v>0.59440602666983899</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>630</v>
+      </c>
+      <c r="B685">
+        <v>-1.0414985189107699</v>
+      </c>
+      <c r="C685">
+        <v>-1.1364312074966201</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>631</v>
+      </c>
+      <c r="B686">
+        <v>-0.13230970426795299</v>
+      </c>
+      <c r="C686">
+        <v>0.543072749790528</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>632</v>
+      </c>
+      <c r="B687">
+        <v>0.70854291453734097</v>
+      </c>
+      <c r="C687">
+        <v>0.27658356740950402</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>633</v>
+      </c>
+      <c r="B688">
+        <v>-0.42944471324258898</v>
+      </c>
+      <c r="C688">
+        <v>0.18008504681228901</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>634</v>
+      </c>
+      <c r="B689">
+        <v>7.4108484833271399E-2</v>
+      </c>
+      <c r="C689">
+        <v>0.55703597100838598</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>635</v>
+      </c>
+      <c r="B690">
+        <v>0.72531617734256904</v>
+      </c>
+      <c r="C690">
+        <v>-3.3740221371384098E-2</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>636</v>
+      </c>
+      <c r="B691">
+        <v>-1.57077337014473</v>
+      </c>
+      <c r="C691">
+        <v>-0.273813189245319</v>
       </c>
     </row>
   </sheetData>
@@ -9650,8 +10103,8 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>9.2600000000000002E-2</v>
+      <c r="A2" s="2">
+        <v>8.77E-2</v>
       </c>
     </row>
   </sheetData>

--- a/nmds_results.xlsx
+++ b/nmds_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drake\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94305BBF-828B-4523-A9B4-875D99E4DB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AED4FA-8080-4BF8-9241-C5D4B23B30AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card_WA_Scores" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="687">
   <si>
     <t>NMDS1</t>
   </si>
@@ -1283,9 +1283,6 @@
     <t>Zagoth Triome</t>
   </si>
   <si>
-    <t>sb_Door to Nothingness</t>
-  </si>
-  <si>
     <t>Cascading Cataracts</t>
   </si>
   <si>
@@ -1304,9 +1301,6 @@
     <t>sb_Boon of Boseiju</t>
   </si>
   <si>
-    <t>sb_Cloudstone Curio</t>
-  </si>
-  <si>
     <t>sb_Colossal Dreadmaw</t>
   </si>
   <si>
@@ -1319,21 +1313,12 @@
     <t>sb_Fable of the Mirror-Breaker</t>
   </si>
   <si>
-    <t>sb_Filigree Sages</t>
-  </si>
-  <si>
     <t>sb_Fracturing Gust</t>
   </si>
   <si>
     <t>sb_Gut Shot</t>
   </si>
   <si>
-    <t>sb_Jegantha, the Wellspring</t>
-  </si>
-  <si>
-    <t>Storm the Festival</t>
-  </si>
-  <si>
     <t>Tatyova, Benthic Druid</t>
   </si>
   <si>
@@ -1346,12 +1331,6 @@
     <t>Wrenn and Six</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Cavalier of Thorns</t>
-  </si>
-  <si>
     <t>Emeritus of Abundance</t>
   </si>
   <si>
@@ -1383,9 +1362,6 @@
   </si>
   <si>
     <t>The Mycotyrant</t>
-  </si>
-  <si>
-    <t>Up the Beanstalk</t>
   </si>
   <si>
     <t>Zuran Orb</t>
@@ -2481,12 +2457,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C691"/>
+  <dimension ref="A1:C684"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2497,7 +2473,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B2">
         <v>-1.0974965157335099</v>
@@ -2530,7 +2506,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B5">
         <v>-0.82407425473404605</v>
@@ -2585,7 +2561,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B10">
         <v>0.57420134525742605</v>
@@ -2640,7 +2616,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B15">
         <v>-0.86422611536318805</v>
@@ -2662,7 +2638,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B17">
         <v>-0.40454719307510101</v>
@@ -2673,7 +2649,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B18">
         <v>-0.45927912661259901</v>
@@ -2684,7 +2660,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B19">
         <v>-1.01025986363218</v>
@@ -2706,7 +2682,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B21">
         <v>-0.47005971994568102</v>
@@ -2717,7 +2693,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B22">
         <v>-0.862531368206366</v>
@@ -2739,7 +2715,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B24">
         <v>0.86751062556934699</v>
@@ -2772,7 +2748,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B27">
         <v>-1.2561098145221701</v>
@@ -2783,7 +2759,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B28">
         <v>5.2110777451958197E-2</v>
@@ -2838,7 +2814,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B33">
         <v>-0.56174831845667705</v>
@@ -2849,7 +2825,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B34">
         <v>-1.43860476874128</v>
@@ -2959,7 +2935,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B44">
         <v>-0.984935422599029</v>
@@ -2981,7 +2957,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B46">
         <v>-0.73349359983166995</v>
@@ -2992,7 +2968,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B47">
         <v>-1.0894123148556101</v>
@@ -3003,7 +2979,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B48">
         <v>-1.27572863671898</v>
@@ -3025,1668 +3001,1668 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>442</v>
-      </c>
-      <c r="B50" t="s">
-        <v>441</v>
-      </c>
-      <c r="C50" t="s">
-        <v>441</v>
+        <v>17</v>
+      </c>
+      <c r="B50">
+        <v>-0.52961953268935302</v>
+      </c>
+      <c r="C50">
+        <v>-5.1044772894628901E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="B51">
-        <v>-0.52961953268935302</v>
+        <v>0.76043747802707495</v>
       </c>
       <c r="C51">
-        <v>-5.1044772894628901E-2</v>
+        <v>6.1146723352316502E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>474</v>
       </c>
       <c r="B52">
-        <v>0.76043747802707495</v>
+        <v>-0.67144834085532801</v>
       </c>
       <c r="C52">
-        <v>6.1146723352316502E-2</v>
+        <v>-0.11493406567781</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="B53">
-        <v>-0.67144834085532801</v>
+        <v>-0.87255572786374103</v>
       </c>
       <c r="C53">
-        <v>-0.11493406567781</v>
+        <v>-7.9147254504863193E-2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>422</v>
+        <v>18</v>
       </c>
       <c r="B54">
-        <v>-0.87255572786374103</v>
+        <v>-1.1290843258050201</v>
       </c>
       <c r="C54">
-        <v>-7.9147254504863193E-2</v>
+        <v>-1.76748851318772</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B55">
-        <v>-1.1290843258050201</v>
+        <v>-1.43449762917943</v>
       </c>
       <c r="C55">
-        <v>-1.76748851318772</v>
+        <v>-1.13727137782784</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>475</v>
       </c>
       <c r="B56">
-        <v>-1.43449762917943</v>
+        <v>0.66147740460946103</v>
       </c>
       <c r="C56">
-        <v>-1.13727137782784</v>
+        <v>-0.28006254560739702</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>483</v>
+        <v>220</v>
       </c>
       <c r="B57">
-        <v>0.66147740460946103</v>
+        <v>0.37868511668107102</v>
       </c>
       <c r="C57">
-        <v>-0.28006254560739702</v>
+        <v>-0.194605330269292</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="B58">
-        <v>0.37868511668107102</v>
+        <v>0.36427826031911698</v>
       </c>
       <c r="C58">
-        <v>-0.194605330269292</v>
+        <v>0.27103778472205498</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="B59">
-        <v>0.36427826031911698</v>
+        <v>-1.27121858479359</v>
       </c>
       <c r="C59">
-        <v>0.27103778472205498</v>
+        <v>-1.7569704716234</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>221</v>
+        <v>422</v>
       </c>
       <c r="B60">
-        <v>-1.27121858479359</v>
+        <v>-1.09246610208797</v>
       </c>
       <c r="C60">
-        <v>-1.7569704716234</v>
+        <v>-1.70239974934585</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="B61">
-        <v>-1.09246610208797</v>
+        <v>-0.96253994134999499</v>
       </c>
       <c r="C61">
-        <v>-1.70239974934585</v>
+        <v>-0.49499617003892998</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B62">
-        <v>-0.96253994134999499</v>
+        <v>0.46668288174558697</v>
       </c>
       <c r="C62">
-        <v>-0.49499617003892998</v>
+        <v>-9.1685453135881695E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>476</v>
       </c>
       <c r="B63">
-        <v>0.46668288174558697</v>
+        <v>-0.455874778619698</v>
       </c>
       <c r="C63">
-        <v>-9.1685453135881695E-2</v>
+        <v>-0.18749652730299399</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>484</v>
+        <v>23</v>
       </c>
       <c r="B64">
-        <v>-0.455874778619698</v>
+        <v>-8.1241375724653495E-2</v>
       </c>
       <c r="C64">
-        <v>-0.18749652730299399</v>
+        <v>0.15486420806376799</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>477</v>
       </c>
       <c r="B65">
-        <v>-8.1241375724653495E-2</v>
+        <v>0.78086962876464805</v>
       </c>
       <c r="C65">
-        <v>0.15486420806376799</v>
+        <v>-0.77632573833830298</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B66">
-        <v>0.78086962876464805</v>
+        <v>0.79406940017545702</v>
       </c>
       <c r="C66">
-        <v>-0.77632573833830298</v>
+        <v>-0.19183393816095501</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B67">
-        <v>0.79406940017545702</v>
+        <v>-0.51886386631873405</v>
       </c>
       <c r="C67">
-        <v>-0.19183393816095501</v>
+        <v>0.45066174428165701</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>487</v>
+        <v>222</v>
       </c>
       <c r="B68">
-        <v>-0.51886386631873405</v>
+        <v>-1.83221051498589</v>
       </c>
       <c r="C68">
-        <v>0.45066174428165701</v>
+        <v>-0.98105146184411196</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69">
-        <v>-1.83221051498589</v>
+        <v>-1.5262857383123201</v>
       </c>
       <c r="C69">
-        <v>-0.98105146184411196</v>
+        <v>-0.62060133504789905</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B70">
-        <v>-1.5262857383123201</v>
+        <v>0.101783349021077</v>
       </c>
       <c r="C70">
-        <v>-0.62060133504789905</v>
+        <v>0.31187618822080798</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>224</v>
+        <v>24</v>
       </c>
       <c r="B71">
-        <v>0.101783349021077</v>
+        <v>-0.695716683095018</v>
       </c>
       <c r="C71">
-        <v>0.31187618822080798</v>
+        <v>-0.137760437555111</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>480</v>
       </c>
       <c r="B72">
-        <v>-0.695716683095018</v>
+        <v>0.66864235973942499</v>
       </c>
       <c r="C72">
-        <v>-0.137760437555111</v>
+        <v>-0.57245990295513904</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B73">
-        <v>0.66864235973942499</v>
+        <v>-1.1763495552655501</v>
       </c>
       <c r="C73">
-        <v>-0.57245990295513904</v>
+        <v>-0.48427427144166402</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>489</v>
+        <v>225</v>
       </c>
       <c r="B74">
-        <v>-1.1763495552655501</v>
+        <v>-0.83520441302280102</v>
       </c>
       <c r="C74">
-        <v>-0.48427427144166402</v>
+        <v>-0.67352270816534998</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B75">
-        <v>-0.83520441302280102</v>
+        <v>-0.50545707700218601</v>
       </c>
       <c r="C75">
-        <v>-0.67352270816534998</v>
+        <v>2.0110191024762698E-2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>226</v>
+        <v>482</v>
       </c>
       <c r="B76">
-        <v>-0.50545707700218601</v>
+        <v>-1.46400113181571</v>
       </c>
       <c r="C76">
-        <v>2.0110191024762698E-2</v>
+        <v>-0.62664340255821105</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>490</v>
+        <v>227</v>
       </c>
       <c r="B77">
-        <v>-1.46400113181571</v>
+        <v>-0.63474409980018298</v>
       </c>
       <c r="C77">
-        <v>-0.62664340255821105</v>
+        <v>0.623167667541214</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>227</v>
+        <v>25</v>
       </c>
       <c r="B78">
-        <v>-0.63474409980018298</v>
+        <v>0.72571361874062201</v>
       </c>
       <c r="C78">
-        <v>0.623167667541214</v>
+        <v>-0.26211107224984698</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B79">
-        <v>0.72571361874062201</v>
+        <v>-0.34046353878423102</v>
       </c>
       <c r="C79">
-        <v>-0.26211107224984698</v>
+        <v>0.18352047350558801</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>26</v>
+        <v>483</v>
       </c>
       <c r="B80">
-        <v>-0.34046353878423102</v>
+        <v>0.73473802934145205</v>
       </c>
       <c r="C80">
-        <v>0.18352047350558801</v>
+        <v>-0.38173854760256798</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>491</v>
+        <v>27</v>
       </c>
       <c r="B81">
-        <v>0.73473802934145205</v>
+        <v>0.70677002652314602</v>
       </c>
       <c r="C81">
-        <v>-0.38173854760256798</v>
+        <v>-0.16734244902560699</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>484</v>
       </c>
       <c r="B82">
-        <v>0.70677002652314602</v>
+        <v>0.64269112949184704</v>
       </c>
       <c r="C82">
-        <v>-0.16734244902560699</v>
+        <v>0.74731759759832805</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>492</v>
+        <v>28</v>
       </c>
       <c r="B83">
-        <v>0.64269112949184704</v>
+        <v>-1.1383493404376801</v>
       </c>
       <c r="C83">
-        <v>0.74731759759832805</v>
+        <v>0.29314960004110902</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="B84">
-        <v>-1.1383493404376801</v>
+        <v>-0.90185709258814695</v>
       </c>
       <c r="C84">
-        <v>0.29314960004110902</v>
+        <v>-0.50410726479131995</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>228</v>
+        <v>485</v>
       </c>
       <c r="B85">
-        <v>-0.90185709258814695</v>
+        <v>-0.71954966374620799</v>
       </c>
       <c r="C85">
-        <v>-0.50410726479131995</v>
+        <v>-0.71986402806081395</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>493</v>
+        <v>29</v>
       </c>
       <c r="B86">
-        <v>-0.71954966374620799</v>
+        <v>-0.15534968661098</v>
       </c>
       <c r="C86">
-        <v>-0.71986402806081395</v>
+        <v>0.54908596042768398</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>486</v>
       </c>
       <c r="B87">
-        <v>-0.15534968661098</v>
+        <v>-0.30434490148468102</v>
       </c>
       <c r="C87">
-        <v>0.54908596042768398</v>
+        <v>1.0306781577405199E-2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>494</v>
+        <v>30</v>
       </c>
       <c r="B88">
-        <v>-0.30434490148468102</v>
+        <v>-0.89275679920081197</v>
       </c>
       <c r="C88">
-        <v>1.0306781577405199E-2</v>
+        <v>0.142287626676216</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>229</v>
       </c>
       <c r="B89">
-        <v>-0.89275679920081197</v>
+        <v>-0.76959791762150997</v>
       </c>
       <c r="C89">
-        <v>0.142287626676216</v>
+        <v>0.31130726040787698</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>229</v>
+        <v>436</v>
       </c>
       <c r="B90">
-        <v>-0.76959791762150997</v>
+        <v>0.766450951294951</v>
       </c>
       <c r="C90">
-        <v>0.31130726040787698</v>
+        <v>-0.174785693859346</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="B91">
-        <v>0.766450951294951</v>
+        <v>-0.63467271822183602</v>
       </c>
       <c r="C91">
-        <v>-0.174785693859346</v>
+        <v>-0.68491318028988502</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>31</v>
+        <v>487</v>
       </c>
       <c r="B92">
-        <v>-0.63467271822183602</v>
+        <v>0.48292534703026702</v>
       </c>
       <c r="C92">
-        <v>-0.68491318028988502</v>
+        <v>-5.0379363792822401E-2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>495</v>
+        <v>32</v>
       </c>
       <c r="B93">
-        <v>0.48292534703026702</v>
+        <v>-0.34673803517006901</v>
       </c>
       <c r="C93">
-        <v>-5.0379363792822401E-2</v>
+        <v>8.1207865418752398E-2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B94">
-        <v>-0.34673803517006901</v>
+        <v>-1.2010618206658801</v>
       </c>
       <c r="C94">
-        <v>8.1207865418752398E-2</v>
+        <v>-0.85492979846370398</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>437</v>
       </c>
       <c r="B95">
-        <v>-1.2010618206658801</v>
+        <v>-0.91881629230239104</v>
       </c>
       <c r="C95">
-        <v>-0.85492979846370398</v>
+        <v>0.36770111894365498</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>444</v>
+        <v>230</v>
       </c>
       <c r="B96">
-        <v>-0.91881629230239104</v>
+        <v>-0.38925319182502799</v>
       </c>
       <c r="C96">
-        <v>0.36770111894365498</v>
+        <v>0.31260322797550999</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>230</v>
+        <v>488</v>
       </c>
       <c r="B97">
-        <v>-0.38925319182502799</v>
+        <v>-0.82251198485406096</v>
       </c>
       <c r="C97">
-        <v>0.31260322797550999</v>
+        <v>0.108735610274437</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="B98">
-        <v>-0.82251198485406096</v>
+        <v>-0.44239265927191801</v>
       </c>
       <c r="C98">
-        <v>0.108735610274437</v>
+        <v>0.134122374818859</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>497</v>
+        <v>34</v>
       </c>
       <c r="B99">
-        <v>-0.44239265927191801</v>
+        <v>-0.15873455841358</v>
       </c>
       <c r="C99">
-        <v>0.134122374818859</v>
+        <v>0.21211494371689599</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B100">
-        <v>-0.15873455841358</v>
+        <v>-5.3791758920691199E-2</v>
       </c>
       <c r="C100">
-        <v>0.21211494371689599</v>
+        <v>2.6301389341183E-2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>35</v>
+        <v>423</v>
       </c>
       <c r="B101">
-        <v>-5.3791758920691199E-2</v>
+        <v>-0.173616952108711</v>
       </c>
       <c r="C101">
-        <v>2.6301389341183E-2</v>
+        <v>0.28657746657521799</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
       <c r="B102">
-        <v>-0.173616952108711</v>
+        <v>0.27387619508687799</v>
       </c>
       <c r="C102">
-        <v>0.28657746657521799</v>
+        <v>-9.9560205137126292E-3</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>498</v>
+        <v>231</v>
       </c>
       <c r="B103">
-        <v>0.27387619508687799</v>
+        <v>0.66766221297918105</v>
       </c>
       <c r="C103">
-        <v>-9.9560205137126292E-3</v>
+        <v>-0.39131743964972998</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>231</v>
+        <v>491</v>
       </c>
       <c r="B104">
-        <v>0.66766221297918105</v>
+        <v>-0.89255945397314695</v>
       </c>
       <c r="C104">
-        <v>-0.39131743964972998</v>
+        <v>0.191057089478473</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>499</v>
+        <v>232</v>
       </c>
       <c r="B105">
-        <v>-0.89255945397314695</v>
+        <v>0.36407106631738001</v>
       </c>
       <c r="C105">
-        <v>0.191057089478473</v>
+        <v>0.24716991824262799</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B106">
-        <v>0.36407106631738001</v>
+        <v>-1.3176490238271601</v>
       </c>
       <c r="C106">
-        <v>0.24716991824262799</v>
+        <v>-1.24270827186831</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="B107">
-        <v>-1.3176490238271601</v>
+        <v>-1.18997194990229</v>
       </c>
       <c r="C107">
-        <v>-1.24270827186831</v>
+        <v>-0.63411238862837205</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>36</v>
+        <v>492</v>
       </c>
       <c r="B108">
-        <v>-1.18997194990229</v>
+        <v>-1.0591710857942001</v>
       </c>
       <c r="C108">
-        <v>-0.63411238862837205</v>
+        <v>-0.24858395833250899</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>500</v>
+        <v>37</v>
       </c>
       <c r="B109">
-        <v>-1.0591710857942001</v>
+        <v>-1.10637073337829</v>
       </c>
       <c r="C109">
-        <v>-0.24858395833250899</v>
+        <v>-0.47652060184095901</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="B110">
-        <v>-1.10637073337829</v>
+        <v>-0.88295795065502303</v>
       </c>
       <c r="C110">
-        <v>-0.47652060184095901</v>
+        <v>-0.21344003026674199</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>493</v>
       </c>
       <c r="B111">
-        <v>-0.88295795065502303</v>
+        <v>-0.29267716208118599</v>
       </c>
       <c r="C111">
-        <v>-0.21344003026674199</v>
+        <v>-0.59015936456152696</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>501</v>
+        <v>235</v>
       </c>
       <c r="B112">
-        <v>-0.29267716208118599</v>
+        <v>-1.2558914720982199</v>
       </c>
       <c r="C112">
-        <v>-0.59015936456152696</v>
+        <v>6.8642687737043101E-2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B113">
-        <v>-1.2558914720982199</v>
+        <v>0.61466559112660901</v>
       </c>
       <c r="C113">
-        <v>6.8642687737043101E-2</v>
+        <v>-0.19750051381334599</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>236</v>
+        <v>494</v>
       </c>
       <c r="B114">
-        <v>0.61466559112660901</v>
+        <v>0.47698895509401901</v>
       </c>
       <c r="C114">
-        <v>-0.19750051381334599</v>
+        <v>-2.3762729042271901E-2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>502</v>
+        <v>237</v>
       </c>
       <c r="B115">
-        <v>0.47698895509401901</v>
+        <v>-0.43035827450676301</v>
       </c>
       <c r="C115">
-        <v>-2.3762729042271901E-2</v>
+        <v>0.25640046203435601</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="B116">
-        <v>-0.43035827450676301</v>
+        <v>-1.2935009305928001E-2</v>
       </c>
       <c r="C116">
-        <v>0.25640046203435601</v>
+        <v>1.89486077123662E-2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B117">
-        <v>-1.2935009305928001E-2</v>
+        <v>0.66873194070578101</v>
       </c>
       <c r="C117">
-        <v>1.89486077123662E-2</v>
+        <v>-0.44706788414929299</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>39</v>
+        <v>495</v>
       </c>
       <c r="B118">
-        <v>0.66873194070578101</v>
+        <v>-0.52079801130133496</v>
       </c>
       <c r="C118">
-        <v>-0.44706788414929299</v>
+        <v>-0.28780290676363002</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>503</v>
+        <v>238</v>
       </c>
       <c r="B119">
-        <v>-0.52079801130133496</v>
+        <v>0.92190648710240197</v>
       </c>
       <c r="C119">
-        <v>-0.28780290676363002</v>
+        <v>-0.382882425684137</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>238</v>
+        <v>496</v>
       </c>
       <c r="B120">
-        <v>0.92190648710240197</v>
+        <v>-0.56375259073872497</v>
       </c>
       <c r="C120">
-        <v>-0.382882425684137</v>
+        <v>-0.36149336031097501</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>504</v>
+        <v>239</v>
       </c>
       <c r="B121">
-        <v>-0.56375259073872497</v>
+        <v>-1.3413623872173099</v>
       </c>
       <c r="C121">
-        <v>-0.36149336031097501</v>
+        <v>-1.69987644823073</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>239</v>
+        <v>497</v>
       </c>
       <c r="B122">
-        <v>-1.3413623872173099</v>
+        <v>-0.201062553040501</v>
       </c>
       <c r="C122">
-        <v>-1.69987644823073</v>
+        <v>0.59773113133278</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>505</v>
+        <v>40</v>
       </c>
       <c r="B123">
-        <v>-0.201062553040501</v>
+        <v>-0.27479810615967698</v>
       </c>
       <c r="C123">
-        <v>0.59773113133278</v>
+        <v>0.21383146105496101</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B124">
-        <v>-0.27479810615967698</v>
+        <v>-1.2291223504503801</v>
       </c>
       <c r="C124">
-        <v>0.21383146105496101</v>
+        <v>-1.3651141451488</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>41</v>
+        <v>240</v>
       </c>
       <c r="B125">
-        <v>-1.2291223504503801</v>
+        <v>-0.39927985195646998</v>
       </c>
       <c r="C125">
-        <v>-1.3651141451488</v>
+        <v>0.381937463064079</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>240</v>
+        <v>498</v>
       </c>
       <c r="B126">
-        <v>-0.39927985195646998</v>
+        <v>-0.56834774401390697</v>
       </c>
       <c r="C126">
-        <v>0.381937463064079</v>
+        <v>0.47872528863497199</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>506</v>
+        <v>42</v>
       </c>
       <c r="B127">
-        <v>-0.56834774401390697</v>
+        <v>-0.70643450010697395</v>
       </c>
       <c r="C127">
-        <v>0.47872528863497199</v>
+        <v>-0.62503668381965904</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="B128">
-        <v>-0.70643450010697395</v>
+        <v>-2.02807686940365E-2</v>
       </c>
       <c r="C128">
-        <v>-0.62503668381965904</v>
+        <v>-0.88963199655474701</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>241</v>
+        <v>438</v>
       </c>
       <c r="B129">
-        <v>-2.02807686940365E-2</v>
+        <v>-1.16198189315463</v>
       </c>
       <c r="C129">
-        <v>-0.88963199655474701</v>
+        <v>-1.80738273260841</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>445</v>
+        <v>499</v>
       </c>
       <c r="B130">
-        <v>-1.16198189315463</v>
+        <v>-1.05014312908954</v>
       </c>
       <c r="C130">
-        <v>-1.80738273260841</v>
+        <v>6.7511712260075504E-2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>507</v>
+        <v>242</v>
       </c>
       <c r="B131">
-        <v>-1.05014312908954</v>
+        <v>-1.1713333218538999</v>
       </c>
       <c r="C131">
-        <v>6.7511712260075504E-2</v>
+        <v>-1.77200095383677</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>242</v>
+        <v>500</v>
       </c>
       <c r="B132">
-        <v>-1.1713333218538999</v>
+        <v>0.32568282433377499</v>
       </c>
       <c r="C132">
-        <v>-1.77200095383677</v>
+        <v>-0.38115911274914599</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>508</v>
+        <v>43</v>
       </c>
       <c r="B133">
-        <v>0.32568282433377499</v>
+        <v>-0.29825531484794199</v>
       </c>
       <c r="C133">
-        <v>-0.38115911274914599</v>
+        <v>0.127781368118388</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B134">
-        <v>-0.29825531484794199</v>
+        <v>-1.18848606432624</v>
       </c>
       <c r="C134">
-        <v>0.127781368118388</v>
+        <v>-0.369141057129381</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>44</v>
+        <v>243</v>
       </c>
       <c r="B135">
-        <v>-1.18848606432624</v>
+        <v>-1.4761323249108</v>
       </c>
       <c r="C135">
-        <v>-0.369141057129381</v>
+        <v>-1.0860267166312101</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>243</v>
+        <v>45</v>
       </c>
       <c r="B136">
-        <v>-1.4761323249108</v>
+        <v>-0.50360348544083999</v>
       </c>
       <c r="C136">
-        <v>-1.0860267166312101</v>
+        <v>0.32543405306067302</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B137">
-        <v>-0.50360348544083999</v>
+        <v>0.74184008616877695</v>
       </c>
       <c r="C137">
-        <v>0.32543405306067302</v>
+        <v>-0.26199663250032901</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B138">
-        <v>0.74184008616877695</v>
+        <v>-0.26300759565126702</v>
       </c>
       <c r="C138">
-        <v>-0.26199663250032901</v>
+        <v>-4.0921053765831203E-2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>47</v>
+        <v>501</v>
       </c>
       <c r="B139">
-        <v>-0.26300759565126702</v>
+        <v>0.128866066871165</v>
       </c>
       <c r="C139">
-        <v>-4.0921053765831203E-2</v>
+        <v>-0.41763710920254898</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>509</v>
+        <v>48</v>
       </c>
       <c r="B140">
-        <v>0.128866066871165</v>
+        <v>-1.1761263533997599</v>
       </c>
       <c r="C140">
-        <v>-0.41763710920254898</v>
+        <v>-1.1114724920283601</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>48</v>
+        <v>502</v>
       </c>
       <c r="B141">
-        <v>-1.1761263533997599</v>
+        <v>-3.9552383910932999E-2</v>
       </c>
       <c r="C141">
-        <v>-1.1114724920283601</v>
+        <v>-0.31262008629995702</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>510</v>
+        <v>49</v>
       </c>
       <c r="B142">
-        <v>-3.9552383910932999E-2</v>
+        <v>0.12799841154619701</v>
       </c>
       <c r="C142">
-        <v>-0.31262008629995702</v>
+        <v>-3.2587482187398903E-2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>49</v>
+        <v>503</v>
       </c>
       <c r="B143">
-        <v>0.12799841154619701</v>
+        <v>-0.49431046971943698</v>
       </c>
       <c r="C143">
-        <v>-3.2587482187398903E-2</v>
+        <v>0.10009093369583</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>511</v>
+        <v>244</v>
       </c>
       <c r="B144">
-        <v>-0.49431046971943698</v>
+        <v>-0.65744821123376995</v>
       </c>
       <c r="C144">
-        <v>0.10009093369583</v>
+        <v>-0.60840081764332898</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>504</v>
       </c>
       <c r="B145">
-        <v>-0.65744821123376995</v>
+        <v>-0.41194863583543201</v>
       </c>
       <c r="C145">
-        <v>-0.60840081764332898</v>
+        <v>-2.89917199293276E-2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>512</v>
+        <v>424</v>
       </c>
       <c r="B146">
-        <v>-0.41194863583543201</v>
+        <v>-1.6734193899649901</v>
       </c>
       <c r="C146">
-        <v>-2.89917199293276E-2</v>
+        <v>0.15639188192532899</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>425</v>
+        <v>50</v>
       </c>
       <c r="B147">
-        <v>-1.6734193899649901</v>
+        <v>0.40323167461965198</v>
       </c>
       <c r="C147">
-        <v>0.15639188192532899</v>
+        <v>-8.2152494004752497E-2</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>50</v>
+        <v>505</v>
       </c>
       <c r="B148">
-        <v>0.40323167461965198</v>
+        <v>0.34133407517839298</v>
       </c>
       <c r="C148">
-        <v>-8.2152494004752497E-2</v>
+        <v>-0.20150421647598901</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>513</v>
+        <v>245</v>
       </c>
       <c r="B149">
-        <v>0.34133407517839298</v>
+        <v>-0.36106909811096299</v>
       </c>
       <c r="C149">
-        <v>-0.20150421647598901</v>
+        <v>0.106888159311499</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>245</v>
+        <v>506</v>
       </c>
       <c r="B150">
-        <v>-0.36106909811096299</v>
+        <v>-1.46400113181571</v>
       </c>
       <c r="C150">
-        <v>0.106888159311499</v>
+        <v>-0.62664340255821105</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>514</v>
+        <v>51</v>
       </c>
       <c r="B151">
-        <v>-1.46400113181571</v>
+        <v>0.39535952497971999</v>
       </c>
       <c r="C151">
-        <v>-0.62664340255821105</v>
+        <v>0.131620792840354</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>51</v>
+        <v>507</v>
       </c>
       <c r="B152">
-        <v>0.39535952497971999</v>
+        <v>-0.30531177470981402</v>
       </c>
       <c r="C152">
-        <v>0.131620792840354</v>
+        <v>0.21835663040806699</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>515</v>
+        <v>52</v>
       </c>
       <c r="B153">
-        <v>-0.30531177470981402</v>
+        <v>-1.11852257976392</v>
       </c>
       <c r="C153">
-        <v>0.21835663040806699</v>
+        <v>-1.5985830538238901</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="B154">
-        <v>-1.11852257976392</v>
+        <v>-1.54921959068801</v>
       </c>
       <c r="C154">
-        <v>-1.5985830538238901</v>
+        <v>-1.1819806663122701</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>246</v>
+        <v>53</v>
       </c>
       <c r="B155">
-        <v>-1.54921959068801</v>
+        <v>-1.2572966943245101</v>
       </c>
       <c r="C155">
-        <v>-1.1819806663122701</v>
+        <v>-1.2117706171665701</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>53</v>
+        <v>508</v>
       </c>
       <c r="B156">
-        <v>-1.2572966943245101</v>
+        <v>-0.984935422599029</v>
       </c>
       <c r="C156">
-        <v>-1.2117706171665701</v>
+        <v>0.304142173670365</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>516</v>
+        <v>54</v>
       </c>
       <c r="B157">
-        <v>-0.984935422599029</v>
+        <v>-0.57639081763715905</v>
       </c>
       <c r="C157">
-        <v>0.304142173670365</v>
+        <v>-3.8020149346141799E-2</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B158">
-        <v>-0.57639081763715905</v>
+        <v>0.828513463356496</v>
       </c>
       <c r="C158">
-        <v>-3.8020149346141799E-2</v>
+        <v>-0.33546160986651302</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>55</v>
+        <v>509</v>
       </c>
       <c r="B159">
-        <v>0.828513463356496</v>
+        <v>-0.44374686834483801</v>
       </c>
       <c r="C159">
-        <v>-0.33546160986651302</v>
+        <v>-0.12395568187119201</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>517</v>
+        <v>247</v>
       </c>
       <c r="B160">
-        <v>-0.44374686834483801</v>
+        <v>-1.19655262912182</v>
       </c>
       <c r="C160">
-        <v>-0.12395568187119201</v>
+        <v>-1.7884030049616799</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B161">
-        <v>-1.19655262912182</v>
+        <v>0.759430668237843</v>
       </c>
       <c r="C161">
-        <v>-1.7884030049616799</v>
+        <v>-0.335496227116447</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B162">
-        <v>0.759430668237843</v>
+        <v>-0.47702804871809301</v>
       </c>
       <c r="C162">
-        <v>-0.335496227116447</v>
+        <v>0.17323872205924301</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>249</v>
+        <v>510</v>
       </c>
       <c r="B163">
-        <v>-0.47702804871809301</v>
+        <v>-0.430577965475889</v>
       </c>
       <c r="C163">
-        <v>0.17323872205924301</v>
+        <v>0.41397569372939103</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B164">
-        <v>-0.430577965475889</v>
+        <v>0.76764052144925399</v>
       </c>
       <c r="C164">
-        <v>0.41397569372939103</v>
+        <v>-6.5403685967117597E-2</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>519</v>
+        <v>56</v>
       </c>
       <c r="B165">
-        <v>0.76764052144925399</v>
+        <v>-0.73907247770475304</v>
       </c>
       <c r="C165">
-        <v>-6.5403685967117597E-2</v>
+        <v>-0.51124787416418804</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>56</v>
+        <v>512</v>
       </c>
       <c r="B166">
-        <v>-0.73907247770475304</v>
+        <v>-9.9218877997764895E-2</v>
       </c>
       <c r="C166">
-        <v>-0.51124787416418804</v>
+        <v>0.44145964791312697</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>520</v>
+        <v>250</v>
       </c>
       <c r="B167">
-        <v>-9.9218877997764895E-2</v>
+        <v>-1.11934152277064</v>
       </c>
       <c r="C167">
-        <v>0.44145964791312697</v>
+        <v>-1.21546549801738</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B168">
-        <v>-1.11934152277064</v>
+        <v>-0.338263429605692</v>
       </c>
       <c r="C168">
-        <v>-1.21546549801738</v>
+        <v>0.57560757342219004</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B169">
-        <v>-0.338263429605692</v>
+        <v>-0.44565018598328898</v>
       </c>
       <c r="C169">
-        <v>0.57560757342219004</v>
+        <v>7.5270965068310602E-2</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>252</v>
+        <v>57</v>
       </c>
       <c r="B170">
-        <v>-0.44565018598328898</v>
+        <v>-1.1749925650523501</v>
       </c>
       <c r="C170">
-        <v>7.5270965068310602E-2</v>
+        <v>-1.0216852165245001</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B171">
-        <v>-1.1749925650523501</v>
+        <v>-0.82925021849390101</v>
       </c>
       <c r="C171">
-        <v>-1.0216852165245001</v>
+        <v>-0.14239270635513299</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>58</v>
+        <v>513</v>
       </c>
       <c r="B172">
-        <v>-0.82925021849390101</v>
+        <v>-0.84169930120542602</v>
       </c>
       <c r="C172">
-        <v>-0.14239270635513299</v>
+        <v>-0.62841297582761702</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="B173">
-        <v>-0.84169930120542602</v>
+        <v>7.6953576834418294E-2</v>
       </c>
       <c r="C173">
-        <v>-0.62841297582761702</v>
+        <v>-0.47083946974382301</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>522</v>
+        <v>59</v>
       </c>
       <c r="B174">
-        <v>7.6953576834418294E-2</v>
+        <v>0.125788192539599</v>
       </c>
       <c r="C174">
-        <v>-0.47083946974382301</v>
+        <v>0.35228436097437699</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B175">
-        <v>0.125788192539599</v>
+        <v>-1.0169908918353801</v>
       </c>
       <c r="C175">
-        <v>0.35228436097437699</v>
+        <v>-0.62579565446018404</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B176">
-        <v>-1.0169908918353801</v>
+        <v>-0.92595815869952802</v>
       </c>
       <c r="C176">
-        <v>-0.62579565446018404</v>
+        <v>-0.64023153104095998</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>61</v>
+        <v>253</v>
       </c>
       <c r="B177">
-        <v>-0.92595815869952802</v>
+        <v>-1.35775064477678</v>
       </c>
       <c r="C177">
-        <v>-0.64023153104095998</v>
+        <v>-0.54632305564807904</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>253</v>
+        <v>515</v>
       </c>
       <c r="B178">
-        <v>-1.35775064477678</v>
+        <v>-1.42562020211716</v>
       </c>
       <c r="C178">
-        <v>-0.54632305564807904</v>
+        <v>2.9127690095540601E-2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B179">
-        <v>-1.42562020211716</v>
+        <v>-0.50739601605856699</v>
       </c>
       <c r="C179">
-        <v>2.9127690095540601E-2</v>
+        <v>0.29332095779003098</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>524</v>
+        <v>254</v>
       </c>
       <c r="B180">
-        <v>-0.50739601605856699</v>
+        <v>-0.60287588749340304</v>
       </c>
       <c r="C180">
-        <v>0.29332095779003098</v>
+        <v>1.14116939030555</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>254</v>
+        <v>517</v>
       </c>
       <c r="B181">
-        <v>-0.60287588749340304</v>
+        <v>-0.68279946982437101</v>
       </c>
       <c r="C181">
-        <v>1.14116939030555</v>
+        <v>0.118588853246668</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B182">
-        <v>-0.68279946982437101</v>
+        <v>0.54170356525378804</v>
       </c>
       <c r="C182">
-        <v>0.118588853246668</v>
+        <v>0.65012413841412098</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>526</v>
+        <v>62</v>
       </c>
       <c r="B183">
-        <v>0.54170356525378804</v>
+        <v>-0.493401101167041</v>
       </c>
       <c r="C183">
-        <v>0.65012413841412098</v>
+        <v>-8.0784400789341904E-2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>62</v>
+        <v>519</v>
       </c>
       <c r="B184">
-        <v>-0.493401101167041</v>
+        <v>-0.37420009930272202</v>
       </c>
       <c r="C184">
-        <v>-8.0784400789341904E-2</v>
+        <v>0.25190594043628101</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>527</v>
+        <v>439</v>
       </c>
       <c r="B185">
-        <v>-0.37420009930272202</v>
+        <v>0.16319963889146299</v>
       </c>
       <c r="C185">
-        <v>0.25190594043628101</v>
+        <v>-1.2543407206480699</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>446</v>
+        <v>520</v>
       </c>
       <c r="B186">
-        <v>0.16319963889146299</v>
+        <v>-0.19825959184401901</v>
       </c>
       <c r="C186">
-        <v>-1.2543407206480699</v>
+        <v>-1.3117296719139899</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B187">
-        <v>-0.19825959184401901</v>
+        <v>-0.52812603316137996</v>
       </c>
       <c r="C187">
-        <v>-1.3117296719139899</v>
+        <v>0.69934076361381603</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>529</v>
+        <v>63</v>
       </c>
       <c r="B188">
-        <v>-0.52812603316137996</v>
+        <v>-0.20011135930150101</v>
       </c>
       <c r="C188">
-        <v>0.69934076361381603</v>
+        <v>0.40537182049144899</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B189">
-        <v>-0.20011135930150101</v>
+        <v>-1.0462030084040901</v>
       </c>
       <c r="C189">
-        <v>0.40537182049144899</v>
+        <v>-1.5334018197511401</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="B190">
-        <v>-1.0462030084040901</v>
+        <v>-1.12974960153319</v>
       </c>
       <c r="C190">
-        <v>-1.5334018197511401</v>
+        <v>-1.42968251980371</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>255</v>
+        <v>65</v>
       </c>
       <c r="B191">
-        <v>-1.12974960153319</v>
+        <v>0.69803474092422202</v>
       </c>
       <c r="C191">
-        <v>-1.42968251980371</v>
+        <v>-0.159125278683663</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B192">
-        <v>0.69803474092422202</v>
+        <v>0.65102423538069298</v>
       </c>
       <c r="C192">
-        <v>-0.159125278683663</v>
+        <v>2.3322960697690801E-2</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>66</v>
+        <v>256</v>
       </c>
       <c r="B193">
-        <v>0.65102423538069298</v>
+        <v>0.75971897716283299</v>
       </c>
       <c r="C193">
-        <v>2.3322960697690801E-2</v>
+        <v>0.110286742789026</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>256</v>
+        <v>67</v>
       </c>
       <c r="B194">
-        <v>0.75971897716283299</v>
+        <v>-2.1045052836688002E-2</v>
       </c>
       <c r="C194">
-        <v>0.110286742789026</v>
+        <v>0.439544096718265</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B195">
-        <v>-2.1045052836688002E-2</v>
+        <v>0.76157882514745301</v>
       </c>
       <c r="C195">
-        <v>0.439544096718265</v>
+        <v>-0.212299786398641</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B196">
-        <v>0.76157882514745301</v>
+        <v>-1.14651067233534</v>
       </c>
       <c r="C196">
-        <v>-0.212299786398641</v>
+        <v>-1.70401600465238</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>69</v>
+        <v>522</v>
       </c>
       <c r="B197">
-        <v>-1.14651067233534</v>
+        <v>-1.0567066982137201</v>
       </c>
       <c r="C197">
-        <v>-1.70401600465238</v>
+        <v>-0.46083263357288901</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>530</v>
+        <v>257</v>
       </c>
       <c r="B198">
-        <v>-1.0567066982137201</v>
+        <v>-1.4075793003083099</v>
       </c>
       <c r="C198">
-        <v>-0.46083263357288901</v>
+        <v>-1.0222593995245199</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B199">
-        <v>-1.4075793003083099</v>
+        <v>-1.21843421285792</v>
       </c>
       <c r="C199">
-        <v>-1.0222593995245199</v>
+        <v>-1.75209421492788</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>258</v>
+        <v>523</v>
       </c>
       <c r="B200">
-        <v>-1.21843421285792</v>
+        <v>0.15708920999993001</v>
       </c>
       <c r="C200">
-        <v>-1.75209421492788</v>
+        <v>-1.1018456897925399</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B201">
         <v>0.15708920999993001</v>
@@ -4697,5391 +4673,5314 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B202">
-        <v>0.15708920999993001</v>
+        <v>-0.18792951144797901</v>
       </c>
       <c r="C202">
-        <v>-1.1018456897925399</v>
+        <v>0.63054573664728297</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B203">
-        <v>-0.18792951144797901</v>
+        <v>0.76406961762539305</v>
       </c>
       <c r="C203">
-        <v>0.63054573664728297</v>
+        <v>-0.17869575746820199</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>534</v>
+        <v>259</v>
       </c>
       <c r="B204">
-        <v>0.76406961762539305</v>
+        <v>0.29032639076649303</v>
       </c>
       <c r="C204">
-        <v>-0.17869575746820199</v>
+        <v>0.170626299893019</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>259</v>
+        <v>70</v>
       </c>
       <c r="B205">
-        <v>0.29032639076649303</v>
+        <v>0.51393757502179305</v>
       </c>
       <c r="C205">
-        <v>0.170626299893019</v>
+        <v>-1.98769859782757E-2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>70</v>
+        <v>527</v>
       </c>
       <c r="B206">
-        <v>0.51393757502179305</v>
+        <v>0.69360962688099204</v>
       </c>
       <c r="C206">
-        <v>-1.98769859782757E-2</v>
+        <v>-0.25097334423728901</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>535</v>
+        <v>71</v>
       </c>
       <c r="B207">
-        <v>0.69360962688099204</v>
+        <v>-0.265069890205262</v>
       </c>
       <c r="C207">
-        <v>-0.25097334423728901</v>
+        <v>-6.3599074997436E-2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>71</v>
+        <v>260</v>
       </c>
       <c r="B208">
-        <v>-0.265069890205262</v>
+        <v>-0.55777150926444996</v>
       </c>
       <c r="C208">
-        <v>-6.3599074997436E-2</v>
+        <v>8.7252941207337606E-2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>260</v>
+        <v>528</v>
       </c>
       <c r="B209">
-        <v>-0.55777150926444996</v>
+        <v>1.1557697054495399</v>
       </c>
       <c r="C209">
-        <v>8.7252941207337606E-2</v>
+        <v>-0.53567919227818495</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B210">
-        <v>1.1557697054495399</v>
+        <v>-0.71954966374620799</v>
       </c>
       <c r="C210">
-        <v>-0.53567919227818495</v>
+        <v>-0.71986402806081395</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>537</v>
+        <v>261</v>
       </c>
       <c r="B211">
-        <v>-0.71954966374620799</v>
+        <v>2.8869132162066002E-2</v>
       </c>
       <c r="C211">
-        <v>-0.71986402806081395</v>
+        <v>0.497361782076646</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>261</v>
+        <v>530</v>
       </c>
       <c r="B212">
-        <v>2.8869132162066002E-2</v>
+        <v>0.735099780395575</v>
       </c>
       <c r="C212">
-        <v>0.497361782076646</v>
+        <v>-7.3168724493208104E-2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B213">
-        <v>0.735099780395575</v>
+        <v>-0.70466940789312504</v>
       </c>
       <c r="C213">
-        <v>-7.3168724493208104E-2</v>
+        <v>0.42878634121067699</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>539</v>
+        <v>262</v>
       </c>
       <c r="B214">
-        <v>-0.70466940789312504</v>
+        <v>-0.41998476329395301</v>
       </c>
       <c r="C214">
-        <v>0.42878634121067699</v>
+        <v>-0.30514591208882602</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B215">
-        <v>-0.41998476329395301</v>
+        <v>0.74256970950453005</v>
       </c>
       <c r="C215">
-        <v>-0.30514591208882602</v>
+        <v>-0.23100879825826101</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>263</v>
+        <v>532</v>
       </c>
       <c r="B216">
-        <v>0.74256970950453005</v>
+        <v>-1.5434220959370899</v>
       </c>
       <c r="C216">
-        <v>-0.23100879825826101</v>
+        <v>-0.31333698340315203</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>540</v>
+        <v>440</v>
       </c>
       <c r="B217">
-        <v>-1.5434220959370899</v>
+        <v>0.16319963889146299</v>
       </c>
       <c r="C217">
-        <v>-0.31333698340315203</v>
+        <v>-1.2543407206480699</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>447</v>
+        <v>264</v>
       </c>
       <c r="B218">
-        <v>0.16319963889146299</v>
+        <v>-1.33066563983345</v>
       </c>
       <c r="C218">
-        <v>-1.2543407206480699</v>
+        <v>-0.85394135761163503</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>264</v>
+        <v>533</v>
       </c>
       <c r="B219">
-        <v>-1.33066563983345</v>
+        <v>-0.64775816554569399</v>
       </c>
       <c r="C219">
-        <v>-0.85394135761163503</v>
+        <v>0.581782123666858</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>541</v>
+        <v>265</v>
       </c>
       <c r="B220">
-        <v>-0.64775816554569399</v>
+        <v>-1.0536647617088899</v>
       </c>
       <c r="C220">
-        <v>0.581782123666858</v>
+        <v>-1.0822173157294901</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="B221">
-        <v>-1.0536647617088899</v>
+        <v>-1.33154304511565</v>
       </c>
       <c r="C221">
-        <v>-1.0822173157294901</v>
+        <v>-1.0226639968800399</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B222">
-        <v>-1.33154304511565</v>
+        <v>-1.3717949115366801</v>
       </c>
       <c r="C222">
-        <v>-1.0226639968800399</v>
+        <v>-0.86977400219716805</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="B223">
-        <v>-1.3717949115366801</v>
+        <v>-0.601549002545404</v>
       </c>
       <c r="C223">
-        <v>-0.86977400219716805</v>
+        <v>0.71721857109897802</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>542</v>
+        <v>74</v>
       </c>
       <c r="B224">
-        <v>-0.601549002545404</v>
+        <v>-0.92348682649992297</v>
       </c>
       <c r="C224">
-        <v>0.71721857109897802</v>
+        <v>-1.2115678740047</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="B225">
-        <v>-0.92348682649992297</v>
+        <v>-0.97279124212686996</v>
       </c>
       <c r="C225">
-        <v>-1.2115678740047</v>
+        <v>-0.26366094764366499</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>266</v>
+        <v>75</v>
       </c>
       <c r="B226">
-        <v>-0.97279124212686996</v>
+        <v>6.5358003605795495E-2</v>
       </c>
       <c r="C226">
-        <v>-0.26366094764366499</v>
+        <v>0.366747584930675</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>75</v>
+        <v>535</v>
       </c>
       <c r="B227">
-        <v>6.5358003605795495E-2</v>
+        <v>-0.52050524318245905</v>
       </c>
       <c r="C227">
-        <v>0.366747584930675</v>
+        <v>0.67173670379657102</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>543</v>
+        <v>76</v>
       </c>
       <c r="B228">
-        <v>-0.52050524318245905</v>
+        <v>0.35259109640168601</v>
       </c>
       <c r="C228">
-        <v>0.67173670379657102</v>
+        <v>4.7084642788553802E-2</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>76</v>
+        <v>536</v>
       </c>
       <c r="B229">
-        <v>0.35259109640168601</v>
+        <v>-0.47711853860087</v>
       </c>
       <c r="C229">
-        <v>4.7084642788553802E-2</v>
+        <v>-6.0276891548252602E-2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>544</v>
+        <v>267</v>
       </c>
       <c r="B230">
-        <v>-0.47711853860087</v>
+        <v>-0.709915768798413</v>
       </c>
       <c r="C230">
-        <v>-6.0276891548252602E-2</v>
+        <v>-0.42284150597161302</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>267</v>
+        <v>537</v>
       </c>
       <c r="B231">
-        <v>-0.709915768798413</v>
+        <v>8.8176976859703105E-2</v>
       </c>
       <c r="C231">
-        <v>-0.42284150597161302</v>
+        <v>-0.59372876859264601</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>545</v>
+        <v>77</v>
       </c>
       <c r="B232">
-        <v>8.8176976859703105E-2</v>
+        <v>-1.1091757440124801</v>
       </c>
       <c r="C232">
-        <v>-0.59372876859264601</v>
+        <v>-1.09836127525647</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>77</v>
+        <v>538</v>
       </c>
       <c r="B233">
-        <v>-1.1091757440124801</v>
+        <v>-0.47482789844480899</v>
       </c>
       <c r="C233">
-        <v>-1.09836127525647</v>
+        <v>4.6854225294799502E-3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B234">
-        <v>-0.47482789844480899</v>
+        <v>-1.20230349163161</v>
       </c>
       <c r="C234">
-        <v>4.6854225294799502E-3</v>
+        <v>0.90415071105196698</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>547</v>
+        <v>268</v>
       </c>
       <c r="B235">
-        <v>-1.20230349163161</v>
+        <v>-1.5434142102954</v>
       </c>
       <c r="C235">
-        <v>0.90415071105196698</v>
+        <v>-1.23986890642715</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B236">
-        <v>-1.5434142102954</v>
+        <v>-0.18324109757087001</v>
       </c>
       <c r="C236">
-        <v>-1.23986890642715</v>
+        <v>0.35823915916212201</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>269</v>
+        <v>441</v>
       </c>
       <c r="B237">
-        <v>-0.18324109757087001</v>
+        <v>-0.19947801126267301</v>
       </c>
       <c r="C237">
-        <v>0.35823915916212201</v>
+        <v>-0.152413897863727</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>448</v>
+        <v>540</v>
       </c>
       <c r="B238">
-        <v>-0.19947801126267301</v>
+        <v>-1.1470654543808501</v>
       </c>
       <c r="C238">
-        <v>-0.152413897863727</v>
+        <v>0.64617414160358699</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="B239">
-        <v>-1.1470654543808501</v>
+        <v>-0.54387749544736697</v>
       </c>
       <c r="C239">
-        <v>0.64617414160358699</v>
+        <v>0.294979910138429</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B240">
-        <v>-0.54387749544736697</v>
+        <v>0.74544926030089598</v>
       </c>
       <c r="C240">
-        <v>0.294979910138429</v>
+        <v>-0.146727777627985</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="B241">
-        <v>0.74544926030089598</v>
+        <v>-0.51965848106670098</v>
       </c>
       <c r="C241">
-        <v>-0.146727777627985</v>
+        <v>0.137976875769144</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B242">
-        <v>-0.51965848106670098</v>
+        <v>-0.731804739827845</v>
       </c>
       <c r="C242">
-        <v>0.137976875769144</v>
+        <v>0.39887779091864001</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>271</v>
+        <v>541</v>
       </c>
       <c r="B243">
-        <v>-0.731804739827845</v>
+        <v>0.83573615306128302</v>
       </c>
       <c r="C243">
-        <v>0.39887779091864001</v>
+        <v>-0.42418371178164999</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>549</v>
+        <v>272</v>
       </c>
       <c r="B244">
-        <v>0.83573615306128302</v>
+        <v>0.81777786923636198</v>
       </c>
       <c r="C244">
-        <v>-0.42418371178164999</v>
+        <v>-2.7133265749358398E-2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>272</v>
+        <v>542</v>
       </c>
       <c r="B245">
-        <v>0.81777786923636198</v>
+        <v>-0.19825959184401901</v>
       </c>
       <c r="C245">
-        <v>-2.7133265749358398E-2</v>
+        <v>-1.3117296719139899</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>550</v>
+        <v>80</v>
       </c>
       <c r="B246">
-        <v>-0.19825959184401901</v>
+        <v>0.22368262151805099</v>
       </c>
       <c r="C246">
-        <v>-1.3117296719139899</v>
+        <v>-0.131314237437373</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B247">
-        <v>0.22368262151805099</v>
+        <v>-1.11111181865778</v>
       </c>
       <c r="C247">
-        <v>-0.131314237437373</v>
+        <v>-0.63844303231717303</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>81</v>
+        <v>543</v>
       </c>
       <c r="B248">
-        <v>-1.11111181865778</v>
+        <v>-0.73042946598315395</v>
       </c>
       <c r="C248">
-        <v>-0.63844303231717303</v>
+        <v>0.45555348995684802</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="B249">
-        <v>-0.73042946598315395</v>
+        <v>-7.3175356830046103E-3</v>
       </c>
       <c r="C249">
-        <v>0.45555348995684802</v>
+        <v>-1.5751781582405899E-3</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="B250">
-        <v>-7.3175356830046103E-3</v>
+        <v>-0.82098097213306598</v>
       </c>
       <c r="C250">
-        <v>-1.5751781582405899E-3</v>
+        <v>2.6992851100427599E-2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B251">
-        <v>-0.82098097213306598</v>
+        <v>-0.52822307891953602</v>
       </c>
       <c r="C251">
-        <v>2.6992851100427599E-2</v>
+        <v>3.7138048541363398E-2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>553</v>
+        <v>273</v>
       </c>
       <c r="B252">
-        <v>-0.52822307891953602</v>
+        <v>-0.46896655627538197</v>
       </c>
       <c r="C252">
-        <v>3.7138048541363398E-2</v>
+        <v>0.10413894602778399</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>273</v>
+        <v>546</v>
       </c>
       <c r="B253">
-        <v>-0.46896655627538197</v>
+        <v>-0.44064708947596098</v>
       </c>
       <c r="C253">
-        <v>0.10413894602778399</v>
+        <v>0.36596863329296903</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B254">
-        <v>-0.44064708947596098</v>
+        <v>0.83535411394299997</v>
       </c>
       <c r="C254">
-        <v>0.36596863329296903</v>
+        <v>-0.38996589884502197</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>555</v>
+        <v>274</v>
       </c>
       <c r="B255">
-        <v>0.83535411394299997</v>
+        <v>-0.35426080077605698</v>
       </c>
       <c r="C255">
-        <v>-0.38996589884502197</v>
+        <v>0.36573224638226398</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B256">
-        <v>-0.35426080077605698</v>
+        <v>-1.1341742240289101</v>
       </c>
       <c r="C256">
-        <v>0.36573224638226398</v>
+        <v>-1.6525041500886799</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>275</v>
+        <v>83</v>
       </c>
       <c r="B257">
-        <v>-1.1341742240289101</v>
+        <v>-0.67649364922503497</v>
       </c>
       <c r="C257">
-        <v>-1.6525041500886799</v>
+        <v>-0.162953625137536</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="B258">
-        <v>-0.67649364922503497</v>
+        <v>-1.1659382723534799</v>
       </c>
       <c r="C258">
-        <v>-0.162953625137536</v>
+        <v>-0.56064746371194896</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>556</v>
+        <v>276</v>
       </c>
       <c r="B259">
-        <v>-1.1659382723534799</v>
+        <v>-1.59752391473969</v>
       </c>
       <c r="C259">
-        <v>-0.56064746371194896</v>
+        <v>-1.1398585920231401</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B260">
-        <v>-1.59752391473969</v>
+        <v>0.76445388413194004</v>
       </c>
       <c r="C260">
-        <v>-1.1398585920231401</v>
+        <v>0.77684219370114305</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B261">
-        <v>0.76445388413194004</v>
+        <v>-0.80544590722792098</v>
       </c>
       <c r="C261">
-        <v>0.77684219370114305</v>
+        <v>-0.68711354455372098</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="B262">
-        <v>-0.80544590722792098</v>
+        <v>-1.31231934779604</v>
       </c>
       <c r="C262">
-        <v>-0.68711354455372098</v>
+        <v>-1.09439529652454</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="B263">
-        <v>-1.31231934779604</v>
+        <v>-1.1155032520713699</v>
       </c>
       <c r="C263">
-        <v>-1.09439529652454</v>
+        <v>-1.71204630184014</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="B264">
-        <v>-1.1155032520713699</v>
+        <v>-0.625243008417392</v>
       </c>
       <c r="C264">
-        <v>-1.71204630184014</v>
+        <v>-0.14959070570353</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="B265">
-        <v>-0.625243008417392</v>
+        <v>-0.28117261600389898</v>
       </c>
       <c r="C265">
-        <v>-0.14959070570353</v>
+        <v>-0.51213113067541205</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>557</v>
+        <v>280</v>
       </c>
       <c r="B266">
-        <v>-0.28117261600389898</v>
+        <v>-0.43809801265308601</v>
       </c>
       <c r="C266">
-        <v>-0.51213113067541205</v>
+        <v>0.31351621030094801</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>280</v>
+        <v>550</v>
       </c>
       <c r="B267">
-        <v>-0.43809801265308601</v>
+        <v>-1.0236852989060601</v>
       </c>
       <c r="C267">
-        <v>0.31351621030094801</v>
+        <v>0.68081113893351897</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B268">
-        <v>-1.0236852989060601</v>
+        <v>-0.372467693324256</v>
       </c>
       <c r="C268">
-        <v>0.68081113893351897</v>
+        <v>0.38506497874073897</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>559</v>
+        <v>281</v>
       </c>
       <c r="B269">
-        <v>-0.372467693324256</v>
+        <v>0.102058331886571</v>
       </c>
       <c r="C269">
-        <v>0.38506497874073897</v>
+        <v>0.35402198468597501</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B270">
-        <v>0.102058331886571</v>
+        <v>-1.20817256149929</v>
       </c>
       <c r="C270">
-        <v>0.35402198468597501</v>
+        <v>-1.64595902034346</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>282</v>
+        <v>552</v>
       </c>
       <c r="B271">
-        <v>-1.20817256149929</v>
+        <v>0.84355646837768505</v>
       </c>
       <c r="C271">
-        <v>-1.64595902034346</v>
+        <v>-0.38041441945031801</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B272">
-        <v>0.84355646837768505</v>
+        <v>-1.76688293182406</v>
       </c>
       <c r="C272">
-        <v>-0.38041441945031801</v>
+        <v>0.115880279795706</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>561</v>
+        <v>86</v>
       </c>
       <c r="B273">
-        <v>-1.76688293182406</v>
+        <v>-0.60718303304377197</v>
       </c>
       <c r="C273">
-        <v>0.115880279795706</v>
+        <v>-4.0703813937077102E-3</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B274">
-        <v>-0.60718303304377197</v>
+        <v>-1.2518764817483199</v>
       </c>
       <c r="C274">
-        <v>-4.0703813937077102E-3</v>
+        <v>-0.71281639003016195</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B275">
-        <v>-1.2518764817483199</v>
+        <v>0.73089431805055505</v>
       </c>
       <c r="C275">
-        <v>-0.71281639003016195</v>
+        <v>-0.22578934835186801</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>88</v>
+        <v>442</v>
       </c>
       <c r="B276">
-        <v>0.73089431805055505</v>
+        <v>0.33208054130758502</v>
       </c>
       <c r="C276">
-        <v>-0.22578934835186801</v>
+        <v>-0.29687614856708</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>449</v>
+        <v>381</v>
       </c>
       <c r="B277">
-        <v>0.33208054130758502</v>
+        <v>-1.0237015748121501</v>
       </c>
       <c r="C277">
-        <v>-0.29687614856708</v>
+        <v>-1.6765175581249501</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>381</v>
+        <v>443</v>
       </c>
       <c r="B278">
-        <v>-1.0237015748121501</v>
+        <v>-1.40540932776938</v>
       </c>
       <c r="C278">
-        <v>-1.6765175581249501</v>
+        <v>-1.8681377655701801</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="B279">
-        <v>-1.40540932776938</v>
+        <v>-1.0251368592056</v>
       </c>
       <c r="C279">
-        <v>-1.8681377655701801</v>
+        <v>0.71851598767595903</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>382</v>
+        <v>554</v>
       </c>
       <c r="B280">
-        <v>-1.0251368592056</v>
+        <v>-0.16945778576001799</v>
       </c>
       <c r="C280">
-        <v>0.71851598767595903</v>
+        <v>0.41344898790765899</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>562</v>
+        <v>89</v>
       </c>
       <c r="B281">
-        <v>-0.16945778576001799</v>
+        <v>-0.39992303650827099</v>
       </c>
       <c r="C281">
-        <v>0.41344898790765899</v>
+        <v>0.14591696457605599</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>89</v>
+        <v>555</v>
       </c>
       <c r="B282">
-        <v>-0.39992303650827099</v>
+        <v>-0.237430223154345</v>
       </c>
       <c r="C282">
-        <v>0.14591696457605599</v>
+        <v>0.53171079635007601</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>563</v>
+        <v>90</v>
       </c>
       <c r="B283">
-        <v>-0.237430223154345</v>
+        <v>-1.1496352318427101</v>
       </c>
       <c r="C283">
-        <v>0.53171079635007601</v>
+        <v>-1.7177693798586799</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>90</v>
+        <v>383</v>
       </c>
       <c r="B284">
-        <v>-1.1496352318427101</v>
+        <v>-0.507625430332314</v>
       </c>
       <c r="C284">
-        <v>-1.7177693798586799</v>
+        <v>0.160530161366954</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>383</v>
+        <v>556</v>
       </c>
       <c r="B285">
-        <v>-0.507625430332314</v>
+        <v>-0.67453168077331405</v>
       </c>
       <c r="C285">
-        <v>0.160530161366954</v>
+        <v>0.25870882149993002</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B286">
-        <v>-0.67453168077331405</v>
+        <v>-0.25847766857457299</v>
       </c>
       <c r="C286">
-        <v>0.25870882149993002</v>
+        <v>0.40634916962016199</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="B287">
-        <v>-0.25847766857457299</v>
+        <v>-0.52050524318245905</v>
       </c>
       <c r="C287">
-        <v>0.40634916962016199</v>
+        <v>0.67173670379657102</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>566</v>
+        <v>91</v>
       </c>
       <c r="B288">
-        <v>-0.52050524318245905</v>
+        <v>0.68739400480663304</v>
       </c>
       <c r="C288">
-        <v>0.67173670379657102</v>
+        <v>-0.122103247458515</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>91</v>
+        <v>384</v>
       </c>
       <c r="B289">
-        <v>0.68739400480663304</v>
+        <v>-2.16736817292753E-2</v>
       </c>
       <c r="C289">
-        <v>-0.122103247458515</v>
+        <v>0.51701785348625595</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B290">
-        <v>-2.16736817292753E-2</v>
+        <v>-0.47721067797052202</v>
       </c>
       <c r="C290">
-        <v>0.51701785348625595</v>
+        <v>0.35447910146009198</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>385</v>
+        <v>92</v>
       </c>
       <c r="B291">
-        <v>-0.47721067797052202</v>
+        <v>-1.0711525317794699</v>
       </c>
       <c r="C291">
-        <v>0.35447910146009198</v>
+        <v>-1.47862481880102</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B292">
-        <v>-1.0711525317794699</v>
+        <v>-5.8061286531591198E-2</v>
       </c>
       <c r="C292">
-        <v>-1.47862481880102</v>
+        <v>4.8868109470981301E-3</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B293">
-        <v>-5.8061286531591198E-2</v>
+        <v>0.69805755239649903</v>
       </c>
       <c r="C293">
-        <v>4.8868109470981301E-3</v>
+        <v>-0.16238044136128099</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>94</v>
+        <v>386</v>
       </c>
       <c r="B294">
-        <v>0.69805755239649903</v>
+        <v>0.69780092578833697</v>
       </c>
       <c r="C294">
-        <v>-0.16238044136128099</v>
+        <v>-0.48181466328863798</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>386</v>
+        <v>559</v>
       </c>
       <c r="B295">
-        <v>0.69780092578833697</v>
+        <v>0.599253968967985</v>
       </c>
       <c r="C295">
-        <v>-0.48181466328863798</v>
+        <v>-0.48483382239754902</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>567</v>
+        <v>95</v>
       </c>
       <c r="B296">
-        <v>0.599253968967985</v>
+        <v>-1.4424187261739101</v>
       </c>
       <c r="C296">
-        <v>-0.48483382239754902</v>
+        <v>-1.23748481073539</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>95</v>
+        <v>560</v>
       </c>
       <c r="B297">
-        <v>-1.4424187261739101</v>
+        <v>-0.97754720344081802</v>
       </c>
       <c r="C297">
-        <v>-1.23748481073539</v>
+        <v>-0.71997098202996601</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>568</v>
+        <v>96</v>
       </c>
       <c r="B298">
-        <v>-0.97754720344081802</v>
+        <v>-1.15113678737029</v>
       </c>
       <c r="C298">
-        <v>-0.71997098202996601</v>
+        <v>-1.68489853408781</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B299">
-        <v>-1.15113678737029</v>
+        <v>-0.51071051809396795</v>
       </c>
       <c r="C299">
-        <v>-1.68489853408781</v>
+        <v>9.6316208390011607E-2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B300">
-        <v>-0.51071051809396795</v>
+        <v>-1.1500991135163099</v>
       </c>
       <c r="C300">
-        <v>9.6316208390011607E-2</v>
+        <v>-1.68390694812102</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>98</v>
+        <v>561</v>
       </c>
       <c r="B301">
-        <v>-1.1500991135163099</v>
+        <v>0.72173688759621302</v>
       </c>
       <c r="C301">
-        <v>-1.68390694812102</v>
+        <v>0.65312285614846799</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>569</v>
+        <v>387</v>
       </c>
       <c r="B302">
-        <v>0.72173688759621302</v>
+        <v>-0.124804354860597</v>
       </c>
       <c r="C302">
-        <v>0.65312285614846799</v>
+        <v>0.52285661474368506</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>387</v>
+        <v>99</v>
       </c>
       <c r="B303">
-        <v>-0.124804354860597</v>
+        <v>-0.89136460126439299</v>
       </c>
       <c r="C303">
-        <v>0.52285661474368506</v>
+        <v>-0.433268177145751</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>99</v>
+        <v>388</v>
       </c>
       <c r="B304">
-        <v>-0.89136460126439299</v>
+        <v>-1.06323962610157</v>
       </c>
       <c r="C304">
-        <v>-0.433268177145751</v>
+        <v>-7.3320493798051797E-3</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>388</v>
+        <v>562</v>
       </c>
       <c r="B305">
-        <v>-1.06323962610157</v>
+        <v>-1.7831820016841999</v>
       </c>
       <c r="C305">
-        <v>-7.3320493798051797E-3</v>
+        <v>0.24518000691467001</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B306">
-        <v>-1.7831820016841999</v>
+        <v>6.5542360948198097E-2</v>
       </c>
       <c r="C306">
-        <v>0.24518000691467001</v>
+        <v>1.30427701988192</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="B307">
-        <v>6.5542360948198097E-2</v>
+        <v>-0.71954966374620799</v>
       </c>
       <c r="C307">
-        <v>1.30427701988192</v>
+        <v>-0.71986402806081395</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>572</v>
+        <v>389</v>
       </c>
       <c r="B308">
-        <v>-0.71954966374620799</v>
+        <v>-0.35813601661845401</v>
       </c>
       <c r="C308">
-        <v>-0.71986402806081395</v>
+        <v>-0.30987283543608102</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>389</v>
+        <v>565</v>
       </c>
       <c r="B309">
-        <v>-0.35813601661845401</v>
+        <v>0.31982954400855501</v>
       </c>
       <c r="C309">
-        <v>-0.30987283543608102</v>
+        <v>0.50939285189280004</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B310">
-        <v>0.31982954400855501</v>
+        <v>-0.77943968187253898</v>
       </c>
       <c r="C310">
-        <v>0.50939285189280004</v>
+        <v>0.205449713537496</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>574</v>
+        <v>390</v>
       </c>
       <c r="B311">
-        <v>-0.77943968187253898</v>
+        <v>-1.07350472242808</v>
       </c>
       <c r="C311">
-        <v>0.205449713537496</v>
+        <v>-1.3868647777277801</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="B312">
-        <v>-1.07350472242808</v>
+        <v>0.66558359141832202</v>
       </c>
       <c r="C312">
-        <v>-1.3868647777277801</v>
+        <v>-0.176260649786428</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>100</v>
+        <v>567</v>
       </c>
       <c r="B313">
-        <v>0.66558359141832202</v>
+        <v>-1.8306199767439999</v>
       </c>
       <c r="C313">
-        <v>-0.176260649786428</v>
+        <v>0.205102813231515</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>575</v>
+        <v>101</v>
       </c>
       <c r="B314">
-        <v>-1.8306199767439999</v>
+        <v>5.26898354515292E-2</v>
       </c>
       <c r="C314">
-        <v>0.205102813231515</v>
+        <v>0.26385599317809</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B315">
-        <v>5.26898354515292E-2</v>
+        <v>0.75880758892809697</v>
       </c>
       <c r="C315">
-        <v>0.26385599317809</v>
+        <v>-0.30572525719328297</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B316">
-        <v>0.75880758892809697</v>
+        <v>-0.33392222295797502</v>
       </c>
       <c r="C316">
-        <v>-0.30572525719328297</v>
+        <v>0.238297803864774</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>103</v>
+        <v>568</v>
       </c>
       <c r="B317">
-        <v>-0.33392222295797502</v>
+        <v>-0.64775816554569399</v>
       </c>
       <c r="C317">
-        <v>0.238297803864774</v>
+        <v>0.581782123666858</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>436</v>
-      </c>
-      <c r="B318" t="s">
-        <v>441</v>
-      </c>
-      <c r="C318" t="s">
-        <v>441</v>
+        <v>391</v>
+      </c>
+      <c r="B318">
+        <v>-0.56113455409064095</v>
+      </c>
+      <c r="C318">
+        <v>0.61340718873858102</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>576</v>
+        <v>104</v>
       </c>
       <c r="B319">
-        <v>-0.64775816554569399</v>
+        <v>-1.1405779915027401</v>
       </c>
       <c r="C319">
-        <v>0.581782123666858</v>
+        <v>-1.7277314304945599</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="B320">
-        <v>-0.56113455409064095</v>
+        <v>-1.6108914822221501</v>
       </c>
       <c r="C320">
-        <v>0.61340718873858102</v>
+        <v>-1.6071496831082599</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B321">
-        <v>-1.1405779915027401</v>
+        <v>-0.14826315154499001</v>
       </c>
       <c r="C321">
-        <v>-1.7277314304945599</v>
+        <v>2.5437814404543801E-2</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>451</v>
+        <v>106</v>
       </c>
       <c r="B322">
-        <v>-1.6108914822221501</v>
+        <v>-0.52616753193564503</v>
       </c>
       <c r="C322">
-        <v>-1.6071496831082599</v>
+        <v>7.5324656935843906E-2</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B323">
-        <v>-0.14826315154499001</v>
+        <v>5.1135529467849203E-2</v>
       </c>
       <c r="C323">
-        <v>2.5437814404543801E-2</v>
+        <v>0.18958048667633501</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>106</v>
+        <v>392</v>
       </c>
       <c r="B324">
-        <v>-0.52616753193564503</v>
+        <v>-0.49127597911711202</v>
       </c>
       <c r="C324">
-        <v>7.5324656935843906E-2</v>
+        <v>0.44863368050547803</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>107</v>
+        <v>569</v>
       </c>
       <c r="B325">
-        <v>5.1135529467849203E-2</v>
+        <v>-0.34793884512748802</v>
       </c>
       <c r="C325">
-        <v>0.18958048667633501</v>
+        <v>0.35992754510099501</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>392</v>
+        <v>570</v>
       </c>
       <c r="B326">
-        <v>-0.49127597911711202</v>
+        <v>-1.1485347054791</v>
       </c>
       <c r="C326">
-        <v>0.44863368050547803</v>
+        <v>-0.15157889069529401</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>577</v>
+        <v>393</v>
       </c>
       <c r="B327">
-        <v>-0.34793884512748802</v>
+        <v>-0.61513181149524798</v>
       </c>
       <c r="C327">
-        <v>0.35992754510099501</v>
+        <v>0.39412481745502498</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>578</v>
+        <v>445</v>
       </c>
       <c r="B328">
-        <v>-1.1485347054791</v>
+        <v>0.78507653291912305</v>
       </c>
       <c r="C328">
-        <v>-0.15157889069529401</v>
+        <v>-0.196872676927419</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B329">
-        <v>-0.61513181149524798</v>
+        <v>-0.72629164849211802</v>
       </c>
       <c r="C329">
-        <v>0.39412481745502498</v>
+        <v>0.20348460646417799</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>452</v>
+        <v>395</v>
       </c>
       <c r="B330">
-        <v>0.78507653291912305</v>
+        <v>-1.64851967663016</v>
       </c>
       <c r="C330">
-        <v>-0.196872676927419</v>
+        <v>-0.86709547079402005</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B331">
-        <v>-0.72629164849211802</v>
+        <v>0.55014694660927699</v>
       </c>
       <c r="C331">
-        <v>0.20348460646417799</v>
+        <v>-0.21815373826892701</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>395</v>
+        <v>571</v>
       </c>
       <c r="B332">
-        <v>-1.64851967663016</v>
+        <v>-1.10363283231939</v>
       </c>
       <c r="C332">
-        <v>-0.86709547079402005</v>
+        <v>0.654402674686276</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>396</v>
+        <v>572</v>
       </c>
       <c r="B333">
-        <v>0.55014694660927699</v>
+        <v>-0.93775688969417204</v>
       </c>
       <c r="C333">
-        <v>-0.21815373826892701</v>
+        <v>0.25257046452223503</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>579</v>
+        <v>432</v>
       </c>
       <c r="B334">
-        <v>-1.10363283231939</v>
+        <v>-0.97597060968822302</v>
       </c>
       <c r="C334">
-        <v>0.654402674686276</v>
+        <v>-0.48749204271153401</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B335">
-        <v>-0.93775688969417204</v>
+        <v>-0.24378951950658201</v>
       </c>
       <c r="C335">
-        <v>0.25257046452223503</v>
+        <v>-0.11892102717929801</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="B336">
-        <v>-0.97597060968822302</v>
+        <v>-0.79655186372648801</v>
       </c>
       <c r="C336">
-        <v>-0.48749204271153401</v>
+        <v>-1.1459607119048201</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>581</v>
+        <v>398</v>
       </c>
       <c r="B337">
-        <v>-0.24378951950658201</v>
+        <v>-1.1277020267361899</v>
       </c>
       <c r="C337">
-        <v>-0.11892102717929801</v>
+        <v>-1.9285115118782099</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>397</v>
+        <v>108</v>
       </c>
       <c r="B338">
-        <v>-0.79655186372648801</v>
+        <v>-0.93677576241885196</v>
       </c>
       <c r="C338">
-        <v>-1.1459607119048201</v>
+        <v>0.10113464292942401</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>398</v>
+        <v>574</v>
       </c>
       <c r="B339">
-        <v>-1.1277020267361899</v>
+        <v>-0.70850297782165805</v>
       </c>
       <c r="C339">
-        <v>-1.9285115118782099</v>
+        <v>-0.90271861082553095</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B340">
-        <v>-0.93677576241885196</v>
+        <v>-1.1076115401578299</v>
       </c>
       <c r="C340">
-        <v>0.10113464292942401</v>
+        <v>-1.7011957380960001</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>582</v>
+        <v>399</v>
       </c>
       <c r="B341">
-        <v>-0.70850297782165805</v>
+        <v>-1.1296948727447</v>
       </c>
       <c r="C341">
-        <v>-0.90271861082553095</v>
+        <v>-1.6910978979679301</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B342">
-        <v>-1.1076115401578299</v>
+        <v>-1.1469026916469101</v>
       </c>
       <c r="C342">
-        <v>-1.7011957380960001</v>
+        <v>-1.75380479687683</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>399</v>
+        <v>575</v>
       </c>
       <c r="B343">
-        <v>-1.1296948727447</v>
+        <v>-0.52812603316137996</v>
       </c>
       <c r="C343">
-        <v>-1.6910978979679301</v>
+        <v>0.69934076361381603</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>110</v>
+        <v>576</v>
       </c>
       <c r="B344">
-        <v>-1.1469026916469101</v>
+        <v>-0.18792951144797901</v>
       </c>
       <c r="C344">
-        <v>-1.75380479687683</v>
+        <v>0.63054573664728297</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B345">
-        <v>-0.52812603316137996</v>
+        <v>-1.46400113181571</v>
       </c>
       <c r="C345">
-        <v>0.69934076361381603</v>
+        <v>-0.62664340255821105</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B346">
-        <v>-0.18792951144797901</v>
+        <v>-0.41892671988956198</v>
       </c>
       <c r="C346">
-        <v>0.63054573664728297</v>
+        <v>0.70686488887717103</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>585</v>
+        <v>111</v>
       </c>
       <c r="B347">
-        <v>-1.46400113181571</v>
+        <v>-7.9444916661848206E-2</v>
       </c>
       <c r="C347">
-        <v>-0.62664340255821105</v>
+        <v>0.28063978239728499</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>586</v>
+        <v>446</v>
       </c>
       <c r="B348">
-        <v>-0.41892671988956198</v>
+        <v>0.49895968325011603</v>
       </c>
       <c r="C348">
-        <v>0.70686488887717103</v>
+        <v>-0.42683009261760402</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B349">
-        <v>-7.9444916661848206E-2</v>
+        <v>-0.14837008833691001</v>
       </c>
       <c r="C349">
-        <v>0.28063978239728499</v>
+        <v>0.396615731850533</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>453</v>
+        <v>579</v>
       </c>
       <c r="B350">
-        <v>0.49895968325011603</v>
+        <v>-0.461337043106682</v>
       </c>
       <c r="C350">
-        <v>-0.42683009261760402</v>
+        <v>0.47073003338831099</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>112</v>
+        <v>580</v>
       </c>
       <c r="B351">
-        <v>-0.14837008833691001</v>
+        <v>-0.64647035660262897</v>
       </c>
       <c r="C351">
-        <v>0.396615731850533</v>
+        <v>-0.90281670486851895</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>587</v>
+        <v>113</v>
       </c>
       <c r="B352">
-        <v>-0.461337043106682</v>
+        <v>0.77380862791503102</v>
       </c>
       <c r="C352">
-        <v>0.47073003338831099</v>
+        <v>-0.323096994607039</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B353">
-        <v>-0.64647035660262897</v>
+        <v>-1.00331237862972</v>
       </c>
       <c r="C353">
-        <v>-0.90281670486851895</v>
+        <v>0.50626847880038905</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>113</v>
+        <v>582</v>
       </c>
       <c r="B354">
-        <v>0.77380862791503102</v>
+        <v>-0.14418564154850799</v>
       </c>
       <c r="C354">
-        <v>-0.323096994607039</v>
+        <v>-1.8591037263274501E-2</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>589</v>
+        <v>400</v>
       </c>
       <c r="B355">
-        <v>-1.00331237862972</v>
+        <v>-0.87224136343790404</v>
       </c>
       <c r="C355">
-        <v>0.50626847880038905</v>
+        <v>-0.22675691273255599</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B356">
-        <v>-0.14418564154850799</v>
+        <v>-0.52828591766032196</v>
       </c>
       <c r="C356">
-        <v>-1.8591037263274501E-2</v>
+        <v>-0.14108600572542199</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>400</v>
+        <v>114</v>
       </c>
       <c r="B357">
-        <v>-0.87224136343790404</v>
+        <v>-0.66242784825997503</v>
       </c>
       <c r="C357">
-        <v>-0.22675691273255599</v>
+        <v>-0.73868052859081201</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>591</v>
+        <v>401</v>
       </c>
       <c r="B358">
-        <v>-0.52828591766032196</v>
+        <v>-0.44721244506369001</v>
       </c>
       <c r="C358">
-        <v>-0.14108600572542199</v>
+        <v>0.27295076199351398</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>114</v>
+        <v>584</v>
       </c>
       <c r="B359">
-        <v>-0.66242784825997503</v>
+        <v>-0.35390993020474198</v>
       </c>
       <c r="C359">
-        <v>-0.73868052859081201</v>
+        <v>-0.12315947141763101</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B360">
-        <v>-0.44721244506369001</v>
+        <v>0.81828738920542599</v>
       </c>
       <c r="C360">
-        <v>0.27295076199351398</v>
+        <v>-0.36732370722019098</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="B361">
-        <v>-0.35390993020474198</v>
+        <v>-0.65596559740083005</v>
       </c>
       <c r="C361">
-        <v>-0.12315947141763101</v>
+        <v>0.350912519841244</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>402</v>
+        <v>586</v>
       </c>
       <c r="B362">
-        <v>0.81828738920542599</v>
+        <v>-1.4176490515070901</v>
       </c>
       <c r="C362">
-        <v>-0.36732370722019098</v>
+        <v>0.15933795993755401</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>593</v>
+        <v>115</v>
       </c>
       <c r="B363">
-        <v>-0.65596559740083005</v>
+        <v>-0.70235314317118103</v>
       </c>
       <c r="C363">
-        <v>0.350912519841244</v>
+        <v>-0.13342175518884</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>594</v>
+        <v>403</v>
       </c>
       <c r="B364">
-        <v>-1.4176490515070901</v>
+        <v>-0.67004757929802605</v>
       </c>
       <c r="C364">
-        <v>0.15933795993755401</v>
+        <v>0.16421618875260699</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>115</v>
+        <v>587</v>
       </c>
       <c r="B365">
-        <v>-0.70235314317118103</v>
+        <v>0.51980223567127304</v>
       </c>
       <c r="C365">
-        <v>-0.13342175518884</v>
+        <v>0.87222157221478502</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>403</v>
+        <v>116</v>
       </c>
       <c r="B366">
-        <v>-0.67004757929802605</v>
+        <v>-0.19842080270110701</v>
       </c>
       <c r="C366">
-        <v>0.16421618875260699</v>
+        <v>-1.8703807360035799E-2</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="B367">
-        <v>0.51980223567127304</v>
+        <v>-0.56597915611959504</v>
       </c>
       <c r="C367">
-        <v>0.87222157221478502</v>
+        <v>0.38145416032389501</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>116</v>
+        <v>589</v>
       </c>
       <c r="B368">
-        <v>-0.19842080270110701</v>
+        <v>0.84243858192915799</v>
       </c>
       <c r="C368">
-        <v>-1.8703807360035799E-2</v>
+        <v>-0.30431015129713801</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B369">
-        <v>-0.56597915611959504</v>
+        <v>-0.76631960875743599</v>
       </c>
       <c r="C369">
-        <v>0.38145416032389501</v>
+        <v>0.238364961137671</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>597</v>
+        <v>404</v>
       </c>
       <c r="B370">
-        <v>0.84243858192915799</v>
+        <v>-1.1183556335659099</v>
       </c>
       <c r="C370">
-        <v>-0.30431015129713801</v>
+        <v>-1.7810642923718301</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B371">
-        <v>-0.76631960875743599</v>
+        <v>-0.16039579067654999</v>
       </c>
       <c r="C371">
-        <v>0.238364961137671</v>
+        <v>1.02760081519618</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>404</v>
+        <v>592</v>
       </c>
       <c r="B372">
-        <v>-1.1183556335659099</v>
+        <v>0.76844457076997497</v>
       </c>
       <c r="C372">
-        <v>-1.7810642923718301</v>
+        <v>-0.14574262693585299</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>599</v>
+        <v>117</v>
       </c>
       <c r="B373">
-        <v>-0.16039579067654999</v>
+        <v>-1.29606197937677</v>
       </c>
       <c r="C373">
-        <v>1.02760081519618</v>
+        <v>-0.96716552734418604</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>600</v>
+        <v>118</v>
       </c>
       <c r="B374">
-        <v>0.76844457076997497</v>
+        <v>-0.64387551161978296</v>
       </c>
       <c r="C374">
-        <v>-0.14574262693585299</v>
+        <v>-0.18800202752829701</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>117</v>
+        <v>405</v>
       </c>
       <c r="B375">
-        <v>-1.29606197937677</v>
+        <v>-0.63692892657782296</v>
       </c>
       <c r="C375">
-        <v>-0.96716552734418604</v>
+        <v>5.0502479643761297E-2</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>118</v>
+        <v>406</v>
       </c>
       <c r="B376">
-        <v>-0.64387551161978296</v>
+        <v>-1.1703086990639</v>
       </c>
       <c r="C376">
-        <v>-0.18800202752829701</v>
+        <v>-1.58932668730142</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>405</v>
+        <v>593</v>
       </c>
       <c r="B377">
-        <v>-0.63692892657782296</v>
+        <v>-0.984935422599029</v>
       </c>
       <c r="C377">
-        <v>5.0502479643761297E-2</v>
+        <v>0.304142173670365</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>406</v>
+        <v>594</v>
       </c>
       <c r="B378">
-        <v>-1.1703086990639</v>
+        <v>-0.984935422599029</v>
       </c>
       <c r="C378">
-        <v>-1.58932668730142</v>
+        <v>0.304142173670365</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>601</v>
+        <v>407</v>
       </c>
       <c r="B379">
-        <v>-0.984935422599029</v>
+        <v>0.59781579097791704</v>
       </c>
       <c r="C379">
-        <v>0.304142173670365</v>
+        <v>-0.70755163989581005</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="B380">
-        <v>-0.984935422599029</v>
-      </c>
-      <c r="C380">
-        <v>0.304142173670365</v>
+        <v>-0.45371252320785399</v>
+      </c>
+      <c r="C380" s="3">
+        <v>-1.13766251399316E-5</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B381">
-        <v>0.59781579097791704</v>
+        <v>9.0287367799972706E-2</v>
       </c>
       <c r="C381">
-        <v>-0.70755163989581005</v>
+        <v>0.93978404142674699</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B382">
-        <v>-0.45371252320785399</v>
-      </c>
-      <c r="C382" s="3">
-        <v>-1.13766251399316E-5</v>
+        <v>-0.52392433050799103</v>
+      </c>
+      <c r="C382">
+        <v>7.5791254963403595E-2</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="B383">
-        <v>9.0287367799972706E-2</v>
+        <v>-1.1379755586578899</v>
       </c>
       <c r="C383">
-        <v>0.93978404142674699</v>
+        <v>-1.7091999422200701</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="B384">
-        <v>-0.52392433050799103</v>
+        <v>-0.62952594897343905</v>
       </c>
       <c r="C384">
-        <v>7.5791254963403595E-2</v>
+        <v>-0.93500054910096597</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>438</v>
+        <v>598</v>
       </c>
       <c r="B385">
-        <v>-1.1379755586578899</v>
+        <v>-0.88160529395917597</v>
       </c>
       <c r="C385">
-        <v>-1.7091999422200701</v>
+        <v>5.2398590511349701E-2</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B386">
-        <v>-0.62952594897343905</v>
+        <v>0.79719950224659697</v>
       </c>
       <c r="C386">
-        <v>-0.93500054910096597</v>
+        <v>-0.47255185964075602</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>454</v>
-      </c>
-      <c r="B387" t="s">
-        <v>441</v>
-      </c>
-      <c r="C387" t="s">
-        <v>441</v>
+        <v>600</v>
+      </c>
+      <c r="B387">
+        <v>-1.1896215700723001</v>
+      </c>
+      <c r="C387">
+        <v>-0.60192321598288501</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>606</v>
+        <v>119</v>
       </c>
       <c r="B388">
-        <v>-0.88160529395917597</v>
+        <v>-1.1495148969594899</v>
       </c>
       <c r="C388">
-        <v>5.2398590511349701E-2</v>
+        <v>-0.47399010378831602</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>607</v>
+        <v>120</v>
       </c>
       <c r="B389">
-        <v>0.79719950224659697</v>
+        <v>0.73987098904489801</v>
       </c>
       <c r="C389">
-        <v>-0.47255185964075602</v>
+        <v>-0.17525079784887701</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>608</v>
+        <v>121</v>
       </c>
       <c r="B390">
-        <v>-1.1896215700723001</v>
+        <v>0.111994934485234</v>
       </c>
       <c r="C390">
-        <v>-0.60192321598288501</v>
+        <v>7.87036213211212E-2</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B391">
-        <v>-1.1495148969594899</v>
+        <v>-0.29459205519402398</v>
       </c>
       <c r="C391">
-        <v>-0.47399010378831602</v>
+        <v>0.15907623119505701</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>120</v>
+        <v>601</v>
       </c>
       <c r="B392">
-        <v>0.73987098904489801</v>
+        <v>-0.52219292766257397</v>
       </c>
       <c r="C392">
-        <v>-0.17525079784887701</v>
+        <v>-0.24389518838080401</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B393">
-        <v>0.111994934485234</v>
+        <v>-0.389142794986581</v>
       </c>
       <c r="C393">
-        <v>7.87036213211212E-2</v>
+        <v>1.8616539764584699E-2</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B394">
-        <v>-0.29459205519402398</v>
+        <v>-3.1957038029935499E-2</v>
       </c>
       <c r="C394">
-        <v>0.15907623119505701</v>
+        <v>2.8423922976560601E-2</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>609</v>
+        <v>125</v>
       </c>
       <c r="B395">
-        <v>-0.52219292766257397</v>
+        <v>0.79538073488230399</v>
       </c>
       <c r="C395">
-        <v>-0.24389518838080401</v>
+        <v>-0.29390227084947401</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>123</v>
+        <v>602</v>
       </c>
       <c r="B396">
-        <v>-0.389142794986581</v>
+        <v>0.938433090538216</v>
       </c>
       <c r="C396">
-        <v>1.8616539764584699E-2</v>
+        <v>0.56345232508797505</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>124</v>
+        <v>409</v>
       </c>
       <c r="B397">
-        <v>-3.1957038029935499E-2</v>
+        <v>0.684147559376309</v>
       </c>
       <c r="C397">
-        <v>2.8423922976560601E-2</v>
+        <v>-0.415667298917346</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>125</v>
+        <v>434</v>
       </c>
       <c r="B398">
-        <v>0.79538073488230399</v>
+        <v>0.96045879033572201</v>
       </c>
       <c r="C398">
-        <v>-0.29390227084947401</v>
+        <v>-3.2881511317396403E-2</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="B399">
-        <v>0.938433090538216</v>
+        <v>-0.97970837817891099</v>
       </c>
       <c r="C399">
-        <v>0.56345232508797505</v>
+        <v>5.9968071539824801E-2</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B400">
-        <v>0.684147559376309</v>
+        <v>-1.83221051498589</v>
       </c>
       <c r="C400">
-        <v>-0.415667298917346</v>
+        <v>-0.98105146184411196</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>439</v>
+        <v>604</v>
       </c>
       <c r="B401">
-        <v>0.96045879033572201</v>
+        <v>-0.56312513650429796</v>
       </c>
       <c r="C401">
-        <v>-3.2881511317396403E-2</v>
+        <v>0.37156645801517102</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B402">
-        <v>-0.97970837817891099</v>
+        <v>-0.49234163971421702</v>
       </c>
       <c r="C402">
-        <v>5.9968071539824801E-2</v>
+        <v>0.52234497368495802</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="B403">
-        <v>-1.83221051498589</v>
+        <v>-1.1992070031414701</v>
       </c>
       <c r="C403">
-        <v>-0.98105146184411196</v>
+        <v>-1.0707323103908499</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B404">
-        <v>-0.56312513650429796</v>
+        <v>-0.892084080733478</v>
       </c>
       <c r="C404">
-        <v>0.37156645801517102</v>
+        <v>0.22873991025489801</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>613</v>
+        <v>411</v>
       </c>
       <c r="B405">
-        <v>-0.49234163971421702</v>
+        <v>-1.25422438677342</v>
       </c>
       <c r="C405">
-        <v>0.52234497368495802</v>
+        <v>-0.51563468763343701</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>126</v>
+        <v>607</v>
       </c>
       <c r="B406">
-        <v>-1.1992070031414701</v>
+        <v>-0.59491924520964001</v>
       </c>
       <c r="C406">
-        <v>-1.0707323103908499</v>
+        <v>5.38551731136876E-3</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>614</v>
+        <v>412</v>
       </c>
       <c r="B407">
-        <v>-0.892084080733478</v>
+        <v>0.258312788836561</v>
       </c>
       <c r="C407">
-        <v>0.22873991025489801</v>
+        <v>-9.9773505573777801E-2</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B408">
-        <v>-1.25422438677342</v>
+        <v>-1.1905400334445799</v>
       </c>
       <c r="C408">
-        <v>-0.51563468763343701</v>
+        <v>-1.4345609469531699</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>615</v>
+        <v>127</v>
       </c>
       <c r="B409">
-        <v>-0.59491924520964001</v>
+        <v>-0.672115202619879</v>
       </c>
       <c r="C409">
-        <v>5.38551731136876E-3</v>
+        <v>-0.15516845278094901</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>412</v>
+        <v>608</v>
       </c>
       <c r="B410">
-        <v>0.258312788836561</v>
+        <v>0.938433090538216</v>
       </c>
       <c r="C410">
-        <v>-9.9773505573777801E-2</v>
+        <v>0.56345232508797505</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>413</v>
+        <v>609</v>
       </c>
       <c r="B411">
-        <v>-1.1905400334445799</v>
+        <v>-0.68252686373617399</v>
       </c>
       <c r="C411">
-        <v>-1.4345609469531699</v>
+        <v>-1.12693544891041</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B412">
-        <v>-0.672115202619879</v>
+        <v>-0.59255071164881301</v>
       </c>
       <c r="C412">
-        <v>-0.15516845278094901</v>
+        <v>-0.22587209449239301</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B413">
-        <v>0.938433090538216</v>
+        <v>-0.601549002545404</v>
       </c>
       <c r="C413">
-        <v>0.56345232508797505</v>
+        <v>0.71721857109897802</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>617</v>
+        <v>129</v>
       </c>
       <c r="B414">
-        <v>-0.68252686373617399</v>
+        <v>-0.121089495982781</v>
       </c>
       <c r="C414">
-        <v>-1.12693544891041</v>
+        <v>0.53137882325288399</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>128</v>
+        <v>414</v>
       </c>
       <c r="B415">
-        <v>-0.59255071164881301</v>
+        <v>-0.77429368172197499</v>
       </c>
       <c r="C415">
-        <v>-0.22587209449239301</v>
+        <v>-7.5570523111655801E-3</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>618</v>
+        <v>435</v>
       </c>
       <c r="B416">
-        <v>-0.601549002545404</v>
+        <v>5.92943389868806E-2</v>
       </c>
       <c r="C416">
-        <v>0.71721857109897802</v>
+        <v>1.4031753749459099</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>129</v>
+        <v>415</v>
       </c>
       <c r="B417">
-        <v>-0.121089495982781</v>
+        <v>-0.77294177624025695</v>
       </c>
       <c r="C417">
-        <v>0.53137882325288399</v>
+        <v>-0.284379529388813</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B418">
-        <v>-0.77429368172197499</v>
+        <v>-0.73692951405083296</v>
       </c>
       <c r="C418">
-        <v>-7.5570523111655801E-3</v>
+        <v>0.39725974854295998</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="B419">
-        <v>5.92943389868806E-2</v>
+        <v>-1.0272531766002799</v>
       </c>
       <c r="C419">
-        <v>1.4031753749459099</v>
+        <v>-0.88838465458276505</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>415</v>
+        <v>130</v>
       </c>
       <c r="B420">
-        <v>-0.77294177624025695</v>
+        <v>-0.62934474503703597</v>
       </c>
       <c r="C420">
-        <v>-0.284379529388813</v>
+        <v>-5.2961779604244003E-2</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B421">
-        <v>-0.73692951405083296</v>
+        <v>-1.25509883706923</v>
       </c>
       <c r="C421">
-        <v>0.39725974854295998</v>
+        <v>-1.01593054631512</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B422">
-        <v>-1.0272531766002799</v>
+        <v>-1.0996499822705801</v>
       </c>
       <c r="C422">
-        <v>-0.88838465458276505</v>
+        <v>-0.52215607575774903</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>130</v>
+        <v>611</v>
       </c>
       <c r="B423">
-        <v>-0.62934474503703597</v>
+        <v>0.77660911619630202</v>
       </c>
       <c r="C423">
-        <v>-5.2961779604244003E-2</v>
+        <v>-0.12588326476692099</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="B424">
-        <v>-1.25509883706923</v>
+        <v>0.82264094446835101</v>
       </c>
       <c r="C424">
-        <v>-1.01593054631512</v>
+        <v>-0.16002003445969301</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>419</v>
+        <v>131</v>
       </c>
       <c r="B425">
-        <v>-1.0996499822705801</v>
+        <v>-1.1840138074283999</v>
       </c>
       <c r="C425">
-        <v>-0.52215607575774903</v>
+        <v>-1.2450848518253901</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>619</v>
+        <v>283</v>
       </c>
       <c r="B426">
-        <v>0.77660911619630202</v>
+        <v>-1.29780126554912</v>
       </c>
       <c r="C426">
-        <v>-0.12588326476692099</v>
+        <v>-0.24408031487303</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B427">
-        <v>0.82264094446835101</v>
+        <v>0.83403962491553096</v>
       </c>
       <c r="C427">
-        <v>-0.16002003445969301</v>
+        <v>-0.25140040366640898</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>131</v>
+        <v>612</v>
       </c>
       <c r="B428">
-        <v>-1.1840138074283999</v>
+        <v>-0.49263470858921699</v>
       </c>
       <c r="C428">
-        <v>-1.2450848518253901</v>
+        <v>0.16287891772021501</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B429">
-        <v>-1.29780126554912</v>
+        <v>-0.48553370862136802</v>
       </c>
       <c r="C429">
-        <v>-0.24408031487303</v>
+        <v>-0.15615945531265599</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>456</v>
+        <v>285</v>
       </c>
       <c r="B430">
-        <v>0.83403962491553096</v>
+        <v>-1.0615687459629399</v>
       </c>
       <c r="C430">
-        <v>-0.25140040366640898</v>
+        <v>-1.3037385735625699</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>620</v>
+        <v>286</v>
       </c>
       <c r="B431">
-        <v>-0.49263470858921699</v>
+        <v>0.77411652013477505</v>
       </c>
       <c r="C431">
-        <v>0.16287891772021501</v>
+        <v>-0.302679250841356</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>284</v>
+        <v>132</v>
       </c>
       <c r="B432">
-        <v>-0.48553370862136802</v>
+        <v>-1.19874345853044</v>
       </c>
       <c r="C432">
-        <v>-0.15615945531265599</v>
+        <v>-0.56701714570233497</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>285</v>
+        <v>133</v>
       </c>
       <c r="B433">
-        <v>-1.0615687459629399</v>
+        <v>0.709533598154242</v>
       </c>
       <c r="C433">
-        <v>-1.3037385735625699</v>
+        <v>-4.8834317702327198E-2</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B434">
-        <v>0.77411652013477505</v>
+        <v>-1.0440292418661301</v>
       </c>
       <c r="C434">
-        <v>-0.302679250841356</v>
+        <v>-2.0020151312200198</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B435">
-        <v>-1.19874345853044</v>
+        <v>0.77635444776405604</v>
       </c>
       <c r="C435">
-        <v>-0.56701714570233497</v>
+        <v>-0.137667438207243</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>133</v>
+        <v>613</v>
       </c>
       <c r="B436">
-        <v>0.709533598154242</v>
+        <v>-3.4078710504241598E-2</v>
       </c>
       <c r="C436">
-        <v>-4.8834317702327198E-2</v>
+        <v>0.26075694638131502</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B437">
-        <v>-1.0440292418661301</v>
+        <v>-0.30398471566495699</v>
       </c>
       <c r="C437">
-        <v>-2.0020151312200198</v>
+        <v>6.8452246261796995E-2</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B438">
-        <v>0.77635444776405604</v>
+        <v>-0.41868360143621097</v>
       </c>
       <c r="C438">
-        <v>-0.137667438207243</v>
+        <v>0.13073570660886</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>621</v>
+        <v>289</v>
       </c>
       <c r="B439">
-        <v>-3.4078710504241598E-2</v>
+        <v>-0.97291098592413805</v>
       </c>
       <c r="C439">
-        <v>0.26075694638131502</v>
+        <v>0.23124593679941999</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B440">
-        <v>-0.30398471566495699</v>
+        <v>-1.1202934713945101</v>
       </c>
       <c r="C440">
-        <v>6.8452246261796995E-2</v>
+        <v>-1.5023203384464401</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>135</v>
+        <v>291</v>
       </c>
       <c r="B441">
-        <v>-0.41868360143621097</v>
+        <v>-0.35764964249679698</v>
       </c>
       <c r="C441">
-        <v>0.13073570660886</v>
+        <v>-0.128217085404325</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>289</v>
+        <v>614</v>
       </c>
       <c r="B442">
-        <v>-0.97291098592413805</v>
+        <v>-0.88207605738476702</v>
       </c>
       <c r="C442">
-        <v>0.23124593679941999</v>
+        <v>0.46048524070317298</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>290</v>
+        <v>615</v>
       </c>
       <c r="B443">
-        <v>-1.1202934713945101</v>
+        <v>-0.69649601322015597</v>
       </c>
       <c r="C443">
-        <v>-1.5023203384464401</v>
+        <v>0.73378526269176403</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>291</v>
+        <v>616</v>
       </c>
       <c r="B444">
-        <v>-0.35764964249679698</v>
+        <v>-0.53574139135725796</v>
       </c>
       <c r="C444">
-        <v>-0.128217085404325</v>
+        <v>-3.2698995508802703E-2</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>622</v>
+        <v>292</v>
       </c>
       <c r="B445">
-        <v>-0.88207605738476702</v>
+        <v>-0.89375064877555199</v>
       </c>
       <c r="C445">
-        <v>0.46048524070317298</v>
+        <v>-8.4456085194204597E-2</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>623</v>
+        <v>136</v>
       </c>
       <c r="B446">
-        <v>-0.69649601322015597</v>
+        <v>-0.89786106019972001</v>
       </c>
       <c r="C446">
-        <v>0.73378526269176403</v>
+        <v>-0.11675982153449301</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B447">
-        <v>-0.53574139135725796</v>
+        <v>0.11499830620109699</v>
       </c>
       <c r="C447">
-        <v>-3.2698995508802703E-2</v>
+        <v>1.24852750461325</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>292</v>
+        <v>618</v>
       </c>
       <c r="B448">
-        <v>-0.89375064877555199</v>
+        <v>0.70555846071940698</v>
       </c>
       <c r="C448">
-        <v>-8.4456085194204597E-2</v>
+        <v>-0.447398532797529</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="B449">
-        <v>-0.89786106019972001</v>
+        <v>-0.39253330387992302</v>
       </c>
       <c r="C449">
-        <v>-0.11675982153449301</v>
+        <v>-0.27091426290414899</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>625</v>
+        <v>294</v>
       </c>
       <c r="B450">
-        <v>0.11499830620109699</v>
+        <v>-0.60126391123822098</v>
       </c>
       <c r="C450">
-        <v>1.24852750461325</v>
+        <v>-0.46897285790877202</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="B451">
-        <v>0.70555846071940698</v>
+        <v>-0.476504304218547</v>
       </c>
       <c r="C451">
-        <v>-0.447398532797529</v>
+        <v>0.81332963979969897</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B452">
-        <v>-0.39253330387992302</v>
+        <v>0.50295101934583297</v>
       </c>
       <c r="C452">
-        <v>-0.27091426290414899</v>
+        <v>0.31211974052747998</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B453">
-        <v>-0.60126391123822098</v>
+        <v>-0.41892369517811801</v>
       </c>
       <c r="C453">
-        <v>-0.46897285790877202</v>
+        <v>0.250703885461382</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>627</v>
+        <v>297</v>
       </c>
       <c r="B454">
-        <v>-0.476504304218547</v>
+        <v>-1.5992926120914299</v>
       </c>
       <c r="C454">
-        <v>0.81332963979969897</v>
+        <v>0.15886200318048499</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>295</v>
+        <v>449</v>
       </c>
       <c r="B455">
-        <v>0.50295101934583297</v>
+        <v>0.65584311983973498</v>
       </c>
       <c r="C455">
-        <v>0.31211974052747998</v>
+        <v>-3.10031873461027E-2</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B456">
-        <v>-0.41892369517811801</v>
+        <v>-0.61132692837666802</v>
       </c>
       <c r="C456">
-        <v>0.250703885461382</v>
+        <v>0.209164199653608</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B457">
-        <v>-1.5992926120914299</v>
+        <v>0.251757079833341</v>
       </c>
       <c r="C457">
-        <v>0.15886200318048499</v>
+        <v>0.31147452691960398</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>457</v>
+        <v>300</v>
       </c>
       <c r="B458">
-        <v>0.65584311983973498</v>
+        <v>0.63721489008550203</v>
       </c>
       <c r="C458">
-        <v>-3.10031873461027E-2</v>
+        <v>-0.29374452485847402</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B459">
-        <v>-0.61132692837666802</v>
+        <v>-0.35777283413940703</v>
       </c>
       <c r="C459">
-        <v>0.209164199653608</v>
+        <v>0.14015425259966899</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>299</v>
+        <v>620</v>
       </c>
       <c r="B460">
-        <v>0.251757079833341</v>
+        <v>0.180731422303644</v>
       </c>
       <c r="C460">
-        <v>0.31147452691960398</v>
+        <v>0.166934551367108</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>300</v>
+        <v>621</v>
       </c>
       <c r="B461">
-        <v>0.63721489008550203</v>
+        <v>-1.08177878265289</v>
       </c>
       <c r="C461">
-        <v>-0.29374452485847402</v>
+        <v>-0.24077772079058399</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>301</v>
+        <v>622</v>
       </c>
       <c r="B462">
-        <v>-0.35777283413940703</v>
+        <v>-0.62323585228998801</v>
       </c>
       <c r="C462">
-        <v>0.14015425259966899</v>
+        <v>0.12613919828126699</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>628</v>
+        <v>302</v>
       </c>
       <c r="B463">
-        <v>0.180731422303644</v>
+        <v>-1.10912601448294</v>
       </c>
       <c r="C463">
-        <v>0.166934551367108</v>
+        <v>-0.75987752162933897</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B464">
-        <v>-1.08177878265289</v>
+        <v>0.75293428054338196</v>
       </c>
       <c r="C464">
-        <v>-0.24077772079058399</v>
+        <v>-0.30548154840173602</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>630</v>
+        <v>303</v>
       </c>
       <c r="B465">
-        <v>-0.62323585228998801</v>
+        <v>0.90695911371752502</v>
       </c>
       <c r="C465">
-        <v>0.12613919828126699</v>
+        <v>-2.39753218859101E-2</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="B466">
-        <v>-1.10912601448294</v>
+        <v>-0.633729771183142</v>
       </c>
       <c r="C466">
-        <v>-0.75987752162933897</v>
+        <v>-0.248888671211206</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>631</v>
+        <v>304</v>
       </c>
       <c r="B467">
-        <v>0.75293428054338196</v>
+        <v>0.29065314378337698</v>
       </c>
       <c r="C467">
-        <v>-0.30548154840173602</v>
+        <v>0.36850230010466101</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B468">
-        <v>0.90695911371752502</v>
+        <v>-0.60044735912867797</v>
       </c>
       <c r="C468">
-        <v>-2.39753218859101E-2</v>
+        <v>-0.165118737146671</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="B469">
-        <v>-0.633729771183142</v>
+        <v>-0.71096230389259396</v>
       </c>
       <c r="C469">
-        <v>-0.248888671211206</v>
+        <v>-0.163842545348932</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>304</v>
+        <v>624</v>
       </c>
       <c r="B470">
-        <v>0.29065314378337698</v>
+        <v>0.888228582961202</v>
       </c>
       <c r="C470">
-        <v>0.36850230010466101</v>
+        <v>-0.57960682346370096</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B471">
-        <v>-0.60044735912867797</v>
+        <v>0.82506997983923502</v>
       </c>
       <c r="C471">
-        <v>-0.165118737146671</v>
+        <v>-8.8906651978865898E-3</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="B472">
-        <v>-0.71096230389259396</v>
+        <v>-0.85562910901080302</v>
       </c>
       <c r="C472">
-        <v>-0.163842545348932</v>
+        <v>-0.60113034849570801</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>632</v>
+        <v>139</v>
       </c>
       <c r="B473">
-        <v>0.888228582961202</v>
+        <v>0.20245658312012199</v>
       </c>
       <c r="C473">
-        <v>-0.57960682346370096</v>
+        <v>2.58168464774612E-2</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>307</v>
+        <v>625</v>
       </c>
       <c r="B474">
-        <v>0.82506997983923502</v>
+        <v>-0.65837115468027496</v>
       </c>
       <c r="C474">
-        <v>-8.8906651978865898E-3</v>
+        <v>-1.11429554433448</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B475">
-        <v>-0.85562910901080302</v>
+        <v>-0.15504466897035499</v>
       </c>
       <c r="C475">
-        <v>-0.60113034849570801</v>
+        <v>0.48292553927975301</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>139</v>
+        <v>308</v>
       </c>
       <c r="B476">
-        <v>0.20245658312012199</v>
+        <v>-1.2800885859311499</v>
       </c>
       <c r="C476">
-        <v>2.58168464774612E-2</v>
+        <v>-1.2795907965243301</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="B477">
-        <v>-0.65837115468027496</v>
+        <v>-0.12045127611458099</v>
       </c>
       <c r="C477">
-        <v>-1.11429554433448</v>
+        <v>0.21651887382961801</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="B478">
-        <v>-0.15504466897035499</v>
+        <v>0.95254018247439998</v>
       </c>
       <c r="C478">
-        <v>0.48292553927975301</v>
+        <v>-0.29813738579272703</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>308</v>
+        <v>425</v>
       </c>
       <c r="B479">
-        <v>-1.2800885859311499</v>
+        <v>0.716494619124593</v>
       </c>
       <c r="C479">
-        <v>-1.2795907965243301</v>
+        <v>-0.50913464879592396</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>634</v>
+        <v>310</v>
       </c>
       <c r="B480">
-        <v>-0.12045127611458099</v>
+        <v>-0.437763635310713</v>
       </c>
       <c r="C480">
-        <v>0.21651887382961801</v>
+        <v>0.83209813207832795</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>309</v>
+        <v>627</v>
       </c>
       <c r="B481">
-        <v>0.95254018247439998</v>
+        <v>0.73352774923415898</v>
       </c>
       <c r="C481">
-        <v>-0.29813738579272703</v>
+        <v>-0.32417897043932797</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>426</v>
+        <v>141</v>
       </c>
       <c r="B482">
-        <v>0.716494619124593</v>
+        <v>-1.04449061896365E-2</v>
       </c>
       <c r="C482">
-        <v>-0.50913464879592396</v>
+        <v>0.102879675786531</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B483">
-        <v>-0.437763635310713</v>
+        <v>-0.73397169153234298</v>
       </c>
       <c r="C483">
-        <v>0.83209813207832795</v>
+        <v>-0.55518538889385405</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="B484">
-        <v>0.73352774923415898</v>
+        <v>-0.23097798936506</v>
       </c>
       <c r="C484">
-        <v>-0.32417897043932797</v>
+        <v>0.203159097543781</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>141</v>
+        <v>312</v>
       </c>
       <c r="B485">
-        <v>-1.04449061896365E-2</v>
+        <v>0.59008466277278304</v>
       </c>
       <c r="C485">
-        <v>0.102879675786531</v>
+        <v>0.17816305955714201</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B486">
-        <v>-0.73397169153234298</v>
+        <v>0.48281253060752199</v>
       </c>
       <c r="C486">
-        <v>-0.55518538889385405</v>
+        <v>-0.10897984694799399</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>636</v>
+        <v>314</v>
       </c>
       <c r="B487">
-        <v>-0.23097798936506</v>
+        <v>-1.2974593388358799</v>
       </c>
       <c r="C487">
-        <v>0.203159097543781</v>
+        <v>-1.40356630900069</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B488">
-        <v>0.59008466277278304</v>
+        <v>-0.73277754335977097</v>
       </c>
       <c r="C488">
-        <v>0.17816305955714201</v>
+        <v>-0.13478244927376101</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>313</v>
+        <v>629</v>
       </c>
       <c r="B489">
-        <v>0.48281253060752199</v>
+        <v>0.25508905424240202</v>
       </c>
       <c r="C489">
-        <v>-0.10897984694799399</v>
+        <v>0.39507222684632898</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>314</v>
+        <v>630</v>
       </c>
       <c r="B490">
-        <v>-1.2974593388358799</v>
+        <v>5.4677285342947197E-2</v>
       </c>
       <c r="C490">
-        <v>-1.40356630900069</v>
+        <v>0.45269595618399899</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>315</v>
+        <v>450</v>
       </c>
       <c r="B491">
-        <v>-0.73277754335977097</v>
+        <v>-1.1698164769794399</v>
       </c>
       <c r="C491">
-        <v>-0.13478244927376101</v>
+        <v>-1.68355299059775</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B492">
-        <v>0.25508905424240202</v>
+        <v>4.1531310062497703E-2</v>
       </c>
       <c r="C492">
-        <v>0.39507222684632898</v>
+        <v>-0.17065776406233099</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>638</v>
+        <v>451</v>
       </c>
       <c r="B493">
-        <v>5.4677285342947197E-2</v>
+        <v>0.58710144109540796</v>
       </c>
       <c r="C493">
-        <v>0.45269595618399899</v>
+        <v>-6.9184665518606206E-2</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>458</v>
+        <v>316</v>
       </c>
       <c r="B494">
-        <v>-1.1698164769794399</v>
+        <v>-0.37917021838248599</v>
       </c>
       <c r="C494">
-        <v>-1.68355299059775</v>
+        <v>-0.385518873891387</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B495">
-        <v>4.1531310062497703E-2</v>
+        <v>-7.1837502579441395E-2</v>
       </c>
       <c r="C495">
-        <v>-0.17065776406233099</v>
+        <v>0.49117778386820599</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>459</v>
+        <v>142</v>
       </c>
       <c r="B496">
-        <v>0.58710144109540796</v>
+        <v>0.14757696610137799</v>
       </c>
       <c r="C496">
-        <v>-6.9184665518606206E-2</v>
+        <v>0.29697396825886702</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>316</v>
+        <v>633</v>
       </c>
       <c r="B497">
-        <v>-0.37917021838248599</v>
+        <v>-0.47327535467884402</v>
       </c>
       <c r="C497">
-        <v>-0.385518873891387</v>
+        <v>-4.73664960447258E-2</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>640</v>
+        <v>143</v>
       </c>
       <c r="B498">
-        <v>-7.1837502579441395E-2</v>
+        <v>-0.28988161117937</v>
       </c>
       <c r="C498">
-        <v>0.49117778386820599</v>
+        <v>4.7472142655991201E-2</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B499">
-        <v>0.14757696610137799</v>
+        <v>-0.80840193164144702</v>
       </c>
       <c r="C499">
-        <v>0.29697396825886702</v>
+        <v>0.127294654586498</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>641</v>
+        <v>145</v>
       </c>
       <c r="B500">
-        <v>-0.47327535467884402</v>
+        <v>-0.66047038422998505</v>
       </c>
       <c r="C500">
-        <v>-4.73664960447258E-2</v>
+        <v>-0.45410640924149698</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B501">
-        <v>-0.28988161117937</v>
+        <v>-1.30992283867105</v>
       </c>
       <c r="C501">
-        <v>4.7472142655991201E-2</v>
+        <v>-0.93978505824297898</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>144</v>
+        <v>317</v>
       </c>
       <c r="B502">
-        <v>-0.80840193164144702</v>
+        <v>-0.30736678771503001</v>
       </c>
       <c r="C502">
-        <v>0.127294654586498</v>
+        <v>-0.218030710065299</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B503">
-        <v>-0.66047038422998505</v>
+        <v>-5.4402064692069103E-2</v>
       </c>
       <c r="C503">
-        <v>-0.45410640924149698</v>
+        <v>-0.62112408225384996</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>146</v>
+        <v>318</v>
       </c>
       <c r="B504">
-        <v>-1.30992283867105</v>
+        <v>-1.11077442592539</v>
       </c>
       <c r="C504">
-        <v>-0.93978505824297898</v>
+        <v>-1.4838638812442799</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>317</v>
+        <v>634</v>
       </c>
       <c r="B505">
-        <v>-0.30736678771503001</v>
+        <v>5.2959591955320899E-2</v>
       </c>
       <c r="C505">
-        <v>-0.218030710065299</v>
+        <v>0.560811856732083</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>147</v>
+        <v>635</v>
       </c>
       <c r="B506">
-        <v>-5.4402064692069103E-2</v>
+        <v>-0.51554988085686404</v>
       </c>
       <c r="C506">
-        <v>-0.62112408225384996</v>
+        <v>0.19904126463479699</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>318</v>
+        <v>148</v>
       </c>
       <c r="B507">
-        <v>-1.11077442592539</v>
+        <v>-0.38914718609023502</v>
       </c>
       <c r="C507">
-        <v>-1.4838638812442799</v>
+        <v>0.41318332878642</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>642</v>
+        <v>319</v>
       </c>
       <c r="B508">
-        <v>5.2959591955320899E-2</v>
+        <v>0.41189155715155101</v>
       </c>
       <c r="C508">
-        <v>0.560811856732083</v>
+        <v>0.12697128818973699</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B509">
-        <v>-0.51554988085686404</v>
+        <v>-0.56453694151371203</v>
       </c>
       <c r="C509">
-        <v>0.19904126463479699</v>
+        <v>5.3900014640647601E-2</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>148</v>
+        <v>637</v>
       </c>
       <c r="B510">
-        <v>-0.38914718609023502</v>
+        <v>-1.8662618045069201E-2</v>
       </c>
       <c r="C510">
-        <v>0.41318332878642</v>
+        <v>0.46753628142445502</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>319</v>
+        <v>149</v>
       </c>
       <c r="B511">
-        <v>0.41189155715155101</v>
+        <v>0.71469863309380999</v>
       </c>
       <c r="C511">
-        <v>0.12697128818973699</v>
+        <v>-0.24954668953522099</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>427</v>
-      </c>
-      <c r="B512" t="s">
-        <v>441</v>
-      </c>
-      <c r="C512" t="s">
-        <v>441</v>
+        <v>426</v>
+      </c>
+      <c r="B512">
+        <v>-0.34925303988599399</v>
+      </c>
+      <c r="C512">
+        <v>0.39724394857850798</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>644</v>
+        <v>150</v>
       </c>
       <c r="B513">
-        <v>-0.56453694151371203</v>
+        <v>0.51308531407128199</v>
       </c>
       <c r="C513">
-        <v>5.3900014640647601E-2</v>
+        <v>0.29690713398607399</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>645</v>
+        <v>320</v>
       </c>
       <c r="B514">
-        <v>-1.8662618045069201E-2</v>
+        <v>0.51448621964070296</v>
       </c>
       <c r="C514">
-        <v>0.46753628142445502</v>
+        <v>1.28663566293319E-2</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>149</v>
+        <v>321</v>
       </c>
       <c r="B515">
-        <v>0.71469863309380999</v>
+        <v>-0.438698784827312</v>
       </c>
       <c r="C515">
-        <v>-0.24954668953522099</v>
+        <v>0.37420057388134498</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>428</v>
+        <v>638</v>
       </c>
       <c r="B516">
-        <v>-0.34925303988599399</v>
+        <v>-0.77053646640738405</v>
       </c>
       <c r="C516">
-        <v>0.39724394857850798</v>
+        <v>-3.5953332948192002E-2</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B517">
-        <v>0.51308531407128199</v>
+        <v>0.64625059670559104</v>
       </c>
       <c r="C517">
-        <v>0.29690713398607399</v>
+        <v>-0.23580568535229601</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B518">
-        <v>0.51448621964070296</v>
+        <v>-1.51869955647629</v>
       </c>
       <c r="C518">
-        <v>1.28663566293319E-2</v>
+        <v>-1.24620455062628</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>321</v>
+        <v>639</v>
       </c>
       <c r="B519">
-        <v>-0.438698784827312</v>
+        <v>-1.08177878265289</v>
       </c>
       <c r="C519">
-        <v>0.37420057388134498</v>
+        <v>-0.24077772079058399</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B520">
-        <v>-0.77053646640738405</v>
+        <v>-0.27545530398978402</v>
       </c>
       <c r="C520">
-        <v>-3.5953332948192002E-2</v>
+        <v>8.5979551147453898E-2</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>151</v>
+        <v>323</v>
       </c>
       <c r="B521">
-        <v>0.64625059670559104</v>
+        <v>-0.77135523957130203</v>
       </c>
       <c r="C521">
-        <v>-0.23580568535229601</v>
+        <v>-0.307832220654711</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>322</v>
+        <v>641</v>
       </c>
       <c r="B522">
-        <v>-1.51869955647629</v>
+        <v>0.938433090538216</v>
       </c>
       <c r="C522">
-        <v>-1.24620455062628</v>
+        <v>0.56345232508797505</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>647</v>
+        <v>152</v>
       </c>
       <c r="B523">
-        <v>-1.08177878265289</v>
+        <v>-0.98270757198505498</v>
       </c>
       <c r="C523">
-        <v>-0.24077772079058399</v>
+        <v>-1.6814535351052899</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B524">
-        <v>-0.27545530398978402</v>
+        <v>-1.8651451187805701</v>
       </c>
       <c r="C524">
-        <v>8.5979551147453898E-2</v>
+        <v>0.188330823892217</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>323</v>
+        <v>153</v>
       </c>
       <c r="B525">
-        <v>-0.77135523957130203</v>
+        <v>-1.3112857358355301</v>
       </c>
       <c r="C525">
-        <v>-0.307832220654711</v>
+        <v>-0.81086067248626803</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>649</v>
+        <v>324</v>
       </c>
       <c r="B526">
-        <v>0.938433090538216</v>
+        <v>-0.534323223461042</v>
       </c>
       <c r="C526">
-        <v>0.56345232508797505</v>
+        <v>-0.34143317835180798</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>152</v>
+        <v>325</v>
       </c>
       <c r="B527">
-        <v>-0.98270757198505498</v>
+        <v>0.25492140895753801</v>
       </c>
       <c r="C527">
-        <v>-1.6814535351052899</v>
+        <v>-0.23302550426271201</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>650</v>
+        <v>326</v>
       </c>
       <c r="B528">
-        <v>-1.8651451187805701</v>
+        <v>-0.136456240262326</v>
       </c>
       <c r="C528">
-        <v>0.188330823892217</v>
+        <v>0.501125798420056</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="B529">
-        <v>-1.3112857358355301</v>
+        <v>0.82349370023277302</v>
       </c>
       <c r="C529">
-        <v>-0.81086067248626803</v>
+        <v>-0.39859468211041899</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>324</v>
+        <v>154</v>
       </c>
       <c r="B530">
-        <v>-0.534323223461042</v>
+        <v>2.6972406864160501E-2</v>
       </c>
       <c r="C530">
-        <v>-0.34143317835180798</v>
+        <v>4.6987391426459003E-2</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>325</v>
+        <v>643</v>
       </c>
       <c r="B531">
-        <v>0.25492140895753801</v>
+        <v>0.80519795368720004</v>
       </c>
       <c r="C531">
-        <v>-0.23302550426271201</v>
+        <v>9.8299246474196203E-2</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>326</v>
+        <v>155</v>
       </c>
       <c r="B532">
-        <v>-0.136456240262326</v>
+        <v>-0.25592153790046002</v>
       </c>
       <c r="C532">
-        <v>0.501125798420056</v>
+        <v>0.40332856411907603</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
       <c r="B533">
-        <v>0.82349370023277302</v>
+        <v>-1.3011773236739099</v>
       </c>
       <c r="C533">
-        <v>-0.39859468211041899</v>
+        <v>-0.38485620744812399</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="B534">
-        <v>2.6972406864160501E-2</v>
+        <v>-0.52915586653698998</v>
       </c>
       <c r="C534">
-        <v>4.6987391426459003E-2</v>
+        <v>-0.28185697251212199</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>651</v>
+        <v>329</v>
       </c>
       <c r="B535">
-        <v>0.80519795368720004</v>
+        <v>0.27945819746218598</v>
       </c>
       <c r="C535">
-        <v>9.8299246474196203E-2</v>
+        <v>0.101795203139029</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>155</v>
+        <v>427</v>
       </c>
       <c r="B536">
-        <v>-0.25592153790046002</v>
+        <v>-0.62960093137346096</v>
       </c>
       <c r="C536">
-        <v>0.40332856411907603</v>
+        <v>2.4140521842876898E-2</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B537">
-        <v>-1.3011773236739099</v>
+        <v>-0.55488592885907595</v>
       </c>
       <c r="C537">
-        <v>-0.38485620744812399</v>
+        <v>6.2491043023582098E-2</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B538">
-        <v>-0.52915586653698998</v>
+        <v>-0.130267163881192</v>
       </c>
       <c r="C538">
-        <v>-0.28185697251212199</v>
+        <v>-1.1301672686245099E-2</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>329</v>
+        <v>646</v>
       </c>
       <c r="B539">
-        <v>0.27945819746218598</v>
+        <v>-0.97937766411386495</v>
       </c>
       <c r="C539">
-        <v>0.101795203139029</v>
+        <v>-0.14242009930761201</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>429</v>
+        <v>331</v>
       </c>
       <c r="B540">
-        <v>-0.62960093137346096</v>
+        <v>-0.60287588749340304</v>
       </c>
       <c r="C540">
-        <v>2.4140521842876898E-2</v>
+        <v>1.14116939030555</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>653</v>
+        <v>428</v>
       </c>
       <c r="B541">
-        <v>-0.55488592885907595</v>
+        <v>-0.93512970814919105</v>
       </c>
       <c r="C541">
-        <v>6.2491043023582098E-2</v>
+        <v>-0.57553176079857504</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>330</v>
+        <v>156</v>
       </c>
       <c r="B542">
-        <v>-0.130267163881192</v>
+        <v>-0.13034169633518999</v>
       </c>
       <c r="C542">
-        <v>-1.1301672686245099E-2</v>
+        <v>0.381460919943511</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B543">
-        <v>-0.97937766411386495</v>
+        <v>-0.392690243073398</v>
       </c>
       <c r="C543">
-        <v>-0.14242009930761201</v>
+        <v>-3.0805617377827901E-2</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B544">
-        <v>-0.60287588749340304</v>
+        <v>-1.3255191413145699</v>
       </c>
       <c r="C544">
-        <v>1.14116939030555</v>
+        <v>0.11663045847159501</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>430</v>
+        <v>648</v>
       </c>
       <c r="B545">
-        <v>-0.93512970814919105</v>
+        <v>-1.4969235176148701</v>
       </c>
       <c r="C545">
-        <v>-0.57553176079857504</v>
+        <v>-0.405185830859491</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>156</v>
+        <v>649</v>
       </c>
       <c r="B546">
-        <v>-0.13034169633518999</v>
+        <v>-0.61372805537506503</v>
       </c>
       <c r="C546">
-        <v>0.381460919943511</v>
+        <v>0.240729382820355</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>655</v>
+        <v>157</v>
       </c>
       <c r="B547">
-        <v>-0.392690243073398</v>
+        <v>-1.38560842765425</v>
       </c>
       <c r="C547">
-        <v>-3.0805617377827901E-2</v>
+        <v>-0.99974404451582299</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>332</v>
+        <v>158</v>
       </c>
       <c r="B548">
-        <v>-1.3255191413145699</v>
+        <v>8.93742769035379E-2</v>
       </c>
       <c r="C548">
-        <v>0.11663045847159501</v>
+        <v>-3.4646812110204301E-3</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>656</v>
+        <v>333</v>
       </c>
       <c r="B549">
-        <v>-1.4969235176148701</v>
+        <v>-1.4880632426384699</v>
       </c>
       <c r="C549">
-        <v>-0.405185830859491</v>
+        <v>-0.89878037703485203</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>657</v>
+        <v>159</v>
       </c>
       <c r="B550">
-        <v>-0.61372805537506503</v>
+        <v>0.399709349475662</v>
       </c>
       <c r="C550">
-        <v>0.240729382820355</v>
+        <v>8.0297421667986701E-2</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>157</v>
+        <v>650</v>
       </c>
       <c r="B551">
-        <v>-1.38560842765425</v>
+        <v>-0.71702531431152905</v>
       </c>
       <c r="C551">
-        <v>-0.99974404451582299</v>
+        <v>1.93664404058729E-2</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B552">
-        <v>8.93742769035379E-2</v>
+        <v>0.69311064328790895</v>
       </c>
       <c r="C552">
-        <v>-3.4646812110204301E-3</v>
+        <v>-0.27334165191193899</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>333</v>
+        <v>161</v>
       </c>
       <c r="B553">
-        <v>-1.4880632426384699</v>
+        <v>-0.38818951612692199</v>
       </c>
       <c r="C553">
-        <v>-0.89878037703485203</v>
+        <v>-2.99368100286816E-2</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B554">
-        <v>0.399709349475662</v>
+        <v>-0.36560662501968799</v>
       </c>
       <c r="C554">
-        <v>8.0297421667986701E-2</v>
+        <v>0.32555559585595001</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>658</v>
+        <v>334</v>
       </c>
       <c r="B555">
-        <v>-0.71702531431152905</v>
+        <v>-0.36175320701125002</v>
       </c>
       <c r="C555">
-        <v>1.93664404058729E-2</v>
+        <v>-0.11591541530405999</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>420</v>
-      </c>
-      <c r="B556" t="s">
-        <v>441</v>
-      </c>
-      <c r="C556" t="s">
-        <v>441</v>
+        <v>651</v>
+      </c>
+      <c r="B556">
+        <v>-0.66245382792426699</v>
+      </c>
+      <c r="C556">
+        <v>-2.2471380051139702</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>160</v>
+        <v>652</v>
       </c>
       <c r="B557">
-        <v>0.69311064328790895</v>
+        <v>-0.50817506001853197</v>
       </c>
       <c r="C557">
-        <v>-0.27334165191193899</v>
+        <v>0.27919610364335701</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B558">
-        <v>-0.38818951612692199</v>
+        <v>0.68964081579431102</v>
       </c>
       <c r="C558">
-        <v>-2.99368100286816E-2</v>
+        <v>-0.25650349046846499</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>162</v>
+        <v>335</v>
       </c>
       <c r="B559">
-        <v>-0.36560662501968799</v>
+        <v>0.79654996281225199</v>
       </c>
       <c r="C559">
-        <v>0.32555559585595001</v>
+        <v>-0.31757060227275802</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>334</v>
+        <v>164</v>
       </c>
       <c r="B560">
-        <v>-0.36175320701125002</v>
+        <v>0.64759015023403699</v>
       </c>
       <c r="C560">
-        <v>-0.11591541530405999</v>
+        <v>-0.23401595761840999</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>659</v>
+        <v>165</v>
       </c>
       <c r="B561">
-        <v>-0.66245382792426699</v>
+        <v>-0.141342192170655</v>
       </c>
       <c r="C561">
-        <v>-2.2471380051139702</v>
+        <v>0.40787722740025101</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>660</v>
+        <v>336</v>
       </c>
       <c r="B562">
-        <v>-0.50817506001853197</v>
+        <v>-0.29021571014533998</v>
       </c>
       <c r="C562">
-        <v>0.27919610364335701</v>
+        <v>0.58621736157813298</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>163</v>
+        <v>337</v>
       </c>
       <c r="B563">
-        <v>0.68964081579431102</v>
+        <v>-1.0776078965448499</v>
       </c>
       <c r="C563">
-        <v>-0.25650349046846499</v>
+        <v>-0.33656969180290602</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>335</v>
+        <v>166</v>
       </c>
       <c r="B564">
-        <v>0.79654996281225199</v>
+        <v>0.48349461977318597</v>
       </c>
       <c r="C564">
-        <v>-0.31757060227275802</v>
+        <v>-0.167476236076015</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="B565">
-        <v>0.64759015023403699</v>
+        <v>-1.14378690123685</v>
       </c>
       <c r="C565">
-        <v>-0.23401595761840999</v>
+        <v>-1.76119125131981</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>165</v>
+        <v>653</v>
       </c>
       <c r="B566">
-        <v>-0.141342192170655</v>
+        <v>-0.28195266360400101</v>
       </c>
       <c r="C566">
-        <v>0.40787722740025101</v>
+        <v>0.57536635924721202</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>336</v>
+        <v>167</v>
       </c>
       <c r="B567">
-        <v>-0.29021571014533998</v>
+        <v>0.11055243588402</v>
       </c>
       <c r="C567">
-        <v>0.58621736157813298</v>
+        <v>0.20297342187543699</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B568">
-        <v>-1.0776078965448499</v>
+        <v>-0.69573371257156802</v>
       </c>
       <c r="C568">
-        <v>-0.33656969180290602</v>
+        <v>1.6464969008021101E-2</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B569">
-        <v>0.48349461977318597</v>
+        <v>0.77434417668952904</v>
       </c>
       <c r="C569">
-        <v>-0.167476236076015</v>
+        <v>-0.28994477455894502</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>338</v>
+        <v>654</v>
       </c>
       <c r="B570">
-        <v>-1.14378690123685</v>
+        <v>0.78343827877343497</v>
       </c>
       <c r="C570">
-        <v>-1.76119125131981</v>
+        <v>4.1019864169007603E-2</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>661</v>
+        <v>169</v>
       </c>
       <c r="B571">
-        <v>-0.28195266360400101</v>
+        <v>-0.54260005357839403</v>
       </c>
       <c r="C571">
-        <v>0.57536635924721202</v>
+        <v>9.29407267681614E-3</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B572">
-        <v>0.11055243588402</v>
+        <v>-0.49478872242477601</v>
       </c>
       <c r="C572">
-        <v>0.20297342187543699</v>
+        <v>4.7988806952235799E-2</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>339</v>
+        <v>171</v>
       </c>
       <c r="B573">
-        <v>-0.69573371257156802</v>
+        <v>-0.27129133457397497</v>
       </c>
       <c r="C573">
-        <v>1.6464969008021101E-2</v>
+        <v>0.18519407228524101</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B574">
-        <v>0.77434417668952904</v>
+        <v>-0.50061883492667303</v>
       </c>
       <c r="C574">
-        <v>-0.28994477455894502</v>
+        <v>0.10499193537727899</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="B575">
-        <v>0.78343827877343497</v>
+        <v>-0.53178580162660505</v>
       </c>
       <c r="C575">
-        <v>4.1019864169007603E-2</v>
+        <v>0.189956031227347</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B576">
-        <v>-0.54260005357839403</v>
+        <v>-0.74602636750140805</v>
       </c>
       <c r="C576">
-        <v>9.29407267681614E-3</v>
+        <v>5.3790995924028202E-2</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>170</v>
+        <v>656</v>
       </c>
       <c r="B577">
-        <v>-0.49478872242477601</v>
+        <v>-1.05131402036505</v>
       </c>
       <c r="C577">
-        <v>4.7988806952235799E-2</v>
+        <v>-2.6678259554166299E-2</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>171</v>
+        <v>452</v>
       </c>
       <c r="B578">
-        <v>-0.27129133457397497</v>
+        <v>0.98374920090672202</v>
       </c>
       <c r="C578">
-        <v>0.18519407228524101</v>
+        <v>-0.191722543914011</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>172</v>
+        <v>340</v>
       </c>
       <c r="B579">
-        <v>-0.50061883492667303</v>
+        <v>9.9895810093406895E-2</v>
       </c>
       <c r="C579">
-        <v>0.10499193537727899</v>
+        <v>0.45802230177338199</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>663</v>
+        <v>341</v>
       </c>
       <c r="B580">
-        <v>-0.53178580162660505</v>
+        <v>-0.630058011195751</v>
       </c>
       <c r="C580">
-        <v>0.189956031227347</v>
+        <v>0.18449832446021999</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>173</v>
+        <v>453</v>
       </c>
       <c r="B581">
-        <v>-0.74602636750140805</v>
+        <v>-1.01636368812283</v>
       </c>
       <c r="C581">
-        <v>5.3790995924028202E-2</v>
+        <v>-0.66268903678208202</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>664</v>
+        <v>342</v>
       </c>
       <c r="B582">
-        <v>-1.05131402036505</v>
+        <v>-1.29326033544227</v>
       </c>
       <c r="C582">
-        <v>-2.6678259554166299E-2</v>
+        <v>-1.7523857110718499</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>460</v>
+        <v>343</v>
       </c>
       <c r="B583">
-        <v>0.98374920090672202</v>
+        <v>0.82611677632355396</v>
       </c>
       <c r="C583">
-        <v>-0.191722543914011</v>
+        <v>-0.42257291815588699</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B584">
-        <v>9.9895810093406895E-2</v>
+        <v>-0.16152115694921301</v>
       </c>
       <c r="C584">
-        <v>0.45802230177338199</v>
+        <v>-5.8964594191385097E-2</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>341</v>
+        <v>174</v>
       </c>
       <c r="B585">
-        <v>-0.630058011195751</v>
+        <v>-0.13904766024607501</v>
       </c>
       <c r="C585">
-        <v>0.18449832446021999</v>
+        <v>0.43210044538093101</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="B586">
-        <v>-1.01636368812283</v>
+        <v>7.1062389371823506E-2</v>
       </c>
       <c r="C586">
-        <v>-0.66268903678208202</v>
+        <v>-5.4240827596319499E-2</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>342</v>
+        <v>429</v>
       </c>
       <c r="B587">
-        <v>-1.29326033544227</v>
+        <v>-8.7612986351523398E-2</v>
       </c>
       <c r="C587">
-        <v>-1.7523857110718499</v>
+        <v>0.69323330575002795</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B588">
-        <v>0.82611677632355396</v>
+        <v>-1.3268199133715199</v>
       </c>
       <c r="C588">
-        <v>-0.42257291815588699</v>
+        <v>-1.70869523621873</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B589">
-        <v>-0.16152115694921301</v>
+        <v>0.75390777053953295</v>
       </c>
       <c r="C589">
-        <v>-5.8964594191385097E-2</v>
+        <v>-0.36581120803658301</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>174</v>
+        <v>347</v>
       </c>
       <c r="B590">
-        <v>-0.13904766024607501</v>
+        <v>0.76764455965168199</v>
       </c>
       <c r="C590">
-        <v>0.43210044538093101</v>
+        <v>-0.30251934165475097</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B591">
-        <v>7.1062389371823506E-2</v>
+        <v>-1.23835942874686</v>
       </c>
       <c r="C591">
-        <v>-5.4240827596319499E-2</v>
+        <v>-0.45275534752919699</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>431</v>
+        <v>175</v>
       </c>
       <c r="B592">
-        <v>-8.7612986351523398E-2</v>
+        <v>0.50780681565914998</v>
       </c>
       <c r="C592">
-        <v>0.69323330575002795</v>
+        <v>0.120866469241072</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>345</v>
+        <v>659</v>
       </c>
       <c r="B593">
-        <v>-1.3268199133715199</v>
+        <v>-0.226444363866774</v>
       </c>
       <c r="C593">
-        <v>-1.70869523621873</v>
+        <v>-1.3880016416452501</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B594">
-        <v>0.75390777053953295</v>
+        <v>-0.91243595905352104</v>
       </c>
       <c r="C594">
-        <v>-0.36581120803658301</v>
+        <v>-0.109563583149621</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>347</v>
+        <v>660</v>
       </c>
       <c r="B595">
-        <v>0.76764455965168199</v>
+        <v>-0.41892671988956198</v>
       </c>
       <c r="C595">
-        <v>-0.30251934165475097</v>
+        <v>0.70686488887717103</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>666</v>
+        <v>349</v>
       </c>
       <c r="B596">
-        <v>-1.23835942874686</v>
+        <v>-1.32441203796407</v>
       </c>
       <c r="C596">
-        <v>-0.45275534752919699</v>
+        <v>-0.90079500577348903</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B597">
-        <v>0.50780681565914998</v>
+        <v>-1.2263510357724501</v>
       </c>
       <c r="C597">
-        <v>0.120866469241072</v>
+        <v>-0.69490343644838304</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>667</v>
+        <v>350</v>
       </c>
       <c r="B598">
-        <v>-0.226444363866774</v>
+        <v>-0.51362702149450601</v>
       </c>
       <c r="C598">
-        <v>-1.3880016416452501</v>
+        <v>-1.9166812655167301E-2</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B599">
-        <v>-0.91243595905352104</v>
+        <v>0.36264401505287203</v>
       </c>
       <c r="C599">
-        <v>-0.109563583149621</v>
+        <v>0.32707963874225898</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>668</v>
+        <v>177</v>
       </c>
       <c r="B600">
-        <v>-0.41892671988956198</v>
+        <v>0.78430658349835503</v>
       </c>
       <c r="C600">
-        <v>0.70686488887717103</v>
+        <v>-0.25433663860750799</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B601">
-        <v>-1.32441203796407</v>
+        <v>0.782768083830503</v>
       </c>
       <c r="C601">
-        <v>-0.90079500577348903</v>
+        <v>-0.35704067733388001</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B602">
-        <v>-1.2263510357724501</v>
+        <v>0.30401971836149899</v>
       </c>
       <c r="C602">
-        <v>-0.69490343644838304</v>
+        <v>-4.9071816638664799E-2</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>350</v>
+        <v>661</v>
       </c>
       <c r="B603">
-        <v>-0.51362702149450601</v>
+        <v>0.79650217539319301</v>
       </c>
       <c r="C603">
-        <v>-1.9166812655167301E-2</v>
+        <v>-0.288802745620097</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B604">
-        <v>0.36264401505287203</v>
+        <v>0.36039883087959501</v>
       </c>
       <c r="C604">
-        <v>0.32707963874225898</v>
+        <v>0.208084097424279</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>432</v>
-      </c>
-      <c r="B605" t="s">
-        <v>441</v>
-      </c>
-      <c r="C605" t="s">
-        <v>441</v>
+        <v>662</v>
+      </c>
+      <c r="B605">
+        <v>-2.4450471736232202E-2</v>
+      </c>
+      <c r="C605">
+        <v>0.45907151709795901</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>177</v>
+        <v>663</v>
       </c>
       <c r="B606">
-        <v>0.78430658349835503</v>
+        <v>-1.0375810870612101</v>
       </c>
       <c r="C606">
-        <v>-0.25433663860750799</v>
+        <v>-0.69582934008836805</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B607">
-        <v>0.782768083830503</v>
+        <v>-0.83017145970296402</v>
       </c>
       <c r="C607">
-        <v>-0.35704067733388001</v>
+        <v>0.19290041037538999</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B608">
-        <v>0.30401971836149899</v>
+        <v>0.119899740343113</v>
       </c>
       <c r="C608">
-        <v>-4.9071816638664799E-2</v>
+        <v>-7.6853846331367201E-2</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B609">
-        <v>0.79650217539319301</v>
+        <v>0.79008242488976799</v>
       </c>
       <c r="C609">
-        <v>-0.288802745620097</v>
+        <v>-0.44017038978052297</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>353</v>
+        <v>180</v>
       </c>
       <c r="B610">
-        <v>0.36039883087959501</v>
+        <v>0.48674432656786798</v>
       </c>
       <c r="C610">
-        <v>0.208084097424279</v>
+        <v>-4.0094528530782998E-2</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>670</v>
+        <v>355</v>
       </c>
       <c r="B611">
-        <v>-2.4450471736232202E-2</v>
+        <v>0.69136796588023297</v>
       </c>
       <c r="C611">
-        <v>0.45907151709795901</v>
+        <v>-0.38623141448250697</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>671</v>
+        <v>181</v>
       </c>
       <c r="B612">
-        <v>-1.0375810870612101</v>
+        <v>-0.68470806121411099</v>
       </c>
       <c r="C612">
-        <v>-0.69582934008836805</v>
+        <v>-8.8221701159287694E-2</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>354</v>
+        <v>430</v>
       </c>
       <c r="B613">
-        <v>-0.83017145970296402</v>
+        <v>-0.67942854489914595</v>
       </c>
       <c r="C613">
-        <v>0.19290041037538999</v>
+        <v>-0.75423188779120698</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>179</v>
+        <v>356</v>
       </c>
       <c r="B614">
-        <v>0.119899740343113</v>
+        <v>-0.53234969452953895</v>
       </c>
       <c r="C614">
-        <v>-7.6853846331367201E-2</v>
+        <v>-5.2842867061767003E-2</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>672</v>
+        <v>357</v>
       </c>
       <c r="B615">
-        <v>0.79008242488976799</v>
+        <v>7.2379883990211294E-2</v>
       </c>
       <c r="C615">
-        <v>-0.44017038978052297</v>
+        <v>-0.54770524034254697</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>180</v>
+        <v>358</v>
       </c>
       <c r="B616">
-        <v>0.48674432656786798</v>
+        <v>0.67596877240321196</v>
       </c>
       <c r="C616">
-        <v>-4.0094528530782998E-2</v>
+        <v>-0.392846495607794</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>355</v>
+        <v>182</v>
       </c>
       <c r="B617">
-        <v>0.69136796588023297</v>
+        <v>0.71105317712858795</v>
       </c>
       <c r="C617">
-        <v>-0.38623141448250697</v>
+        <v>-0.43206324152362002</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B618">
-        <v>-0.68470806121411099</v>
+        <v>-0.89240160450934802</v>
       </c>
       <c r="C618">
-        <v>-8.8221701159287694E-2</v>
+        <v>-0.26449895614555302</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>433</v>
+        <v>359</v>
       </c>
       <c r="B619">
-        <v>-0.67942854489914595</v>
+        <v>-0.53445101006543305</v>
       </c>
       <c r="C619">
-        <v>-0.75423188779120698</v>
+        <v>-5.1703059089352299E-2</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B620">
-        <v>-0.53234969452953895</v>
+        <v>-1.29326033544227</v>
       </c>
       <c r="C620">
-        <v>-5.2842867061767003E-2</v>
+        <v>-1.7523857110718499</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B621">
-        <v>7.2379883990211294E-2</v>
+        <v>-1.0440292418661301</v>
       </c>
       <c r="C621">
-        <v>-0.54770524034254697</v>
+        <v>-2.0020151312200198</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>358</v>
+        <v>665</v>
       </c>
       <c r="B622">
-        <v>0.67596877240321196</v>
+        <v>-0.61760126580920505</v>
       </c>
       <c r="C622">
-        <v>-0.392846495607794</v>
+        <v>8.9664101125246004E-2</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B623">
-        <v>0.71105317712858795</v>
+        <v>0.20931931511528801</v>
       </c>
       <c r="C623">
-        <v>-0.43206324152362002</v>
+        <v>0.14856889975170301</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B624">
-        <v>-0.89240160450934802</v>
+        <v>-0.15923020409275199</v>
       </c>
       <c r="C624">
-        <v>-0.26449895614555302</v>
+        <v>0.40459821432790499</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>359</v>
+        <v>666</v>
       </c>
       <c r="B625">
-        <v>-0.53445101006543305</v>
+        <v>-1.7196038350763501</v>
       </c>
       <c r="C625">
-        <v>-5.1703059089352299E-2</v>
+        <v>-0.24989724849984701</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>360</v>
+        <v>667</v>
       </c>
       <c r="B626">
-        <v>-1.29326033544227</v>
+        <v>-0.64787954468967202</v>
       </c>
       <c r="C626">
-        <v>-1.7523857110718499</v>
+        <v>0.61081637053840798</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B627">
-        <v>-1.0440292418661301</v>
+        <v>-0.129951103079991</v>
       </c>
       <c r="C627">
-        <v>-2.0020151312200198</v>
+        <v>0.45499556962637699</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>673</v>
+        <v>186</v>
       </c>
       <c r="B628">
-        <v>-0.61760126580920505</v>
+        <v>-0.33161564895021001</v>
       </c>
       <c r="C628">
-        <v>8.9664101125246004E-2</v>
+        <v>-0.48280694929409002</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B629">
-        <v>0.20931931511528801</v>
+        <v>0.75332199524421295</v>
       </c>
       <c r="C629">
-        <v>0.14856889975170301</v>
+        <v>-0.18429459005042401</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>185</v>
+        <v>668</v>
       </c>
       <c r="B630">
-        <v>-0.15923020409275199</v>
+        <v>0.17138370773851699</v>
       </c>
       <c r="C630">
-        <v>0.40459821432790499</v>
+        <v>0.602044085523471</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B631">
-        <v>-1.7196038350763501</v>
+        <v>0.938433090538216</v>
       </c>
       <c r="C631">
-        <v>-0.24989724849984701</v>
+        <v>0.56345232508797505</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>675</v>
+        <v>363</v>
       </c>
       <c r="B632">
-        <v>-0.64787954468967202</v>
+        <v>0.20404619494471099</v>
       </c>
       <c r="C632">
-        <v>0.61081637053840798</v>
+        <v>-5.0595541527897497E-2</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>362</v>
+        <v>188</v>
       </c>
       <c r="B633">
-        <v>-0.129951103079991</v>
+        <v>-0.79351826396693304</v>
       </c>
       <c r="C633">
-        <v>0.45499556962637699</v>
+        <v>-0.101259355816879</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B634">
-        <v>-0.33161564895021001</v>
+        <v>-0.38788729211695999</v>
       </c>
       <c r="C634">
-        <v>-0.48280694929409002</v>
+        <v>9.8036259748807197E-2</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>187</v>
+        <v>670</v>
       </c>
       <c r="B635">
-        <v>0.75332199524421295</v>
+        <v>0.81982931019686101</v>
       </c>
       <c r="C635">
-        <v>-0.18429459005042401</v>
+        <v>-0.324640877743062</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B636">
-        <v>0.17138370773851699</v>
+        <v>-0.20002114329205301</v>
       </c>
       <c r="C636">
-        <v>0.602044085523471</v>
+        <v>0.41676207849096197</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>677</v>
+        <v>190</v>
       </c>
       <c r="B637">
-        <v>0.938433090538216</v>
+        <v>0.70707304270373295</v>
       </c>
       <c r="C637">
-        <v>0.56345232508797505</v>
+        <v>-0.21601954760843101</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>363</v>
+        <v>191</v>
       </c>
       <c r="B638">
-        <v>0.20404619494471099</v>
+        <v>0.65063222259140896</v>
       </c>
       <c r="C638">
-        <v>-5.0595541527897497E-2</v>
+        <v>-0.21905738863292801</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>188</v>
+        <v>364</v>
       </c>
       <c r="B639">
-        <v>-0.79351826396693304</v>
+        <v>0.62387446541084002</v>
       </c>
       <c r="C639">
-        <v>-0.101259355816879</v>
+        <v>-0.44121216350576198</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>189</v>
+        <v>365</v>
       </c>
       <c r="B640">
-        <v>-0.38788729211695999</v>
+        <v>0.73018678206233101</v>
       </c>
       <c r="C640">
-        <v>9.8036259748807197E-2</v>
+        <v>-6.3468506867938798E-2</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>678</v>
+        <v>454</v>
       </c>
       <c r="B641">
-        <v>0.81982931019686101</v>
+        <v>0.82368689629908698</v>
       </c>
       <c r="C641">
-        <v>-0.324640877743062</v>
+        <v>-0.15666541516568899</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>679</v>
+        <v>431</v>
       </c>
       <c r="B642">
-        <v>-0.20002114329205301</v>
+        <v>-0.71897104321854499</v>
       </c>
       <c r="C642">
-        <v>0.41676207849096197</v>
+        <v>-0.58998485690220204</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>190</v>
+        <v>366</v>
       </c>
       <c r="B643">
-        <v>0.70707304270373295</v>
+        <v>-1.1925378527958801</v>
       </c>
       <c r="C643">
-        <v>-0.21601954760843101</v>
+        <v>-0.51774823465576403</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>191</v>
+        <v>367</v>
       </c>
       <c r="B644">
-        <v>0.65063222259140896</v>
+        <v>-0.57698247462276697</v>
       </c>
       <c r="C644">
-        <v>-0.21905738863292801</v>
+        <v>-6.1112601816996903E-2</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>364</v>
+        <v>672</v>
       </c>
       <c r="B645">
-        <v>0.62387446541084002</v>
+        <v>-0.408818541116097</v>
       </c>
       <c r="C645">
-        <v>-0.44121216350576198</v>
+        <v>9.0870192211887899E-2</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B646">
-        <v>0.73018678206233101</v>
+        <v>-0.77758054461141901</v>
       </c>
       <c r="C646">
-        <v>-6.3468506867938798E-2</v>
+        <v>0.44497357009358501</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B647">
-        <v>0.82368689629908698</v>
+        <v>0.78948764007956096</v>
       </c>
       <c r="C647">
-        <v>-0.15666541516568899</v>
+        <v>-0.36098525682216298</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>434</v>
+        <v>369</v>
       </c>
       <c r="B648">
-        <v>-0.71897104321854499</v>
+        <v>-1.1817212510831301</v>
       </c>
       <c r="C648">
-        <v>-0.58998485690220204</v>
+        <v>-1.7513935877167901</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>366</v>
+        <v>673</v>
       </c>
       <c r="B649">
-        <v>-1.1925378527958801</v>
+        <v>7.6273882908626203E-2</v>
       </c>
       <c r="C649">
-        <v>-0.51774823465576403</v>
+        <v>0.70783600455552997</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>367</v>
+        <v>192</v>
       </c>
       <c r="B650">
-        <v>-0.57698247462276697</v>
+        <v>-0.31514385287191699</v>
       </c>
       <c r="C650">
-        <v>-6.1112601816996903E-2</v>
+        <v>0.24254904802739999</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B651">
-        <v>-0.408818541116097</v>
+        <v>-0.19816519950300401</v>
       </c>
       <c r="C651">
-        <v>9.0870192211887899E-2</v>
+        <v>0.27959372763931201</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B652">
-        <v>-0.77758054461141901</v>
+        <v>0.703560045775252</v>
       </c>
       <c r="C652">
-        <v>0.44497357009358501</v>
+        <v>0.175330540296459</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>463</v>
+        <v>675</v>
       </c>
       <c r="B653">
-        <v>0.78948764007956096</v>
+        <v>0.77417983695430403</v>
       </c>
       <c r="C653">
-        <v>-0.36098525682216298</v>
+        <v>-0.228474466035781</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>369</v>
+        <v>676</v>
       </c>
       <c r="B654">
-        <v>-1.1817212510831301</v>
+        <v>-0.48463670782888801</v>
       </c>
       <c r="C654">
-        <v>-1.7513935877167901</v>
+        <v>0.15480367897282499</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>681</v>
+        <v>193</v>
       </c>
       <c r="B655">
-        <v>7.6273882908626203E-2</v>
+        <v>0.695087637689211</v>
       </c>
       <c r="C655">
-        <v>0.70783600455552997</v>
+        <v>-0.19573314065448999</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>192</v>
+        <v>677</v>
       </c>
       <c r="B656">
-        <v>-0.31514385287191699</v>
+        <v>-0.156000512725045</v>
       </c>
       <c r="C656">
-        <v>0.24254904802739999</v>
+        <v>0.51540285022183896</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>682</v>
+        <v>456</v>
       </c>
       <c r="B657">
-        <v>-0.19816519950300401</v>
+        <v>0.75827499991367597</v>
       </c>
       <c r="C657">
-        <v>0.27959372763931201</v>
+        <v>-0.54696662837501597</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B658">
-        <v>0.703560045775252</v>
+        <v>-0.88794650774365402</v>
       </c>
       <c r="C658">
-        <v>0.175330540296459</v>
+        <v>-0.60191874824812397</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>683</v>
+        <v>372</v>
       </c>
       <c r="B659">
-        <v>0.77417983695430403</v>
+        <v>-1.13717653259567</v>
       </c>
       <c r="C659">
-        <v>-0.228474466035781</v>
+        <v>-1.3499957270724701</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>684</v>
+        <v>194</v>
       </c>
       <c r="B660">
-        <v>-0.48463670782888801</v>
+        <v>-1.1933976661397301</v>
       </c>
       <c r="C660">
-        <v>0.15480367897282499</v>
+        <v>-1.24176022108423</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="B661">
-        <v>0.695087637689211</v>
+        <v>-0.89291507451522301</v>
       </c>
       <c r="C661">
-        <v>-0.19573314065448999</v>
+        <v>-0.24218678217676401</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B662">
-        <v>-0.156000512725045</v>
+        <v>-0.24810790730811</v>
       </c>
       <c r="C662">
-        <v>0.51540285022183896</v>
+        <v>0.32730629966839903</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>464</v>
+        <v>374</v>
       </c>
       <c r="B663">
-        <v>0.75827499991367597</v>
+        <v>-0.33803305329057998</v>
       </c>
       <c r="C663">
-        <v>-0.54696662837501597</v>
+        <v>-0.38037161014975901</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>371</v>
+        <v>195</v>
       </c>
       <c r="B664">
-        <v>-0.88794650774365402</v>
+        <v>0.57380826065866597</v>
       </c>
       <c r="C664">
-        <v>-0.60191874824812397</v>
+        <v>-0.19341870956202101</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>372</v>
+        <v>196</v>
       </c>
       <c r="B665">
-        <v>-1.13717653259567</v>
+        <v>-0.50967241007816</v>
       </c>
       <c r="C665">
-        <v>-1.3499957270724701</v>
+        <v>8.9333970185673101E-2</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B666">
-        <v>-1.1933976661397301</v>
+        <v>0.81919773341105495</v>
       </c>
       <c r="C666">
-        <v>-1.24176022108423</v>
+        <v>-0.31238896675854499</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>373</v>
+        <v>679</v>
       </c>
       <c r="B667">
-        <v>-0.89291507451522301</v>
+        <v>-0.47327535467884402</v>
       </c>
       <c r="C667">
-        <v>-0.24218678217676401</v>
+        <v>-4.73664960447258E-2</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>686</v>
+        <v>198</v>
       </c>
       <c r="B668">
-        <v>-0.24810790730811</v>
+        <v>-0.54473390383241704</v>
       </c>
       <c r="C668">
-        <v>0.32730629966839903</v>
+        <v>-3.7571050969328501E-2</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>374</v>
+        <v>680</v>
       </c>
       <c r="B669">
-        <v>-0.33803305329057998</v>
+        <v>-1.0935507004802001</v>
       </c>
       <c r="C669">
-        <v>-0.38037161014975901</v>
+        <v>-0.70065478282781701</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B670">
-        <v>0.57380826065866597</v>
+        <v>0.73881651067763299</v>
       </c>
       <c r="C670">
-        <v>-0.19341870956202101</v>
+        <v>-0.25087739578844998</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>196</v>
+        <v>375</v>
       </c>
       <c r="B671">
-        <v>-0.50967241007816</v>
+        <v>-1.1048347472856801</v>
       </c>
       <c r="C671">
-        <v>8.9333970185673101E-2</v>
+        <v>-1.86321685185312</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B672">
-        <v>0.81919773341105495</v>
+        <v>0.68734255485831797</v>
       </c>
       <c r="C672">
-        <v>-0.31238896675854499</v>
+        <v>1.0772320342040001E-2</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B673">
-        <v>-0.47327535467884402</v>
+        <v>-1.2359969708610601</v>
       </c>
       <c r="C673">
-        <v>-4.73664960447258E-2</v>
+        <v>6.0584338104897599E-2</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>198</v>
+        <v>682</v>
       </c>
       <c r="B674">
-        <v>-0.54473390383241704</v>
+        <v>-0.58979948330505005</v>
       </c>
       <c r="C674">
-        <v>-3.7571050969328501E-2</v>
+        <v>0.30541749973877402</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B675">
-        <v>-1.0935507004802001</v>
+        <v>-0.37734731482801698</v>
       </c>
       <c r="C675">
-        <v>-0.70065478282781701</v>
+        <v>1.3112385110186899</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>199</v>
+        <v>376</v>
       </c>
       <c r="B676">
-        <v>0.73881651067763299</v>
+        <v>0.56672838938695103</v>
       </c>
       <c r="C676">
-        <v>-0.25087739578844998</v>
+        <v>0.33097270902371201</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>375</v>
+        <v>201</v>
       </c>
       <c r="B677">
-        <v>-1.1048347472856801</v>
+        <v>-0.56265890154894804</v>
       </c>
       <c r="C677">
-        <v>-1.86321685185312</v>
+        <v>7.3727889589332595E-4</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>200</v>
+        <v>377</v>
       </c>
       <c r="B678">
-        <v>0.68734255485831797</v>
+        <v>-0.31073438536417602</v>
       </c>
       <c r="C678">
-        <v>1.0772320342040001E-2</v>
+        <v>0.39279832468577502</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>689</v>
+        <v>378</v>
       </c>
       <c r="B679">
-        <v>-1.2359969708610601</v>
+        <v>-1.4003081210025401</v>
       </c>
       <c r="C679">
-        <v>6.0584338104897599E-2</v>
+        <v>-0.65163662091113395</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>690</v>
+        <v>379</v>
       </c>
       <c r="B680">
-        <v>-0.58979948330505005</v>
+        <v>-0.36410577087822699</v>
       </c>
       <c r="C680">
-        <v>0.30541749973877402</v>
+        <v>0.48944318586458502</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B681">
-        <v>-0.37734731482801698</v>
+        <v>-0.627375475149062</v>
       </c>
       <c r="C681">
-        <v>1.3112385110186899</v>
+        <v>0.44783317050060401</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B682">
-        <v>0.56672838938695103</v>
+        <v>-0.75198679317173101</v>
       </c>
       <c r="C682">
-        <v>0.33097270902371201</v>
+        <v>-0.12179247116484899</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B683">
-        <v>-0.56265890154894804</v>
+        <v>0.71105738411934205</v>
       </c>
       <c r="C683">
-        <v>7.3727889589332595E-4</v>
+        <v>-0.26548407537367102</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>377</v>
+        <v>685</v>
       </c>
       <c r="B684">
-        <v>-0.31073438536417602</v>
+        <v>-1.2976050898621001</v>
       </c>
       <c r="C684">
-        <v>0.39279832468577502</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A685" t="s">
-        <v>378</v>
-      </c>
-      <c r="B685">
-        <v>-1.4003081210025401</v>
-      </c>
-      <c r="C685">
-        <v>-0.65163662091113395</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A686" t="s">
-        <v>435</v>
-      </c>
-      <c r="B686" t="s">
-        <v>441</v>
-      </c>
-      <c r="C686" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A687" t="s">
-        <v>379</v>
-      </c>
-      <c r="B687">
-        <v>-0.36410577087822699</v>
-      </c>
-      <c r="C687">
-        <v>0.48944318586458502</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A688" t="s">
-        <v>692</v>
-      </c>
-      <c r="B688">
-        <v>-0.627375475149062</v>
-      </c>
-      <c r="C688">
-        <v>0.44783317050060401</v>
-      </c>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A689" t="s">
-        <v>380</v>
-      </c>
-      <c r="B689">
-        <v>-0.75198679317173101</v>
-      </c>
-      <c r="C689">
-        <v>-0.12179247116484899</v>
-      </c>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A690" t="s">
-        <v>202</v>
-      </c>
-      <c r="B690">
-        <v>0.71105738411934205</v>
-      </c>
-      <c r="C690">
-        <v>-0.26548407537367102</v>
-      </c>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A691" t="s">
-        <v>693</v>
-      </c>
-      <c r="B691">
-        <v>-1.2976050898621001</v>
-      </c>
-      <c r="C691">
         <v>-0.67403926212023901</v>
       </c>
     </row>

--- a/nmds_results.xlsx
+++ b/nmds_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drake\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F515D08-B098-4B2E-9766-789B5A440612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB25B01-B006-4216-83C3-010B9E999A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card_WA_Scores" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t>NMDS1</t>
   </si>
@@ -890,9 +890,6 @@
     <t>Cultivate</t>
   </si>
   <si>
-    <t>Dark Depths</t>
-  </si>
-  <si>
     <t>Deeproot Wayfinder</t>
   </si>
   <si>
@@ -1443,6 +1440,108 @@
   </si>
   <si>
     <t>Worldspine Wurm</t>
+  </si>
+  <si>
+    <t>Augur of Autumn</t>
+  </si>
+  <si>
+    <t>Boggart Trawler</t>
+  </si>
+  <si>
+    <t>Devourer of Destiny</t>
+  </si>
+  <si>
+    <t>Emrakul, the World Anew</t>
+  </si>
+  <si>
+    <t>Esper Origins</t>
+  </si>
+  <si>
+    <t>Etali, Primal Conqueror</t>
+  </si>
+  <si>
+    <t>Farseek</t>
+  </si>
+  <si>
+    <t>Fire Magic</t>
+  </si>
+  <si>
+    <t>Force of Negation</t>
+  </si>
+  <si>
+    <t>Ghost Vacuum</t>
+  </si>
+  <si>
+    <t>Hanweir Garrison</t>
+  </si>
+  <si>
+    <t>Hexdrinker</t>
+  </si>
+  <si>
+    <t>Hit the Mother Lode</t>
+  </si>
+  <si>
+    <t>Howlpack Piper</t>
+  </si>
+  <si>
+    <t>Incubation / Incongruity</t>
+  </si>
+  <si>
+    <t>Lantern of the Lost</t>
+  </si>
+  <si>
+    <t>Make Your Own Luck</t>
+  </si>
+  <si>
+    <t>Ojer Kaslem, Deepest Growth</t>
+  </si>
+  <si>
+    <t>Omniscience</t>
+  </si>
+  <si>
+    <t>One with the Multiverse</t>
+  </si>
+  <si>
+    <t>Primeval Shambler</t>
+  </si>
+  <si>
+    <t>Shivan Dragon</t>
+  </si>
+  <si>
+    <t>Summon the Pack</t>
+  </si>
+  <si>
+    <t>Sundering Eruption</t>
+  </si>
+  <si>
+    <t>Tezzeret, Cruel Captain</t>
+  </si>
+  <si>
+    <t>The World Spell</t>
+  </si>
+  <si>
+    <t>Tifa Lockhart</t>
+  </si>
+  <si>
+    <t>Tolarian Winds</t>
+  </si>
+  <si>
+    <t>Ugin's Labyrinth</t>
+  </si>
+  <si>
+    <t>Ulamog, the Defiler</t>
+  </si>
+  <si>
+    <t>Unexpected Results</t>
+  </si>
+  <si>
+    <t>Wayfarer's Bauble</t>
+  </si>
+  <si>
+    <t>Winding Way</t>
+  </si>
+  <si>
+    <t>Woodland Bellower</t>
   </si>
 </sst>
 </file>
@@ -1815,12 +1914,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C471"/>
+  <dimension ref="A1:C504"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1834,10 +1933,10 @@
         <v>269</v>
       </c>
       <c r="B2">
-        <v>-0.79048369416224096</v>
+        <v>-0.77945149116279999</v>
       </c>
       <c r="C2">
-        <v>0.41711004861151901</v>
+        <v>0.43022510374583001</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1845,10 +1944,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-0.55834413256149296</v>
+        <v>-0.54517206665541795</v>
       </c>
       <c r="C3">
-        <v>0.32768176475121802</v>
+        <v>0.32329488734327799</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1856,10 +1955,10 @@
         <v>132</v>
       </c>
       <c r="B4">
-        <v>-0.80324954197809295</v>
+        <v>-0.84939058553352598</v>
       </c>
       <c r="C4">
-        <v>-9.1259684459006701E-2</v>
+        <v>-0.128152984350454</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1867,10 +1966,10 @@
         <v>270</v>
       </c>
       <c r="B5">
-        <v>-0.76373145356051497</v>
+        <v>-0.757445974708717</v>
       </c>
       <c r="C5">
-        <v>0.57784088867480199</v>
+        <v>0.57058547019309602</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1878,10 +1977,10 @@
         <v>133</v>
       </c>
       <c r="B6">
-        <v>4.6903891884946702E-2</v>
+        <v>5.5971460597889502E-2</v>
       </c>
       <c r="C6">
-        <v>-7.7062392771637095E-2</v>
+        <v>-6.2377720030919001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1889,10 +1988,10 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>-1.05909496682808</v>
+        <v>-1.0421743070702201</v>
       </c>
       <c r="C7">
-        <v>-8.3160569517801694E-2</v>
+        <v>-0.100409249381609</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1900,10 +1999,10 @@
         <v>134</v>
       </c>
       <c r="B8">
-        <v>-1.2201004779970099</v>
+        <v>-1.2137010617223201</v>
       </c>
       <c r="C8">
-        <v>-0.87769684302252604</v>
+        <v>-0.87762469051633196</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1911,21 +2010,21 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>0.72250381873851299</v>
+        <v>0.72782608871975596</v>
       </c>
       <c r="C9">
-        <v>-0.23312578970918599</v>
+        <v>-0.24091639319368299</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B10">
-        <v>-1.0314636506668999</v>
+        <v>-1.0295111469034901</v>
       </c>
       <c r="C10">
-        <v>0.89406442552762899</v>
+        <v>0.88564175601686201</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1933,10 +2032,10 @@
         <v>271</v>
       </c>
       <c r="B11">
-        <v>0.52140024829450504</v>
+        <v>0.52636760146043804</v>
       </c>
       <c r="C11">
-        <v>-0.54284782896527395</v>
+        <v>-0.55187764069290601</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1944,10 +2043,10 @@
         <v>135</v>
       </c>
       <c r="B12">
-        <v>-0.21454148865184899</v>
+        <v>-0.20539388321761501</v>
       </c>
       <c r="C12">
-        <v>0.22935739740765701</v>
+        <v>0.25646200512969303</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1955,10 +2054,10 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <v>-3.87285541077043E-4</v>
+        <v>-4.1321286266338798E-4</v>
       </c>
       <c r="C13">
-        <v>-1.21394990775573E-4</v>
+        <v>-1.2533452355779499E-4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1966,10 +2065,10 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>-1.2238932959345501</v>
+        <v>-1.21563165855078</v>
       </c>
       <c r="C14">
-        <v>-0.60861115703982904</v>
+        <v>-0.60785985999883496</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1977,10 +2076,10 @@
         <v>136</v>
       </c>
       <c r="B15">
-        <v>-1.1702218308223999</v>
+        <v>-1.1463692772938701</v>
       </c>
       <c r="C15">
-        <v>-1.1430685356439301</v>
+        <v>-1.16358737520852</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1988,10 +2087,10 @@
         <v>272</v>
       </c>
       <c r="B16">
-        <v>-0.60616606089625202</v>
+        <v>-0.60836470221083805</v>
       </c>
       <c r="C16">
-        <v>0.65875931803398002</v>
+        <v>0.63727748255027605</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1999,10 +2098,10 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>0.20035216017819499</v>
+        <v>0.20282351807472801</v>
       </c>
       <c r="C17">
-        <v>7.6835192432959998E-2</v>
+        <v>7.97445152109581E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2010,10 +2109,10 @@
         <v>273</v>
       </c>
       <c r="B18">
-        <v>-0.16140079809416699</v>
+        <v>-5.1995035192883003E-2</v>
       </c>
       <c r="C18">
-        <v>0.37782953897164301</v>
+        <v>0.85410485971786698</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2021,10 +2120,10 @@
         <v>274</v>
       </c>
       <c r="B19">
-        <v>-0.18529607417789801</v>
+        <v>-0.173109635194305</v>
       </c>
       <c r="C19">
-        <v>0.46276828168967299</v>
+        <v>0.47291047947977399</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2032,10 +2131,10 @@
         <v>275</v>
       </c>
       <c r="B20">
-        <v>-0.77028131048499704</v>
+        <v>-0.75985713287553802</v>
       </c>
       <c r="C20">
-        <v>0.30143789661114001</v>
+        <v>0.31404112619500801</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2043,4960 +2142,5323 @@
         <v>137</v>
       </c>
       <c r="B21">
-        <v>-0.282816280494605</v>
+        <v>-0.27168037970951198</v>
       </c>
       <c r="C21">
-        <v>0.131796170479278</v>
+        <v>0.14255968504314101</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>276</v>
+        <v>473</v>
       </c>
       <c r="B22">
-        <v>-0.32749720011713901</v>
+        <v>0.43390021362555098</v>
       </c>
       <c r="C22">
-        <v>0.103355601043072</v>
+        <v>0.40743924059037001</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B23">
-        <v>-0.39012310406718298</v>
+        <v>-0.31742801183063901</v>
       </c>
       <c r="C23">
-        <v>0.78773010601848903</v>
+        <v>0.122948581336395</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>277</v>
       </c>
       <c r="B24">
-        <v>-0.67165538073617204</v>
+        <v>-0.37914544901270802</v>
       </c>
       <c r="C24">
-        <v>-5.7349491185797699E-2</v>
+        <v>0.79761598369488196</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>278</v>
+        <v>8</v>
       </c>
       <c r="B25">
-        <v>0.76854898845864605</v>
+        <v>-0.67218268419570304</v>
       </c>
       <c r="C25">
-        <v>-0.44122631562235798</v>
+        <v>-6.0661592610142701E-2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>278</v>
       </c>
       <c r="B26">
-        <v>0.79456515436520403</v>
+        <v>0.77286034994778796</v>
       </c>
       <c r="C26">
-        <v>-0.36124554378573298</v>
+        <v>-0.45414049393761502</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="B27">
-        <v>-1.2701846923501701</v>
+        <v>0.80068264758097296</v>
       </c>
       <c r="C27">
-        <v>-0.67142215713740405</v>
+        <v>-0.39230727757060002</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="B28">
-        <v>-0.86818099640005697</v>
+        <v>-1.2581285131669799</v>
       </c>
       <c r="C28">
-        <v>0.61320580015095505</v>
+        <v>-0.68922561757911505</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>423</v>
+        <v>279</v>
       </c>
       <c r="B29">
-        <v>-0.19512325329934699</v>
+        <v>-0.85872282990029702</v>
       </c>
       <c r="C29">
-        <v>-3.4888346353967101</v>
+        <v>0.61104666996227797</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>280</v>
+        <v>422</v>
       </c>
       <c r="B30">
-        <v>0.20184914429386899</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C30">
-        <v>0.36057270609041697</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="B31">
-        <v>-0.67846815879686695</v>
+        <v>0.216448774903025</v>
       </c>
       <c r="C31">
-        <v>0.27142270267644603</v>
+        <v>0.36188179762143402</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>10</v>
       </c>
       <c r="B32">
-        <v>-1.03092967861549</v>
+        <v>-0.74472515378533299</v>
       </c>
       <c r="C32">
-        <v>-0.59119030757082103</v>
+        <v>0.17420209297715</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33">
-        <v>1.0431622308781401</v>
+        <v>-1.01609030863463</v>
       </c>
       <c r="C33">
-        <v>-0.244410493323409</v>
+        <v>-0.60718134452146399</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="B34">
-        <v>-0.473198131496889</v>
+        <v>1.0511411468126099</v>
       </c>
       <c r="C34">
-        <v>0.130792553068417</v>
+        <v>-0.25961757988877998</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>281</v>
+        <v>474</v>
       </c>
       <c r="B35">
-        <v>-0.34507090135392599</v>
+        <v>0.243297777705103</v>
       </c>
       <c r="C35">
-        <v>-0.74039052580860298</v>
+        <v>0.67633598230301195</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>11</v>
       </c>
       <c r="B36">
-        <v>-1.0441183077204601</v>
+        <v>-0.47173365887296698</v>
       </c>
       <c r="C36">
-        <v>0.48126366508907198</v>
+        <v>0.122079912341314</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="B37">
-        <v>8.9685721858313704E-3</v>
+        <v>-0.33460630837021099</v>
       </c>
       <c r="C37">
-        <v>0.59538638116170095</v>
+        <v>-0.73858316725492501</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>424</v>
+        <v>282</v>
       </c>
       <c r="B38">
-        <v>-1.1187095734349799</v>
+        <v>-1.0361017931843499</v>
       </c>
       <c r="C38">
-        <v>-1.2201777828823099</v>
+        <v>0.47108159652458498</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="B39">
-        <v>-0.45706713827120399</v>
+        <v>1.8631021149943701E-2</v>
       </c>
       <c r="C39">
-        <v>7.6178410884208195E-2</v>
+        <v>0.58894300913721598</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
       <c r="B40">
-        <v>0.30907796848610097</v>
+        <v>-1.0955235438863999</v>
       </c>
       <c r="C40">
-        <v>2.73601745957038E-2</v>
+        <v>-1.2355708021652401</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41">
-        <v>-1.2873128148164501</v>
+        <v>-0.453884300873932</v>
       </c>
       <c r="C41">
-        <v>-0.59999150736589502</v>
+        <v>7.9154125767880903E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B42">
-        <v>-0.80598045664748996</v>
+        <v>0.31544640963659198</v>
       </c>
       <c r="C42">
-        <v>0.28646614336913601</v>
+        <v>2.7754185367540599E-2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="B43">
-        <v>0.68323000228183906</v>
+        <v>-1.27250733198477</v>
       </c>
       <c r="C43">
-        <v>-0.38224967685317601</v>
+        <v>-0.63260505017318502</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="B44">
-        <v>0.77049822390989198</v>
+        <v>-0.79835643649483201</v>
       </c>
       <c r="C44">
-        <v>-9.6602362564151403E-2</v>
+        <v>0.27815258070526999</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B45">
-        <v>0.69315906081789103</v>
+        <v>0.68956447264697396</v>
       </c>
       <c r="C45">
-        <v>7.7940997606777404E-2</v>
+        <v>-0.39137116896548102</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B46">
-        <v>0.34748392951634299</v>
+        <v>0.76418023557675696</v>
       </c>
       <c r="C46">
-        <v>0.60831175550612404</v>
+        <v>-0.17679742114534799</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>425</v>
+        <v>144</v>
       </c>
       <c r="B47">
-        <v>-1.2014272557185099</v>
+        <v>0.70659641250626704</v>
       </c>
       <c r="C47">
-        <v>-0.46826268132445098</v>
+        <v>2.7721222964760501E-2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>283</v>
+        <v>145</v>
       </c>
       <c r="B48">
-        <v>-0.51000466349986795</v>
+        <v>0.362711992791038</v>
       </c>
       <c r="C48">
-        <v>0.73200590467200399</v>
+        <v>0.60810572855513201</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>424</v>
       </c>
       <c r="B49">
-        <v>-0.41563799942845903</v>
+        <v>-1.1837828760346201</v>
       </c>
       <c r="C49">
-        <v>0.40918016830120202</v>
+        <v>-0.48921230178879599</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B50">
-        <v>-0.46799234297639197</v>
+        <v>-0.50017678503622998</v>
       </c>
       <c r="C50">
-        <v>0.34882678805971001</v>
+        <v>0.73366358430202805</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>250</v>
+        <v>146</v>
       </c>
       <c r="B51">
-        <v>-0.70401873764802103</v>
+        <v>-0.40332460196186998</v>
       </c>
       <c r="C51">
-        <v>0.67365270983885195</v>
+        <v>0.41275437928830899</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B52">
-        <v>3.0485403728814701E-2</v>
+        <v>-0.45724612372321199</v>
       </c>
       <c r="C52">
-        <v>2.1747282658484002</v>
+        <v>0.360803702824463</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="B53">
-        <v>-0.56117956440630301</v>
+        <v>-0.69549633934842203</v>
       </c>
       <c r="C53">
-        <v>0.30169531158792401</v>
+        <v>0.66994391627905303</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c r="B54">
-        <v>-0.461769333641535</v>
+        <v>-1.8331705035761999E-3</v>
       </c>
       <c r="C54">
-        <v>9.9504849446101301E-2</v>
+        <v>2.1391236296463698</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="B55">
-        <v>0.79379654893188301</v>
+        <v>-0.55380642067688501</v>
       </c>
       <c r="C55">
-        <v>-9.4309861737912198E-2</v>
+        <v>0.29889683906143999</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>286</v>
+        <v>17</v>
       </c>
       <c r="B56">
-        <v>-0.57076743036733102</v>
+        <v>-0.44738601252076698</v>
       </c>
       <c r="C56">
-        <v>-0.30941983095506997</v>
+        <v>0.10617439241863599</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>251</v>
+        <v>147</v>
       </c>
       <c r="B57">
-        <v>-0.59140541253856704</v>
+        <v>0.78874871656015599</v>
       </c>
       <c r="C57">
-        <v>0.56723820562713601</v>
+        <v>-0.14023402480998201</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>18</v>
+        <v>286</v>
       </c>
       <c r="B58">
-        <v>-1.22100898867721</v>
+        <v>-0.56185184877803296</v>
       </c>
       <c r="C58">
-        <v>-1.0419260751617401</v>
+        <v>-0.29881046910699499</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="B59">
-        <v>-1.39486157459995</v>
+        <v>-0.58439016974940505</v>
       </c>
       <c r="C59">
-        <v>-0.44483753690994199</v>
+        <v>0.56471407730665102</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="B60">
-        <v>-0.19512325329934699</v>
+        <v>-1.198372401746</v>
       </c>
       <c r="C60">
-        <v>-3.4888346353967101</v>
+        <v>-1.0614758416031</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="B61">
-        <v>0.56989551780025605</v>
+        <v>-1.3842317678632601</v>
       </c>
       <c r="C61">
-        <v>-0.31606151034039998</v>
+        <v>-0.46339910882102497</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>148</v>
+        <v>425</v>
       </c>
       <c r="B62">
-        <v>0.51790481052516202</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C62">
-        <v>8.9291959771589796E-2</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="B63">
-        <v>0.463710685644521</v>
+        <v>0.65760767705960299</v>
       </c>
       <c r="C63">
-        <v>0.14173140121332001</v>
+        <v>-0.39954531751337802</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B64">
-        <v>-1.2493654341088301</v>
+        <v>0.50256978246329698</v>
       </c>
       <c r="C64">
-        <v>-1.1323852482199599</v>
+        <v>0.105327065925695</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="B65">
-        <v>-1.1962307835085599</v>
+        <v>0.477730120733946</v>
       </c>
       <c r="C65">
-        <v>-0.88233768038695504</v>
+        <v>0.137666526621118</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>427</v>
+        <v>149</v>
       </c>
       <c r="B66">
-        <v>-1.10182067403623</v>
+        <v>-1.2150562656250801</v>
       </c>
       <c r="C66">
-        <v>-1.7463874601095299</v>
+        <v>-1.1683127431051601</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="B67">
-        <v>-1.0194741650727199</v>
+        <v>-1.1729707757180901</v>
       </c>
       <c r="C67">
-        <v>-0.20957809251939</v>
+        <v>-0.90453548363442604</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B68">
-        <v>-1.3825956635594701</v>
+        <v>-1.07610632062936</v>
       </c>
       <c r="C68">
-        <v>0.10083603325418999</v>
+        <v>-1.7628865193313401</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B69">
-        <v>0.496759666864521</v>
+        <v>-1.0087656791291599</v>
       </c>
       <c r="C69">
-        <v>-0.13531652936873401</v>
+        <v>-0.248036293691032</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>288</v>
+        <v>427</v>
       </c>
       <c r="B70">
-        <v>-0.30806553434256601</v>
+        <v>-1.3664436699486699</v>
       </c>
       <c r="C70">
-        <v>0.517546616444581</v>
+        <v>0.101234565033237</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B71">
-        <v>8.332226554411E-2</v>
+        <v>0.50202741344879598</v>
       </c>
       <c r="C71">
-        <v>0.16925328069297799</v>
+        <v>-0.14223484036205999</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B72">
-        <v>0.62567338704878706</v>
+        <v>-0.29826045340525698</v>
       </c>
       <c r="C72">
-        <v>-0.89646610927053405</v>
+        <v>0.52091144276756596</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>429</v>
+        <v>23</v>
       </c>
       <c r="B73">
-        <v>-1.2954342637587499</v>
+        <v>8.8575996730802894E-2</v>
       </c>
       <c r="C73">
-        <v>-0.51437756801578005</v>
+        <v>0.17212860897749599</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>290</v>
+        <v>428</v>
       </c>
       <c r="B74">
-        <v>0.83978686695517701</v>
+        <v>-1.2796723945295501</v>
       </c>
       <c r="C74">
-        <v>-0.30009022947345798</v>
+        <v>-0.53461124608996302</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B75">
-        <v>-0.245969077658649</v>
+        <v>0.84543639674300297</v>
       </c>
       <c r="C75">
-        <v>0.61582959929758097</v>
+        <v>-0.31618129564109998</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>430</v>
+        <v>290</v>
       </c>
       <c r="B76">
-        <v>-1.1734878344002799</v>
+        <v>-0.23450494022891899</v>
       </c>
       <c r="C76">
-        <v>-0.96749487380861299</v>
+        <v>0.62845453974021603</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>150</v>
+        <v>429</v>
       </c>
       <c r="B77">
-        <v>-1.4925604543753299</v>
+        <v>-1.15190285558911</v>
       </c>
       <c r="C77">
-        <v>-0.35309484755270798</v>
+        <v>-0.98512489138428305</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>431</v>
+        <v>150</v>
       </c>
       <c r="B78">
-        <v>-1.24756857120862</v>
+        <v>-1.4760040671306001</v>
       </c>
       <c r="C78">
-        <v>-0.99019881936468801</v>
+        <v>-0.37718693635320399</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>475</v>
       </c>
       <c r="B79">
-        <v>-1.2855855180487501</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C79">
-        <v>0.56175859756902002</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>152</v>
+        <v>430</v>
       </c>
       <c r="B80">
-        <v>0.25725991371245699</v>
+        <v>-1.2255956664135701</v>
       </c>
       <c r="C80">
-        <v>0.31356431896879799</v>
+        <v>-1.0082233311301201</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="B81">
-        <v>-0.64003233890245104</v>
+        <v>-1.2780766336293199</v>
       </c>
       <c r="C81">
-        <v>0.13122354734181099</v>
+        <v>0.54840432346600398</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>292</v>
+        <v>152</v>
       </c>
       <c r="B82">
-        <v>0.63164055530958896</v>
+        <v>0.27846020306337199</v>
       </c>
       <c r="C82">
-        <v>-0.56301403470792599</v>
+        <v>0.31437435599196301</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>293</v>
+        <v>24</v>
       </c>
       <c r="B83">
-        <v>-0.99439863871621503</v>
+        <v>-0.59322793101993099</v>
       </c>
       <c r="C83">
-        <v>3.5321420703022403E-2</v>
+        <v>0.101632447207244</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="B84">
-        <v>-1.0259427538368999</v>
+        <v>0.63561721879472299</v>
       </c>
       <c r="C84">
-        <v>-0.66894870464129297</v>
+        <v>-0.575090296390523</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="B85">
-        <v>-0.239203924155869</v>
+        <v>-1.00852751040717</v>
       </c>
       <c r="C85">
-        <v>7.7836572884907099E-2</v>
+        <v>-3.8012507382782598E-2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>294</v>
+        <v>153</v>
       </c>
       <c r="B86">
-        <v>-0.74934947309977396</v>
+        <v>-0.86136849246691205</v>
       </c>
       <c r="C86">
-        <v>1.72495114568604</v>
+        <v>-0.48444094036240398</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B87">
-        <v>-0.25828959528406298</v>
+        <v>-0.22826462606356401</v>
       </c>
       <c r="C87">
-        <v>0.71227941282184304</v>
+        <v>8.8242519085391893E-2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>25</v>
+        <v>293</v>
       </c>
       <c r="B88">
-        <v>0.71468008523037196</v>
+        <v>-0.76142448459670597</v>
       </c>
       <c r="C88">
-        <v>-0.31373356636844202</v>
+        <v>1.71784947378876</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="B89">
-        <v>-0.155212831467055</v>
+        <v>-0.244023274021337</v>
       </c>
       <c r="C89">
-        <v>0.29741514358782001</v>
+        <v>0.72366315737451703</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>432</v>
+        <v>25</v>
       </c>
       <c r="B90">
-        <v>-1.4634594566657699</v>
+        <v>0.72326226599588594</v>
       </c>
       <c r="C90">
-        <v>-0.46402719912448098</v>
+        <v>-0.32267032515872901</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>295</v>
+        <v>26</v>
       </c>
       <c r="B91">
-        <v>0.71020121332110298</v>
+        <v>-0.14877163825435399</v>
       </c>
       <c r="C91">
-        <v>-0.37840112908686602</v>
+        <v>0.30363796169163598</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>431</v>
       </c>
       <c r="B92">
-        <v>0.69981035413734005</v>
+        <v>-1.44591982429221</v>
       </c>
       <c r="C92">
-        <v>-0.240974217347067</v>
+        <v>-0.49067652983346599</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B93">
-        <v>0.69981425095788996</v>
+        <v>0.71565710858413301</v>
       </c>
       <c r="C93">
-        <v>0.51565576222160903</v>
+        <v>-0.38966534474534498</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B94">
-        <v>-0.60296985807796699</v>
+        <v>0.70475896539094396</v>
       </c>
       <c r="C94">
-        <v>0.85752915331594604</v>
+        <v>-0.249521296705147</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>156</v>
+        <v>295</v>
       </c>
       <c r="B95">
-        <v>-0.64243556996195605</v>
+        <v>0.71340620940548605</v>
       </c>
       <c r="C95">
-        <v>0.49021500893888598</v>
+        <v>0.49977219626437802</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>28</v>
       </c>
       <c r="B96">
-        <v>-0.74111782981025798</v>
+        <v>-0.56890944551876099</v>
       </c>
       <c r="C96">
-        <v>0.97278157281503397</v>
+        <v>0.830176316316244</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>433</v>
+        <v>156</v>
       </c>
       <c r="B97">
-        <v>-1.3548648342286</v>
+        <v>-0.78585990956319796</v>
       </c>
       <c r="C97">
-        <v>-0.68434773086826794</v>
+        <v>0.48907013986949499</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="B98">
-        <v>0.122464375555262</v>
+        <v>-0.73696210973923604</v>
       </c>
       <c r="C98">
-        <v>0.52951158555796696</v>
+        <v>0.96984105164312095</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>298</v>
+        <v>432</v>
       </c>
       <c r="B99">
-        <v>-0.167540833502904</v>
+        <v>-1.3331092739206101</v>
       </c>
       <c r="C99">
-        <v>0.106412504192236</v>
+        <v>-0.71873554687649899</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B100">
-        <v>-0.46276999309509098</v>
+        <v>0.13563094405158399</v>
       </c>
       <c r="C100">
-        <v>0.57638719016796902</v>
+        <v>0.53051307190837904</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>157</v>
+        <v>297</v>
       </c>
       <c r="B101">
-        <v>-0.36442744376710701</v>
+        <v>-0.15689881093026001</v>
       </c>
       <c r="C101">
-        <v>0.59115697678174095</v>
+        <v>0.117006608106273</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>259</v>
+        <v>30</v>
       </c>
       <c r="B102">
-        <v>0.80466708480905202</v>
+        <v>-0.45539296173072502</v>
       </c>
       <c r="C102">
-        <v>-0.20931231415416601</v>
+        <v>0.57815798590524303</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="B103">
-        <v>-0.58758305060000504</v>
+        <v>-0.44002547323366098</v>
       </c>
       <c r="C103">
-        <v>-0.42691474552363401</v>
+        <v>0.46679373819922598</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="B104">
-        <v>0.56447644557294097</v>
+        <v>0.80932661769950798</v>
       </c>
       <c r="C104">
-        <v>4.7930889406339799E-2</v>
+        <v>-0.23002082691235901</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>434</v>
+        <v>31</v>
       </c>
       <c r="B105">
-        <v>-0.93768252161721499</v>
+        <v>-0.54024622765428199</v>
       </c>
       <c r="C105">
-        <v>-1.33584798246672</v>
+        <v>-0.51709575620686099</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="B106">
-        <v>-0.13868674108101001</v>
+        <v>0.34241804156963102</v>
       </c>
       <c r="C106">
-        <v>0.24116377440683401</v>
+        <v>0.217476004544706</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>476</v>
       </c>
       <c r="B107">
-        <v>-1.1975028382567401</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C107">
-        <v>-0.26749363837990098</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="B108">
-        <v>-0.393178642673225</v>
+        <v>-0.92866327447299302</v>
       </c>
       <c r="C108">
-        <v>0.89299709341376898</v>
+        <v>-1.3371126639111199</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="B109">
-        <v>-0.192544236737033</v>
+        <v>-0.10748550999147</v>
       </c>
       <c r="C109">
-        <v>0.397194723826024</v>
+        <v>0.248587886374454</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>300</v>
+        <v>33</v>
       </c>
       <c r="B110">
-        <v>-0.34682443778008099</v>
+        <v>-1.1894575195004999</v>
       </c>
       <c r="C110">
-        <v>0.68612642968182302</v>
+        <v>-0.28471520363328201</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>435</v>
+        <v>260</v>
       </c>
       <c r="B111">
-        <v>-1.16575748487314</v>
+        <v>-0.38134038761855998</v>
       </c>
       <c r="C111">
-        <v>-1.41459940523387</v>
+        <v>0.88549553949720095</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>301</v>
+        <v>158</v>
       </c>
       <c r="B112">
-        <v>-0.234057489291704</v>
+        <v>-0.259374424750974</v>
       </c>
       <c r="C112">
-        <v>0.27307327529173803</v>
+        <v>0.42328866796845199</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>477</v>
       </c>
       <c r="B113">
-        <v>2.1953319450545499E-2</v>
+        <v>0.69252403655489503</v>
       </c>
       <c r="C113">
-        <v>0.23377510394055201</v>
+        <v>-0.26405192086525803</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>35</v>
+        <v>478</v>
       </c>
       <c r="B114">
-        <v>1.83645501986591E-2</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C114">
-        <v>0.114803184504712</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>253</v>
+        <v>299</v>
       </c>
       <c r="B115">
-        <v>3.27307735671514E-2</v>
+        <v>-0.33890164486412699</v>
       </c>
       <c r="C115">
-        <v>0.28681947225766802</v>
+        <v>0.687238968785573</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>302</v>
+        <v>434</v>
       </c>
       <c r="B116">
-        <v>-0.22639078579785599</v>
+        <v>-1.14187521954017</v>
       </c>
       <c r="C116">
-        <v>-0.219705541715288</v>
+        <v>-1.4311157653623401</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>436</v>
+        <v>300</v>
       </c>
       <c r="B117">
-        <v>-1.1624226484723601</v>
+        <v>-0.22309937888456299</v>
       </c>
       <c r="C117">
-        <v>-0.96394546729673103</v>
+        <v>0.28266442329507901</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>159</v>
+        <v>34</v>
       </c>
       <c r="B118">
-        <v>0.84151600300269802</v>
+        <v>2.82583549767761E-2</v>
       </c>
       <c r="C118">
-        <v>-8.97629377532108E-2</v>
+        <v>0.23999512776644</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>303</v>
+        <v>35</v>
       </c>
       <c r="B119">
-        <v>-0.45937396964710597</v>
+        <v>2.4247893229996299E-2</v>
       </c>
       <c r="C119">
-        <v>0.63994612317463895</v>
+        <v>0.108740971946426</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="B120">
-        <v>0.40853063802356099</v>
+        <v>4.9077527387323502E-2</v>
       </c>
       <c r="C120">
-        <v>0.18959440502746799</v>
+        <v>0.29094821413739702</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>161</v>
+        <v>301</v>
       </c>
       <c r="B121">
-        <v>-1.3397694289992099</v>
+        <v>-0.211911293140887</v>
       </c>
       <c r="C121">
-        <v>-0.22245638162190701</v>
+        <v>-0.23807672857800899</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>36</v>
+        <v>435</v>
       </c>
       <c r="B122">
-        <v>-1.0704900402342901</v>
+        <v>-1.13714625092064</v>
       </c>
       <c r="C122">
-        <v>0.33621672520482399</v>
+        <v>-0.98887796925923399</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
       <c r="B123">
-        <v>-0.73554220674811199</v>
+        <v>0.84933724277470202</v>
       </c>
       <c r="C123">
-        <v>0.490731085730579</v>
+        <v>-0.108581660343943</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="B124">
-        <v>-0.88525141370586202</v>
+        <v>-0.44845078890400097</v>
       </c>
       <c r="C124">
-        <v>0.49125084624391702</v>
+        <v>0.64458656455514296</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="B125">
-        <v>-1.25743371231045</v>
+        <v>-1.560909853514</v>
       </c>
       <c r="C125">
-        <v>-0.95815032702268499</v>
+        <v>-0.22477529910379199</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B126">
-        <v>-1.1140628530468499</v>
+        <v>0.36588340401253999</v>
       </c>
       <c r="C126">
-        <v>-0.193741272243382</v>
+        <v>0.21708656517573699</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>305</v>
+        <v>161</v>
       </c>
       <c r="B127">
-        <v>-0.133580277307386</v>
+        <v>-1.2454753857779799</v>
       </c>
       <c r="C127">
-        <v>-0.50100540034436802</v>
+        <v>-0.109755990221368</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>438</v>
+        <v>36</v>
       </c>
       <c r="B128">
-        <v>-1.27254107031248</v>
+        <v>-1.0804804613813299</v>
       </c>
       <c r="C128">
-        <v>-1.0222694212265</v>
+        <v>0.289573889619611</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>163</v>
+        <v>303</v>
       </c>
       <c r="B129">
-        <v>-0.70139291136049298</v>
+        <v>-0.72624344618937697</v>
       </c>
       <c r="C129">
-        <v>0.76868549403342201</v>
+        <v>0.49232952586495299</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B130">
-        <v>0.59405795467425504</v>
+        <v>-0.73335913503458705</v>
       </c>
       <c r="C130">
-        <v>-0.19523492138912599</v>
+        <v>0.461351878550467</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>306</v>
+        <v>436</v>
       </c>
       <c r="B131">
-        <v>0.49854531531543</v>
+        <v>-1.22991238942991</v>
       </c>
       <c r="C131">
-        <v>-0.14670471245262701</v>
+        <v>-0.98405353778434201</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B132">
-        <v>-0.16022682767501101</v>
+        <v>-1.0999742210651999</v>
       </c>
       <c r="C132">
-        <v>0.37052750356768199</v>
+        <v>-0.200679210627453</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>480</v>
       </c>
       <c r="B133">
-        <v>3.9753606856211703E-2</v>
+        <v>0.90090779060111803</v>
       </c>
       <c r="C133">
-        <v>4.3788325093820003E-2</v>
+        <v>-0.64132176347422598</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>39</v>
+        <v>304</v>
       </c>
       <c r="B134">
-        <v>0.71317315941494797</v>
+        <v>-0.126786852134468</v>
       </c>
       <c r="C134">
-        <v>-0.31242799665572402</v>
+        <v>-0.49216976579239202</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>307</v>
+        <v>437</v>
       </c>
       <c r="B135">
-        <v>-0.342777596084412</v>
+        <v>-1.2526540106389299</v>
       </c>
       <c r="C135">
-        <v>3.8511953128197399E-2</v>
+        <v>-1.0382790805592399</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B136">
-        <v>0.80641224437495895</v>
+        <v>-0.69591338920289703</v>
       </c>
       <c r="C136">
-        <v>-0.44794704931040102</v>
+        <v>0.76683611587881595</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>308</v>
+        <v>164</v>
       </c>
       <c r="B137">
-        <v>-0.40785969930624399</v>
+        <v>0.60204320470821004</v>
       </c>
       <c r="C137">
-        <v>8.94245132007844E-2</v>
+        <v>-0.20243059964670501</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>439</v>
+        <v>305</v>
       </c>
       <c r="B138">
-        <v>-1.1732997408636501</v>
+        <v>0.56132771981454899</v>
       </c>
       <c r="C138">
-        <v>-1.13781581823473</v>
+        <v>-9.1048511961741505E-2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>167</v>
+        <v>481</v>
       </c>
       <c r="B139">
-        <v>-1.3191831844453099</v>
+        <v>-1.4513709198151501</v>
       </c>
       <c r="C139">
-        <v>-0.97141407716019401</v>
+        <v>-0.18581059476582201</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
       <c r="B140">
-        <v>5.3780211077675798E-2</v>
+        <v>2.5478690995699299E-2</v>
       </c>
       <c r="C140">
-        <v>0.62474996279366601</v>
+        <v>0.20795472888017399</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B141">
-        <v>-0.15690945772682799</v>
+        <v>3.5073624859287097E-2</v>
       </c>
       <c r="C141">
-        <v>0.182964604200576</v>
+        <v>4.4403479199987599E-2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B142">
-        <v>-1.25555961177345</v>
+        <v>0.72214900225104794</v>
       </c>
       <c r="C142">
-        <v>-0.73938391897231104</v>
+        <v>-0.294272629706538</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="B143">
-        <v>-0.133796790065044</v>
+        <v>-0.33151743233921499</v>
       </c>
       <c r="C143">
-        <v>0.44099328845387398</v>
+        <v>5.03096224353827E-2</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="B144">
-        <v>-0.244620114727157</v>
+        <v>0.80978508592138698</v>
       </c>
       <c r="C144">
-        <v>0.56559573350071202</v>
+        <v>-0.46315497868949101</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>42</v>
+        <v>307</v>
       </c>
       <c r="B145">
-        <v>-0.86455065696325395</v>
+        <v>-0.397376194549454</v>
       </c>
       <c r="C145">
-        <v>-0.15640657857229801</v>
+        <v>9.982556536494E-2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>169</v>
+        <v>438</v>
       </c>
       <c r="B146">
-        <v>2.33547205693822E-2</v>
+        <v>-1.14886554596409</v>
       </c>
       <c r="C146">
-        <v>-0.94940409848193497</v>
+        <v>-1.1591707869429899</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>261</v>
+        <v>167</v>
       </c>
       <c r="B147">
-        <v>-1.2720330159378901</v>
+        <v>-1.2917463159523499</v>
       </c>
       <c r="C147">
-        <v>-1.02116055366467</v>
+        <v>-1.0049040549808199</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B148">
-        <v>-0.64384149294860504</v>
+        <v>6.8086637691088497E-2</v>
       </c>
       <c r="C148">
-        <v>1.2347080142354501</v>
+        <v>0.63165069800399098</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="B149">
-        <v>-1.2474086028673701</v>
+        <v>-0.13571415136402801</v>
       </c>
       <c r="C149">
-        <v>-1.0837710783088299</v>
+        <v>0.192557476465853</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>440</v>
+        <v>41</v>
       </c>
       <c r="B150">
-        <v>-1.5320308575449799</v>
+        <v>-1.24315138570925</v>
       </c>
       <c r="C150">
-        <v>-0.41287315636678501</v>
+        <v>-0.73519074619975</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>312</v>
+        <v>168</v>
       </c>
       <c r="B151">
-        <v>0.32933336812456598</v>
+        <v>-0.13505493727031001</v>
       </c>
       <c r="C151">
-        <v>-0.18177120287829401</v>
+        <v>0.494129637844889</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>43</v>
+        <v>309</v>
       </c>
       <c r="B152">
-        <v>-0.24108989821419</v>
+        <v>-0.231349201333198</v>
       </c>
       <c r="C152">
-        <v>0.13802024376836899</v>
+        <v>0.57785909395790402</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B153">
-        <v>-0.95835743484823399</v>
+        <v>-0.872421207210621</v>
       </c>
       <c r="C153">
-        <v>0.36207074043044302</v>
+        <v>-0.17355824097525699</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>171</v>
+        <v>482</v>
       </c>
       <c r="B154">
-        <v>-1.3821291525841299</v>
+        <v>0.43390021362555098</v>
       </c>
       <c r="C154">
-        <v>-0.34533086280583702</v>
+        <v>0.40743924059037001</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>441</v>
+        <v>169</v>
       </c>
       <c r="B155">
-        <v>-1.37487606697214</v>
+        <v>3.3156917318441698E-2</v>
       </c>
       <c r="C155">
-        <v>-0.95708614303891604</v>
+        <v>-0.95550907628308701</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>45</v>
+        <v>261</v>
       </c>
       <c r="B156">
-        <v>-0.18111101073559499</v>
+        <v>-1.2477438854479901</v>
       </c>
       <c r="C156">
-        <v>0.53140568356177198</v>
+        <v>-1.04451275220688</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="B157">
-        <v>0.72478826521589201</v>
+        <v>-0.64439594565387504</v>
       </c>
       <c r="C157">
-        <v>-0.32017056614218597</v>
+        <v>1.23431090222143</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B158">
-        <v>-7.8147604524963193E-2</v>
+        <v>-1.2206884646699201</v>
       </c>
       <c r="C158">
-        <v>0.14913490982911801</v>
+        <v>-1.1082961806176601</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B159">
-        <v>-1.0314636506668999</v>
+        <v>-1.50940805932625</v>
       </c>
       <c r="C159">
-        <v>0.89406442552762899</v>
+        <v>-0.48055986232461301</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B160">
-        <v>0.45239119942446299</v>
+        <v>0.336194323672664</v>
       </c>
       <c r="C160">
-        <v>0.547450633621403</v>
+        <v>-0.18012639318625101</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B161">
-        <v>-1.2603353524810199</v>
+        <v>-0.23360997665809899</v>
       </c>
       <c r="C161">
-        <v>-0.43671128713671298</v>
+        <v>0.14547132521602801</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>314</v>
+        <v>44</v>
       </c>
       <c r="B162">
-        <v>8.5562958757728902E-2</v>
+        <v>-1.05600790815164</v>
       </c>
       <c r="C162">
-        <v>-0.26151944313272601</v>
+        <v>7.7257036875912399E-2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="B163">
-        <v>0.101941955176447</v>
+        <v>-1.3661577899279</v>
       </c>
       <c r="C163">
-        <v>-6.1112994036856397E-2</v>
+        <v>-0.366241607546061</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>315</v>
+        <v>440</v>
       </c>
       <c r="B164">
-        <v>-0.25941199517046798</v>
+        <v>-1.3488849765050399</v>
       </c>
       <c r="C164">
-        <v>0.187546669578531</v>
+        <v>-0.98857776281510201</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="B165">
-        <v>-0.91575299007088895</v>
+        <v>-0.16768599858000299</v>
       </c>
       <c r="C165">
-        <v>-0.63441527545523502</v>
+        <v>0.54231858216107498</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>316</v>
+        <v>46</v>
       </c>
       <c r="B166">
-        <v>-0.184398521801176</v>
+        <v>0.72991351042078101</v>
       </c>
       <c r="C166">
-        <v>0.12692386111517201</v>
+        <v>-0.32907592011639802</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>254</v>
+        <v>47</v>
       </c>
       <c r="B167">
-        <v>-0.87142236413552698</v>
+        <v>-8.3288614507372002E-2</v>
       </c>
       <c r="C167">
-        <v>1.31416182461384</v>
+        <v>0.171324532316141</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>50</v>
+        <v>441</v>
       </c>
       <c r="B168">
-        <v>0.42697434583656202</v>
+        <v>-1.0295111469034901</v>
       </c>
       <c r="C168">
-        <v>-6.7417274336162E-2</v>
+        <v>0.88564175601686201</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="B169">
-        <v>-0.139315103840357</v>
+        <v>0.46326861439295602</v>
       </c>
       <c r="C169">
-        <v>0.25025452586760499</v>
+        <v>0.54292784837292696</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>317</v>
+        <v>48</v>
       </c>
       <c r="B170">
-        <v>-0.74934947309977396</v>
+        <v>-1.24483561890476</v>
       </c>
       <c r="C170">
-        <v>1.72495114568604</v>
+        <v>-0.46276671908146699</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>51</v>
+        <v>313</v>
       </c>
       <c r="B171">
-        <v>0.46876475103301302</v>
+        <v>-0.206164298996898</v>
       </c>
       <c r="C171">
-        <v>4.704500142622E-2</v>
+        <v>0.13369077087430201</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>318</v>
+        <v>49</v>
       </c>
       <c r="B172">
-        <v>-8.7932608740044702E-2</v>
+        <v>0.10569391319032199</v>
       </c>
       <c r="C172">
-        <v>0.46003111752171399</v>
+        <v>-6.3050531646964905E-2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>52</v>
+        <v>314</v>
       </c>
       <c r="B173">
-        <v>-1.2270430649594599</v>
+        <v>-0.24939657961224501</v>
       </c>
       <c r="C173">
-        <v>-0.99074415430021201</v>
+        <v>0.201148348822659</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B174">
-        <v>-1.4487892762732599</v>
+        <v>-0.89541438761895598</v>
       </c>
       <c r="C174">
-        <v>-0.40826803090134101</v>
+        <v>-0.64789425869046302</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>53</v>
+        <v>315</v>
       </c>
       <c r="B175">
-        <v>-1.2487455823845299</v>
+        <v>-0.173836808352445</v>
       </c>
       <c r="C175">
-        <v>-0.46915798023278998</v>
+        <v>0.136945843110656</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="B176">
-        <v>-0.51000466349986795</v>
+        <v>-0.86843960054666502</v>
       </c>
       <c r="C176">
-        <v>0.73200590467200399</v>
+        <v>1.30924465926912</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B177">
-        <v>-0.332334661804284</v>
+        <v>0.43105957773173098</v>
       </c>
       <c r="C177">
-        <v>0.293385973862617</v>
+        <v>-7.0977440309975506E-2</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>55</v>
+        <v>483</v>
       </c>
       <c r="B178">
-        <v>0.77877290832843404</v>
+        <v>0.25354475874174498</v>
       </c>
       <c r="C178">
-        <v>-0.39878852144063198</v>
+        <v>0.63092927125175002</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>320</v>
+        <v>173</v>
       </c>
       <c r="B179">
-        <v>-0.61928831838334597</v>
+        <v>-0.14370594449235699</v>
       </c>
       <c r="C179">
-        <v>-0.280788207765028</v>
+        <v>0.26134902199569399</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="B180">
-        <v>-1.2506978225199199</v>
+        <v>-0.76142448459670597</v>
       </c>
       <c r="C180">
-        <v>-1.07946220302894</v>
+        <v>1.71784947378876</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="B181">
-        <v>0.73083113472716299</v>
+        <v>0.489040374864881</v>
       </c>
       <c r="C181">
-        <v>-0.28446015100556898</v>
+        <v>3.15396092023933E-2</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>177</v>
+        <v>484</v>
       </c>
       <c r="B182">
-        <v>-0.210060314244982</v>
+        <v>-1.48833344861127</v>
       </c>
       <c r="C182">
-        <v>0.28849356137192</v>
+        <v>-0.40145608377657399</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B183">
-        <v>-0.18153798017429201</v>
+        <v>-7.5034469308869506E-2</v>
       </c>
       <c r="C183">
-        <v>0.56374048316512904</v>
+        <v>0.469921216698028</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>322</v>
+        <v>485</v>
       </c>
       <c r="B184">
-        <v>0.65104141691957396</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C184">
-        <v>-0.29406741589646801</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B185">
-        <v>-0.92178645186449903</v>
+        <v>-1.2064210451734201</v>
       </c>
       <c r="C185">
-        <v>-0.594749379726774</v>
+        <v>-1.0037918795127201</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>323</v>
+        <v>174</v>
       </c>
       <c r="B186">
-        <v>-0.68951312374961404</v>
+        <v>-1.43152664956541</v>
       </c>
       <c r="C186">
-        <v>-1.0114190318342899</v>
+        <v>-0.432859175192843</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="B187">
-        <v>-1.2189728071858901</v>
+        <v>-1.2484826511062601</v>
       </c>
       <c r="C187">
-        <v>-0.46747423654422599</v>
+        <v>-0.472380827356426</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="B188">
-        <v>-8.2277849497908895E-2</v>
+        <v>-0.50017678503622998</v>
       </c>
       <c r="C188">
-        <v>0.55389389466393302</v>
+        <v>0.73366358430202805</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>180</v>
+        <v>486</v>
       </c>
       <c r="B189">
-        <v>-0.34667579991116398</v>
+        <v>-0.165687371558221</v>
       </c>
       <c r="C189">
-        <v>9.6579494452320502E-2</v>
+        <v>1.68279171965891E-3</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B190">
-        <v>-1.2288043026965001</v>
+        <v>-0.338241517161886</v>
       </c>
       <c r="C190">
-        <v>-0.63851139659641698</v>
+        <v>0.276986261967886</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B191">
-        <v>-0.63074944651143305</v>
+        <v>0.78299587654934699</v>
       </c>
       <c r="C191">
-        <v>0.30246893990111101</v>
+        <v>-0.41352147235810299</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>324</v>
+        <v>487</v>
       </c>
       <c r="B192">
-        <v>-0.70596949512200902</v>
+        <v>0.46296224919875301</v>
       </c>
       <c r="C192">
-        <v>0.61963392103413695</v>
+        <v>0.97015519998512401</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B193">
-        <v>0.40165026458886</v>
+        <v>-0.60368902878839603</v>
       </c>
       <c r="C193">
-        <v>0.38708640206367601</v>
+        <v>-0.28242191030539898</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="B194">
-        <v>0.23363482249748799</v>
+        <v>-1.2257918225051601</v>
       </c>
       <c r="C194">
-        <v>0.20477000939722101</v>
+        <v>-1.10380739530399</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="B195">
-        <v>-0.85116156561942702</v>
+        <v>0.73637790771748501</v>
       </c>
       <c r="C195">
-        <v>0.50113523180437802</v>
+        <v>-0.26868024263950502</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="B196">
-        <v>-1.0553587721037301</v>
+        <v>-0.19926809255858</v>
       </c>
       <c r="C196">
-        <v>-0.51365932091141997</v>
+        <v>0.29874740395733901</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>181</v>
+        <v>320</v>
       </c>
       <c r="B197">
-        <v>-1.0620989344998399</v>
+        <v>-0.16944955808800499</v>
       </c>
       <c r="C197">
-        <v>0.40178484358633298</v>
+        <v>0.57826042587031801</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B198">
-        <v>-0.93375562302727</v>
+        <v>0.70054153930692997</v>
       </c>
       <c r="C198">
-        <v>0.82622308109861897</v>
+        <v>-0.30825049987506098</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>443</v>
+        <v>56</v>
       </c>
       <c r="B199">
-        <v>-0.19512325329934699</v>
+        <v>-0.88015808530447004</v>
       </c>
       <c r="C199">
-        <v>-3.4888346353967101</v>
+        <v>-0.58269924865963796</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B200">
-        <v>-0.22849430982265101</v>
+        <v>-0.71689866719056505</v>
       </c>
       <c r="C200">
-        <v>0.36514926138055298</v>
+        <v>-1.02855825998929</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B201">
-        <v>-6.7783564021317105E-2</v>
+        <v>-1.18068043323422</v>
       </c>
       <c r="C201">
-        <v>1.13991852924285</v>
+        <v>-0.55278472936077805</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>328</v>
+        <v>179</v>
       </c>
       <c r="B202">
-        <v>-0.38732373888036897</v>
+        <v>-6.8894660598682197E-2</v>
       </c>
       <c r="C202">
-        <v>0.37982165038215698</v>
+        <v>0.55969567598870795</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>329</v>
+        <v>180</v>
       </c>
       <c r="B203">
-        <v>0.61221277114704897</v>
+        <v>-0.33047436459323798</v>
       </c>
       <c r="C203">
-        <v>0.45097189488420703</v>
+        <v>0.106801171306853</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B204">
-        <v>-0.28395697515354901</v>
+        <v>-1.21571233021657</v>
       </c>
       <c r="C204">
-        <v>0.16296188214797799</v>
+        <v>-0.628780490006005</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>330</v>
+        <v>58</v>
       </c>
       <c r="B205">
-        <v>-0.14674265028361499</v>
+        <v>-0.65484129689861303</v>
       </c>
       <c r="C205">
-        <v>0.24254398261211699</v>
+        <v>0.26764366225876002</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>444</v>
+        <v>323</v>
       </c>
       <c r="B206">
-        <v>-1.1055117889591599</v>
+        <v>-0.70826508167427005</v>
       </c>
       <c r="C206">
-        <v>-1.1727033581845201</v>
+        <v>0.598327000360248</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="B207">
-        <v>0.256312474546319</v>
+        <v>0.40954930955054197</v>
       </c>
       <c r="C207">
-        <v>-1.0526934980726601</v>
+        <v>0.37843831108158799</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>331</v>
+        <v>59</v>
       </c>
       <c r="B208">
-        <v>-0.155214882925301</v>
+        <v>0.254010504718437</v>
       </c>
       <c r="C208">
-        <v>-1.2868219555432701</v>
+        <v>0.20186876135594001</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="B209">
-        <v>-0.16613059356496901</v>
+        <v>-0.84802420372693899</v>
       </c>
       <c r="C209">
-        <v>0.66018663600787897</v>
+        <v>0.49485853374793898</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B210">
-        <v>1.5111049453334999E-2</v>
+        <v>-1.0412138404970199</v>
       </c>
       <c r="C210">
-        <v>0.32334640436412099</v>
+        <v>-0.50592483902320595</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="B211">
-        <v>-1.20536754503012</v>
+        <v>-1.05475721885561</v>
       </c>
       <c r="C211">
-        <v>-0.88451797923307396</v>
+        <v>0.386542104466089</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>183</v>
+        <v>325</v>
       </c>
       <c r="B212">
-        <v>-0.55772153159319404</v>
+        <v>-0.92941596606577104</v>
       </c>
       <c r="C212">
-        <v>-2.4593225617857901</v>
+        <v>0.81872957529480195</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>65</v>
+        <v>442</v>
       </c>
       <c r="B213">
-        <v>0.69069533601086397</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C213">
-        <v>-0.23590506294240501</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>66</v>
+        <v>326</v>
       </c>
       <c r="B214">
-        <v>0.66775461906790801</v>
+        <v>-0.194320175249309</v>
       </c>
       <c r="C214">
-        <v>-6.6052090860169901E-2</v>
+        <v>0.332126431077994</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B215">
-        <v>0.78975042630660297</v>
+        <v>-5.4654642660057103E-2</v>
       </c>
       <c r="C215">
-        <v>-6.4899588051367696E-2</v>
+        <v>1.1479641031891601</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>67</v>
+        <v>327</v>
       </c>
       <c r="B216">
-        <v>0.16872008417710699</v>
+        <v>-0.13786178573527699</v>
       </c>
       <c r="C216">
-        <v>0.39418654887538901</v>
+        <v>-0.75836416423375597</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>68</v>
+        <v>328</v>
       </c>
       <c r="B217">
-        <v>0.75039884777344501</v>
+        <v>0.38498787037035098</v>
       </c>
       <c r="C217">
-        <v>-0.29171342641528503</v>
+        <v>0.43854764172355398</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B218">
-        <v>-1.2379657447368699</v>
+        <v>-0.27632793199731598</v>
       </c>
       <c r="C218">
-        <v>-1.00821586244627</v>
+        <v>0.15590527430555101</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>333</v>
+        <v>488</v>
       </c>
       <c r="B219">
-        <v>-0.96186950448309005</v>
+        <v>-0.351475253482256</v>
       </c>
       <c r="C219">
-        <v>-4.3279574754208301E-2</v>
+        <v>0.47908894407659502</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>185</v>
+        <v>329</v>
       </c>
       <c r="B220">
-        <v>-1.4157153107928999</v>
+        <v>-0.135575985638059</v>
       </c>
       <c r="C220">
-        <v>-0.14349068086327499</v>
+        <v>0.254894677863441</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>186</v>
+        <v>443</v>
       </c>
       <c r="B221">
-        <v>-1.23762871959968</v>
+        <v>-1.0910362536573499</v>
       </c>
       <c r="C221">
-        <v>-1.1021140238023099</v>
+        <v>-1.1817167896894301</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>334</v>
+        <v>262</v>
       </c>
       <c r="B222">
-        <v>0.64158478245484496</v>
+        <v>0.25653430852946801</v>
       </c>
       <c r="C222">
-        <v>0.95809346413601604</v>
+        <v>-1.05956341109875</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B223">
-        <v>0.64158478245484496</v>
+        <v>-0.146350698302121</v>
       </c>
       <c r="C223">
-        <v>0.95809346413601604</v>
+        <v>-1.2903703868756999</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B224">
-        <v>0.10561922105312201</v>
+        <v>-0.15307768415946399</v>
       </c>
       <c r="C224">
-        <v>0.67077242447853302</v>
+        <v>0.67325783606707301</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>337</v>
+        <v>63</v>
       </c>
       <c r="B225">
-        <v>0.76375156362721497</v>
+        <v>2.9398337169769501E-2</v>
       </c>
       <c r="C225">
-        <v>-0.257876755510551</v>
+        <v>0.33777330332768801</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="B226">
-        <v>0.40016596260697701</v>
+        <v>-1.1939182888616899</v>
       </c>
       <c r="C226">
-        <v>0.11727260120185599</v>
+        <v>-0.89288557071928898</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="B227">
-        <v>0.55499434353345001</v>
+        <v>-0.54175080062314496</v>
       </c>
       <c r="C227">
-        <v>-9.6620796871301595E-2</v>
+        <v>-2.3400779794723201</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>338</v>
+        <v>65</v>
       </c>
       <c r="B228">
-        <v>0.65230592753917405</v>
+        <v>0.695802890830994</v>
       </c>
       <c r="C228">
-        <v>-0.32121495524289501</v>
+        <v>-0.24493894252561399</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B229">
-        <v>-0.15760802634864701</v>
+        <v>0.67598094030659295</v>
       </c>
       <c r="C229">
-        <v>0.158861849130113</v>
+        <v>-6.2378575381187303E-2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B230">
-        <v>-0.47995657563004401</v>
+        <v>0.80064750294994202</v>
       </c>
       <c r="C230">
-        <v>2.52649076361189E-3</v>
+        <v>-7.6864794755077001E-2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>445</v>
+        <v>67</v>
       </c>
       <c r="B231">
-        <v>-0.33514678746911197</v>
+        <v>0.18114685310803499</v>
       </c>
       <c r="C231">
-        <v>-3.1647064835673699</v>
+        <v>0.39267211321338802</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>339</v>
+        <v>489</v>
       </c>
       <c r="B232">
-        <v>1.0391118733979401</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C232">
-        <v>-0.66071161612615703</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="B233">
-        <v>-0.45077200895361202</v>
+        <v>0.75351632326393703</v>
       </c>
       <c r="C233">
-        <v>1.0514987201024399</v>
+        <v>-0.29902121559053002</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>446</v>
+        <v>69</v>
       </c>
       <c r="B234">
-        <v>-0.52747909151488204</v>
+        <v>-1.21360895379207</v>
       </c>
       <c r="C234">
-        <v>-2.6839762831576999</v>
+        <v>-1.0291375886643499</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>189</v>
+        <v>332</v>
       </c>
       <c r="B235">
-        <v>0.21611143226828</v>
+        <v>-0.947196858520026</v>
       </c>
       <c r="C235">
-        <v>0.48708748672267699</v>
+        <v>-4.8221718231648697E-2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>341</v>
+        <v>185</v>
       </c>
       <c r="B236">
-        <v>0.72689047193449297</v>
+        <v>-1.40157812779399</v>
       </c>
       <c r="C236">
-        <v>-0.214571450707745</v>
+        <v>-0.16157780431573199</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>447</v>
+        <v>186</v>
       </c>
       <c r="B237">
-        <v>-1.2539308784491101</v>
+        <v>-1.2120510052807401</v>
       </c>
       <c r="C237">
-        <v>-1.33483952448302</v>
+        <v>-1.1269772953572801</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>448</v>
+        <v>333</v>
       </c>
       <c r="B238">
-        <v>-0.19512325329934699</v>
+        <v>0.65728264977696804</v>
       </c>
       <c r="C238">
-        <v>-3.4888346353967101</v>
+        <v>0.95577650776746004</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B239">
-        <v>-0.356059603318161</v>
+        <v>0.65728264977696804</v>
       </c>
       <c r="C239">
-        <v>0.55105661535560202</v>
+        <v>0.95577650776746004</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>190</v>
+        <v>335</v>
       </c>
       <c r="B240">
-        <v>-0.210465937697637</v>
+        <v>0.11736641046950599</v>
       </c>
       <c r="C240">
-        <v>-2.0109932762010101E-2</v>
+        <v>0.67697661652671504</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>449</v>
+        <v>336</v>
       </c>
       <c r="B241">
-        <v>-1.21066724247278</v>
+        <v>0.76136836892925197</v>
       </c>
       <c r="C241">
-        <v>-0.45539607395196502</v>
+        <v>-0.31393731807347602</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>450</v>
+        <v>187</v>
       </c>
       <c r="B242">
-        <v>-0.19512325329934699</v>
+        <v>0.41084609114779702</v>
       </c>
       <c r="C242">
-        <v>-3.4888346353967101</v>
+        <v>0.117797568262123</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="B243">
-        <v>0.75143577100923498</v>
+        <v>0.56391774265230199</v>
       </c>
       <c r="C243">
-        <v>-0.31091914385368202</v>
+        <v>-0.102734814105128</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>451</v>
+        <v>337</v>
       </c>
       <c r="B244">
-        <v>-1.3023855142798699</v>
+        <v>0.67586559846391703</v>
       </c>
       <c r="C244">
-        <v>-1.0042707367702399</v>
+        <v>-0.35077558524956198</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>343</v>
+        <v>71</v>
       </c>
       <c r="B245">
-        <v>-0.71809365947187398</v>
+        <v>-0.150110003212028</v>
       </c>
       <c r="C245">
-        <v>1.4619094527876599</v>
+        <v>0.16303572100737199</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="B246">
-        <v>0.256312474546319</v>
+        <v>-0.46726144940756198</v>
       </c>
       <c r="C246">
-        <v>-1.0526934980726601</v>
+        <v>6.3934647548618403E-3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>192</v>
+        <v>444</v>
       </c>
       <c r="B247">
-        <v>-1.2332851061632499</v>
+        <v>-0.31446406256695503</v>
       </c>
       <c r="C247">
-        <v>-2.12291350224257E-2</v>
+        <v>-2.9971518074221501</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B248">
-        <v>-0.260037973673724</v>
+        <v>1.0386187559198601</v>
       </c>
       <c r="C248">
-        <v>0.679095725487038</v>
+        <v>-0.68229078538077204</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>193</v>
+        <v>339</v>
       </c>
       <c r="B249">
-        <v>-1.20276012407399</v>
+        <v>-0.44441307257498702</v>
       </c>
       <c r="C249">
-        <v>-0.43533597426425003</v>
+        <v>1.05404034726938</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>72</v>
+        <v>445</v>
       </c>
       <c r="B250">
-        <v>-1.35858258478822</v>
+        <v>-0.50688429103620702</v>
       </c>
       <c r="C250">
-        <v>-0.15925425807947899</v>
+        <v>-2.54818622199112</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="B251">
-        <v>-1.23107756596245</v>
+        <v>0.28648699231966601</v>
       </c>
       <c r="C251">
-        <v>0.22528275608078199</v>
+        <v>0.61619258644233099</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B252">
-        <v>-0.32749300983102198</v>
+        <v>0.73507909212601796</v>
       </c>
       <c r="C252">
-        <v>-0.17593138093465399</v>
+        <v>-0.223898024384724</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>74</v>
+        <v>446</v>
       </c>
       <c r="B253">
-        <v>-1.07043372709166</v>
+        <v>-1.22836553429186</v>
       </c>
       <c r="C253">
-        <v>-0.87395991245693805</v>
+        <v>-1.3557637777365501</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>194</v>
+        <v>447</v>
       </c>
       <c r="B254">
-        <v>-0.81619025024893099</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C254">
-        <v>0.43123748396505102</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
       <c r="B255">
-        <v>0.23046394200081699</v>
+        <v>-0.34277784050551902</v>
       </c>
       <c r="C255">
-        <v>0.34994930305752597</v>
+        <v>0.56486135724178899</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>346</v>
+        <v>190</v>
       </c>
       <c r="B256">
-        <v>-7.3636924302094606E-2</v>
+        <v>-0.26789431907932398</v>
       </c>
       <c r="C256">
-        <v>0.824638892898646</v>
+        <v>0.12815946574847001</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>76</v>
+        <v>448</v>
       </c>
       <c r="B257">
-        <v>0.429365333236086</v>
+        <v>-1.1961526922897401</v>
       </c>
       <c r="C257">
-        <v>-1.8697924962483001E-2</v>
+        <v>-0.47065464544583502</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>347</v>
+        <v>449</v>
       </c>
       <c r="B258">
-        <v>-0.28243219814086701</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C258">
-        <v>0.117584936868007</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B259">
-        <v>-0.40030381855849001</v>
+        <v>0.74363614561847502</v>
       </c>
       <c r="C259">
-        <v>0.73783010812860905</v>
+        <v>-0.31743362628854099</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>348</v>
+        <v>450</v>
       </c>
       <c r="B260">
-        <v>0.16157948964225</v>
+        <v>-1.27529456334631</v>
       </c>
       <c r="C260">
-        <v>-0.44853372103529598</v>
+        <v>-1.0310096670103199</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="B261">
-        <v>-1.18733669027856</v>
+        <v>-0.72303247220491795</v>
       </c>
       <c r="C261">
-        <v>-0.66136064412834705</v>
+        <v>1.45640063611375</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>452</v>
+        <v>263</v>
       </c>
       <c r="B262">
-        <v>-1.22718779844128</v>
+        <v>0.25653430852946801</v>
       </c>
       <c r="C262">
-        <v>-0.99104608852661302</v>
+        <v>-1.05956341109875</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>349</v>
+        <v>192</v>
       </c>
       <c r="B263">
-        <v>-0.26347918152772798</v>
+        <v>-1.2290421719559701</v>
       </c>
       <c r="C263">
-        <v>0.16559820104314099</v>
+        <v>-0.19388065790819201</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B264">
-        <v>-0.71866759801472802</v>
+        <v>-0.25087032061103598</v>
       </c>
       <c r="C264">
-        <v>0.75937201459012404</v>
+        <v>0.68775640721354203</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B265">
-        <v>-1.3306709650327699</v>
+        <v>-1.20025329289149</v>
       </c>
       <c r="C265">
-        <v>-0.77566638591194403</v>
+        <v>-0.46982732153934298</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>197</v>
+        <v>490</v>
       </c>
       <c r="B266">
-        <v>-1.89664993794516E-2</v>
+        <v>-0.12685983240107601</v>
       </c>
       <c r="C266">
-        <v>0.42046248280528098</v>
+        <v>-0.13136664428432299</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>264</v>
+        <v>72</v>
       </c>
       <c r="B267">
-        <v>-4.6412892106198499E-2</v>
+        <v>-1.3750130406774801</v>
       </c>
       <c r="C267">
-        <v>-1.18699447531945E-2</v>
+        <v>-0.17127172677080299</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="B268">
-        <v>-0.51091475720171597</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C268">
-        <v>1.13960419760474</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B269">
-        <v>-0.26146515019995198</v>
+        <v>-1.2411480439101701</v>
       </c>
       <c r="C269">
-        <v>0.41744359244475399</v>
+        <v>0.18445795959512601</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>79</v>
+        <v>492</v>
       </c>
       <c r="B270">
-        <v>0.707257569474394</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C270">
-        <v>-0.223009002660147</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="B271">
-        <v>-0.28607603211252702</v>
+        <v>-0.319463830589439</v>
       </c>
       <c r="C271">
-        <v>0.34524225712269802</v>
+        <v>-0.16233776724848101</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="B272">
-        <v>-0.31116294886243301</v>
+        <v>-1.0246231121615601</v>
       </c>
       <c r="C272">
-        <v>0.65022715605561199</v>
+        <v>-0.88382128463568999</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>352</v>
+        <v>194</v>
       </c>
       <c r="B273">
-        <v>0.79626433507361605</v>
+        <v>-0.84766553565806502</v>
       </c>
       <c r="C273">
-        <v>-0.50531979645490099</v>
+        <v>0.502504405171736</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="B274">
-        <v>0.85260714597873499</v>
+        <v>0.25180081408667998</v>
       </c>
       <c r="C274">
-        <v>-0.13355855513214801</v>
+        <v>0.36880625856174198</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B275">
-        <v>-0.155214882925301</v>
+        <v>-6.1406214562418203E-2</v>
       </c>
       <c r="C275">
-        <v>-1.2868219555432701</v>
+        <v>0.833804247213491</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B276">
-        <v>0.33731940554567502</v>
+        <v>0.44047395455656801</v>
       </c>
       <c r="C276">
-        <v>-0.25253946249049902</v>
+        <v>-2.3263905406719E-2</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="B277">
-        <v>-1.0869688580553201</v>
+        <v>-0.27273234440545202</v>
       </c>
       <c r="C277">
-        <v>0.165280004617257</v>
+        <v>0.12786405657438599</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="B278">
-        <v>-7.1910867179791902E-3</v>
+        <v>-0.38519639234955899</v>
       </c>
       <c r="C278">
-        <v>2.02458453298594E-3</v>
+        <v>0.754538875084654</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B279">
-        <v>-0.13081846899220201</v>
+        <v>0.167035512573803</v>
       </c>
       <c r="C279">
-        <v>1.42615566092048</v>
+        <v>-0.43829453796409101</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="B280">
-        <v>-0.32870154617515501</v>
+        <v>-1.1712406352763201</v>
       </c>
       <c r="C280">
-        <v>0.22961230200602101</v>
+        <v>-0.65794872682411198</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>201</v>
+        <v>451</v>
       </c>
       <c r="B281">
-        <v>-0.19562935640006099</v>
+        <v>-1.20680043818597</v>
       </c>
       <c r="C281">
-        <v>0.32851846935983198</v>
+        <v>-1.0081832653784299</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>453</v>
+        <v>348</v>
       </c>
       <c r="B282">
-        <v>-1.2539308784491101</v>
+        <v>-0.25396984614856999</v>
       </c>
       <c r="C282">
-        <v>-1.33483952448302</v>
+        <v>0.17415371902773799</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B283">
-        <v>-0.16802514434159399</v>
+        <v>-0.72157855965389595</v>
       </c>
       <c r="C283">
-        <v>0.29293481293247597</v>
+        <v>0.73844369000396604</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>454</v>
+        <v>196</v>
       </c>
       <c r="B284">
-        <v>-1.2539308784491101</v>
+        <v>-1.31355272361995</v>
       </c>
       <c r="C284">
-        <v>-1.33483952448302</v>
+        <v>-0.79623041894783497</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>357</v>
+        <v>197</v>
       </c>
       <c r="B285">
-        <v>0.74154029819910205</v>
+        <v>-4.2034142329046398E-2</v>
       </c>
       <c r="C285">
-        <v>-0.4375614516088</v>
+        <v>0.48901584128389097</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="B286">
-        <v>-7.82582434594815E-2</v>
+        <v>-3.5464473835693698E-2</v>
       </c>
       <c r="C286">
-        <v>0.44158257693729103</v>
+        <v>8.9358690389052305E-3</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>203</v>
+        <v>350</v>
       </c>
       <c r="B287">
-        <v>-1.22908994745266</v>
+        <v>-0.50359547628229195</v>
       </c>
       <c r="C287">
-        <v>-0.95147836587585599</v>
+        <v>1.1446597085310799</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B288">
-        <v>-0.66772933037022497</v>
+        <v>-0.24427402672925999</v>
       </c>
       <c r="C288">
-        <v>2.6761609557331902E-2</v>
+        <v>0.42478152768675798</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="B289">
-        <v>-1.2160896965005501</v>
+        <v>0.72135908680101701</v>
       </c>
       <c r="C289">
-        <v>-1.0331610150733499</v>
+        <v>-0.25709992305472901</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>358</v>
+        <v>198</v>
       </c>
       <c r="B290">
-        <v>-0.78927980863648195</v>
+        <v>-0.24295898060910001</v>
       </c>
       <c r="C290">
-        <v>0.88466852164298804</v>
+        <v>0.36431432156583099</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B291">
-        <v>-1.46159095885803</v>
+        <v>-0.248204154836628</v>
       </c>
       <c r="C291">
-        <v>-0.39887823569449998</v>
+        <v>0.61075594013302603</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>205</v>
+        <v>351</v>
       </c>
       <c r="B292">
-        <v>0.831125062983187</v>
+        <v>0.63334896986652101</v>
       </c>
       <c r="C292">
-        <v>0.38548441526160399</v>
+        <v>-0.22290961621788999</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B293">
-        <v>-0.94321948274366096</v>
+        <v>0.76160310138617304</v>
       </c>
       <c r="C293">
-        <v>-0.39452085121602598</v>
+        <v>-5.4627230973792601E-2</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="B294">
-        <v>-1.2761491966595699</v>
+        <v>-0.146350698302121</v>
       </c>
       <c r="C294">
-        <v>-0.30411463067710598</v>
+        <v>-1.2903703868756999</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="B295">
-        <v>-1.1639224593014099</v>
+        <v>0.35298605903893299</v>
       </c>
       <c r="C295">
-        <v>-1.0955399023482799</v>
+        <v>-0.219654579536677</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B296">
-        <v>-0.533336667851665</v>
+        <v>-1.09910989015169</v>
       </c>
       <c r="C296">
-        <v>0.170022579929552</v>
+        <v>0.13770865344556199</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>359</v>
+        <v>493</v>
       </c>
       <c r="B297">
-        <v>-0.115540096582488</v>
+        <v>-0.50094131567671296</v>
       </c>
       <c r="C297">
-        <v>-0.39872014844890302</v>
+        <v>-0.38147877080658799</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="B298">
-        <v>-0.17522829953879299</v>
+        <v>-7.0752211454431701E-3</v>
       </c>
       <c r="C298">
-        <v>0.37098847198485002</v>
+        <v>2.2421048649931201E-3</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B299">
-        <v>-0.42302658669365201</v>
+        <v>-0.13686783899733901</v>
       </c>
       <c r="C299">
-        <v>1.0079504495354901</v>
+        <v>1.4155227426019801</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>456</v>
+        <v>354</v>
       </c>
       <c r="B300">
-        <v>-0.79565242430759497</v>
+        <v>-0.31809988449582299</v>
       </c>
       <c r="C300">
-        <v>-1.8463545157418899</v>
+        <v>0.25093052964953499</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>361</v>
+        <v>201</v>
       </c>
       <c r="B301">
-        <v>-0.11220227128243</v>
+        <v>-0.25650095368083597</v>
       </c>
       <c r="C301">
-        <v>0.44711562639137398</v>
+        <v>0.38128057643586399</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B302">
-        <v>-0.95585850958577201</v>
+        <v>-1.22836553429186</v>
       </c>
       <c r="C302">
-        <v>-1.34840294459513</v>
+        <v>-1.3557637777365501</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>209</v>
+        <v>355</v>
       </c>
       <c r="B303">
-        <v>0.26337548993138798</v>
+        <v>-0.155531428296869</v>
       </c>
       <c r="C303">
-        <v>0.30977668712472001</v>
+        <v>0.30566915032373398</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>210</v>
+        <v>453</v>
       </c>
       <c r="B304">
-        <v>-1.24862275464882</v>
+        <v>-1.22836553429186</v>
       </c>
       <c r="C304">
-        <v>-0.98341171460677601</v>
+        <v>-1.3557637777365501</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B305">
-        <v>0.77355166882954196</v>
+        <v>0.74456623906484198</v>
       </c>
       <c r="C305">
-        <v>-0.46902511097455701</v>
+        <v>-0.45215614188081499</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>363</v>
+        <v>202</v>
       </c>
       <c r="B306">
-        <v>-0.79884597209378905</v>
+        <v>-6.6213872664099699E-2</v>
       </c>
       <c r="C306">
-        <v>1.50480232203442</v>
+        <v>0.45043389690552899</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>458</v>
+        <v>203</v>
       </c>
       <c r="B307">
-        <v>-1.2023916002974899</v>
+        <v>-1.20353844484466</v>
       </c>
       <c r="C307">
-        <v>-1.12725971639051</v>
+        <v>-0.97613687180805797</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B308">
-        <v>-0.41357439706854598</v>
+        <v>-0.66166024983593996</v>
       </c>
       <c r="C308">
-        <v>0.210154362684257</v>
+        <v>2.40224814656942E-2</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>87</v>
+        <v>454</v>
       </c>
       <c r="B309">
-        <v>-1.1987561984828801</v>
+        <v>-1.19643596247258</v>
       </c>
       <c r="C309">
-        <v>-5.1069512042124697E-2</v>
+        <v>-1.04923080496231</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>459</v>
+        <v>357</v>
       </c>
       <c r="B310">
-        <v>-1.2542470310284199</v>
+        <v>-0.54144951350799397</v>
       </c>
       <c r="C310">
-        <v>-0.96524216970058696</v>
+        <v>0.64287563803121495</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>460</v>
+        <v>204</v>
       </c>
       <c r="B311">
-        <v>-1.10182067403623</v>
+        <v>-1.44438754523605</v>
       </c>
       <c r="C311">
-        <v>-1.7463874601095299</v>
+        <v>-0.42369498965631702</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="B312">
-        <v>0.71218119896778798</v>
+        <v>0.84619202463257803</v>
       </c>
       <c r="C312">
-        <v>-0.298291742801719</v>
+        <v>0.36607527564793801</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="B313">
-        <v>0.394028558789148</v>
+        <v>-0.92924785528529696</v>
       </c>
       <c r="C313">
-        <v>-0.18206654015948401</v>
+        <v>-0.40409548216146501</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="B314">
-        <v>-1.09194234071414</v>
+        <v>-1.2681906202692901</v>
       </c>
       <c r="C314">
-        <v>-1.00837816964863</v>
+        <v>-0.32615128621593198</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>266</v>
+        <v>207</v>
       </c>
       <c r="B315">
-        <v>-1.4147491512567201</v>
+        <v>-1.1403261116560699</v>
       </c>
       <c r="C315">
-        <v>-1.09654718812186</v>
+        <v>-1.11431565506278</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>212</v>
+        <v>85</v>
       </c>
       <c r="B316">
-        <v>-0.34796230574528603</v>
+        <v>-0.52388777552493904</v>
       </c>
       <c r="C316">
-        <v>1.15321322262177</v>
+        <v>0.17088962269365501</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>89</v>
+        <v>358</v>
       </c>
       <c r="B317">
-        <v>-0.29575889482628098</v>
+        <v>5.3258963165876201E-2</v>
       </c>
       <c r="C317">
-        <v>0.17400458414584799</v>
+        <v>0.41112585784292499</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>364</v>
+        <v>208</v>
       </c>
       <c r="B318">
-        <v>-8.8515922437792695E-3</v>
+        <v>-0.16176833637542801</v>
       </c>
       <c r="C318">
-        <v>0.28956049449462401</v>
+        <v>0.38475755395879302</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>90</v>
+        <v>359</v>
       </c>
       <c r="B319">
-        <v>-1.23973913910186</v>
+        <v>-0.41640217168689198</v>
       </c>
       <c r="C319">
-        <v>-1.0031321977435299</v>
+        <v>1.0093010730291401</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>213</v>
+        <v>455</v>
       </c>
       <c r="B320">
-        <v>-0.25603936325558901</v>
+        <v>-0.783981804683613</v>
       </c>
       <c r="C320">
-        <v>0.29480304937579799</v>
+        <v>-1.76812904260202</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B321">
-        <v>-0.31300926842729798</v>
+        <v>-9.9479815344425196E-2</v>
       </c>
       <c r="C321">
-        <v>0.13601348940101801</v>
+        <v>0.45755072394726798</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>366</v>
+        <v>456</v>
       </c>
       <c r="B322">
-        <v>-3.2962209702295901E-2</v>
+        <v>-0.95249791295719799</v>
       </c>
       <c r="C322">
-        <v>0.27496679855094303</v>
+        <v>-1.3241474280490899</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>367</v>
+        <v>209</v>
       </c>
       <c r="B323">
-        <v>-7.3636924302094606E-2</v>
+        <v>0.24910978209493501</v>
       </c>
       <c r="C323">
-        <v>0.824638892898646</v>
+        <v>0.32466478682517902</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="B324">
-        <v>0.68823845444435205</v>
+        <v>-1.22482851977549</v>
       </c>
       <c r="C324">
-        <v>-0.20320058327450499</v>
+        <v>-1.0036334267717999</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>214</v>
+        <v>361</v>
       </c>
       <c r="B325">
-        <v>0.165407535448379</v>
+        <v>0.77828576453740905</v>
       </c>
       <c r="C325">
-        <v>0.48865041198772702</v>
+        <v>-0.48139816108945399</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>461</v>
+        <v>362</v>
       </c>
       <c r="B326">
-        <v>-1.2884272949892599</v>
+        <v>-0.79511482092131502</v>
       </c>
       <c r="C326">
-        <v>-1.03735453434353</v>
+        <v>1.5017454534133601</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>215</v>
+        <v>457</v>
       </c>
       <c r="B327">
-        <v>-0.202935312049769</v>
+        <v>-1.1785022250872299</v>
       </c>
       <c r="C327">
-        <v>0.45491031134433502</v>
+        <v>-1.1459003247194901</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B328">
-        <v>-1.1803448960840299</v>
+        <v>-0.42316443975884699</v>
       </c>
       <c r="C328">
-        <v>-0.92293644391627006</v>
+        <v>0.210210615966335</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B329">
-        <v>-5.3944084952574002E-2</v>
+        <v>-1.19902808635165</v>
       </c>
       <c r="C329">
-        <v>1.4388429042721401E-2</v>
+        <v>-9.6424069016281602E-2</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>94</v>
+        <v>458</v>
       </c>
       <c r="B330">
-        <v>0.68371575733902601</v>
+        <v>-1.2271149208002801</v>
       </c>
       <c r="C330">
-        <v>-0.239521620021869</v>
+        <v>-0.990387966707162</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>216</v>
+        <v>459</v>
       </c>
       <c r="B331">
-        <v>0.41996530563046103</v>
+        <v>-1.07610632062936</v>
       </c>
       <c r="C331">
-        <v>-0.32006389378551198</v>
+        <v>-1.7628865193313401</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>368</v>
+        <v>88</v>
       </c>
       <c r="B332">
-        <v>0.68784937979457705</v>
+        <v>0.71614108122137199</v>
       </c>
       <c r="C332">
-        <v>-0.13021659518319501</v>
+        <v>-0.30949451870920203</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>95</v>
+        <v>265</v>
       </c>
       <c r="B333">
-        <v>-1.34627874966943</v>
+        <v>0.40073587624843698</v>
       </c>
       <c r="C333">
-        <v>-0.50880144063673005</v>
+        <v>-0.187716801136463</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>369</v>
+        <v>211</v>
       </c>
       <c r="B334">
-        <v>-0.81637411092883505</v>
+        <v>-1.07440836960386</v>
       </c>
       <c r="C334">
-        <v>0.66205271277726097</v>
+        <v>-1.0237564053191801</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="B335">
-        <v>-1.23735399394635</v>
+        <v>-1.36673711028038</v>
       </c>
       <c r="C335">
-        <v>-1.0015351167539801</v>
+        <v>-1.15851661567669</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="B336">
-        <v>-0.45742208318226302</v>
+        <v>-0.347280133202856</v>
       </c>
       <c r="C336">
-        <v>7.54937212725003E-2</v>
+        <v>1.14882550907212</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B337">
-        <v>-1.23414657419139</v>
+        <v>-0.29351441022927899</v>
       </c>
       <c r="C337">
-        <v>-1.0426794892553399</v>
+        <v>0.17795875304907499</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B338">
-        <v>0.79727338463650699</v>
+        <v>4.2945616665017996E-3</v>
       </c>
       <c r="C338">
-        <v>0.36692347188115898</v>
+        <v>0.29790121310804402</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="B339">
-        <v>0.114646249569758</v>
+        <v>-1.21807978924438</v>
       </c>
       <c r="C339">
-        <v>0.48723299465195002</v>
+        <v>-1.0176526178159799</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>99</v>
+        <v>213</v>
       </c>
       <c r="B340">
-        <v>-0.81288037864257301</v>
+        <v>-0.229302954700636</v>
       </c>
       <c r="C340">
-        <v>0.29926302530050702</v>
+        <v>0.27477673474797498</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>218</v>
+        <v>364</v>
       </c>
       <c r="B341">
-        <v>-0.81134901445403795</v>
+        <v>-0.30250704475277201</v>
       </c>
       <c r="C341">
-        <v>0.42723560807852401</v>
+        <v>0.23289134014021901</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B342">
-        <v>-0.82837379638042397</v>
+        <v>-2.0833940576044201E-2</v>
       </c>
       <c r="C342">
-        <v>1.42200956598391</v>
+        <v>0.28170041190530998</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B343">
-        <v>0.36100933693050302</v>
+        <v>-6.1406214562418203E-2</v>
       </c>
       <c r="C343">
-        <v>1.0000543974074501</v>
+        <v>0.833804247213491</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>373</v>
+        <v>91</v>
       </c>
       <c r="B344">
-        <v>-0.45077200895361202</v>
+        <v>0.69256370018948399</v>
       </c>
       <c r="C344">
-        <v>1.0514987201024399</v>
+        <v>-0.20733092637737299</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>219</v>
+        <v>494</v>
       </c>
       <c r="B345">
-        <v>-0.22401571415872701</v>
+        <v>0.74799697172174895</v>
       </c>
       <c r="C345">
-        <v>0.20183372001393701</v>
+        <v>0.21757774066132701</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>374</v>
+        <v>214</v>
       </c>
       <c r="B346">
-        <v>0.42602368572473298</v>
+        <v>0.24332192771569899</v>
       </c>
       <c r="C346">
-        <v>0.41218017302536197</v>
+        <v>0.61637505692442096</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>375</v>
+        <v>460</v>
       </c>
       <c r="B347">
-        <v>-0.38065065134174603</v>
+        <v>-1.2609965728763299</v>
       </c>
       <c r="C347">
-        <v>0.49803260578397301</v>
+        <v>-1.06327021399176</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B348">
-        <v>-1.3047813910922601</v>
+        <v>-0.19005217858863499</v>
       </c>
       <c r="C348">
-        <v>-0.71467265089355503</v>
+        <v>0.46764761216244899</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>462</v>
+        <v>92</v>
       </c>
       <c r="B349">
-        <v>-0.19512325329934699</v>
+        <v>-1.1665506967752</v>
       </c>
       <c r="C349">
-        <v>-3.4888346353967101</v>
+        <v>-0.93263891912715302</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>463</v>
+        <v>93</v>
       </c>
       <c r="B350">
-        <v>-1.27077338336565</v>
+        <v>-5.4101352587657699E-2</v>
       </c>
       <c r="C350">
-        <v>-0.76116732760547301</v>
+        <v>1.49337801048713E-2</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B351">
-        <v>0.66453730973284497</v>
+        <v>0.69362676766285802</v>
       </c>
       <c r="C351">
-        <v>-0.24615732098293799</v>
+        <v>-0.24513223422008901</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>464</v>
+        <v>216</v>
       </c>
       <c r="B352">
-        <v>-0.98305584518863498</v>
+        <v>0.42821341338910202</v>
       </c>
       <c r="C352">
-        <v>-1.44742070055524</v>
+        <v>-0.33208590524743298</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B353">
-        <v>-0.85446259608675301</v>
+        <v>0.70482763423804995</v>
       </c>
       <c r="C353">
-        <v>1.52720460154726</v>
+        <v>-0.115429485252111</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B354">
-        <v>0.21855650531335299</v>
+        <v>-1.3360278503760299</v>
       </c>
       <c r="C354">
-        <v>0.318868171586843</v>
+        <v>-0.520578071436122</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>465</v>
+        <v>368</v>
       </c>
       <c r="B355">
-        <v>-1.10182067403623</v>
+        <v>-0.812557223121948</v>
       </c>
       <c r="C355">
-        <v>-1.7463874601095299</v>
+        <v>0.65106574712264298</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>466</v>
+        <v>96</v>
       </c>
       <c r="B356">
-        <v>-0.19512325329934699</v>
+        <v>-1.21504279654104</v>
       </c>
       <c r="C356">
-        <v>-3.4888346353967101</v>
+        <v>-1.01847101610324</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B357">
-        <v>0.73164516309252103</v>
+        <v>-0.45433294469072799</v>
       </c>
       <c r="C357">
-        <v>-0.38408584692445102</v>
+        <v>7.8445497526666103E-2</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B358">
-        <v>-0.14278435386907201</v>
+        <v>-1.20897318008264</v>
       </c>
       <c r="C358">
-        <v>0.35201383856285501</v>
+        <v>-1.06456372889752</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B359">
-        <v>-0.260037973673724</v>
+        <v>0.81113243976517602</v>
       </c>
       <c r="C359">
-        <v>0.679095725487038</v>
+        <v>0.35160728836099298</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B360">
-        <v>-0.220354883374584</v>
+        <v>0.13757667481747499</v>
       </c>
       <c r="C360">
-        <v>0.69625881350688901</v>
+        <v>0.50030434682166902</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B361">
-        <v>-1.2342027406179601</v>
+        <v>-0.81638999481839603</v>
       </c>
       <c r="C361">
-        <v>-1.0311984312750999</v>
+        <v>0.27164284035487202</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="B362">
-        <v>-0.13516798906885399</v>
+        <v>-0.80008956433128797</v>
       </c>
       <c r="C362">
-        <v>4.0343127447336202E-2</v>
+        <v>0.42437535514939401</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>106</v>
+        <v>370</v>
       </c>
       <c r="B363">
-        <v>-0.47892552121870602</v>
+        <v>-0.82306049641585499</v>
       </c>
       <c r="C363">
-        <v>5.6215773960175401E-2</v>
+        <v>1.41921421078406</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>107</v>
+        <v>371</v>
       </c>
       <c r="B364">
-        <v>0.211229670015357</v>
+        <v>0.37880798185527997</v>
       </c>
       <c r="C364">
-        <v>0.18232881574944601</v>
+        <v>1.00379538672975</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>222</v>
+        <v>372</v>
       </c>
       <c r="B365">
-        <v>-0.20033067997929799</v>
+        <v>-0.44441307257498702</v>
       </c>
       <c r="C365">
-        <v>0.498021751956159</v>
+        <v>1.05404034726938</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>378</v>
+        <v>219</v>
       </c>
       <c r="B366">
-        <v>-9.1496558999631106E-2</v>
+        <v>3.4502813289062598E-3</v>
       </c>
       <c r="C366">
-        <v>0.52848009310005095</v>
+        <v>2.6478836821238302E-2</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B367">
-        <v>-0.52340297603588104</v>
+        <v>0.50817524912543</v>
       </c>
       <c r="C367">
-        <v>1.5978216301468999</v>
+        <v>0.37372797150032699</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="B368">
-        <v>-0.37490595348515499</v>
+        <v>-0.370424501253862</v>
       </c>
       <c r="C368">
-        <v>0.42687438170754999</v>
+        <v>0.50643185755280995</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="B369">
-        <v>-1.26285218146802</v>
+        <v>-1.2637484588919199</v>
       </c>
       <c r="C369">
-        <v>-0.98576081191439302</v>
+        <v>-0.73306054772240703</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="B370">
-        <v>0.80540938264898398</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C370">
-        <v>-0.29894309007171899</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>224</v>
+        <v>462</v>
       </c>
       <c r="B371">
-        <v>-0.86789144559450204</v>
+        <v>-1.2529764984085401</v>
       </c>
       <c r="C371">
-        <v>-0.480015666489718</v>
+        <v>-0.77944027164262997</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="B372">
-        <v>-1.4920756190011699</v>
+        <v>0.670417433516313</v>
       </c>
       <c r="C372">
-        <v>0.17687658590541999</v>
+        <v>-0.25563913334508198</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>226</v>
+        <v>463</v>
       </c>
       <c r="B373">
-        <v>0.560644848572731</v>
+        <v>-0.96706839781767995</v>
       </c>
       <c r="C373">
-        <v>-0.211333273092846</v>
+        <v>-1.4525275091761101</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B374">
-        <v>-0.52042411588749304</v>
+        <v>-0.84951188449488901</v>
       </c>
       <c r="C374">
-        <v>0.97913454283720402</v>
+        <v>1.5232789744197299</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>381</v>
+        <v>101</v>
       </c>
       <c r="B375">
-        <v>-0.45227559019121599</v>
+        <v>0.24698237734773901</v>
       </c>
       <c r="C375">
-        <v>0.79963510115532799</v>
+        <v>0.37713233884457698</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>255</v>
+        <v>464</v>
       </c>
       <c r="B376">
-        <v>-0.83331777438162502</v>
+        <v>-1.07610632062936</v>
       </c>
       <c r="C376">
-        <v>0.315567138365341</v>
+        <v>-1.7628865193313401</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>382</v>
+        <v>465</v>
       </c>
       <c r="B377">
-        <v>-0.493573139706245</v>
+        <v>-0.175030818752968</v>
       </c>
       <c r="C377">
-        <v>0.48354599631756601</v>
+        <v>-3.2765280424137302</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="B378">
-        <v>-0.84539178009012095</v>
+        <v>0.72673795396848995</v>
       </c>
       <c r="C378">
-        <v>-1.00275690920772</v>
+        <v>-0.38825797732126399</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="B379">
-        <v>-1.17113295250755</v>
+        <v>-0.13147187492547099</v>
       </c>
       <c r="C379">
-        <v>-1.47670879499969</v>
+        <v>0.35283663631105699</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>108</v>
+        <v>376</v>
       </c>
       <c r="B380">
-        <v>-0.51117722653165198</v>
+        <v>-0.25087032061103598</v>
       </c>
       <c r="C380">
-        <v>0.44220970554373501</v>
+        <v>0.68775640721354203</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>383</v>
+        <v>221</v>
       </c>
       <c r="B381">
-        <v>-0.66418551692398697</v>
+        <v>-0.19077046828879801</v>
       </c>
       <c r="C381">
-        <v>0.77235747353309403</v>
+        <v>0.68164042806784597</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B382">
-        <v>-1.2237631618512601</v>
+        <v>-1.2132715792531099</v>
       </c>
       <c r="C382">
-        <v>-1.00341295587996</v>
+        <v>-1.05103631083421</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>229</v>
+        <v>495</v>
       </c>
       <c r="B383">
-        <v>-1.1634798448105901</v>
+        <v>-1.6851056173930199</v>
       </c>
       <c r="C383">
-        <v>-1.0219031183446701</v>
+        <v>-0.52778704040619695</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B384">
-        <v>-1.2353129808519401</v>
+        <v>-0.13501596046359601</v>
       </c>
       <c r="C384">
-        <v>-1.0508008330355401</v>
+        <v>4.12336132635059E-2</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>384</v>
+        <v>496</v>
       </c>
       <c r="B385">
-        <v>-0.16613059356496901</v>
+        <v>0.243297777705103</v>
       </c>
       <c r="C385">
-        <v>0.66018663600787897</v>
+        <v>0.67633598230301195</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>468</v>
+        <v>106</v>
       </c>
       <c r="B386">
-        <v>-1.18047842413708</v>
+        <v>-0.47452159269161498</v>
       </c>
       <c r="C386">
-        <v>-0.44128783184853299</v>
+        <v>6.09279852973241E-2</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>385</v>
+        <v>107</v>
       </c>
       <c r="B387">
-        <v>0.10561922105312201</v>
+        <v>0.23581706099165101</v>
       </c>
       <c r="C387">
-        <v>0.67077242447853302</v>
+        <v>0.20155619558545501</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>386</v>
+        <v>222</v>
       </c>
       <c r="B388">
-        <v>-0.74934947309977396</v>
+        <v>-0.186786361711334</v>
       </c>
       <c r="C388">
-        <v>1.72495114568604</v>
+        <v>0.51058082314375797</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B389">
-        <v>-7.1311486361971002E-2</v>
+        <v>-7.7346198797695095E-2</v>
       </c>
       <c r="C389">
-        <v>0.471159299152342</v>
+        <v>0.54088745591175003</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>111</v>
+        <v>378</v>
       </c>
       <c r="B390">
-        <v>9.8179243886652695E-2</v>
+        <v>-0.52848754421479105</v>
       </c>
       <c r="C390">
-        <v>0.240416415662282</v>
+        <v>1.59418152755025</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="B391">
-        <v>5.6424265793645297E-2</v>
+        <v>-0.36210446517788097</v>
       </c>
       <c r="C391">
-        <v>0.33603632523791799</v>
+        <v>0.434229359672819</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>388</v>
+        <v>466</v>
       </c>
       <c r="B392">
-        <v>-0.14952913827845901</v>
+        <v>-1.2410297869223601</v>
       </c>
       <c r="C392">
-        <v>0.40313557917029602</v>
+        <v>-1.00414854405079</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>389</v>
+        <v>267</v>
       </c>
       <c r="B393">
-        <v>-0.376427362602136</v>
+        <v>0.97961303113609199</v>
       </c>
       <c r="C393">
-        <v>1.1944695595056201</v>
+        <v>-0.24107494276529501</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>113</v>
+        <v>224</v>
       </c>
       <c r="B394">
-        <v>0.73255969541772503</v>
+        <v>-0.76187211186622905</v>
       </c>
       <c r="C394">
-        <v>-0.39410842190275402</v>
+        <v>-0.38911828645407198</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>390</v>
+        <v>225</v>
       </c>
       <c r="B395">
-        <v>-0.42731153385426601</v>
+        <v>-1.48084005161305</v>
       </c>
       <c r="C395">
-        <v>0.85289224976574396</v>
+        <v>0.162434663038689</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="B396">
-        <v>2.3926754314291299E-2</v>
+        <v>0.61007091908378597</v>
       </c>
       <c r="C396">
-        <v>3.1351814802173902E-2</v>
+        <v>-0.26643461814835401</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>230</v>
+        <v>379</v>
       </c>
       <c r="B397">
-        <v>-1.0485960328403601</v>
+        <v>-0.509318212813333</v>
       </c>
       <c r="C397">
-        <v>-0.46013774035342397</v>
+        <v>0.986535934935447</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B398">
-        <v>-0.29199924446897002</v>
+        <v>-0.44211622293276198</v>
       </c>
       <c r="C398">
-        <v>0.41440731953590698</v>
+        <v>0.808251329312767</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="B399">
-        <v>-0.64389099887197199</v>
+        <v>-0.86849183070641101</v>
       </c>
       <c r="C399">
-        <v>-0.13321989870659601</v>
+        <v>0.21104510010142899</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>231</v>
+        <v>381</v>
       </c>
       <c r="B400">
-        <v>-0.186690792962764</v>
+        <v>-0.49044699114189499</v>
       </c>
       <c r="C400">
-        <v>0.44653297191716301</v>
+        <v>0.46098585753166699</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>393</v>
+        <v>227</v>
       </c>
       <c r="B401">
-        <v>-0.20423072939824999</v>
+        <v>-0.83909424520038101</v>
       </c>
       <c r="C401">
-        <v>3.45426953222032E-2</v>
+        <v>-0.99335776362472294</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B402">
-        <v>0.72985139619012696</v>
+        <v>-1.1460793927502599</v>
       </c>
       <c r="C402">
-        <v>-0.33903796891327798</v>
+        <v>-1.49399889380163</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>394</v>
+        <v>108</v>
       </c>
       <c r="B403">
-        <v>-0.31328472200430901</v>
+        <v>-0.50090853772661503</v>
       </c>
       <c r="C403">
-        <v>0.63839944859257802</v>
+        <v>0.45142190140124</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="B404">
-        <v>-0.49865452668684002</v>
+        <v>-0.68756288854721204</v>
       </c>
       <c r="C404">
-        <v>1.26662331382038</v>
+        <v>0.70992549673747496</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B405">
-        <v>-0.64074284532983505</v>
+        <v>-1.2044510399071999</v>
       </c>
       <c r="C405">
-        <v>9.8670732080028495E-2</v>
+        <v>-1.0172397254155501</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B406">
-        <v>-0.35681180370243698</v>
+        <v>-1.1422249593637399</v>
       </c>
       <c r="C406">
-        <v>0.43401137685644903</v>
+        <v>-1.0393001325239799</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>396</v>
+        <v>110</v>
       </c>
       <c r="B407">
-        <v>0.82107039679611105</v>
+        <v>-1.21225124008681</v>
       </c>
       <c r="C407">
-        <v>0.63959369787589904</v>
+        <v>-1.0705219368829599</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>116</v>
+        <v>383</v>
       </c>
       <c r="B408">
-        <v>-0.23726191079765099</v>
+        <v>-0.15307768415946399</v>
       </c>
       <c r="C408">
-        <v>-1.7364861861377701E-2</v>
+        <v>0.67325783606707301</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>397</v>
+        <v>467</v>
       </c>
       <c r="B409">
-        <v>-0.58641089633559196</v>
+        <v>-1.1654898587210001</v>
       </c>
       <c r="C409">
-        <v>-0.135944796740669</v>
+        <v>-0.45535382858559598</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>398</v>
+        <v>497</v>
       </c>
       <c r="B410">
-        <v>0.83320080052605305</v>
+        <v>0.85624157068647999</v>
       </c>
       <c r="C410">
-        <v>-0.42261798163965197</v>
+        <v>-3.6579110882493403E-2</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="B411">
-        <v>-0.40994810608855498</v>
+        <v>0.11736641046950599</v>
       </c>
       <c r="C411">
-        <v>0.62430822786431905</v>
+        <v>0.67697661652671504</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>234</v>
+        <v>385</v>
       </c>
       <c r="B412">
-        <v>-1.2345031706360801</v>
+        <v>-0.76142448459670597</v>
       </c>
       <c r="C412">
-        <v>-1.0285689983994799</v>
+        <v>1.71784947378876</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="B413">
-        <v>-0.949649055737388</v>
+        <v>-5.8394185604637702E-2</v>
       </c>
       <c r="C413">
-        <v>-0.25497607626680002</v>
+        <v>0.47791904110670302</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>401</v>
+        <v>111</v>
       </c>
       <c r="B414">
-        <v>0.71079316067458198</v>
+        <v>0.10834844465433301</v>
       </c>
       <c r="C414">
-        <v>-0.242460345107922</v>
+        <v>0.24402089158014301</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>469</v>
+        <v>112</v>
       </c>
       <c r="B415">
-        <v>-1.22042720517343</v>
+        <v>7.1808845476450001E-2</v>
       </c>
       <c r="C415">
-        <v>-1.10250928152745</v>
+        <v>0.34356164433712699</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>470</v>
+        <v>387</v>
       </c>
       <c r="B416">
-        <v>-1.20657038415359</v>
+        <v>-0.137698634624776</v>
       </c>
       <c r="C416">
-        <v>-0.46456900593679401</v>
+        <v>0.41655122361856201</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>117</v>
+        <v>388</v>
       </c>
       <c r="B417">
-        <v>-1.2937224656469799</v>
+        <v>-0.34084390917488799</v>
       </c>
       <c r="C417">
-        <v>-0.36843005833485198</v>
+        <v>1.11660052443237</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B418">
-        <v>-0.450980226393706</v>
+        <v>0.738822424143041</v>
       </c>
       <c r="C418">
-        <v>0.27328343798846899</v>
+        <v>-0.40373409357263201</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="B419">
-        <v>-1.5320308575449799</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C419">
-        <v>-0.41287315636678501</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="B420">
-        <v>-0.40144540491095598</v>
+        <v>-0.418960567467203</v>
       </c>
       <c r="C420">
-        <v>0.39385163740908702</v>
+        <v>0.85408823273964096</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>236</v>
+        <v>390</v>
       </c>
       <c r="B421">
-        <v>-1.2362395251779399</v>
+        <v>-8.4945649642561294E-2</v>
       </c>
       <c r="C421">
-        <v>-0.95368565544820205</v>
+        <v>0.223851629008428</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>402</v>
+        <v>230</v>
       </c>
       <c r="B422">
-        <v>-0.51000466349986795</v>
+        <v>-1.06248310221728</v>
       </c>
       <c r="C422">
-        <v>0.73200590467200399</v>
+        <v>-0.48264285627610298</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B423">
-        <v>-0.51000466349986795</v>
+        <v>-0.280479612349814</v>
       </c>
       <c r="C423">
-        <v>0.73200590467200399</v>
+        <v>0.42158550722280602</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="B424">
-        <v>0.56784668580686004</v>
+        <v>-0.64425604467687103</v>
       </c>
       <c r="C424">
-        <v>-0.62303482226407303</v>
+        <v>-9.9014771004376806E-2</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>404</v>
+        <v>231</v>
       </c>
       <c r="B425">
-        <v>-0.32847156969186903</v>
+        <v>-0.17385771563501901</v>
       </c>
       <c r="C425">
-        <v>0.22090994524785501</v>
+        <v>0.45892451594067601</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>238</v>
+        <v>392</v>
       </c>
       <c r="B426">
-        <v>0.216597716654853</v>
+        <v>-0.19552075032800201</v>
       </c>
       <c r="C426">
-        <v>0.19937519351729499</v>
+        <v>4.6011615545184903E-2</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>405</v>
+        <v>232</v>
       </c>
       <c r="B427">
-        <v>-0.272448727637495</v>
+        <v>0.71984410239489505</v>
       </c>
       <c r="C427">
-        <v>0.173625766303657</v>
+        <v>-0.42056334300659398</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>256</v>
+        <v>393</v>
       </c>
       <c r="B428">
-        <v>-1.21344378361059</v>
+        <v>-0.30186283036580902</v>
       </c>
       <c r="C428">
-        <v>-1.0692334273613699</v>
+        <v>0.64918643774961404</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>406</v>
+        <v>499</v>
       </c>
       <c r="B429">
-        <v>-0.37015607035249398</v>
+        <v>0.75270849806601303</v>
       </c>
       <c r="C429">
-        <v>0.80749754244277405</v>
+        <v>-0.275114958573205</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B430">
-        <v>-0.48175208027736799</v>
+        <v>-0.49526960856671298</v>
       </c>
       <c r="C430">
-        <v>0.65363471460448197</v>
+        <v>1.2700344055697499</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>408</v>
+        <v>115</v>
       </c>
       <c r="B431">
-        <v>0.76319670057486599</v>
+        <v>-0.64240867527115397</v>
       </c>
       <c r="C431">
-        <v>-0.53454796863106102</v>
+        <v>6.2844998274744296E-2</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>409</v>
+        <v>233</v>
       </c>
       <c r="B432">
-        <v>-0.63668953773124104</v>
+        <v>-0.34569011286107498</v>
       </c>
       <c r="C432">
-        <v>1.4301036334986901</v>
+        <v>0.44517475776572601</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>119</v>
+        <v>395</v>
       </c>
       <c r="B433">
-        <v>-0.97218121625938403</v>
+        <v>0.83986674199874201</v>
       </c>
       <c r="C433">
-        <v>0.43605718912236402</v>
+        <v>0.62756001128734196</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B434">
-        <v>0.72427824426946796</v>
+        <v>-0.23873508090433901</v>
       </c>
       <c r="C434">
-        <v>-0.26539631756293303</v>
+        <v>-1.74424564440082E-2</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>121</v>
+        <v>500</v>
       </c>
       <c r="B435">
-        <v>0.233399386826836</v>
+        <v>6.0290773893059403E-2</v>
       </c>
       <c r="C435">
-        <v>6.9936461964266006E-2</v>
+        <v>0.48634523794423701</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>122</v>
+        <v>396</v>
       </c>
       <c r="B436">
-        <v>-0.11938628663244</v>
+        <v>-0.56992791139145704</v>
       </c>
       <c r="C436">
-        <v>0.26935823157760702</v>
+        <v>-0.13288911608244799</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="B437">
-        <v>-0.33925719302366403</v>
+        <v>0.838662739130697</v>
       </c>
       <c r="C437">
-        <v>-4.1069729047220699E-2</v>
+        <v>-0.43636684132336601</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>123</v>
+        <v>398</v>
       </c>
       <c r="B438">
-        <v>-0.25559831016568901</v>
+        <v>-0.397844269133319</v>
       </c>
       <c r="C438">
-        <v>0.27542911112907098</v>
+        <v>0.63420607185177302</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>124</v>
+        <v>234</v>
       </c>
       <c r="B439">
-        <v>-2.5468044557414599E-2</v>
+        <v>-1.1773406050733299</v>
       </c>
       <c r="C439">
-        <v>2.04792774703032E-2</v>
+        <v>-1.0941718183209601</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>125</v>
+        <v>399</v>
       </c>
       <c r="B440">
-        <v>0.76542286033722096</v>
+        <v>-1.05190947164079</v>
       </c>
       <c r="C440">
-        <v>-0.36469299649589698</v>
+        <v>-0.189405430739539</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B441">
-        <v>0.90801536084349499</v>
+        <v>0.71864282997419804</v>
       </c>
       <c r="C441">
-        <v>0.38956863002744602</v>
+        <v>-0.25235168510318801</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>239</v>
+        <v>468</v>
       </c>
       <c r="B442">
-        <v>0.64590066988444395</v>
+        <v>-1.1974542014112599</v>
       </c>
       <c r="C442">
-        <v>-0.42346422723987198</v>
+        <v>-1.12022703579915</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>257</v>
+        <v>469</v>
       </c>
       <c r="B443">
-        <v>0.80251021227576602</v>
+        <v>-1.19122592290879</v>
       </c>
       <c r="C443">
-        <v>-0.19296513944770399</v>
+        <v>-0.48150857124871699</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>412</v>
+        <v>117</v>
       </c>
       <c r="B444">
-        <v>-0.46731446225281997</v>
+        <v>-1.27998002165215</v>
       </c>
       <c r="C444">
-        <v>0.84535490409962899</v>
+        <v>-0.39106889816670998</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>240</v>
+        <v>118</v>
       </c>
       <c r="B445">
-        <v>-1.4925604543753299</v>
+        <v>-0.43900298645543201</v>
       </c>
       <c r="C445">
-        <v>-0.35309484755270798</v>
+        <v>0.275788625350399</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>413</v>
+        <v>470</v>
       </c>
       <c r="B446">
-        <v>-0.26548543371642103</v>
+        <v>-1.50940805932625</v>
       </c>
       <c r="C446">
-        <v>0.40348396848437201</v>
+        <v>-0.48055986232461301</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>414</v>
+        <v>235</v>
       </c>
       <c r="B447">
-        <v>-0.17022558739310401</v>
+        <v>-0.34112468273149399</v>
       </c>
       <c r="C447">
-        <v>0.63870090011808001</v>
+        <v>0.35438485966542399</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>126</v>
+        <v>501</v>
       </c>
       <c r="B448">
-        <v>-1.2651006572254899</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C448">
-        <v>-0.41593339023112202</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>415</v>
+        <v>236</v>
       </c>
       <c r="B449">
-        <v>-0.38903961591333103</v>
+        <v>-1.21304703654734</v>
       </c>
       <c r="C449">
-        <v>0.92972949744121502</v>
+        <v>-0.97864236408246796</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>241</v>
+        <v>401</v>
       </c>
       <c r="B450">
-        <v>-0.98725069399540999</v>
+        <v>-0.16351624475438101</v>
       </c>
       <c r="C450">
-        <v>-0.50223895027435095</v>
+        <v>-0.78024845036407497</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="B451">
-        <v>-0.32974742569543802</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C451">
-        <v>0.112076536482474</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>242</v>
+        <v>402</v>
       </c>
       <c r="B452">
-        <v>6.9639336781859199E-2</v>
+        <v>-7.93511096839183E-2</v>
       </c>
       <c r="C452">
-        <v>5.6247896139143098E-2</v>
+        <v>-1.1587264590305999</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B453">
-        <v>-1.1895895964904699</v>
+        <v>0.57338178565015496</v>
       </c>
       <c r="C453">
-        <v>-0.72666895846497903</v>
+        <v>-0.63118517325961898</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>472</v>
+        <v>403</v>
       </c>
       <c r="B454">
-        <v>-0.19512325329934699</v>
+        <v>-0.31770843613006799</v>
       </c>
       <c r="C454">
-        <v>-3.4888346353967101</v>
+        <v>0.23499581221424401</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="B455">
-        <v>-0.46724283871272598</v>
+        <v>0.26473094085717302</v>
       </c>
       <c r="C455">
-        <v>0.32022122755028598</v>
+        <v>0.22445935575244999</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="B456">
-        <v>0.90801536084349499</v>
+        <v>-0.26318939090312199</v>
       </c>
       <c r="C456">
-        <v>0.38956863002744602</v>
+        <v>0.18088483777557801</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>418</v>
+        <v>503</v>
       </c>
       <c r="B457">
-        <v>-0.38429501844347402</v>
+        <v>0.34147456566839401</v>
       </c>
       <c r="C457">
-        <v>1.3511988423627601</v>
+        <v>-3.0511165023632301</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="B458">
-        <v>-0.51355408248237799</v>
+        <v>-1.18926394789559</v>
       </c>
       <c r="C458">
-        <v>0.30248678262679901</v>
+        <v>-1.0888021417492</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B459">
-        <v>-0.77040927089975597</v>
+        <v>-0.356784719574742</v>
       </c>
       <c r="C459">
-        <v>-0.347132911106245</v>
+        <v>0.853681762200734</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>129</v>
+        <v>406</v>
       </c>
       <c r="B460">
-        <v>0.10400242523577</v>
+        <v>-0.47340584271811897</v>
       </c>
       <c r="C460">
-        <v>0.366918676099661</v>
+        <v>0.65439974647144905</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="B461">
-        <v>-0.93768252161721499</v>
+        <v>0.77091314790214205</v>
       </c>
       <c r="C461">
-        <v>-1.33584798246672</v>
+        <v>-0.544797247294738</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>244</v>
+        <v>408</v>
       </c>
       <c r="B462">
-        <v>-0.479595245400114</v>
+        <v>-0.62115941541547603</v>
       </c>
       <c r="C462">
-        <v>0.39792808920685202</v>
+        <v>1.4053254807878801</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="B463">
-        <v>1.5702501746083099E-2</v>
+        <v>-0.96648867155139495</v>
       </c>
       <c r="C463">
-        <v>0.33727075092741998</v>
+        <v>0.42578059509955901</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="B464">
-        <v>-0.84550195862654798</v>
+        <v>0.72946038481051201</v>
       </c>
       <c r="C464">
-        <v>-0.33661249012399902</v>
+        <v>-0.275278102136153</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="B465">
-        <v>-0.28737381189296002</v>
+        <v>0.23695395957477799</v>
       </c>
       <c r="C465">
-        <v>0.49998594094410997</v>
+        <v>7.3088784016570305E-2</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>247</v>
+        <v>122</v>
       </c>
       <c r="B466">
-        <v>-1.1424765849177101</v>
+        <v>-0.11369478873023101</v>
       </c>
       <c r="C466">
-        <v>-0.78359300943186605</v>
+        <v>0.275758031363463</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>130</v>
+        <v>409</v>
       </c>
       <c r="B467">
-        <v>-0.395979520302773</v>
+        <v>-0.329579473972338</v>
       </c>
       <c r="C467">
-        <v>0.30510839998526501</v>
+        <v>-2.7956541484410201E-2</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>248</v>
+        <v>123</v>
       </c>
       <c r="B468">
-        <v>-1.2337202474109801</v>
+        <v>-0.25744626764904899</v>
       </c>
       <c r="C468">
-        <v>-0.40674310663214303</v>
+        <v>0.28286605917744401</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>249</v>
+        <v>124</v>
       </c>
       <c r="B469">
-        <v>-0.65792707190355104</v>
+        <v>-2.3485547291690501E-2</v>
       </c>
       <c r="C469">
-        <v>0.85642561118717897</v>
+        <v>1.9917427964979199E-2</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>420</v>
+        <v>125</v>
       </c>
       <c r="B470">
-        <v>0.73229223172138902</v>
+        <v>0.77121244943301304</v>
       </c>
       <c r="C470">
-        <v>-0.24074852259980301</v>
+        <v>-0.37590841665434399</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
+        <v>410</v>
+      </c>
+      <c r="B471">
+        <v>0.92117241210067102</v>
+      </c>
+      <c r="C471">
+        <v>0.37311235878871801</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>239</v>
+      </c>
+      <c r="B472">
+        <v>0.65530359887532497</v>
+      </c>
+      <c r="C472">
+        <v>-0.44689405301964602</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>257</v>
+      </c>
+      <c r="B473">
+        <v>0.81024795166988495</v>
+      </c>
+      <c r="C473">
+        <v>-0.20630880175635199</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>411</v>
+      </c>
+      <c r="B474">
+        <v>-0.460426423956871</v>
+      </c>
+      <c r="C474">
+        <v>0.84461242185958996</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>240</v>
+      </c>
+      <c r="B475">
+        <v>-1.4760040671306001</v>
+      </c>
+      <c r="C475">
+        <v>-0.37718693635320399</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>412</v>
+      </c>
+      <c r="B476">
+        <v>-0.25411620774460297</v>
+      </c>
+      <c r="C476">
+        <v>0.41475593384348203</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>413</v>
+      </c>
+      <c r="B477">
+        <v>-0.155991637386487</v>
+      </c>
+      <c r="C477">
+        <v>0.65286625446498803</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>126</v>
+      </c>
+      <c r="B478">
+        <v>-1.2573871089825699</v>
+      </c>
+      <c r="C478">
+        <v>-0.42945713824092402</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>414</v>
+      </c>
+      <c r="B479">
+        <v>-0.38071166234749898</v>
+      </c>
+      <c r="C479">
+        <v>0.93222325834814601</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>241</v>
+      </c>
+      <c r="B480">
+        <v>-0.95270802996624804</v>
+      </c>
+      <c r="C480">
+        <v>-0.51207844868194796</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>415</v>
+      </c>
+      <c r="B481">
+        <v>-0.30433039752404101</v>
+      </c>
+      <c r="C481">
+        <v>0.11918634315514599</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>242</v>
+      </c>
+      <c r="B482">
+        <v>-0.40411388203467002</v>
+      </c>
+      <c r="C482">
+        <v>-9.5330995786350098E-2</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>504</v>
+      </c>
+      <c r="B483">
+        <v>0.84905555738026595</v>
+      </c>
+      <c r="C483">
+        <v>0.22693570573463001</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>243</v>
+      </c>
+      <c r="B484">
+        <v>-1.18119326643939</v>
+      </c>
+      <c r="C484">
+        <v>-0.73082687974271499</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>471</v>
+      </c>
+      <c r="B485">
+        <v>-0.175030818752968</v>
+      </c>
+      <c r="C485">
+        <v>-3.2765280424137302</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>505</v>
+      </c>
+      <c r="B486">
+        <v>-1.19865627122106</v>
+      </c>
+      <c r="C486">
+        <v>-8.9242385202495403E-2</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>127</v>
+      </c>
+      <c r="B487">
+        <v>-0.45850762506008402</v>
+      </c>
+      <c r="C487">
+        <v>0.31713999781637497</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>416</v>
+      </c>
+      <c r="B488">
+        <v>0.92117241210067102</v>
+      </c>
+      <c r="C488">
+        <v>0.37311235878871801</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>417</v>
+      </c>
+      <c r="B489">
+        <v>-0.37442511850954302</v>
+      </c>
+      <c r="C489">
+        <v>1.35930344400898</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>128</v>
+      </c>
+      <c r="B490">
+        <v>-0.50556022159526104</v>
+      </c>
+      <c r="C490">
+        <v>0.29695905916695198</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>506</v>
+      </c>
+      <c r="B491">
+        <v>-0.111869451301275</v>
+      </c>
+      <c r="C491">
+        <v>0.42179275272419398</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>418</v>
+      </c>
+      <c r="B492">
+        <v>-0.75878911592095899</v>
+      </c>
+      <c r="C492">
+        <v>-0.351621465414301</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>129</v>
+      </c>
+      <c r="B493">
+        <v>0.118098607862115</v>
+      </c>
+      <c r="C493">
+        <v>0.380423458521502</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>472</v>
+      </c>
+      <c r="B494">
+        <v>-0.92866327447299302</v>
+      </c>
+      <c r="C494">
+        <v>-1.3371126639111199</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>244</v>
+      </c>
+      <c r="B495">
+        <v>-0.46294680914795699</v>
+      </c>
+      <c r="C495">
+        <v>0.39510782928428601</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>258</v>
+      </c>
+      <c r="B496">
+        <v>-0.123744491817961</v>
+      </c>
+      <c r="C496">
+        <v>0.22031479957256001</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>245</v>
+      </c>
+      <c r="B497">
+        <v>-0.826610576911183</v>
+      </c>
+      <c r="C497">
+        <v>-0.35026889546677298</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>246</v>
+      </c>
+      <c r="B498">
+        <v>-0.27508819051195599</v>
+      </c>
+      <c r="C498">
+        <v>0.51098832995222898</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>247</v>
+      </c>
+      <c r="B499">
+        <v>-1.1220363221949401</v>
+      </c>
+      <c r="C499">
+        <v>-0.80001977286210701</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>130</v>
+      </c>
+      <c r="B500">
+        <v>-0.40555879760550301</v>
+      </c>
+      <c r="C500">
+        <v>0.31278437574422502</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>248</v>
+      </c>
+      <c r="B501">
+        <v>-1.22287292873353</v>
+      </c>
+      <c r="C501">
+        <v>-0.431716285208394</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>249</v>
+      </c>
+      <c r="B502">
+        <v>-0.65495193118962902</v>
+      </c>
+      <c r="C502">
+        <v>0.85586654146678498</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>419</v>
+      </c>
+      <c r="B503">
+        <v>0.73965743279269103</v>
+      </c>
+      <c r="C503">
+        <v>-0.25227041063584099</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
         <v>268</v>
       </c>
-      <c r="B471">
-        <v>0.84127291302069296</v>
-      </c>
-      <c r="C471">
-        <v>-0.26651945272694699</v>
+      <c r="B504">
+        <v>0.84904601003443003</v>
+      </c>
+      <c r="C504">
+        <v>-0.28224560997688303</v>
       </c>
     </row>
   </sheetData>
@@ -7016,7 +7478,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>8.7599999999999997E-2</v>
+        <v>8.8099999999999998E-2</v>
       </c>
     </row>
   </sheetData>
